--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10941" uniqueCount="5429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10941" uniqueCount="5428">
   <si>
     <t>연번</t>
   </si>
@@ -1502,12 +1502,12 @@
     <t>오르노 합정점</t>
   </si>
   <si>
+    <t>서울특별시 마포구 월드컵로3길 14(지1층 B113,114호 합정동, 마포 한강 2차 푸르지오)</t>
+  </si>
+  <si>
     <t>서울특별시 마포구 월드컵로3길 14(지1층 B149,B150,B151, B152,B153,B154호 합정동, 마포 한강 2차 푸르지오)</t>
   </si>
   <si>
-    <t>서울특별시 마포구 월드컵로3길 14(지1층 B113,114호 합정동, 마포 한강 2차 푸르지오)</t>
-  </si>
-  <si>
     <t>오베뉴 한남</t>
   </si>
   <si>
@@ -3326,12 +3326,12 @@
     <t>전남광주통합특별시 화순군 도곡면 덕리길 10-5(1층)</t>
   </si>
   <si>
+    <t>전남광주통합특별시 동구 동명로14번길 19-8(2층 동명동)</t>
+  </si>
+  <si>
     <t>전남광주통합특별시 서구 상무시민로 136(수성빌딩 1층 치평동)</t>
   </si>
   <si>
-    <t>전남광주통합특별시 동구 동명로14번길 19-8(2층 동명동)</t>
-  </si>
-  <si>
     <t>쉘터커피로스터스</t>
   </si>
   <si>
@@ -4115,12 +4115,12 @@
     <t>스트럿</t>
   </si>
   <si>
+    <t>부산광역시 부산진구 동성로39번길 28(1층 전포동)</t>
+  </si>
+  <si>
     <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
   </si>
   <si>
-    <t>부산광역시 부산진구 동성로39번길 28(1층 전포동)</t>
-  </si>
-  <si>
     <t>스팅프리 로스팅하우스</t>
   </si>
   <si>
@@ -11738,6 +11738,12 @@
     <t>충청북도 충주시 대흥길 42(교현동)</t>
   </si>
   <si>
+    <t>애플즈금관</t>
+  </si>
+  <si>
+    <t>충청북도 청주시 상당구 미원면 운암계원로 614-2(1층)</t>
+  </si>
+  <si>
     <t>워킹스톤</t>
   </si>
   <si>
@@ -16290,15 +16296,6 @@
   </si>
   <si>
     <t>전북특별자치도 김제시 만경읍 대동길 609</t>
-  </si>
-  <si>
-    <t>애플즈금관</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>충청북도 청주시 상당구 미원면 운암계원로 614-2(1층)</t>
   </si>
 </sst>
 </file>
@@ -49931,7 +49928,7 @@
         <v>3916</v>
       </c>
       <c r="C1973" t="s" s="2">
-        <v>984</v>
+        <v>767</v>
       </c>
       <c r="D1973" t="s" s="2">
         <v>3802</v>
@@ -49948,13 +49945,13 @@
         <v>3918</v>
       </c>
       <c r="C1974" t="s" s="2">
-        <v>6</v>
+        <v>984</v>
       </c>
       <c r="D1974" t="s" s="2">
+        <v>3802</v>
+      </c>
+      <c r="E1974" t="s" s="3">
         <v>3919</v>
-      </c>
-      <c r="E1974" t="s" s="3">
-        <v>3920</v>
       </c>
     </row>
     <row r="1975" ht="36.0" customHeight="true">
@@ -49962,13 +49959,13 @@
         <v>1974.0</v>
       </c>
       <c r="B1975" t="s" s="3">
+        <v>3920</v>
+      </c>
+      <c r="C1975" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1975" t="s" s="2">
         <v>3921</v>
-      </c>
-      <c r="C1975" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1975" t="s" s="2">
-        <v>3919</v>
       </c>
       <c r="E1975" t="s" s="3">
         <v>3922</v>
@@ -49985,7 +49982,7 @@
         <v>6</v>
       </c>
       <c r="D1976" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1976" t="s" s="3">
         <v>3924</v>
@@ -50002,7 +49999,7 @@
         <v>6</v>
       </c>
       <c r="D1977" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1977" t="s" s="3">
         <v>3926</v>
@@ -50019,7 +50016,7 @@
         <v>6</v>
       </c>
       <c r="D1978" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1978" t="s" s="3">
         <v>3928</v>
@@ -50036,7 +50033,7 @@
         <v>6</v>
       </c>
       <c r="D1979" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1979" t="s" s="3">
         <v>3930</v>
@@ -50053,7 +50050,7 @@
         <v>6</v>
       </c>
       <c r="D1980" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1980" t="s" s="3">
         <v>3932</v>
@@ -50070,7 +50067,7 @@
         <v>6</v>
       </c>
       <c r="D1981" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1981" t="s" s="3">
         <v>3934</v>
@@ -50087,7 +50084,7 @@
         <v>6</v>
       </c>
       <c r="D1982" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1982" t="s" s="3">
         <v>3936</v>
@@ -50104,7 +50101,7 @@
         <v>6</v>
       </c>
       <c r="D1983" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1983" t="s" s="3">
         <v>3938</v>
@@ -50121,7 +50118,7 @@
         <v>6</v>
       </c>
       <c r="D1984" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1984" t="s" s="3">
         <v>3940</v>
@@ -50138,7 +50135,7 @@
         <v>6</v>
       </c>
       <c r="D1985" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1985" t="s" s="3">
         <v>3942</v>
@@ -50155,7 +50152,7 @@
         <v>6</v>
       </c>
       <c r="D1986" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1986" t="s" s="3">
         <v>3944</v>
@@ -50172,7 +50169,7 @@
         <v>6</v>
       </c>
       <c r="D1987" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1987" t="s" s="3">
         <v>3946</v>
@@ -50189,7 +50186,7 @@
         <v>6</v>
       </c>
       <c r="D1988" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1988" t="s" s="3">
         <v>3948</v>
@@ -50206,7 +50203,7 @@
         <v>6</v>
       </c>
       <c r="D1989" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1989" t="s" s="3">
         <v>3950</v>
@@ -50223,7 +50220,7 @@
         <v>6</v>
       </c>
       <c r="D1990" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1990" t="s" s="3">
         <v>3952</v>
@@ -50240,7 +50237,7 @@
         <v>6</v>
       </c>
       <c r="D1991" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1991" t="s" s="3">
         <v>3954</v>
@@ -50257,7 +50254,7 @@
         <v>6</v>
       </c>
       <c r="D1992" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1992" t="s" s="3">
         <v>3956</v>
@@ -50274,7 +50271,7 @@
         <v>6</v>
       </c>
       <c r="D1993" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1993" t="s" s="3">
         <v>3958</v>
@@ -50291,7 +50288,7 @@
         <v>6</v>
       </c>
       <c r="D1994" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1994" t="s" s="3">
         <v>3960</v>
@@ -50308,7 +50305,7 @@
         <v>6</v>
       </c>
       <c r="D1995" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1995" t="s" s="3">
         <v>3962</v>
@@ -50325,7 +50322,7 @@
         <v>6</v>
       </c>
       <c r="D1996" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1996" t="s" s="3">
         <v>3964</v>
@@ -50342,7 +50339,7 @@
         <v>6</v>
       </c>
       <c r="D1997" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1997" t="s" s="3">
         <v>3966</v>
@@ -50359,7 +50356,7 @@
         <v>6</v>
       </c>
       <c r="D1998" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1998" t="s" s="3">
         <v>3968</v>
@@ -50376,7 +50373,7 @@
         <v>6</v>
       </c>
       <c r="D1999" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E1999" t="s" s="3">
         <v>3970</v>
@@ -50393,7 +50390,7 @@
         <v>6</v>
       </c>
       <c r="D2000" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2000" t="s" s="3">
         <v>3972</v>
@@ -50410,7 +50407,7 @@
         <v>6</v>
       </c>
       <c r="D2001" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2001" t="s" s="3">
         <v>3974</v>
@@ -50427,7 +50424,7 @@
         <v>6</v>
       </c>
       <c r="D2002" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2002" t="s" s="3">
         <v>3976</v>
@@ -50444,7 +50441,7 @@
         <v>6</v>
       </c>
       <c r="D2003" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2003" t="s" s="3">
         <v>3978</v>
@@ -50461,7 +50458,7 @@
         <v>6</v>
       </c>
       <c r="D2004" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2004" t="s" s="3">
         <v>3980</v>
@@ -50478,7 +50475,7 @@
         <v>6</v>
       </c>
       <c r="D2005" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2005" t="s" s="3">
         <v>3982</v>
@@ -50495,7 +50492,7 @@
         <v>6</v>
       </c>
       <c r="D2006" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2006" t="s" s="3">
         <v>3984</v>
@@ -50512,7 +50509,7 @@
         <v>6</v>
       </c>
       <c r="D2007" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2007" t="s" s="3">
         <v>3986</v>
@@ -50529,7 +50526,7 @@
         <v>6</v>
       </c>
       <c r="D2008" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2008" t="s" s="3">
         <v>3988</v>
@@ -50546,7 +50543,7 @@
         <v>6</v>
       </c>
       <c r="D2009" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2009" t="s" s="3">
         <v>3990</v>
@@ -50563,7 +50560,7 @@
         <v>6</v>
       </c>
       <c r="D2010" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2010" t="s" s="3">
         <v>3992</v>
@@ -50580,7 +50577,7 @@
         <v>6</v>
       </c>
       <c r="D2011" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2011" t="s" s="3">
         <v>3994</v>
@@ -50597,7 +50594,7 @@
         <v>6</v>
       </c>
       <c r="D2012" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2012" t="s" s="3">
         <v>3996</v>
@@ -50614,7 +50611,7 @@
         <v>6</v>
       </c>
       <c r="D2013" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2013" t="s" s="3">
         <v>3998</v>
@@ -50631,7 +50628,7 @@
         <v>6</v>
       </c>
       <c r="D2014" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2014" t="s" s="3">
         <v>4000</v>
@@ -50648,7 +50645,7 @@
         <v>6</v>
       </c>
       <c r="D2015" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2015" t="s" s="3">
         <v>4002</v>
@@ -50665,7 +50662,7 @@
         <v>6</v>
       </c>
       <c r="D2016" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2016" t="s" s="3">
         <v>4004</v>
@@ -50682,7 +50679,7 @@
         <v>6</v>
       </c>
       <c r="D2017" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2017" t="s" s="3">
         <v>4006</v>
@@ -50699,7 +50696,7 @@
         <v>6</v>
       </c>
       <c r="D2018" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2018" t="s" s="3">
         <v>4008</v>
@@ -50716,7 +50713,7 @@
         <v>6</v>
       </c>
       <c r="D2019" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2019" t="s" s="3">
         <v>4010</v>
@@ -50733,7 +50730,7 @@
         <v>6</v>
       </c>
       <c r="D2020" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2020" t="s" s="3">
         <v>4012</v>
@@ -50750,7 +50747,7 @@
         <v>6</v>
       </c>
       <c r="D2021" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2021" t="s" s="3">
         <v>4014</v>
@@ -50767,7 +50764,7 @@
         <v>6</v>
       </c>
       <c r="D2022" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2022" t="s" s="3">
         <v>4016</v>
@@ -50784,7 +50781,7 @@
         <v>6</v>
       </c>
       <c r="D2023" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2023" t="s" s="3">
         <v>4018</v>
@@ -50801,7 +50798,7 @@
         <v>6</v>
       </c>
       <c r="D2024" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2024" t="s" s="3">
         <v>4020</v>
@@ -50818,7 +50815,7 @@
         <v>6</v>
       </c>
       <c r="D2025" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2025" t="s" s="3">
         <v>4022</v>
@@ -50835,7 +50832,7 @@
         <v>6</v>
       </c>
       <c r="D2026" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2026" t="s" s="3">
         <v>4024</v>
@@ -50852,7 +50849,7 @@
         <v>6</v>
       </c>
       <c r="D2027" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2027" t="s" s="3">
         <v>4026</v>
@@ -50869,7 +50866,7 @@
         <v>6</v>
       </c>
       <c r="D2028" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2028" t="s" s="3">
         <v>4028</v>
@@ -50886,7 +50883,7 @@
         <v>6</v>
       </c>
       <c r="D2029" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2029" t="s" s="3">
         <v>4030</v>
@@ -50903,7 +50900,7 @@
         <v>6</v>
       </c>
       <c r="D2030" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2030" t="s" s="3">
         <v>4032</v>
@@ -50920,7 +50917,7 @@
         <v>6</v>
       </c>
       <c r="D2031" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2031" t="s" s="3">
         <v>4034</v>
@@ -50937,7 +50934,7 @@
         <v>6</v>
       </c>
       <c r="D2032" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2032" t="s" s="3">
         <v>4036</v>
@@ -50954,7 +50951,7 @@
         <v>6</v>
       </c>
       <c r="D2033" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2033" t="s" s="3">
         <v>4038</v>
@@ -50968,10 +50965,10 @@
         <v>4039</v>
       </c>
       <c r="C2034" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2034" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2034" t="s" s="3">
         <v>4040</v>
@@ -50988,7 +50985,7 @@
         <v>767</v>
       </c>
       <c r="D2035" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2035" t="s" s="3">
         <v>4042</v>
@@ -51005,7 +51002,7 @@
         <v>767</v>
       </c>
       <c r="D2036" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2036" t="s" s="3">
         <v>4044</v>
@@ -51022,7 +51019,7 @@
         <v>767</v>
       </c>
       <c r="D2037" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2037" t="s" s="3">
         <v>4046</v>
@@ -51039,7 +51036,7 @@
         <v>767</v>
       </c>
       <c r="D2038" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2038" t="s" s="3">
         <v>4048</v>
@@ -51056,7 +51053,7 @@
         <v>767</v>
       </c>
       <c r="D2039" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2039" t="s" s="3">
         <v>4050</v>
@@ -51073,7 +51070,7 @@
         <v>767</v>
       </c>
       <c r="D2040" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2040" t="s" s="3">
         <v>4052</v>
@@ -51090,7 +51087,7 @@
         <v>767</v>
       </c>
       <c r="D2041" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2041" t="s" s="3">
         <v>4054</v>
@@ -51107,7 +51104,7 @@
         <v>767</v>
       </c>
       <c r="D2042" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2042" t="s" s="3">
         <v>4056</v>
@@ -51124,7 +51121,7 @@
         <v>767</v>
       </c>
       <c r="D2043" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2043" t="s" s="3">
         <v>4058</v>
@@ -51141,7 +51138,7 @@
         <v>767</v>
       </c>
       <c r="D2044" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2044" t="s" s="3">
         <v>4060</v>
@@ -51158,7 +51155,7 @@
         <v>767</v>
       </c>
       <c r="D2045" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2045" t="s" s="3">
         <v>4062</v>
@@ -51175,7 +51172,7 @@
         <v>767</v>
       </c>
       <c r="D2046" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2046" t="s" s="3">
         <v>4064</v>
@@ -51192,7 +51189,7 @@
         <v>767</v>
       </c>
       <c r="D2047" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2047" t="s" s="3">
         <v>4066</v>
@@ -51209,7 +51206,7 @@
         <v>767</v>
       </c>
       <c r="D2048" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2048" t="s" s="3">
         <v>4068</v>
@@ -51226,7 +51223,7 @@
         <v>767</v>
       </c>
       <c r="D2049" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2049" t="s" s="3">
         <v>4070</v>
@@ -51243,7 +51240,7 @@
         <v>767</v>
       </c>
       <c r="D2050" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2050" t="s" s="3">
         <v>4072</v>
@@ -51260,7 +51257,7 @@
         <v>767</v>
       </c>
       <c r="D2051" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2051" t="s" s="3">
         <v>4074</v>
@@ -51277,7 +51274,7 @@
         <v>767</v>
       </c>
       <c r="D2052" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2052" t="s" s="3">
         <v>4076</v>
@@ -51288,16 +51285,16 @@
         <v>2052.0</v>
       </c>
       <c r="B2053" t="s" s="3">
-        <v>4013</v>
+        <v>4077</v>
       </c>
       <c r="C2053" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2053" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2053" t="s" s="3">
-        <v>4014</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="2054" ht="36.0" customHeight="true">
@@ -51305,16 +51302,16 @@
         <v>2053.0</v>
       </c>
       <c r="B2054" t="s" s="3">
-        <v>4077</v>
+        <v>4015</v>
       </c>
       <c r="C2054" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2054" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2054" t="s" s="3">
-        <v>4078</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="2055" ht="36.0" customHeight="true">
@@ -51328,7 +51325,7 @@
         <v>767</v>
       </c>
       <c r="D2055" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2055" t="s" s="3">
         <v>4080</v>
@@ -51345,7 +51342,7 @@
         <v>767</v>
       </c>
       <c r="D2056" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2056" t="s" s="3">
         <v>4082</v>
@@ -51362,7 +51359,7 @@
         <v>767</v>
       </c>
       <c r="D2057" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2057" t="s" s="3">
         <v>4084</v>
@@ -51379,7 +51376,7 @@
         <v>767</v>
       </c>
       <c r="D2058" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2058" t="s" s="3">
         <v>4086</v>
@@ -51396,7 +51393,7 @@
         <v>767</v>
       </c>
       <c r="D2059" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2059" t="s" s="3">
         <v>4088</v>
@@ -51413,7 +51410,7 @@
         <v>767</v>
       </c>
       <c r="D2060" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2060" t="s" s="3">
         <v>4090</v>
@@ -51430,7 +51427,7 @@
         <v>767</v>
       </c>
       <c r="D2061" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2061" t="s" s="3">
         <v>4092</v>
@@ -51447,7 +51444,7 @@
         <v>767</v>
       </c>
       <c r="D2062" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2062" t="s" s="3">
         <v>4094</v>
@@ -51461,10 +51458,10 @@
         <v>4095</v>
       </c>
       <c r="C2063" t="s" s="2">
-        <v>984</v>
+        <v>767</v>
       </c>
       <c r="D2063" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2063" t="s" s="3">
         <v>4096</v>
@@ -51481,7 +51478,7 @@
         <v>984</v>
       </c>
       <c r="D2064" t="s" s="2">
-        <v>3919</v>
+        <v>3921</v>
       </c>
       <c r="E2064" t="s" s="3">
         <v>4098</v>
@@ -51495,13 +51492,13 @@
         <v>4099</v>
       </c>
       <c r="C2065" t="s" s="2">
-        <v>6</v>
+        <v>984</v>
       </c>
       <c r="D2065" t="s" s="2">
+        <v>3921</v>
+      </c>
+      <c r="E2065" t="s" s="3">
         <v>4100</v>
-      </c>
-      <c r="E2065" t="s" s="3">
-        <v>4101</v>
       </c>
     </row>
     <row r="2066" ht="36.0" customHeight="true">
@@ -51509,13 +51506,13 @@
         <v>2065.0</v>
       </c>
       <c r="B2066" t="s" s="3">
+        <v>4101</v>
+      </c>
+      <c r="C2066" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2066" t="s" s="2">
         <v>4102</v>
-      </c>
-      <c r="C2066" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2066" t="s" s="2">
-        <v>4100</v>
       </c>
       <c r="E2066" t="s" s="3">
         <v>4103</v>
@@ -51532,7 +51529,7 @@
         <v>6</v>
       </c>
       <c r="D2067" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2067" t="s" s="3">
         <v>4105</v>
@@ -51549,7 +51546,7 @@
         <v>6</v>
       </c>
       <c r="D2068" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2068" t="s" s="3">
         <v>4107</v>
@@ -51566,7 +51563,7 @@
         <v>6</v>
       </c>
       <c r="D2069" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2069" t="s" s="3">
         <v>4109</v>
@@ -51583,7 +51580,7 @@
         <v>6</v>
       </c>
       <c r="D2070" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2070" t="s" s="3">
         <v>4111</v>
@@ -51600,7 +51597,7 @@
         <v>6</v>
       </c>
       <c r="D2071" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2071" t="s" s="3">
         <v>4113</v>
@@ -51617,7 +51614,7 @@
         <v>6</v>
       </c>
       <c r="D2072" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2072" t="s" s="3">
         <v>4115</v>
@@ -51634,7 +51631,7 @@
         <v>6</v>
       </c>
       <c r="D2073" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2073" t="s" s="3">
         <v>4117</v>
@@ -51651,7 +51648,7 @@
         <v>6</v>
       </c>
       <c r="D2074" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2074" t="s" s="3">
         <v>4119</v>
@@ -51668,7 +51665,7 @@
         <v>6</v>
       </c>
       <c r="D2075" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2075" t="s" s="3">
         <v>4121</v>
@@ -51685,7 +51682,7 @@
         <v>6</v>
       </c>
       <c r="D2076" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2076" t="s" s="3">
         <v>4123</v>
@@ -51702,7 +51699,7 @@
         <v>6</v>
       </c>
       <c r="D2077" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2077" t="s" s="3">
         <v>4125</v>
@@ -51719,7 +51716,7 @@
         <v>6</v>
       </c>
       <c r="D2078" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2078" t="s" s="3">
         <v>4127</v>
@@ -51736,7 +51733,7 @@
         <v>6</v>
       </c>
       <c r="D2079" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2079" t="s" s="3">
         <v>4129</v>
@@ -51753,7 +51750,7 @@
         <v>6</v>
       </c>
       <c r="D2080" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2080" t="s" s="3">
         <v>4131</v>
@@ -51770,7 +51767,7 @@
         <v>6</v>
       </c>
       <c r="D2081" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2081" t="s" s="3">
         <v>4133</v>
@@ -51787,7 +51784,7 @@
         <v>6</v>
       </c>
       <c r="D2082" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2082" t="s" s="3">
         <v>4135</v>
@@ -51804,7 +51801,7 @@
         <v>6</v>
       </c>
       <c r="D2083" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2083" t="s" s="3">
         <v>4137</v>
@@ -51821,7 +51818,7 @@
         <v>6</v>
       </c>
       <c r="D2084" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2084" t="s" s="3">
         <v>4139</v>
@@ -51838,7 +51835,7 @@
         <v>6</v>
       </c>
       <c r="D2085" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2085" t="s" s="3">
         <v>4141</v>
@@ -51855,7 +51852,7 @@
         <v>6</v>
       </c>
       <c r="D2086" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2086" t="s" s="3">
         <v>4143</v>
@@ -51872,7 +51869,7 @@
         <v>6</v>
       </c>
       <c r="D2087" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2087" t="s" s="3">
         <v>4145</v>
@@ -51889,7 +51886,7 @@
         <v>6</v>
       </c>
       <c r="D2088" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2088" t="s" s="3">
         <v>4147</v>
@@ -51906,7 +51903,7 @@
         <v>6</v>
       </c>
       <c r="D2089" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2089" t="s" s="3">
         <v>4149</v>
@@ -51917,16 +51914,16 @@
         <v>2089.0</v>
       </c>
       <c r="B2090" t="s" s="3">
-        <v>865</v>
+        <v>4150</v>
       </c>
       <c r="C2090" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2090" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2090" t="s" s="3">
-        <v>4150</v>
+        <v>4151</v>
       </c>
     </row>
     <row r="2091" ht="36.0" customHeight="true">
@@ -51934,13 +51931,13 @@
         <v>2090.0</v>
       </c>
       <c r="B2091" t="s" s="3">
-        <v>4151</v>
+        <v>865</v>
       </c>
       <c r="C2091" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2091" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2091" t="s" s="3">
         <v>4152</v>
@@ -51957,7 +51954,7 @@
         <v>6</v>
       </c>
       <c r="D2092" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2092" t="s" s="3">
         <v>4154</v>
@@ -51974,7 +51971,7 @@
         <v>6</v>
       </c>
       <c r="D2093" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2093" t="s" s="3">
         <v>4156</v>
@@ -51991,7 +51988,7 @@
         <v>6</v>
       </c>
       <c r="D2094" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2094" t="s" s="3">
         <v>4158</v>
@@ -52008,7 +52005,7 @@
         <v>6</v>
       </c>
       <c r="D2095" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2095" t="s" s="3">
         <v>4160</v>
@@ -52025,7 +52022,7 @@
         <v>6</v>
       </c>
       <c r="D2096" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2096" t="s" s="3">
         <v>4162</v>
@@ -52042,7 +52039,7 @@
         <v>6</v>
       </c>
       <c r="D2097" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2097" t="s" s="3">
         <v>4164</v>
@@ -52059,7 +52056,7 @@
         <v>6</v>
       </c>
       <c r="D2098" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2098" t="s" s="3">
         <v>4166</v>
@@ -52076,7 +52073,7 @@
         <v>6</v>
       </c>
       <c r="D2099" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2099" t="s" s="3">
         <v>4168</v>
@@ -52093,7 +52090,7 @@
         <v>6</v>
       </c>
       <c r="D2100" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2100" t="s" s="3">
         <v>4170</v>
@@ -52110,7 +52107,7 @@
         <v>6</v>
       </c>
       <c r="D2101" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2101" t="s" s="3">
         <v>4172</v>
@@ -52127,7 +52124,7 @@
         <v>6</v>
       </c>
       <c r="D2102" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2102" t="s" s="3">
         <v>4174</v>
@@ -52144,7 +52141,7 @@
         <v>6</v>
       </c>
       <c r="D2103" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2103" t="s" s="3">
         <v>4176</v>
@@ -52161,7 +52158,7 @@
         <v>6</v>
       </c>
       <c r="D2104" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2104" t="s" s="3">
         <v>4178</v>
@@ -52178,10 +52175,10 @@
         <v>6</v>
       </c>
       <c r="D2105" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2105" t="s" s="3">
-        <v>4152</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="2106" ht="36.0" customHeight="true">
@@ -52189,16 +52186,16 @@
         <v>2105.0</v>
       </c>
       <c r="B2106" t="s" s="3">
-        <v>4180</v>
+        <v>4181</v>
       </c>
       <c r="C2106" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2106" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2106" t="s" s="3">
-        <v>4181</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="2107" ht="36.0" customHeight="true">
@@ -52206,16 +52203,16 @@
         <v>2106.0</v>
       </c>
       <c r="B2107" t="s" s="3">
-        <v>3700</v>
+        <v>4182</v>
       </c>
       <c r="C2107" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2107" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2107" t="s" s="3">
-        <v>4182</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="2108" ht="36.0" customHeight="true">
@@ -52223,13 +52220,13 @@
         <v>2107.0</v>
       </c>
       <c r="B2108" t="s" s="3">
-        <v>4183</v>
+        <v>3700</v>
       </c>
       <c r="C2108" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2108" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2108" t="s" s="3">
         <v>4184</v>
@@ -52246,7 +52243,7 @@
         <v>6</v>
       </c>
       <c r="D2109" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2109" t="s" s="3">
         <v>4186</v>
@@ -52263,7 +52260,7 @@
         <v>6</v>
       </c>
       <c r="D2110" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2110" t="s" s="3">
         <v>4188</v>
@@ -52280,7 +52277,7 @@
         <v>6</v>
       </c>
       <c r="D2111" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2111" t="s" s="3">
         <v>4190</v>
@@ -52297,7 +52294,7 @@
         <v>6</v>
       </c>
       <c r="D2112" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2112" t="s" s="3">
         <v>4192</v>
@@ -52314,7 +52311,7 @@
         <v>6</v>
       </c>
       <c r="D2113" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2113" t="s" s="3">
         <v>4194</v>
@@ -52331,7 +52328,7 @@
         <v>6</v>
       </c>
       <c r="D2114" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2114" t="s" s="3">
         <v>4196</v>
@@ -52345,10 +52342,10 @@
         <v>4197</v>
       </c>
       <c r="C2115" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2115" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2115" t="s" s="3">
         <v>4198</v>
@@ -52365,7 +52362,7 @@
         <v>767</v>
       </c>
       <c r="D2116" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2116" t="s" s="3">
         <v>4200</v>
@@ -52382,7 +52379,7 @@
         <v>767</v>
       </c>
       <c r="D2117" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2117" t="s" s="3">
         <v>4202</v>
@@ -52399,7 +52396,7 @@
         <v>767</v>
       </c>
       <c r="D2118" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2118" t="s" s="3">
         <v>4204</v>
@@ -52416,7 +52413,7 @@
         <v>767</v>
       </c>
       <c r="D2119" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2119" t="s" s="3">
         <v>4206</v>
@@ -52433,7 +52430,7 @@
         <v>767</v>
       </c>
       <c r="D2120" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2120" t="s" s="3">
         <v>4208</v>
@@ -52450,7 +52447,7 @@
         <v>767</v>
       </c>
       <c r="D2121" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2121" t="s" s="3">
         <v>4210</v>
@@ -52467,7 +52464,7 @@
         <v>767</v>
       </c>
       <c r="D2122" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2122" t="s" s="3">
         <v>4212</v>
@@ -52484,7 +52481,7 @@
         <v>767</v>
       </c>
       <c r="D2123" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2123" t="s" s="3">
         <v>4214</v>
@@ -52501,7 +52498,7 @@
         <v>767</v>
       </c>
       <c r="D2124" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2124" t="s" s="3">
         <v>4216</v>
@@ -52518,7 +52515,7 @@
         <v>767</v>
       </c>
       <c r="D2125" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2125" t="s" s="3">
         <v>4218</v>
@@ -52535,7 +52532,7 @@
         <v>767</v>
       </c>
       <c r="D2126" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2126" t="s" s="3">
         <v>4220</v>
@@ -52552,7 +52549,7 @@
         <v>767</v>
       </c>
       <c r="D2127" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2127" t="s" s="3">
         <v>4222</v>
@@ -52569,7 +52566,7 @@
         <v>767</v>
       </c>
       <c r="D2128" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2128" t="s" s="3">
         <v>4224</v>
@@ -52586,7 +52583,7 @@
         <v>767</v>
       </c>
       <c r="D2129" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2129" t="s" s="3">
         <v>4226</v>
@@ -52603,7 +52600,7 @@
         <v>767</v>
       </c>
       <c r="D2130" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2130" t="s" s="3">
         <v>4228</v>
@@ -52620,7 +52617,7 @@
         <v>767</v>
       </c>
       <c r="D2131" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2131" t="s" s="3">
         <v>4230</v>
@@ -52637,7 +52634,7 @@
         <v>767</v>
       </c>
       <c r="D2132" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2132" t="s" s="3">
         <v>4232</v>
@@ -52654,7 +52651,7 @@
         <v>767</v>
       </c>
       <c r="D2133" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2133" t="s" s="3">
         <v>4234</v>
@@ -52671,7 +52668,7 @@
         <v>767</v>
       </c>
       <c r="D2134" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2134" t="s" s="3">
         <v>4236</v>
@@ -52688,7 +52685,7 @@
         <v>767</v>
       </c>
       <c r="D2135" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2135" t="s" s="3">
         <v>4238</v>
@@ -52705,7 +52702,7 @@
         <v>767</v>
       </c>
       <c r="D2136" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2136" t="s" s="3">
         <v>4240</v>
@@ -52722,7 +52719,7 @@
         <v>767</v>
       </c>
       <c r="D2137" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2137" t="s" s="3">
         <v>4242</v>
@@ -52739,7 +52736,7 @@
         <v>767</v>
       </c>
       <c r="D2138" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2138" t="s" s="3">
         <v>4244</v>
@@ -52756,7 +52753,7 @@
         <v>767</v>
       </c>
       <c r="D2139" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2139" t="s" s="3">
         <v>4246</v>
@@ -52773,7 +52770,7 @@
         <v>767</v>
       </c>
       <c r="D2140" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2140" t="s" s="3">
         <v>4248</v>
@@ -52790,7 +52787,7 @@
         <v>767</v>
       </c>
       <c r="D2141" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2141" t="s" s="3">
         <v>4250</v>
@@ -52807,7 +52804,7 @@
         <v>767</v>
       </c>
       <c r="D2142" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2142" t="s" s="3">
         <v>4252</v>
@@ -52824,7 +52821,7 @@
         <v>767</v>
       </c>
       <c r="D2143" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2143" t="s" s="3">
         <v>4254</v>
@@ -52838,10 +52835,10 @@
         <v>4255</v>
       </c>
       <c r="C2144" t="s" s="2">
-        <v>984</v>
+        <v>767</v>
       </c>
       <c r="D2144" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2144" t="s" s="3">
         <v>4256</v>
@@ -52852,16 +52849,16 @@
         <v>2144.0</v>
       </c>
       <c r="B2145" t="s" s="3">
-        <v>4211</v>
+        <v>4257</v>
       </c>
       <c r="C2145" t="s" s="2">
         <v>984</v>
       </c>
       <c r="D2145" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2145" t="s" s="3">
-        <v>4257</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="2146" ht="36.0" customHeight="true">
@@ -52869,13 +52866,13 @@
         <v>2145.0</v>
       </c>
       <c r="B2146" t="s" s="3">
-        <v>4258</v>
+        <v>4213</v>
       </c>
       <c r="C2146" t="s" s="2">
         <v>984</v>
       </c>
       <c r="D2146" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2146" t="s" s="3">
         <v>4259</v>
@@ -52886,16 +52883,16 @@
         <v>2146.0</v>
       </c>
       <c r="B2147" t="s" s="3">
-        <v>4180</v>
+        <v>4260</v>
       </c>
       <c r="C2147" t="s" s="2">
         <v>984</v>
       </c>
       <c r="D2147" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2147" t="s" s="3">
-        <v>4181</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="2148" ht="36.0" customHeight="true">
@@ -52903,16 +52900,16 @@
         <v>2147.0</v>
       </c>
       <c r="B2148" t="s" s="3">
-        <v>4260</v>
+        <v>4182</v>
       </c>
       <c r="C2148" t="s" s="2">
         <v>984</v>
       </c>
       <c r="D2148" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2148" t="s" s="3">
-        <v>4261</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="2149" ht="36.0" customHeight="true">
@@ -52926,7 +52923,7 @@
         <v>984</v>
       </c>
       <c r="D2149" t="s" s="2">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="E2149" t="s" s="3">
         <v>4263</v>
@@ -52940,13 +52937,13 @@
         <v>4264</v>
       </c>
       <c r="C2150" t="s" s="2">
-        <v>6</v>
+        <v>984</v>
       </c>
       <c r="D2150" t="s" s="2">
+        <v>4102</v>
+      </c>
+      <c r="E2150" t="s" s="3">
         <v>4265</v>
-      </c>
-      <c r="E2150" t="s" s="3">
-        <v>4266</v>
       </c>
     </row>
     <row r="2151" ht="36.0" customHeight="true">
@@ -52954,13 +52951,13 @@
         <v>2150.0</v>
       </c>
       <c r="B2151" t="s" s="3">
+        <v>4266</v>
+      </c>
+      <c r="C2151" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2151" t="s" s="2">
         <v>4267</v>
-      </c>
-      <c r="C2151" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2151" t="s" s="2">
-        <v>4265</v>
       </c>
       <c r="E2151" t="s" s="3">
         <v>4268</v>
@@ -52977,7 +52974,7 @@
         <v>6</v>
       </c>
       <c r="D2152" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2152" t="s" s="3">
         <v>4270</v>
@@ -52994,7 +52991,7 @@
         <v>6</v>
       </c>
       <c r="D2153" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2153" t="s" s="3">
         <v>4272</v>
@@ -53011,7 +53008,7 @@
         <v>6</v>
       </c>
       <c r="D2154" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2154" t="s" s="3">
         <v>4274</v>
@@ -53028,7 +53025,7 @@
         <v>6</v>
       </c>
       <c r="D2155" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2155" t="s" s="3">
         <v>4276</v>
@@ -53045,7 +53042,7 @@
         <v>6</v>
       </c>
       <c r="D2156" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2156" t="s" s="3">
         <v>4278</v>
@@ -53062,7 +53059,7 @@
         <v>6</v>
       </c>
       <c r="D2157" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2157" t="s" s="3">
         <v>4280</v>
@@ -53079,7 +53076,7 @@
         <v>6</v>
       </c>
       <c r="D2158" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2158" t="s" s="3">
         <v>4282</v>
@@ -53096,7 +53093,7 @@
         <v>6</v>
       </c>
       <c r="D2159" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2159" t="s" s="3">
         <v>4284</v>
@@ -53113,7 +53110,7 @@
         <v>6</v>
       </c>
       <c r="D2160" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2160" t="s" s="3">
         <v>4286</v>
@@ -53130,7 +53127,7 @@
         <v>6</v>
       </c>
       <c r="D2161" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2161" t="s" s="3">
         <v>4288</v>
@@ -53147,7 +53144,7 @@
         <v>6</v>
       </c>
       <c r="D2162" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2162" t="s" s="3">
         <v>4290</v>
@@ -53164,7 +53161,7 @@
         <v>6</v>
       </c>
       <c r="D2163" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2163" t="s" s="3">
         <v>4292</v>
@@ -53181,7 +53178,7 @@
         <v>6</v>
       </c>
       <c r="D2164" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2164" t="s" s="3">
         <v>4294</v>
@@ -53198,7 +53195,7 @@
         <v>6</v>
       </c>
       <c r="D2165" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2165" t="s" s="3">
         <v>4296</v>
@@ -53215,7 +53212,7 @@
         <v>6</v>
       </c>
       <c r="D2166" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2166" t="s" s="3">
         <v>4298</v>
@@ -53232,7 +53229,7 @@
         <v>6</v>
       </c>
       <c r="D2167" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2167" t="s" s="3">
         <v>4300</v>
@@ -53249,7 +53246,7 @@
         <v>6</v>
       </c>
       <c r="D2168" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2168" t="s" s="3">
         <v>4302</v>
@@ -53266,7 +53263,7 @@
         <v>6</v>
       </c>
       <c r="D2169" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2169" t="s" s="3">
         <v>4304</v>
@@ -53283,7 +53280,7 @@
         <v>6</v>
       </c>
       <c r="D2170" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2170" t="s" s="3">
         <v>4306</v>
@@ -53300,7 +53297,7 @@
         <v>6</v>
       </c>
       <c r="D2171" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2171" t="s" s="3">
         <v>4308</v>
@@ -53317,7 +53314,7 @@
         <v>6</v>
       </c>
       <c r="D2172" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2172" t="s" s="3">
         <v>4310</v>
@@ -53334,7 +53331,7 @@
         <v>6</v>
       </c>
       <c r="D2173" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2173" t="s" s="3">
         <v>4312</v>
@@ -53351,7 +53348,7 @@
         <v>6</v>
       </c>
       <c r="D2174" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2174" t="s" s="3">
         <v>4314</v>
@@ -53368,7 +53365,7 @@
         <v>6</v>
       </c>
       <c r="D2175" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2175" t="s" s="3">
         <v>4316</v>
@@ -53385,7 +53382,7 @@
         <v>6</v>
       </c>
       <c r="D2176" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2176" t="s" s="3">
         <v>4318</v>
@@ -53402,7 +53399,7 @@
         <v>6</v>
       </c>
       <c r="D2177" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2177" t="s" s="3">
         <v>4320</v>
@@ -53419,7 +53416,7 @@
         <v>6</v>
       </c>
       <c r="D2178" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2178" t="s" s="3">
         <v>4322</v>
@@ -53436,7 +53433,7 @@
         <v>6</v>
       </c>
       <c r="D2179" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2179" t="s" s="3">
         <v>4324</v>
@@ -53453,7 +53450,7 @@
         <v>6</v>
       </c>
       <c r="D2180" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2180" t="s" s="3">
         <v>4326</v>
@@ -53470,7 +53467,7 @@
         <v>6</v>
       </c>
       <c r="D2181" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2181" t="s" s="3">
         <v>4328</v>
@@ -53487,7 +53484,7 @@
         <v>6</v>
       </c>
       <c r="D2182" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2182" t="s" s="3">
         <v>4330</v>
@@ -53504,7 +53501,7 @@
         <v>6</v>
       </c>
       <c r="D2183" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2183" t="s" s="3">
         <v>4332</v>
@@ -53521,7 +53518,7 @@
         <v>6</v>
       </c>
       <c r="D2184" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2184" t="s" s="3">
         <v>4334</v>
@@ -53538,7 +53535,7 @@
         <v>6</v>
       </c>
       <c r="D2185" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2185" t="s" s="3">
         <v>4336</v>
@@ -53555,7 +53552,7 @@
         <v>6</v>
       </c>
       <c r="D2186" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2186" t="s" s="3">
         <v>4338</v>
@@ -53572,7 +53569,7 @@
         <v>6</v>
       </c>
       <c r="D2187" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2187" t="s" s="3">
         <v>4340</v>
@@ -53589,7 +53586,7 @@
         <v>6</v>
       </c>
       <c r="D2188" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2188" t="s" s="3">
         <v>4342</v>
@@ -53606,7 +53603,7 @@
         <v>6</v>
       </c>
       <c r="D2189" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2189" t="s" s="3">
         <v>4344</v>
@@ -53623,7 +53620,7 @@
         <v>6</v>
       </c>
       <c r="D2190" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2190" t="s" s="3">
         <v>4346</v>
@@ -53640,7 +53637,7 @@
         <v>6</v>
       </c>
       <c r="D2191" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2191" t="s" s="3">
         <v>4348</v>
@@ -53657,7 +53654,7 @@
         <v>6</v>
       </c>
       <c r="D2192" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2192" t="s" s="3">
         <v>4350</v>
@@ -53674,7 +53671,7 @@
         <v>6</v>
       </c>
       <c r="D2193" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2193" t="s" s="3">
         <v>4352</v>
@@ -53691,7 +53688,7 @@
         <v>6</v>
       </c>
       <c r="D2194" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2194" t="s" s="3">
         <v>4354</v>
@@ -53708,7 +53705,7 @@
         <v>6</v>
       </c>
       <c r="D2195" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2195" t="s" s="3">
         <v>4356</v>
@@ -53725,7 +53722,7 @@
         <v>6</v>
       </c>
       <c r="D2196" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2196" t="s" s="3">
         <v>4358</v>
@@ -53742,7 +53739,7 @@
         <v>6</v>
       </c>
       <c r="D2197" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2197" t="s" s="3">
         <v>4360</v>
@@ -53759,7 +53756,7 @@
         <v>6</v>
       </c>
       <c r="D2198" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2198" t="s" s="3">
         <v>4362</v>
@@ -53776,7 +53773,7 @@
         <v>6</v>
       </c>
       <c r="D2199" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2199" t="s" s="3">
         <v>4364</v>
@@ -53793,7 +53790,7 @@
         <v>6</v>
       </c>
       <c r="D2200" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2200" t="s" s="3">
         <v>4366</v>
@@ -53810,7 +53807,7 @@
         <v>6</v>
       </c>
       <c r="D2201" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2201" t="s" s="3">
         <v>4368</v>
@@ -53827,7 +53824,7 @@
         <v>6</v>
       </c>
       <c r="D2202" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2202" t="s" s="3">
         <v>4370</v>
@@ -53844,7 +53841,7 @@
         <v>6</v>
       </c>
       <c r="D2203" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2203" t="s" s="3">
         <v>4372</v>
@@ -53861,7 +53858,7 @@
         <v>6</v>
       </c>
       <c r="D2204" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2204" t="s" s="3">
         <v>4374</v>
@@ -53878,7 +53875,7 @@
         <v>6</v>
       </c>
       <c r="D2205" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2205" t="s" s="3">
         <v>4376</v>
@@ -53895,7 +53892,7 @@
         <v>6</v>
       </c>
       <c r="D2206" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2206" t="s" s="3">
         <v>4378</v>
@@ -53912,7 +53909,7 @@
         <v>6</v>
       </c>
       <c r="D2207" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2207" t="s" s="3">
         <v>4380</v>
@@ -53929,7 +53926,7 @@
         <v>6</v>
       </c>
       <c r="D2208" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2208" t="s" s="3">
         <v>4382</v>
@@ -53946,7 +53943,7 @@
         <v>6</v>
       </c>
       <c r="D2209" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2209" t="s" s="3">
         <v>4384</v>
@@ -53963,7 +53960,7 @@
         <v>6</v>
       </c>
       <c r="D2210" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2210" t="s" s="3">
         <v>4386</v>
@@ -53980,7 +53977,7 @@
         <v>6</v>
       </c>
       <c r="D2211" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2211" t="s" s="3">
         <v>4388</v>
@@ -53997,7 +53994,7 @@
         <v>6</v>
       </c>
       <c r="D2212" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2212" t="s" s="3">
         <v>4390</v>
@@ -54014,7 +54011,7 @@
         <v>6</v>
       </c>
       <c r="D2213" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2213" t="s" s="3">
         <v>4392</v>
@@ -54031,7 +54028,7 @@
         <v>6</v>
       </c>
       <c r="D2214" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2214" t="s" s="3">
         <v>4394</v>
@@ -54048,7 +54045,7 @@
         <v>6</v>
       </c>
       <c r="D2215" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2215" t="s" s="3">
         <v>4396</v>
@@ -54065,7 +54062,7 @@
         <v>6</v>
       </c>
       <c r="D2216" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2216" t="s" s="3">
         <v>4398</v>
@@ -54082,7 +54079,7 @@
         <v>6</v>
       </c>
       <c r="D2217" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2217" t="s" s="3">
         <v>4400</v>
@@ -54099,7 +54096,7 @@
         <v>6</v>
       </c>
       <c r="D2218" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2218" t="s" s="3">
         <v>4402</v>
@@ -54116,7 +54113,7 @@
         <v>6</v>
       </c>
       <c r="D2219" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2219" t="s" s="3">
         <v>4404</v>
@@ -54133,7 +54130,7 @@
         <v>6</v>
       </c>
       <c r="D2220" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2220" t="s" s="3">
         <v>4406</v>
@@ -54150,7 +54147,7 @@
         <v>6</v>
       </c>
       <c r="D2221" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2221" t="s" s="3">
         <v>4408</v>
@@ -54167,7 +54164,7 @@
         <v>6</v>
       </c>
       <c r="D2222" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2222" t="s" s="3">
         <v>4410</v>
@@ -54184,7 +54181,7 @@
         <v>6</v>
       </c>
       <c r="D2223" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2223" t="s" s="3">
         <v>4412</v>
@@ -54201,7 +54198,7 @@
         <v>6</v>
       </c>
       <c r="D2224" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2224" t="s" s="3">
         <v>4414</v>
@@ -54218,7 +54215,7 @@
         <v>6</v>
       </c>
       <c r="D2225" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2225" t="s" s="3">
         <v>4416</v>
@@ -54235,7 +54232,7 @@
         <v>6</v>
       </c>
       <c r="D2226" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2226" t="s" s="3">
         <v>4418</v>
@@ -54252,7 +54249,7 @@
         <v>6</v>
       </c>
       <c r="D2227" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2227" t="s" s="3">
         <v>4420</v>
@@ -54269,7 +54266,7 @@
         <v>6</v>
       </c>
       <c r="D2228" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2228" t="s" s="3">
         <v>4422</v>
@@ -54286,7 +54283,7 @@
         <v>6</v>
       </c>
       <c r="D2229" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2229" t="s" s="3">
         <v>4424</v>
@@ -54303,7 +54300,7 @@
         <v>6</v>
       </c>
       <c r="D2230" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2230" t="s" s="3">
         <v>4426</v>
@@ -54320,7 +54317,7 @@
         <v>6</v>
       </c>
       <c r="D2231" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2231" t="s" s="3">
         <v>4428</v>
@@ -54337,7 +54334,7 @@
         <v>6</v>
       </c>
       <c r="D2232" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2232" t="s" s="3">
         <v>4430</v>
@@ -54354,7 +54351,7 @@
         <v>6</v>
       </c>
       <c r="D2233" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2233" t="s" s="3">
         <v>4432</v>
@@ -54371,7 +54368,7 @@
         <v>6</v>
       </c>
       <c r="D2234" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2234" t="s" s="3">
         <v>4434</v>
@@ -54388,7 +54385,7 @@
         <v>6</v>
       </c>
       <c r="D2235" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2235" t="s" s="3">
         <v>4436</v>
@@ -54405,7 +54402,7 @@
         <v>6</v>
       </c>
       <c r="D2236" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2236" t="s" s="3">
         <v>4438</v>
@@ -54422,7 +54419,7 @@
         <v>6</v>
       </c>
       <c r="D2237" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2237" t="s" s="3">
         <v>4440</v>
@@ -54439,7 +54436,7 @@
         <v>6</v>
       </c>
       <c r="D2238" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2238" t="s" s="3">
         <v>4442</v>
@@ -54456,7 +54453,7 @@
         <v>6</v>
       </c>
       <c r="D2239" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2239" t="s" s="3">
         <v>4444</v>
@@ -54473,7 +54470,7 @@
         <v>6</v>
       </c>
       <c r="D2240" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2240" t="s" s="3">
         <v>4446</v>
@@ -54490,7 +54487,7 @@
         <v>6</v>
       </c>
       <c r="D2241" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2241" t="s" s="3">
         <v>4448</v>
@@ -54507,7 +54504,7 @@
         <v>6</v>
       </c>
       <c r="D2242" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2242" t="s" s="3">
         <v>4450</v>
@@ -54524,7 +54521,7 @@
         <v>6</v>
       </c>
       <c r="D2243" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2243" t="s" s="3">
         <v>4452</v>
@@ -54541,7 +54538,7 @@
         <v>6</v>
       </c>
       <c r="D2244" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2244" t="s" s="3">
         <v>4454</v>
@@ -54558,7 +54555,7 @@
         <v>6</v>
       </c>
       <c r="D2245" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2245" t="s" s="3">
         <v>4456</v>
@@ -54575,7 +54572,7 @@
         <v>6</v>
       </c>
       <c r="D2246" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2246" t="s" s="3">
         <v>4458</v>
@@ -54592,7 +54589,7 @@
         <v>6</v>
       </c>
       <c r="D2247" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2247" t="s" s="3">
         <v>4460</v>
@@ -54609,7 +54606,7 @@
         <v>6</v>
       </c>
       <c r="D2248" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2248" t="s" s="3">
         <v>4462</v>
@@ -54626,7 +54623,7 @@
         <v>6</v>
       </c>
       <c r="D2249" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2249" t="s" s="3">
         <v>4464</v>
@@ -54643,7 +54640,7 @@
         <v>6</v>
       </c>
       <c r="D2250" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2250" t="s" s="3">
         <v>4466</v>
@@ -54660,7 +54657,7 @@
         <v>6</v>
       </c>
       <c r="D2251" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2251" t="s" s="3">
         <v>4468</v>
@@ -54677,7 +54674,7 @@
         <v>6</v>
       </c>
       <c r="D2252" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2252" t="s" s="3">
         <v>4470</v>
@@ -54688,16 +54685,16 @@
         <v>2252.0</v>
       </c>
       <c r="B2253" t="s" s="3">
-        <v>1418</v>
+        <v>4471</v>
       </c>
       <c r="C2253" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2253" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2253" t="s" s="3">
-        <v>4471</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="2254" ht="36.0" customHeight="true">
@@ -54705,13 +54702,13 @@
         <v>2253.0</v>
       </c>
       <c r="B2254" t="s" s="3">
-        <v>4472</v>
+        <v>1418</v>
       </c>
       <c r="C2254" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2254" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2254" t="s" s="3">
         <v>4473</v>
@@ -54728,7 +54725,7 @@
         <v>6</v>
       </c>
       <c r="D2255" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2255" t="s" s="3">
         <v>4475</v>
@@ -54745,7 +54742,7 @@
         <v>6</v>
       </c>
       <c r="D2256" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2256" t="s" s="3">
         <v>4477</v>
@@ -54762,7 +54759,7 @@
         <v>6</v>
       </c>
       <c r="D2257" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2257" t="s" s="3">
         <v>4479</v>
@@ -54779,7 +54776,7 @@
         <v>6</v>
       </c>
       <c r="D2258" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2258" t="s" s="3">
         <v>4481</v>
@@ -54796,7 +54793,7 @@
         <v>6</v>
       </c>
       <c r="D2259" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2259" t="s" s="3">
         <v>4483</v>
@@ -54813,7 +54810,7 @@
         <v>6</v>
       </c>
       <c r="D2260" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2260" t="s" s="3">
         <v>4485</v>
@@ -54830,7 +54827,7 @@
         <v>6</v>
       </c>
       <c r="D2261" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2261" t="s" s="3">
         <v>4487</v>
@@ -54847,7 +54844,7 @@
         <v>6</v>
       </c>
       <c r="D2262" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2262" t="s" s="3">
         <v>4489</v>
@@ -54864,7 +54861,7 @@
         <v>6</v>
       </c>
       <c r="D2263" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2263" t="s" s="3">
         <v>4491</v>
@@ -54881,7 +54878,7 @@
         <v>6</v>
       </c>
       <c r="D2264" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2264" t="s" s="3">
         <v>4493</v>
@@ -54898,7 +54895,7 @@
         <v>6</v>
       </c>
       <c r="D2265" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2265" t="s" s="3">
         <v>4495</v>
@@ -54915,7 +54912,7 @@
         <v>6</v>
       </c>
       <c r="D2266" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2266" t="s" s="3">
         <v>4497</v>
@@ -54932,7 +54929,7 @@
         <v>6</v>
       </c>
       <c r="D2267" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2267" t="s" s="3">
         <v>4499</v>
@@ -54949,7 +54946,7 @@
         <v>6</v>
       </c>
       <c r="D2268" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2268" t="s" s="3">
         <v>4501</v>
@@ -54966,7 +54963,7 @@
         <v>6</v>
       </c>
       <c r="D2269" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2269" t="s" s="3">
         <v>4503</v>
@@ -54983,7 +54980,7 @@
         <v>6</v>
       </c>
       <c r="D2270" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2270" t="s" s="3">
         <v>4505</v>
@@ -55000,7 +54997,7 @@
         <v>6</v>
       </c>
       <c r="D2271" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2271" t="s" s="3">
         <v>4507</v>
@@ -55017,7 +55014,7 @@
         <v>6</v>
       </c>
       <c r="D2272" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2272" t="s" s="3">
         <v>4509</v>
@@ -55034,7 +55031,7 @@
         <v>6</v>
       </c>
       <c r="D2273" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2273" t="s" s="3">
         <v>4511</v>
@@ -55051,7 +55048,7 @@
         <v>6</v>
       </c>
       <c r="D2274" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2274" t="s" s="3">
         <v>4513</v>
@@ -55068,7 +55065,7 @@
         <v>6</v>
       </c>
       <c r="D2275" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2275" t="s" s="3">
         <v>4515</v>
@@ -55085,7 +55082,7 @@
         <v>6</v>
       </c>
       <c r="D2276" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2276" t="s" s="3">
         <v>4517</v>
@@ -55102,7 +55099,7 @@
         <v>6</v>
       </c>
       <c r="D2277" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2277" t="s" s="3">
         <v>4519</v>
@@ -55119,7 +55116,7 @@
         <v>6</v>
       </c>
       <c r="D2278" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2278" t="s" s="3">
         <v>4521</v>
@@ -55136,7 +55133,7 @@
         <v>6</v>
       </c>
       <c r="D2279" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2279" t="s" s="3">
         <v>4523</v>
@@ -55153,7 +55150,7 @@
         <v>6</v>
       </c>
       <c r="D2280" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2280" t="s" s="3">
         <v>4525</v>
@@ -55170,7 +55167,7 @@
         <v>6</v>
       </c>
       <c r="D2281" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2281" t="s" s="3">
         <v>4527</v>
@@ -55187,7 +55184,7 @@
         <v>6</v>
       </c>
       <c r="D2282" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2282" t="s" s="3">
         <v>4529</v>
@@ -55204,7 +55201,7 @@
         <v>6</v>
       </c>
       <c r="D2283" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2283" t="s" s="3">
         <v>4531</v>
@@ -55221,7 +55218,7 @@
         <v>6</v>
       </c>
       <c r="D2284" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2284" t="s" s="3">
         <v>4533</v>
@@ -55238,7 +55235,7 @@
         <v>6</v>
       </c>
       <c r="D2285" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2285" t="s" s="3">
         <v>4535</v>
@@ -55255,7 +55252,7 @@
         <v>6</v>
       </c>
       <c r="D2286" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2286" t="s" s="3">
         <v>4537</v>
@@ -55272,7 +55269,7 @@
         <v>6</v>
       </c>
       <c r="D2287" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2287" t="s" s="3">
         <v>4539</v>
@@ -55289,7 +55286,7 @@
         <v>6</v>
       </c>
       <c r="D2288" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2288" t="s" s="3">
         <v>4541</v>
@@ -55306,7 +55303,7 @@
         <v>6</v>
       </c>
       <c r="D2289" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2289" t="s" s="3">
         <v>4543</v>
@@ -55323,7 +55320,7 @@
         <v>6</v>
       </c>
       <c r="D2290" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2290" t="s" s="3">
         <v>4545</v>
@@ -55340,7 +55337,7 @@
         <v>6</v>
       </c>
       <c r="D2291" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2291" t="s" s="3">
         <v>4547</v>
@@ -55357,7 +55354,7 @@
         <v>6</v>
       </c>
       <c r="D2292" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2292" t="s" s="3">
         <v>4549</v>
@@ -55374,7 +55371,7 @@
         <v>6</v>
       </c>
       <c r="D2293" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2293" t="s" s="3">
         <v>4551</v>
@@ -55391,7 +55388,7 @@
         <v>6</v>
       </c>
       <c r="D2294" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2294" t="s" s="3">
         <v>4553</v>
@@ -55405,10 +55402,10 @@
         <v>4554</v>
       </c>
       <c r="C2295" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2295" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2295" t="s" s="3">
         <v>4555</v>
@@ -55425,7 +55422,7 @@
         <v>767</v>
       </c>
       <c r="D2296" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2296" t="s" s="3">
         <v>4557</v>
@@ -55442,7 +55439,7 @@
         <v>767</v>
       </c>
       <c r="D2297" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2297" t="s" s="3">
         <v>4559</v>
@@ -55459,7 +55456,7 @@
         <v>767</v>
       </c>
       <c r="D2298" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2298" t="s" s="3">
         <v>4561</v>
@@ -55476,7 +55473,7 @@
         <v>767</v>
       </c>
       <c r="D2299" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2299" t="s" s="3">
         <v>4563</v>
@@ -55493,7 +55490,7 @@
         <v>767</v>
       </c>
       <c r="D2300" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2300" t="s" s="3">
         <v>4565</v>
@@ -55510,7 +55507,7 @@
         <v>767</v>
       </c>
       <c r="D2301" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2301" t="s" s="3">
         <v>4567</v>
@@ -55527,7 +55524,7 @@
         <v>767</v>
       </c>
       <c r="D2302" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2302" t="s" s="3">
         <v>4569</v>
@@ -55544,7 +55541,7 @@
         <v>767</v>
       </c>
       <c r="D2303" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2303" t="s" s="3">
         <v>4571</v>
@@ -55561,7 +55558,7 @@
         <v>767</v>
       </c>
       <c r="D2304" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2304" t="s" s="3">
         <v>4573</v>
@@ -55578,7 +55575,7 @@
         <v>767</v>
       </c>
       <c r="D2305" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2305" t="s" s="3">
         <v>4575</v>
@@ -55595,7 +55592,7 @@
         <v>767</v>
       </c>
       <c r="D2306" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2306" t="s" s="3">
         <v>4577</v>
@@ -55612,7 +55609,7 @@
         <v>767</v>
       </c>
       <c r="D2307" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2307" t="s" s="3">
         <v>4579</v>
@@ -55629,7 +55626,7 @@
         <v>767</v>
       </c>
       <c r="D2308" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2308" t="s" s="3">
         <v>4581</v>
@@ -55646,7 +55643,7 @@
         <v>767</v>
       </c>
       <c r="D2309" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2309" t="s" s="3">
         <v>4583</v>
@@ -55663,7 +55660,7 @@
         <v>767</v>
       </c>
       <c r="D2310" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2310" t="s" s="3">
         <v>4585</v>
@@ -55680,7 +55677,7 @@
         <v>767</v>
       </c>
       <c r="D2311" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2311" t="s" s="3">
         <v>4587</v>
@@ -55697,7 +55694,7 @@
         <v>767</v>
       </c>
       <c r="D2312" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2312" t="s" s="3">
         <v>4589</v>
@@ -55714,7 +55711,7 @@
         <v>767</v>
       </c>
       <c r="D2313" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2313" t="s" s="3">
         <v>4591</v>
@@ -55731,7 +55728,7 @@
         <v>767</v>
       </c>
       <c r="D2314" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2314" t="s" s="3">
         <v>4593</v>
@@ -55748,10 +55745,10 @@
         <v>767</v>
       </c>
       <c r="D2315" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2315" t="s" s="3">
-        <v>4487</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="2316" ht="36.0" customHeight="true">
@@ -55759,16 +55756,16 @@
         <v>2315.0</v>
       </c>
       <c r="B2316" t="s" s="3">
-        <v>4595</v>
+        <v>4596</v>
       </c>
       <c r="C2316" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2316" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2316" t="s" s="3">
-        <v>4596</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="2317" ht="36.0" customHeight="true">
@@ -55782,7 +55779,7 @@
         <v>767</v>
       </c>
       <c r="D2317" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2317" t="s" s="3">
         <v>4598</v>
@@ -55799,7 +55796,7 @@
         <v>767</v>
       </c>
       <c r="D2318" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2318" t="s" s="3">
         <v>4600</v>
@@ -55816,7 +55813,7 @@
         <v>767</v>
       </c>
       <c r="D2319" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2319" t="s" s="3">
         <v>4602</v>
@@ -55833,7 +55830,7 @@
         <v>767</v>
       </c>
       <c r="D2320" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2320" t="s" s="3">
         <v>4604</v>
@@ -55850,7 +55847,7 @@
         <v>767</v>
       </c>
       <c r="D2321" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2321" t="s" s="3">
         <v>4606</v>
@@ -55867,7 +55864,7 @@
         <v>767</v>
       </c>
       <c r="D2322" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2322" t="s" s="3">
         <v>4608</v>
@@ -55884,7 +55881,7 @@
         <v>767</v>
       </c>
       <c r="D2323" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2323" t="s" s="3">
         <v>4610</v>
@@ -55901,7 +55898,7 @@
         <v>767</v>
       </c>
       <c r="D2324" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2324" t="s" s="3">
         <v>4612</v>
@@ -55918,7 +55915,7 @@
         <v>767</v>
       </c>
       <c r="D2325" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2325" t="s" s="3">
         <v>4614</v>
@@ -55935,7 +55932,7 @@
         <v>767</v>
       </c>
       <c r="D2326" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2326" t="s" s="3">
         <v>4616</v>
@@ -55952,7 +55949,7 @@
         <v>767</v>
       </c>
       <c r="D2327" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2327" t="s" s="3">
         <v>4618</v>
@@ -55969,7 +55966,7 @@
         <v>767</v>
       </c>
       <c r="D2328" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2328" t="s" s="3">
         <v>4620</v>
@@ -55986,7 +55983,7 @@
         <v>767</v>
       </c>
       <c r="D2329" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2329" t="s" s="3">
         <v>4622</v>
@@ -56003,7 +56000,7 @@
         <v>767</v>
       </c>
       <c r="D2330" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2330" t="s" s="3">
         <v>4624</v>
@@ -56020,7 +56017,7 @@
         <v>767</v>
       </c>
       <c r="D2331" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2331" t="s" s="3">
         <v>4626</v>
@@ -56037,7 +56034,7 @@
         <v>767</v>
       </c>
       <c r="D2332" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2332" t="s" s="3">
         <v>4628</v>
@@ -56054,7 +56051,7 @@
         <v>767</v>
       </c>
       <c r="D2333" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2333" t="s" s="3">
         <v>4630</v>
@@ -56071,7 +56068,7 @@
         <v>767</v>
       </c>
       <c r="D2334" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2334" t="s" s="3">
         <v>4632</v>
@@ -56088,7 +56085,7 @@
         <v>767</v>
       </c>
       <c r="D2335" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2335" t="s" s="3">
         <v>4634</v>
@@ -56105,7 +56102,7 @@
         <v>767</v>
       </c>
       <c r="D2336" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2336" t="s" s="3">
         <v>4636</v>
@@ -56122,7 +56119,7 @@
         <v>767</v>
       </c>
       <c r="D2337" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2337" t="s" s="3">
         <v>4638</v>
@@ -56139,7 +56136,7 @@
         <v>767</v>
       </c>
       <c r="D2338" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2338" t="s" s="3">
         <v>4640</v>
@@ -56156,7 +56153,7 @@
         <v>767</v>
       </c>
       <c r="D2339" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2339" t="s" s="3">
         <v>4642</v>
@@ -56173,7 +56170,7 @@
         <v>767</v>
       </c>
       <c r="D2340" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2340" t="s" s="3">
         <v>4644</v>
@@ -56190,7 +56187,7 @@
         <v>767</v>
       </c>
       <c r="D2341" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2341" t="s" s="3">
         <v>4646</v>
@@ -56207,7 +56204,7 @@
         <v>767</v>
       </c>
       <c r="D2342" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2342" t="s" s="3">
         <v>4648</v>
@@ -56224,7 +56221,7 @@
         <v>767</v>
       </c>
       <c r="D2343" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2343" t="s" s="3">
         <v>4650</v>
@@ -56241,7 +56238,7 @@
         <v>767</v>
       </c>
       <c r="D2344" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2344" t="s" s="3">
         <v>4652</v>
@@ -56258,7 +56255,7 @@
         <v>767</v>
       </c>
       <c r="D2345" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2345" t="s" s="3">
         <v>4654</v>
@@ -56275,7 +56272,7 @@
         <v>767</v>
       </c>
       <c r="D2346" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2346" t="s" s="3">
         <v>4656</v>
@@ -56292,7 +56289,7 @@
         <v>767</v>
       </c>
       <c r="D2347" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2347" t="s" s="3">
         <v>4658</v>
@@ -56309,7 +56306,7 @@
         <v>767</v>
       </c>
       <c r="D2348" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2348" t="s" s="3">
         <v>4660</v>
@@ -56326,7 +56323,7 @@
         <v>767</v>
       </c>
       <c r="D2349" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2349" t="s" s="3">
         <v>4662</v>
@@ -56343,7 +56340,7 @@
         <v>767</v>
       </c>
       <c r="D2350" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2350" t="s" s="3">
         <v>4664</v>
@@ -56360,7 +56357,7 @@
         <v>767</v>
       </c>
       <c r="D2351" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2351" t="s" s="3">
         <v>4666</v>
@@ -56377,7 +56374,7 @@
         <v>767</v>
       </c>
       <c r="D2352" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2352" t="s" s="3">
         <v>4668</v>
@@ -56394,7 +56391,7 @@
         <v>767</v>
       </c>
       <c r="D2353" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2353" t="s" s="3">
         <v>4670</v>
@@ -56411,7 +56408,7 @@
         <v>767</v>
       </c>
       <c r="D2354" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2354" t="s" s="3">
         <v>4672</v>
@@ -56428,7 +56425,7 @@
         <v>767</v>
       </c>
       <c r="D2355" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2355" t="s" s="3">
         <v>4674</v>
@@ -56445,7 +56442,7 @@
         <v>767</v>
       </c>
       <c r="D2356" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2356" t="s" s="3">
         <v>4676</v>
@@ -56462,7 +56459,7 @@
         <v>767</v>
       </c>
       <c r="D2357" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2357" t="s" s="3">
         <v>4678</v>
@@ -56479,7 +56476,7 @@
         <v>767</v>
       </c>
       <c r="D2358" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2358" t="s" s="3">
         <v>4680</v>
@@ -56496,7 +56493,7 @@
         <v>767</v>
       </c>
       <c r="D2359" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2359" t="s" s="3">
         <v>4682</v>
@@ -56513,7 +56510,7 @@
         <v>767</v>
       </c>
       <c r="D2360" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2360" t="s" s="3">
         <v>4684</v>
@@ -56530,7 +56527,7 @@
         <v>767</v>
       </c>
       <c r="D2361" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2361" t="s" s="3">
         <v>4686</v>
@@ -56547,7 +56544,7 @@
         <v>767</v>
       </c>
       <c r="D2362" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2362" t="s" s="3">
         <v>4688</v>
@@ -56564,7 +56561,7 @@
         <v>767</v>
       </c>
       <c r="D2363" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2363" t="s" s="3">
         <v>4690</v>
@@ -56581,7 +56578,7 @@
         <v>767</v>
       </c>
       <c r="D2364" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2364" t="s" s="3">
         <v>4692</v>
@@ -56598,7 +56595,7 @@
         <v>767</v>
       </c>
       <c r="D2365" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2365" t="s" s="3">
         <v>4694</v>
@@ -56615,7 +56612,7 @@
         <v>767</v>
       </c>
       <c r="D2366" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2366" t="s" s="3">
         <v>4696</v>
@@ -56632,7 +56629,7 @@
         <v>767</v>
       </c>
       <c r="D2367" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2367" t="s" s="3">
         <v>4698</v>
@@ -56649,7 +56646,7 @@
         <v>767</v>
       </c>
       <c r="D2368" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2368" t="s" s="3">
         <v>4700</v>
@@ -56663,10 +56660,10 @@
         <v>4701</v>
       </c>
       <c r="C2369" t="s" s="2">
-        <v>984</v>
+        <v>767</v>
       </c>
       <c r="D2369" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2369" t="s" s="3">
         <v>4702</v>
@@ -56683,7 +56680,7 @@
         <v>984</v>
       </c>
       <c r="D2370" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2370" t="s" s="3">
         <v>4704</v>
@@ -56700,7 +56697,7 @@
         <v>984</v>
       </c>
       <c r="D2371" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2371" t="s" s="3">
         <v>4706</v>
@@ -56717,7 +56714,7 @@
         <v>984</v>
       </c>
       <c r="D2372" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2372" t="s" s="3">
         <v>4708</v>
@@ -56734,7 +56731,7 @@
         <v>984</v>
       </c>
       <c r="D2373" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2373" t="s" s="3">
         <v>4710</v>
@@ -56751,7 +56748,7 @@
         <v>984</v>
       </c>
       <c r="D2374" t="s" s="2">
-        <v>4265</v>
+        <v>4267</v>
       </c>
       <c r="E2374" t="s" s="3">
         <v>4712</v>
@@ -56765,13 +56762,13 @@
         <v>4713</v>
       </c>
       <c r="C2375" t="s" s="2">
-        <v>6</v>
+        <v>984</v>
       </c>
       <c r="D2375" t="s" s="2">
+        <v>4267</v>
+      </c>
+      <c r="E2375" t="s" s="3">
         <v>4714</v>
-      </c>
-      <c r="E2375" t="s" s="3">
-        <v>4715</v>
       </c>
     </row>
     <row r="2376" ht="36.0" customHeight="true">
@@ -56779,13 +56776,13 @@
         <v>2375.0</v>
       </c>
       <c r="B2376" t="s" s="3">
+        <v>4715</v>
+      </c>
+      <c r="C2376" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2376" t="s" s="2">
         <v>4716</v>
-      </c>
-      <c r="C2376" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2376" t="s" s="2">
-        <v>4714</v>
       </c>
       <c r="E2376" t="s" s="3">
         <v>4717</v>
@@ -56802,7 +56799,7 @@
         <v>6</v>
       </c>
       <c r="D2377" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2377" t="s" s="3">
         <v>4719</v>
@@ -56819,7 +56816,7 @@
         <v>6</v>
       </c>
       <c r="D2378" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2378" t="s" s="3">
         <v>4721</v>
@@ -56836,7 +56833,7 @@
         <v>6</v>
       </c>
       <c r="D2379" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2379" t="s" s="3">
         <v>4723</v>
@@ -56853,7 +56850,7 @@
         <v>6</v>
       </c>
       <c r="D2380" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2380" t="s" s="3">
         <v>4725</v>
@@ -56870,7 +56867,7 @@
         <v>6</v>
       </c>
       <c r="D2381" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2381" t="s" s="3">
         <v>4727</v>
@@ -56887,7 +56884,7 @@
         <v>6</v>
       </c>
       <c r="D2382" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2382" t="s" s="3">
         <v>4729</v>
@@ -56904,7 +56901,7 @@
         <v>6</v>
       </c>
       <c r="D2383" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2383" t="s" s="3">
         <v>4731</v>
@@ -56921,7 +56918,7 @@
         <v>6</v>
       </c>
       <c r="D2384" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2384" t="s" s="3">
         <v>4733</v>
@@ -56938,7 +56935,7 @@
         <v>6</v>
       </c>
       <c r="D2385" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2385" t="s" s="3">
         <v>4735</v>
@@ -56955,7 +56952,7 @@
         <v>6</v>
       </c>
       <c r="D2386" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2386" t="s" s="3">
         <v>4737</v>
@@ -56972,7 +56969,7 @@
         <v>6</v>
       </c>
       <c r="D2387" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2387" t="s" s="3">
         <v>4739</v>
@@ -56989,7 +56986,7 @@
         <v>6</v>
       </c>
       <c r="D2388" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2388" t="s" s="3">
         <v>4741</v>
@@ -57006,7 +57003,7 @@
         <v>6</v>
       </c>
       <c r="D2389" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2389" t="s" s="3">
         <v>4743</v>
@@ -57023,7 +57020,7 @@
         <v>6</v>
       </c>
       <c r="D2390" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2390" t="s" s="3">
         <v>4745</v>
@@ -57040,7 +57037,7 @@
         <v>6</v>
       </c>
       <c r="D2391" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2391" t="s" s="3">
         <v>4747</v>
@@ -57057,7 +57054,7 @@
         <v>6</v>
       </c>
       <c r="D2392" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2392" t="s" s="3">
         <v>4749</v>
@@ -57074,7 +57071,7 @@
         <v>6</v>
       </c>
       <c r="D2393" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2393" t="s" s="3">
         <v>4751</v>
@@ -57091,7 +57088,7 @@
         <v>6</v>
       </c>
       <c r="D2394" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2394" t="s" s="3">
         <v>4753</v>
@@ -57108,7 +57105,7 @@
         <v>6</v>
       </c>
       <c r="D2395" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2395" t="s" s="3">
         <v>4755</v>
@@ -57125,7 +57122,7 @@
         <v>6</v>
       </c>
       <c r="D2396" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2396" t="s" s="3">
         <v>4757</v>
@@ -57142,7 +57139,7 @@
         <v>6</v>
       </c>
       <c r="D2397" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2397" t="s" s="3">
         <v>4759</v>
@@ -57159,7 +57156,7 @@
         <v>6</v>
       </c>
       <c r="D2398" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2398" t="s" s="3">
         <v>4761</v>
@@ -57176,7 +57173,7 @@
         <v>6</v>
       </c>
       <c r="D2399" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2399" t="s" s="3">
         <v>4763</v>
@@ -57193,7 +57190,7 @@
         <v>6</v>
       </c>
       <c r="D2400" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2400" t="s" s="3">
         <v>4765</v>
@@ -57210,7 +57207,7 @@
         <v>6</v>
       </c>
       <c r="D2401" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2401" t="s" s="3">
         <v>4767</v>
@@ -57227,7 +57224,7 @@
         <v>6</v>
       </c>
       <c r="D2402" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2402" t="s" s="3">
         <v>4769</v>
@@ -57244,7 +57241,7 @@
         <v>6</v>
       </c>
       <c r="D2403" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2403" t="s" s="3">
         <v>4771</v>
@@ -57261,7 +57258,7 @@
         <v>6</v>
       </c>
       <c r="D2404" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2404" t="s" s="3">
         <v>4773</v>
@@ -57278,7 +57275,7 @@
         <v>6</v>
       </c>
       <c r="D2405" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2405" t="s" s="3">
         <v>4775</v>
@@ -57295,7 +57292,7 @@
         <v>6</v>
       </c>
       <c r="D2406" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2406" t="s" s="3">
         <v>4777</v>
@@ -57312,7 +57309,7 @@
         <v>6</v>
       </c>
       <c r="D2407" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2407" t="s" s="3">
         <v>4779</v>
@@ -57329,7 +57326,7 @@
         <v>6</v>
       </c>
       <c r="D2408" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2408" t="s" s="3">
         <v>4781</v>
@@ -57346,7 +57343,7 @@
         <v>6</v>
       </c>
       <c r="D2409" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2409" t="s" s="3">
         <v>4783</v>
@@ -57363,7 +57360,7 @@
         <v>6</v>
       </c>
       <c r="D2410" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2410" t="s" s="3">
         <v>4785</v>
@@ -57380,7 +57377,7 @@
         <v>6</v>
       </c>
       <c r="D2411" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2411" t="s" s="3">
         <v>4787</v>
@@ -57397,7 +57394,7 @@
         <v>6</v>
       </c>
       <c r="D2412" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2412" t="s" s="3">
         <v>4789</v>
@@ -57414,7 +57411,7 @@
         <v>6</v>
       </c>
       <c r="D2413" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2413" t="s" s="3">
         <v>4791</v>
@@ -57431,7 +57428,7 @@
         <v>6</v>
       </c>
       <c r="D2414" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2414" t="s" s="3">
         <v>4793</v>
@@ -57448,7 +57445,7 @@
         <v>6</v>
       </c>
       <c r="D2415" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2415" t="s" s="3">
         <v>4795</v>
@@ -57465,7 +57462,7 @@
         <v>6</v>
       </c>
       <c r="D2416" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2416" t="s" s="3">
         <v>4797</v>
@@ -57482,7 +57479,7 @@
         <v>6</v>
       </c>
       <c r="D2417" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2417" t="s" s="3">
         <v>4799</v>
@@ -57499,7 +57496,7 @@
         <v>6</v>
       </c>
       <c r="D2418" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2418" t="s" s="3">
         <v>4801</v>
@@ -57516,7 +57513,7 @@
         <v>6</v>
       </c>
       <c r="D2419" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2419" t="s" s="3">
         <v>4803</v>
@@ -57533,7 +57530,7 @@
         <v>6</v>
       </c>
       <c r="D2420" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2420" t="s" s="3">
         <v>4805</v>
@@ -57550,7 +57547,7 @@
         <v>6</v>
       </c>
       <c r="D2421" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2421" t="s" s="3">
         <v>4807</v>
@@ -57567,7 +57564,7 @@
         <v>6</v>
       </c>
       <c r="D2422" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2422" t="s" s="3">
         <v>4809</v>
@@ -57584,7 +57581,7 @@
         <v>6</v>
       </c>
       <c r="D2423" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2423" t="s" s="3">
         <v>4811</v>
@@ -57601,7 +57598,7 @@
         <v>6</v>
       </c>
       <c r="D2424" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2424" t="s" s="3">
         <v>4813</v>
@@ -57618,7 +57615,7 @@
         <v>6</v>
       </c>
       <c r="D2425" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2425" t="s" s="3">
         <v>4815</v>
@@ -57635,7 +57632,7 @@
         <v>6</v>
       </c>
       <c r="D2426" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2426" t="s" s="3">
         <v>4817</v>
@@ -57652,7 +57649,7 @@
         <v>6</v>
       </c>
       <c r="D2427" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2427" t="s" s="3">
         <v>4819</v>
@@ -57669,7 +57666,7 @@
         <v>6</v>
       </c>
       <c r="D2428" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2428" t="s" s="3">
         <v>4821</v>
@@ -57686,7 +57683,7 @@
         <v>6</v>
       </c>
       <c r="D2429" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2429" t="s" s="3">
         <v>4823</v>
@@ -57700,10 +57697,10 @@
         <v>4824</v>
       </c>
       <c r="C2430" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2430" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2430" t="s" s="3">
         <v>4825</v>
@@ -57720,7 +57717,7 @@
         <v>767</v>
       </c>
       <c r="D2431" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2431" t="s" s="3">
         <v>4827</v>
@@ -57737,7 +57734,7 @@
         <v>767</v>
       </c>
       <c r="D2432" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2432" t="s" s="3">
         <v>4829</v>
@@ -57754,7 +57751,7 @@
         <v>767</v>
       </c>
       <c r="D2433" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2433" t="s" s="3">
         <v>4831</v>
@@ -57771,7 +57768,7 @@
         <v>767</v>
       </c>
       <c r="D2434" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2434" t="s" s="3">
         <v>4833</v>
@@ -57788,7 +57785,7 @@
         <v>767</v>
       </c>
       <c r="D2435" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2435" t="s" s="3">
         <v>4835</v>
@@ -57805,7 +57802,7 @@
         <v>767</v>
       </c>
       <c r="D2436" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2436" t="s" s="3">
         <v>4837</v>
@@ -57822,7 +57819,7 @@
         <v>767</v>
       </c>
       <c r="D2437" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2437" t="s" s="3">
         <v>4839</v>
@@ -57839,7 +57836,7 @@
         <v>767</v>
       </c>
       <c r="D2438" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2438" t="s" s="3">
         <v>4841</v>
@@ -57856,7 +57853,7 @@
         <v>767</v>
       </c>
       <c r="D2439" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2439" t="s" s="3">
         <v>4843</v>
@@ -57873,7 +57870,7 @@
         <v>767</v>
       </c>
       <c r="D2440" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2440" t="s" s="3">
         <v>4845</v>
@@ -57890,7 +57887,7 @@
         <v>767</v>
       </c>
       <c r="D2441" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2441" t="s" s="3">
         <v>4847</v>
@@ -57907,7 +57904,7 @@
         <v>767</v>
       </c>
       <c r="D2442" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2442" t="s" s="3">
         <v>4849</v>
@@ -57924,7 +57921,7 @@
         <v>767</v>
       </c>
       <c r="D2443" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2443" t="s" s="3">
         <v>4851</v>
@@ -57941,7 +57938,7 @@
         <v>767</v>
       </c>
       <c r="D2444" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2444" t="s" s="3">
         <v>4853</v>
@@ -57958,7 +57955,7 @@
         <v>767</v>
       </c>
       <c r="D2445" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2445" t="s" s="3">
         <v>4855</v>
@@ -57975,7 +57972,7 @@
         <v>767</v>
       </c>
       <c r="D2446" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2446" t="s" s="3">
         <v>4857</v>
@@ -57992,7 +57989,7 @@
         <v>767</v>
       </c>
       <c r="D2447" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2447" t="s" s="3">
         <v>4859</v>
@@ -58009,7 +58006,7 @@
         <v>767</v>
       </c>
       <c r="D2448" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2448" t="s" s="3">
         <v>4861</v>
@@ -58026,7 +58023,7 @@
         <v>767</v>
       </c>
       <c r="D2449" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2449" t="s" s="3">
         <v>4863</v>
@@ -58043,7 +58040,7 @@
         <v>767</v>
       </c>
       <c r="D2450" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2450" t="s" s="3">
         <v>4865</v>
@@ -58060,7 +58057,7 @@
         <v>767</v>
       </c>
       <c r="D2451" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2451" t="s" s="3">
         <v>4867</v>
@@ -58077,7 +58074,7 @@
         <v>767</v>
       </c>
       <c r="D2452" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2452" t="s" s="3">
         <v>4869</v>
@@ -58094,7 +58091,7 @@
         <v>767</v>
       </c>
       <c r="D2453" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2453" t="s" s="3">
         <v>4871</v>
@@ -58111,7 +58108,7 @@
         <v>767</v>
       </c>
       <c r="D2454" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2454" t="s" s="3">
         <v>4873</v>
@@ -58128,7 +58125,7 @@
         <v>767</v>
       </c>
       <c r="D2455" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2455" t="s" s="3">
         <v>4875</v>
@@ -58145,7 +58142,7 @@
         <v>767</v>
       </c>
       <c r="D2456" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2456" t="s" s="3">
         <v>4877</v>
@@ -58162,7 +58159,7 @@
         <v>767</v>
       </c>
       <c r="D2457" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2457" t="s" s="3">
         <v>4879</v>
@@ -58179,7 +58176,7 @@
         <v>767</v>
       </c>
       <c r="D2458" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2458" t="s" s="3">
         <v>4881</v>
@@ -58196,7 +58193,7 @@
         <v>767</v>
       </c>
       <c r="D2459" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2459" t="s" s="3">
         <v>4883</v>
@@ -58213,7 +58210,7 @@
         <v>767</v>
       </c>
       <c r="D2460" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2460" t="s" s="3">
         <v>4885</v>
@@ -58230,7 +58227,7 @@
         <v>767</v>
       </c>
       <c r="D2461" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2461" t="s" s="3">
         <v>4887</v>
@@ -58247,7 +58244,7 @@
         <v>767</v>
       </c>
       <c r="D2462" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2462" t="s" s="3">
         <v>4889</v>
@@ -58264,7 +58261,7 @@
         <v>767</v>
       </c>
       <c r="D2463" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2463" t="s" s="3">
         <v>4891</v>
@@ -58281,7 +58278,7 @@
         <v>767</v>
       </c>
       <c r="D2464" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2464" t="s" s="3">
         <v>4893</v>
@@ -58298,7 +58295,7 @@
         <v>767</v>
       </c>
       <c r="D2465" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2465" t="s" s="3">
         <v>4895</v>
@@ -58315,7 +58312,7 @@
         <v>767</v>
       </c>
       <c r="D2466" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2466" t="s" s="3">
         <v>4897</v>
@@ -58332,7 +58329,7 @@
         <v>767</v>
       </c>
       <c r="D2467" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2467" t="s" s="3">
         <v>4899</v>
@@ -58346,10 +58343,10 @@
         <v>4900</v>
       </c>
       <c r="C2468" t="s" s="2">
-        <v>984</v>
+        <v>767</v>
       </c>
       <c r="D2468" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2468" t="s" s="3">
         <v>4901</v>
@@ -58366,7 +58363,7 @@
         <v>984</v>
       </c>
       <c r="D2469" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2469" t="s" s="3">
         <v>4903</v>
@@ -58383,7 +58380,7 @@
         <v>984</v>
       </c>
       <c r="D2470" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2470" t="s" s="3">
         <v>4905</v>
@@ -58400,7 +58397,7 @@
         <v>984</v>
       </c>
       <c r="D2471" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2471" t="s" s="3">
         <v>4907</v>
@@ -58417,7 +58414,7 @@
         <v>984</v>
       </c>
       <c r="D2472" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2472" t="s" s="3">
         <v>4909</v>
@@ -58434,7 +58431,7 @@
         <v>984</v>
       </c>
       <c r="D2473" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2473" t="s" s="3">
         <v>4911</v>
@@ -58451,7 +58448,7 @@
         <v>984</v>
       </c>
       <c r="D2474" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2474" t="s" s="3">
         <v>4913</v>
@@ -58468,7 +58465,7 @@
         <v>984</v>
       </c>
       <c r="D2475" t="s" s="2">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="E2475" t="s" s="3">
         <v>4915</v>
@@ -58482,13 +58479,13 @@
         <v>4916</v>
       </c>
       <c r="C2476" t="s" s="2">
-        <v>6</v>
+        <v>984</v>
       </c>
       <c r="D2476" t="s" s="2">
+        <v>4716</v>
+      </c>
+      <c r="E2476" t="s" s="3">
         <v>4917</v>
-      </c>
-      <c r="E2476" t="s" s="3">
-        <v>4918</v>
       </c>
     </row>
     <row r="2477" ht="36.0" customHeight="true">
@@ -58496,13 +58493,13 @@
         <v>2476.0</v>
       </c>
       <c r="B2477" t="s" s="3">
+        <v>4918</v>
+      </c>
+      <c r="C2477" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2477" t="s" s="2">
         <v>4919</v>
-      </c>
-      <c r="C2477" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2477" t="s" s="2">
-        <v>4917</v>
       </c>
       <c r="E2477" t="s" s="3">
         <v>4920</v>
@@ -58519,7 +58516,7 @@
         <v>6</v>
       </c>
       <c r="D2478" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2478" t="s" s="3">
         <v>4922</v>
@@ -58536,7 +58533,7 @@
         <v>6</v>
       </c>
       <c r="D2479" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2479" t="s" s="3">
         <v>4924</v>
@@ -58553,7 +58550,7 @@
         <v>6</v>
       </c>
       <c r="D2480" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2480" t="s" s="3">
         <v>4926</v>
@@ -58570,7 +58567,7 @@
         <v>6</v>
       </c>
       <c r="D2481" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2481" t="s" s="3">
         <v>4928</v>
@@ -58587,7 +58584,7 @@
         <v>6</v>
       </c>
       <c r="D2482" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2482" t="s" s="3">
         <v>4930</v>
@@ -58604,7 +58601,7 @@
         <v>6</v>
       </c>
       <c r="D2483" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2483" t="s" s="3">
         <v>4932</v>
@@ -58621,7 +58618,7 @@
         <v>6</v>
       </c>
       <c r="D2484" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2484" t="s" s="3">
         <v>4934</v>
@@ -58638,7 +58635,7 @@
         <v>6</v>
       </c>
       <c r="D2485" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2485" t="s" s="3">
         <v>4936</v>
@@ -58655,7 +58652,7 @@
         <v>6</v>
       </c>
       <c r="D2486" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2486" t="s" s="3">
         <v>4938</v>
@@ -58672,7 +58669,7 @@
         <v>6</v>
       </c>
       <c r="D2487" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2487" t="s" s="3">
         <v>4940</v>
@@ -58689,7 +58686,7 @@
         <v>6</v>
       </c>
       <c r="D2488" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2488" t="s" s="3">
         <v>4942</v>
@@ -58706,7 +58703,7 @@
         <v>6</v>
       </c>
       <c r="D2489" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2489" t="s" s="3">
         <v>4944</v>
@@ -58723,7 +58720,7 @@
         <v>6</v>
       </c>
       <c r="D2490" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2490" t="s" s="3">
         <v>4946</v>
@@ -58740,7 +58737,7 @@
         <v>6</v>
       </c>
       <c r="D2491" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2491" t="s" s="3">
         <v>4948</v>
@@ -58757,7 +58754,7 @@
         <v>6</v>
       </c>
       <c r="D2492" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2492" t="s" s="3">
         <v>4950</v>
@@ -58774,7 +58771,7 @@
         <v>6</v>
       </c>
       <c r="D2493" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2493" t="s" s="3">
         <v>4952</v>
@@ -58791,7 +58788,7 @@
         <v>6</v>
       </c>
       <c r="D2494" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2494" t="s" s="3">
         <v>4954</v>
@@ -58808,7 +58805,7 @@
         <v>6</v>
       </c>
       <c r="D2495" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2495" t="s" s="3">
         <v>4956</v>
@@ -58825,7 +58822,7 @@
         <v>6</v>
       </c>
       <c r="D2496" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2496" t="s" s="3">
         <v>4958</v>
@@ -58842,7 +58839,7 @@
         <v>6</v>
       </c>
       <c r="D2497" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2497" t="s" s="3">
         <v>4960</v>
@@ -58859,7 +58856,7 @@
         <v>6</v>
       </c>
       <c r="D2498" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2498" t="s" s="3">
         <v>4962</v>
@@ -58876,7 +58873,7 @@
         <v>6</v>
       </c>
       <c r="D2499" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2499" t="s" s="3">
         <v>4964</v>
@@ -58893,7 +58890,7 @@
         <v>6</v>
       </c>
       <c r="D2500" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2500" t="s" s="3">
         <v>4966</v>
@@ -58910,7 +58907,7 @@
         <v>6</v>
       </c>
       <c r="D2501" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2501" t="s" s="3">
         <v>4968</v>
@@ -58927,7 +58924,7 @@
         <v>6</v>
       </c>
       <c r="D2502" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2502" t="s" s="3">
         <v>4970</v>
@@ -58944,7 +58941,7 @@
         <v>6</v>
       </c>
       <c r="D2503" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2503" t="s" s="3">
         <v>4972</v>
@@ -58961,7 +58958,7 @@
         <v>6</v>
       </c>
       <c r="D2504" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2504" t="s" s="3">
         <v>4974</v>
@@ -58978,7 +58975,7 @@
         <v>6</v>
       </c>
       <c r="D2505" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2505" t="s" s="3">
         <v>4976</v>
@@ -58995,7 +58992,7 @@
         <v>6</v>
       </c>
       <c r="D2506" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2506" t="s" s="3">
         <v>4978</v>
@@ -59012,7 +59009,7 @@
         <v>6</v>
       </c>
       <c r="D2507" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2507" t="s" s="3">
         <v>4980</v>
@@ -59029,7 +59026,7 @@
         <v>6</v>
       </c>
       <c r="D2508" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2508" t="s" s="3">
         <v>4982</v>
@@ -59046,7 +59043,7 @@
         <v>6</v>
       </c>
       <c r="D2509" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2509" t="s" s="3">
         <v>4984</v>
@@ -59063,7 +59060,7 @@
         <v>6</v>
       </c>
       <c r="D2510" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2510" t="s" s="3">
         <v>4986</v>
@@ -59080,7 +59077,7 @@
         <v>6</v>
       </c>
       <c r="D2511" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2511" t="s" s="3">
         <v>4988</v>
@@ -59097,7 +59094,7 @@
         <v>6</v>
       </c>
       <c r="D2512" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2512" t="s" s="3">
         <v>4990</v>
@@ -59114,7 +59111,7 @@
         <v>6</v>
       </c>
       <c r="D2513" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2513" t="s" s="3">
         <v>4992</v>
@@ -59131,7 +59128,7 @@
         <v>6</v>
       </c>
       <c r="D2514" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2514" t="s" s="3">
         <v>4994</v>
@@ -59148,7 +59145,7 @@
         <v>6</v>
       </c>
       <c r="D2515" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2515" t="s" s="3">
         <v>4996</v>
@@ -59165,7 +59162,7 @@
         <v>6</v>
       </c>
       <c r="D2516" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2516" t="s" s="3">
         <v>4998</v>
@@ -59182,7 +59179,7 @@
         <v>6</v>
       </c>
       <c r="D2517" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2517" t="s" s="3">
         <v>5000</v>
@@ -59199,7 +59196,7 @@
         <v>6</v>
       </c>
       <c r="D2518" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2518" t="s" s="3">
         <v>5002</v>
@@ -59216,7 +59213,7 @@
         <v>6</v>
       </c>
       <c r="D2519" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2519" t="s" s="3">
         <v>5004</v>
@@ -59233,7 +59230,7 @@
         <v>6</v>
       </c>
       <c r="D2520" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2520" t="s" s="3">
         <v>5006</v>
@@ -59250,7 +59247,7 @@
         <v>6</v>
       </c>
       <c r="D2521" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2521" t="s" s="3">
         <v>5008</v>
@@ -59267,7 +59264,7 @@
         <v>6</v>
       </c>
       <c r="D2522" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2522" t="s" s="3">
         <v>5010</v>
@@ -59284,7 +59281,7 @@
         <v>6</v>
       </c>
       <c r="D2523" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2523" t="s" s="3">
         <v>5012</v>
@@ -59301,7 +59298,7 @@
         <v>6</v>
       </c>
       <c r="D2524" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2524" t="s" s="3">
         <v>5014</v>
@@ -59318,7 +59315,7 @@
         <v>6</v>
       </c>
       <c r="D2525" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2525" t="s" s="3">
         <v>5016</v>
@@ -59335,7 +59332,7 @@
         <v>6</v>
       </c>
       <c r="D2526" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2526" t="s" s="3">
         <v>5018</v>
@@ -59352,7 +59349,7 @@
         <v>6</v>
       </c>
       <c r="D2527" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2527" t="s" s="3">
         <v>5020</v>
@@ -59369,7 +59366,7 @@
         <v>6</v>
       </c>
       <c r="D2528" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2528" t="s" s="3">
         <v>5022</v>
@@ -59386,7 +59383,7 @@
         <v>6</v>
       </c>
       <c r="D2529" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2529" t="s" s="3">
         <v>5024</v>
@@ -59403,7 +59400,7 @@
         <v>6</v>
       </c>
       <c r="D2530" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2530" t="s" s="3">
         <v>5026</v>
@@ -59420,7 +59417,7 @@
         <v>6</v>
       </c>
       <c r="D2531" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2531" t="s" s="3">
         <v>5028</v>
@@ -59437,7 +59434,7 @@
         <v>6</v>
       </c>
       <c r="D2532" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2532" t="s" s="3">
         <v>5030</v>
@@ -59454,7 +59451,7 @@
         <v>6</v>
       </c>
       <c r="D2533" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2533" t="s" s="3">
         <v>5032</v>
@@ -59471,7 +59468,7 @@
         <v>6</v>
       </c>
       <c r="D2534" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2534" t="s" s="3">
         <v>5034</v>
@@ -59488,7 +59485,7 @@
         <v>6</v>
       </c>
       <c r="D2535" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2535" t="s" s="3">
         <v>5036</v>
@@ -59505,7 +59502,7 @@
         <v>6</v>
       </c>
       <c r="D2536" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2536" t="s" s="3">
         <v>5038</v>
@@ -59522,7 +59519,7 @@
         <v>6</v>
       </c>
       <c r="D2537" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2537" t="s" s="3">
         <v>5040</v>
@@ -59539,7 +59536,7 @@
         <v>6</v>
       </c>
       <c r="D2538" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2538" t="s" s="3">
         <v>5042</v>
@@ -59556,7 +59553,7 @@
         <v>6</v>
       </c>
       <c r="D2539" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2539" t="s" s="3">
         <v>5044</v>
@@ -59573,7 +59570,7 @@
         <v>6</v>
       </c>
       <c r="D2540" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2540" t="s" s="3">
         <v>5046</v>
@@ -59590,7 +59587,7 @@
         <v>6</v>
       </c>
       <c r="D2541" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2541" t="s" s="3">
         <v>5048</v>
@@ -59607,7 +59604,7 @@
         <v>6</v>
       </c>
       <c r="D2542" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2542" t="s" s="3">
         <v>5050</v>
@@ -59624,7 +59621,7 @@
         <v>6</v>
       </c>
       <c r="D2543" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2543" t="s" s="3">
         <v>5052</v>
@@ -59641,7 +59638,7 @@
         <v>6</v>
       </c>
       <c r="D2544" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2544" t="s" s="3">
         <v>5054</v>
@@ -59658,10 +59655,10 @@
         <v>6</v>
       </c>
       <c r="D2545" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2545" t="s" s="3">
-        <v>5028</v>
+        <v>5056</v>
       </c>
     </row>
     <row r="2546" ht="36.0" customHeight="true">
@@ -59669,16 +59666,16 @@
         <v>2545.0</v>
       </c>
       <c r="B2546" t="s" s="3">
-        <v>5056</v>
+        <v>5057</v>
       </c>
       <c r="C2546" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2546" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2546" t="s" s="3">
-        <v>5057</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="2547" ht="36.0" customHeight="true">
@@ -59692,7 +59689,7 @@
         <v>6</v>
       </c>
       <c r="D2547" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2547" t="s" s="3">
         <v>5059</v>
@@ -59709,7 +59706,7 @@
         <v>6</v>
       </c>
       <c r="D2548" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2548" t="s" s="3">
         <v>5061</v>
@@ -59726,7 +59723,7 @@
         <v>6</v>
       </c>
       <c r="D2549" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2549" t="s" s="3">
         <v>5063</v>
@@ -59743,7 +59740,7 @@
         <v>6</v>
       </c>
       <c r="D2550" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2550" t="s" s="3">
         <v>5065</v>
@@ -59760,7 +59757,7 @@
         <v>6</v>
       </c>
       <c r="D2551" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2551" t="s" s="3">
         <v>5067</v>
@@ -59777,7 +59774,7 @@
         <v>6</v>
       </c>
       <c r="D2552" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2552" t="s" s="3">
         <v>5069</v>
@@ -59794,7 +59791,7 @@
         <v>6</v>
       </c>
       <c r="D2553" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2553" t="s" s="3">
         <v>5071</v>
@@ -59811,10 +59808,10 @@
         <v>6</v>
       </c>
       <c r="D2554" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2554" t="s" s="3">
-        <v>4990</v>
+        <v>5073</v>
       </c>
     </row>
     <row r="2555" ht="36.0" customHeight="true">
@@ -59822,16 +59819,16 @@
         <v>2554.0</v>
       </c>
       <c r="B2555" t="s" s="3">
-        <v>4063</v>
+        <v>5074</v>
       </c>
       <c r="C2555" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2555" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2555" t="s" s="3">
-        <v>5073</v>
+        <v>4992</v>
       </c>
     </row>
     <row r="2556" ht="36.0" customHeight="true">
@@ -59839,16 +59836,16 @@
         <v>2555.0</v>
       </c>
       <c r="B2556" t="s" s="3">
-        <v>5074</v>
+        <v>4065</v>
       </c>
       <c r="C2556" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2556" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2556" t="s" s="3">
-        <v>5028</v>
+        <v>5075</v>
       </c>
     </row>
     <row r="2557" ht="36.0" customHeight="true">
@@ -59856,16 +59853,16 @@
         <v>2556.0</v>
       </c>
       <c r="B2557" t="s" s="3">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="C2557" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2557" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2557" t="s" s="3">
-        <v>5076</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="2558" ht="36.0" customHeight="true">
@@ -59879,7 +59876,7 @@
         <v>6</v>
       </c>
       <c r="D2558" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2558" t="s" s="3">
         <v>5078</v>
@@ -59896,7 +59893,7 @@
         <v>6</v>
       </c>
       <c r="D2559" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2559" t="s" s="3">
         <v>5080</v>
@@ -59913,7 +59910,7 @@
         <v>6</v>
       </c>
       <c r="D2560" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2560" t="s" s="3">
         <v>5082</v>
@@ -59930,7 +59927,7 @@
         <v>6</v>
       </c>
       <c r="D2561" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2561" t="s" s="3">
         <v>5084</v>
@@ -59947,7 +59944,7 @@
         <v>6</v>
       </c>
       <c r="D2562" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2562" t="s" s="3">
         <v>5086</v>
@@ -59964,7 +59961,7 @@
         <v>6</v>
       </c>
       <c r="D2563" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2563" t="s" s="3">
         <v>5088</v>
@@ -59981,7 +59978,7 @@
         <v>6</v>
       </c>
       <c r="D2564" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2564" t="s" s="3">
         <v>5090</v>
@@ -59998,7 +59995,7 @@
         <v>6</v>
       </c>
       <c r="D2565" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2565" t="s" s="3">
         <v>5092</v>
@@ -60015,7 +60012,7 @@
         <v>6</v>
       </c>
       <c r="D2566" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2566" t="s" s="3">
         <v>5094</v>
@@ -60032,7 +60029,7 @@
         <v>6</v>
       </c>
       <c r="D2567" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2567" t="s" s="3">
         <v>5096</v>
@@ -60049,7 +60046,7 @@
         <v>6</v>
       </c>
       <c r="D2568" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2568" t="s" s="3">
         <v>5098</v>
@@ -60066,7 +60063,7 @@
         <v>6</v>
       </c>
       <c r="D2569" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2569" t="s" s="3">
         <v>5100</v>
@@ -60083,7 +60080,7 @@
         <v>6</v>
       </c>
       <c r="D2570" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2570" t="s" s="3">
         <v>5102</v>
@@ -60100,7 +60097,7 @@
         <v>6</v>
       </c>
       <c r="D2571" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2571" t="s" s="3">
         <v>5104</v>
@@ -60117,7 +60114,7 @@
         <v>6</v>
       </c>
       <c r="D2572" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2572" t="s" s="3">
         <v>5106</v>
@@ -60134,7 +60131,7 @@
         <v>6</v>
       </c>
       <c r="D2573" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2573" t="s" s="3">
         <v>5108</v>
@@ -60151,7 +60148,7 @@
         <v>6</v>
       </c>
       <c r="D2574" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2574" t="s" s="3">
         <v>5110</v>
@@ -60168,7 +60165,7 @@
         <v>6</v>
       </c>
       <c r="D2575" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2575" t="s" s="3">
         <v>5112</v>
@@ -60185,7 +60182,7 @@
         <v>6</v>
       </c>
       <c r="D2576" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2576" t="s" s="3">
         <v>5114</v>
@@ -60202,7 +60199,7 @@
         <v>6</v>
       </c>
       <c r="D2577" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2577" t="s" s="3">
         <v>5116</v>
@@ -60219,7 +60216,7 @@
         <v>6</v>
       </c>
       <c r="D2578" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2578" t="s" s="3">
         <v>5118</v>
@@ -60236,7 +60233,7 @@
         <v>6</v>
       </c>
       <c r="D2579" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2579" t="s" s="3">
         <v>5120</v>
@@ -60253,7 +60250,7 @@
         <v>6</v>
       </c>
       <c r="D2580" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2580" t="s" s="3">
         <v>5122</v>
@@ -60270,7 +60267,7 @@
         <v>6</v>
       </c>
       <c r="D2581" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2581" t="s" s="3">
         <v>5124</v>
@@ -60287,7 +60284,7 @@
         <v>6</v>
       </c>
       <c r="D2582" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2582" t="s" s="3">
         <v>5126</v>
@@ -60304,7 +60301,7 @@
         <v>6</v>
       </c>
       <c r="D2583" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2583" t="s" s="3">
         <v>5128</v>
@@ -60321,7 +60318,7 @@
         <v>6</v>
       </c>
       <c r="D2584" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2584" t="s" s="3">
         <v>5130</v>
@@ -60338,7 +60335,7 @@
         <v>6</v>
       </c>
       <c r="D2585" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2585" t="s" s="3">
         <v>5132</v>
@@ -60355,7 +60352,7 @@
         <v>6</v>
       </c>
       <c r="D2586" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2586" t="s" s="3">
         <v>5134</v>
@@ -60372,7 +60369,7 @@
         <v>6</v>
       </c>
       <c r="D2587" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2587" t="s" s="3">
         <v>5136</v>
@@ -60389,7 +60386,7 @@
         <v>6</v>
       </c>
       <c r="D2588" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2588" t="s" s="3">
         <v>5138</v>
@@ -60406,7 +60403,7 @@
         <v>6</v>
       </c>
       <c r="D2589" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2589" t="s" s="3">
         <v>5140</v>
@@ -60423,7 +60420,7 @@
         <v>6</v>
       </c>
       <c r="D2590" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2590" t="s" s="3">
         <v>5142</v>
@@ -60440,7 +60437,7 @@
         <v>6</v>
       </c>
       <c r="D2591" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2591" t="s" s="3">
         <v>5144</v>
@@ -60457,7 +60454,7 @@
         <v>6</v>
       </c>
       <c r="D2592" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2592" t="s" s="3">
         <v>5146</v>
@@ -60474,7 +60471,7 @@
         <v>6</v>
       </c>
       <c r="D2593" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2593" t="s" s="3">
         <v>5148</v>
@@ -60491,7 +60488,7 @@
         <v>6</v>
       </c>
       <c r="D2594" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2594" t="s" s="3">
         <v>5150</v>
@@ -60508,7 +60505,7 @@
         <v>6</v>
       </c>
       <c r="D2595" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2595" t="s" s="3">
         <v>5152</v>
@@ -60525,7 +60522,7 @@
         <v>6</v>
       </c>
       <c r="D2596" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2596" t="s" s="3">
         <v>5154</v>
@@ -60542,7 +60539,7 @@
         <v>6</v>
       </c>
       <c r="D2597" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2597" t="s" s="3">
         <v>5156</v>
@@ -60559,7 +60556,7 @@
         <v>6</v>
       </c>
       <c r="D2598" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2598" t="s" s="3">
         <v>5158</v>
@@ -60576,7 +60573,7 @@
         <v>6</v>
       </c>
       <c r="D2599" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2599" t="s" s="3">
         <v>5160</v>
@@ -60593,7 +60590,7 @@
         <v>6</v>
       </c>
       <c r="D2600" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2600" t="s" s="3">
         <v>5162</v>
@@ -60610,7 +60607,7 @@
         <v>6</v>
       </c>
       <c r="D2601" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2601" t="s" s="3">
         <v>5164</v>
@@ -60627,7 +60624,7 @@
         <v>6</v>
       </c>
       <c r="D2602" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2602" t="s" s="3">
         <v>5166</v>
@@ -60644,7 +60641,7 @@
         <v>6</v>
       </c>
       <c r="D2603" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2603" t="s" s="3">
         <v>5168</v>
@@ -60661,7 +60658,7 @@
         <v>6</v>
       </c>
       <c r="D2604" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2604" t="s" s="3">
         <v>5170</v>
@@ -60678,7 +60675,7 @@
         <v>6</v>
       </c>
       <c r="D2605" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2605" t="s" s="3">
         <v>5172</v>
@@ -60695,7 +60692,7 @@
         <v>6</v>
       </c>
       <c r="D2606" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2606" t="s" s="3">
         <v>5174</v>
@@ -60712,7 +60709,7 @@
         <v>6</v>
       </c>
       <c r="D2607" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2607" t="s" s="3">
         <v>5176</v>
@@ -60729,7 +60726,7 @@
         <v>6</v>
       </c>
       <c r="D2608" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2608" t="s" s="3">
         <v>5178</v>
@@ -60746,7 +60743,7 @@
         <v>6</v>
       </c>
       <c r="D2609" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2609" t="s" s="3">
         <v>5180</v>
@@ -60757,16 +60754,16 @@
         <v>2609.0</v>
       </c>
       <c r="B2610" t="s" s="3">
-        <v>3340</v>
+        <v>5181</v>
       </c>
       <c r="C2610" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2610" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2610" t="s" s="3">
-        <v>5181</v>
+        <v>5182</v>
       </c>
     </row>
     <row r="2611" ht="36.0" customHeight="true">
@@ -60774,13 +60771,13 @@
         <v>2610.0</v>
       </c>
       <c r="B2611" t="s" s="3">
-        <v>5182</v>
+        <v>3340</v>
       </c>
       <c r="C2611" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2611" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2611" t="s" s="3">
         <v>5183</v>
@@ -60797,7 +60794,7 @@
         <v>6</v>
       </c>
       <c r="D2612" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2612" t="s" s="3">
         <v>5185</v>
@@ -60814,10 +60811,10 @@
         <v>6</v>
       </c>
       <c r="D2613" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2613" t="s" s="3">
-        <v>5032</v>
+        <v>5187</v>
       </c>
     </row>
     <row r="2614" ht="36.0" customHeight="true">
@@ -60825,16 +60822,16 @@
         <v>2613.0</v>
       </c>
       <c r="B2614" t="s" s="3">
-        <v>5187</v>
+        <v>5188</v>
       </c>
       <c r="C2614" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2614" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2614" t="s" s="3">
-        <v>5188</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="2615" ht="36.0" customHeight="true">
@@ -60848,7 +60845,7 @@
         <v>6</v>
       </c>
       <c r="D2615" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2615" t="s" s="3">
         <v>5190</v>
@@ -60865,7 +60862,7 @@
         <v>6</v>
       </c>
       <c r="D2616" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2616" t="s" s="3">
         <v>5192</v>
@@ -60882,7 +60879,7 @@
         <v>6</v>
       </c>
       <c r="D2617" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2617" t="s" s="3">
         <v>5194</v>
@@ -60899,7 +60896,7 @@
         <v>6</v>
       </c>
       <c r="D2618" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2618" t="s" s="3">
         <v>5196</v>
@@ -60916,7 +60913,7 @@
         <v>6</v>
       </c>
       <c r="D2619" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2619" t="s" s="3">
         <v>5198</v>
@@ -60933,7 +60930,7 @@
         <v>6</v>
       </c>
       <c r="D2620" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2620" t="s" s="3">
         <v>5200</v>
@@ -60947,10 +60944,10 @@
         <v>5201</v>
       </c>
       <c r="C2621" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2621" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2621" t="s" s="3">
         <v>5202</v>
@@ -60967,7 +60964,7 @@
         <v>767</v>
       </c>
       <c r="D2622" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2622" t="s" s="3">
         <v>5204</v>
@@ -60984,7 +60981,7 @@
         <v>767</v>
       </c>
       <c r="D2623" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2623" t="s" s="3">
         <v>5206</v>
@@ -61001,7 +60998,7 @@
         <v>767</v>
       </c>
       <c r="D2624" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2624" t="s" s="3">
         <v>5208</v>
@@ -61018,7 +61015,7 @@
         <v>767</v>
       </c>
       <c r="D2625" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2625" t="s" s="3">
         <v>5210</v>
@@ -61035,7 +61032,7 @@
         <v>767</v>
       </c>
       <c r="D2626" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2626" t="s" s="3">
         <v>5212</v>
@@ -61052,7 +61049,7 @@
         <v>767</v>
       </c>
       <c r="D2627" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2627" t="s" s="3">
         <v>5214</v>
@@ -61069,7 +61066,7 @@
         <v>767</v>
       </c>
       <c r="D2628" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2628" t="s" s="3">
         <v>5216</v>
@@ -61086,7 +61083,7 @@
         <v>767</v>
       </c>
       <c r="D2629" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2629" t="s" s="3">
         <v>5218</v>
@@ -61103,7 +61100,7 @@
         <v>767</v>
       </c>
       <c r="D2630" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2630" t="s" s="3">
         <v>5220</v>
@@ -61120,7 +61117,7 @@
         <v>767</v>
       </c>
       <c r="D2631" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2631" t="s" s="3">
         <v>5222</v>
@@ -61137,7 +61134,7 @@
         <v>767</v>
       </c>
       <c r="D2632" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2632" t="s" s="3">
         <v>5224</v>
@@ -61154,7 +61151,7 @@
         <v>767</v>
       </c>
       <c r="D2633" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2633" t="s" s="3">
         <v>5226</v>
@@ -61171,7 +61168,7 @@
         <v>767</v>
       </c>
       <c r="D2634" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2634" t="s" s="3">
         <v>5228</v>
@@ -61188,7 +61185,7 @@
         <v>767</v>
       </c>
       <c r="D2635" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2635" t="s" s="3">
         <v>5230</v>
@@ -61205,7 +61202,7 @@
         <v>767</v>
       </c>
       <c r="D2636" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2636" t="s" s="3">
         <v>5232</v>
@@ -61222,7 +61219,7 @@
         <v>767</v>
       </c>
       <c r="D2637" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2637" t="s" s="3">
         <v>5234</v>
@@ -61239,7 +61236,7 @@
         <v>767</v>
       </c>
       <c r="D2638" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2638" t="s" s="3">
         <v>5236</v>
@@ -61256,7 +61253,7 @@
         <v>767</v>
       </c>
       <c r="D2639" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2639" t="s" s="3">
         <v>5238</v>
@@ -61273,7 +61270,7 @@
         <v>767</v>
       </c>
       <c r="D2640" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2640" t="s" s="3">
         <v>5240</v>
@@ -61290,7 +61287,7 @@
         <v>767</v>
       </c>
       <c r="D2641" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2641" t="s" s="3">
         <v>5242</v>
@@ -61307,7 +61304,7 @@
         <v>767</v>
       </c>
       <c r="D2642" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2642" t="s" s="3">
         <v>5244</v>
@@ -61324,7 +61321,7 @@
         <v>767</v>
       </c>
       <c r="D2643" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2643" t="s" s="3">
         <v>5246</v>
@@ -61341,7 +61338,7 @@
         <v>767</v>
       </c>
       <c r="D2644" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2644" t="s" s="3">
         <v>5248</v>
@@ -61358,7 +61355,7 @@
         <v>767</v>
       </c>
       <c r="D2645" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2645" t="s" s="3">
         <v>5250</v>
@@ -61375,7 +61372,7 @@
         <v>767</v>
       </c>
       <c r="D2646" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2646" t="s" s="3">
         <v>5252</v>
@@ -61392,7 +61389,7 @@
         <v>767</v>
       </c>
       <c r="D2647" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2647" t="s" s="3">
         <v>5254</v>
@@ -61409,7 +61406,7 @@
         <v>767</v>
       </c>
       <c r="D2648" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2648" t="s" s="3">
         <v>5256</v>
@@ -61426,7 +61423,7 @@
         <v>767</v>
       </c>
       <c r="D2649" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2649" t="s" s="3">
         <v>5258</v>
@@ -61443,7 +61440,7 @@
         <v>767</v>
       </c>
       <c r="D2650" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2650" t="s" s="3">
         <v>5260</v>
@@ -61460,7 +61457,7 @@
         <v>767</v>
       </c>
       <c r="D2651" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2651" t="s" s="3">
         <v>5262</v>
@@ -61477,7 +61474,7 @@
         <v>767</v>
       </c>
       <c r="D2652" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2652" t="s" s="3">
         <v>5264</v>
@@ -61494,7 +61491,7 @@
         <v>767</v>
       </c>
       <c r="D2653" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2653" t="s" s="3">
         <v>5266</v>
@@ -61511,7 +61508,7 @@
         <v>767</v>
       </c>
       <c r="D2654" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2654" t="s" s="3">
         <v>5268</v>
@@ -61528,7 +61525,7 @@
         <v>767</v>
       </c>
       <c r="D2655" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2655" t="s" s="3">
         <v>5270</v>
@@ -61545,7 +61542,7 @@
         <v>767</v>
       </c>
       <c r="D2656" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2656" t="s" s="3">
         <v>5272</v>
@@ -61562,7 +61559,7 @@
         <v>767</v>
       </c>
       <c r="D2657" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2657" t="s" s="3">
         <v>5274</v>
@@ -61579,7 +61576,7 @@
         <v>767</v>
       </c>
       <c r="D2658" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2658" t="s" s="3">
         <v>5276</v>
@@ -61596,7 +61593,7 @@
         <v>767</v>
       </c>
       <c r="D2659" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2659" t="s" s="3">
         <v>5278</v>
@@ -61613,7 +61610,7 @@
         <v>767</v>
       </c>
       <c r="D2660" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2660" t="s" s="3">
         <v>5280</v>
@@ -61630,7 +61627,7 @@
         <v>767</v>
       </c>
       <c r="D2661" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2661" t="s" s="3">
         <v>5282</v>
@@ -61647,7 +61644,7 @@
         <v>767</v>
       </c>
       <c r="D2662" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2662" t="s" s="3">
         <v>5284</v>
@@ -61664,7 +61661,7 @@
         <v>767</v>
       </c>
       <c r="D2663" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2663" t="s" s="3">
         <v>5286</v>
@@ -61681,7 +61678,7 @@
         <v>767</v>
       </c>
       <c r="D2664" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2664" t="s" s="3">
         <v>5288</v>
@@ -61698,7 +61695,7 @@
         <v>767</v>
       </c>
       <c r="D2665" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2665" t="s" s="3">
         <v>5290</v>
@@ -61715,10 +61712,10 @@
         <v>767</v>
       </c>
       <c r="D2666" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2666" t="s" s="3">
-        <v>4968</v>
+        <v>5292</v>
       </c>
     </row>
     <row r="2667" ht="36.0" customHeight="true">
@@ -61726,16 +61723,16 @@
         <v>2666.0</v>
       </c>
       <c r="B2667" t="s" s="3">
-        <v>5292</v>
+        <v>5293</v>
       </c>
       <c r="C2667" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2667" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2667" t="s" s="3">
-        <v>5293</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="2668" ht="36.0" customHeight="true">
@@ -61749,7 +61746,7 @@
         <v>767</v>
       </c>
       <c r="D2668" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2668" t="s" s="3">
         <v>5295</v>
@@ -61766,7 +61763,7 @@
         <v>767</v>
       </c>
       <c r="D2669" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2669" t="s" s="3">
         <v>5297</v>
@@ -61783,7 +61780,7 @@
         <v>767</v>
       </c>
       <c r="D2670" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2670" t="s" s="3">
         <v>5299</v>
@@ -61800,7 +61797,7 @@
         <v>767</v>
       </c>
       <c r="D2671" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2671" t="s" s="3">
         <v>5301</v>
@@ -61817,7 +61814,7 @@
         <v>767</v>
       </c>
       <c r="D2672" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2672" t="s" s="3">
         <v>5303</v>
@@ -61834,7 +61831,7 @@
         <v>767</v>
       </c>
       <c r="D2673" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2673" t="s" s="3">
         <v>5305</v>
@@ -61848,10 +61845,10 @@
         <v>5306</v>
       </c>
       <c r="C2674" t="s" s="2">
-        <v>984</v>
+        <v>767</v>
       </c>
       <c r="D2674" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2674" t="s" s="3">
         <v>5307</v>
@@ -61868,7 +61865,7 @@
         <v>984</v>
       </c>
       <c r="D2675" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2675" t="s" s="3">
         <v>5309</v>
@@ -61879,16 +61876,16 @@
         <v>2675.0</v>
       </c>
       <c r="B2676" t="s" s="3">
-        <v>5287</v>
+        <v>5310</v>
       </c>
       <c r="C2676" t="s" s="2">
         <v>984</v>
       </c>
       <c r="D2676" t="s" s="2">
-        <v>4917</v>
+        <v>4919</v>
       </c>
       <c r="E2676" t="s" s="3">
-        <v>5310</v>
+        <v>5311</v>
       </c>
     </row>
     <row r="2677" ht="36.0" customHeight="true">
@@ -61896,16 +61893,16 @@
         <v>2676.0</v>
       </c>
       <c r="B2677" t="s" s="3">
-        <v>5311</v>
+        <v>5289</v>
       </c>
       <c r="C2677" t="s" s="2">
-        <v>6</v>
+        <v>984</v>
       </c>
       <c r="D2677" t="s" s="2">
+        <v>4919</v>
+      </c>
+      <c r="E2677" t="s" s="3">
         <v>5312</v>
-      </c>
-      <c r="E2677" t="s" s="3">
-        <v>5313</v>
       </c>
     </row>
     <row r="2678" ht="36.0" customHeight="true">
@@ -61913,13 +61910,13 @@
         <v>2677.0</v>
       </c>
       <c r="B2678" t="s" s="3">
+        <v>5313</v>
+      </c>
+      <c r="C2678" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2678" t="s" s="2">
         <v>5314</v>
-      </c>
-      <c r="C2678" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2678" t="s" s="2">
-        <v>5312</v>
       </c>
       <c r="E2678" t="s" s="3">
         <v>5315</v>
@@ -61936,7 +61933,7 @@
         <v>6</v>
       </c>
       <c r="D2679" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2679" t="s" s="3">
         <v>5317</v>
@@ -61953,7 +61950,7 @@
         <v>6</v>
       </c>
       <c r="D2680" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2680" t="s" s="3">
         <v>5319</v>
@@ -61970,7 +61967,7 @@
         <v>6</v>
       </c>
       <c r="D2681" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2681" t="s" s="3">
         <v>5321</v>
@@ -61987,7 +61984,7 @@
         <v>6</v>
       </c>
       <c r="D2682" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2682" t="s" s="3">
         <v>5323</v>
@@ -62004,7 +62001,7 @@
         <v>6</v>
       </c>
       <c r="D2683" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2683" t="s" s="3">
         <v>5325</v>
@@ -62021,7 +62018,7 @@
         <v>6</v>
       </c>
       <c r="D2684" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2684" t="s" s="3">
         <v>5327</v>
@@ -62038,7 +62035,7 @@
         <v>6</v>
       </c>
       <c r="D2685" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2685" t="s" s="3">
         <v>5329</v>
@@ -62055,7 +62052,7 @@
         <v>6</v>
       </c>
       <c r="D2686" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2686" t="s" s="3">
         <v>5331</v>
@@ -62072,7 +62069,7 @@
         <v>6</v>
       </c>
       <c r="D2687" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2687" t="s" s="3">
         <v>5333</v>
@@ -62089,7 +62086,7 @@
         <v>6</v>
       </c>
       <c r="D2688" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2688" t="s" s="3">
         <v>5335</v>
@@ -62106,7 +62103,7 @@
         <v>6</v>
       </c>
       <c r="D2689" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2689" t="s" s="3">
         <v>5337</v>
@@ -62123,7 +62120,7 @@
         <v>6</v>
       </c>
       <c r="D2690" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2690" t="s" s="3">
         <v>5339</v>
@@ -62140,7 +62137,7 @@
         <v>6</v>
       </c>
       <c r="D2691" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2691" t="s" s="3">
         <v>5341</v>
@@ -62157,7 +62154,7 @@
         <v>6</v>
       </c>
       <c r="D2692" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2692" t="s" s="3">
         <v>5343</v>
@@ -62174,7 +62171,7 @@
         <v>6</v>
       </c>
       <c r="D2693" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2693" t="s" s="3">
         <v>5345</v>
@@ -62191,7 +62188,7 @@
         <v>6</v>
       </c>
       <c r="D2694" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2694" t="s" s="3">
         <v>5347</v>
@@ -62208,7 +62205,7 @@
         <v>6</v>
       </c>
       <c r="D2695" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2695" t="s" s="3">
         <v>5349</v>
@@ -62225,7 +62222,7 @@
         <v>6</v>
       </c>
       <c r="D2696" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2696" t="s" s="3">
         <v>5351</v>
@@ -62242,7 +62239,7 @@
         <v>6</v>
       </c>
       <c r="D2697" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2697" t="s" s="3">
         <v>5353</v>
@@ -62259,7 +62256,7 @@
         <v>6</v>
       </c>
       <c r="D2698" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2698" t="s" s="3">
         <v>5355</v>
@@ -62276,7 +62273,7 @@
         <v>6</v>
       </c>
       <c r="D2699" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2699" t="s" s="3">
         <v>5357</v>
@@ -62293,7 +62290,7 @@
         <v>6</v>
       </c>
       <c r="D2700" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2700" t="s" s="3">
         <v>5359</v>
@@ -62310,7 +62307,7 @@
         <v>6</v>
       </c>
       <c r="D2701" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2701" t="s" s="3">
         <v>5361</v>
@@ -62327,7 +62324,7 @@
         <v>6</v>
       </c>
       <c r="D2702" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2702" t="s" s="3">
         <v>5363</v>
@@ -62344,7 +62341,7 @@
         <v>6</v>
       </c>
       <c r="D2703" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2703" t="s" s="3">
         <v>5365</v>
@@ -62361,7 +62358,7 @@
         <v>6</v>
       </c>
       <c r="D2704" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2704" t="s" s="3">
         <v>5367</v>
@@ -62378,7 +62375,7 @@
         <v>6</v>
       </c>
       <c r="D2705" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2705" t="s" s="3">
         <v>5369</v>
@@ -62395,7 +62392,7 @@
         <v>6</v>
       </c>
       <c r="D2706" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2706" t="s" s="3">
         <v>5371</v>
@@ -62412,7 +62409,7 @@
         <v>6</v>
       </c>
       <c r="D2707" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2707" t="s" s="3">
         <v>5373</v>
@@ -62429,7 +62426,7 @@
         <v>6</v>
       </c>
       <c r="D2708" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2708" t="s" s="3">
         <v>5375</v>
@@ -62446,7 +62443,7 @@
         <v>6</v>
       </c>
       <c r="D2709" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2709" t="s" s="3">
         <v>5377</v>
@@ -62463,7 +62460,7 @@
         <v>6</v>
       </c>
       <c r="D2710" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2710" t="s" s="3">
         <v>5379</v>
@@ -62480,7 +62477,7 @@
         <v>6</v>
       </c>
       <c r="D2711" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2711" t="s" s="3">
         <v>5381</v>
@@ -62494,13 +62491,13 @@
         <v>5382</v>
       </c>
       <c r="C2712" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2712" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2712" t="s" s="3">
-        <v>5357</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="2713" ht="36.0" customHeight="true">
@@ -62508,16 +62505,16 @@
         <v>2712.0</v>
       </c>
       <c r="B2713" t="s" s="3">
-        <v>5383</v>
+        <v>5384</v>
       </c>
       <c r="C2713" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2713" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2713" t="s" s="3">
-        <v>5384</v>
+        <v>5359</v>
       </c>
     </row>
     <row r="2714" ht="36.0" customHeight="true">
@@ -62531,7 +62528,7 @@
         <v>767</v>
       </c>
       <c r="D2714" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2714" t="s" s="3">
         <v>5386</v>
@@ -62548,7 +62545,7 @@
         <v>767</v>
       </c>
       <c r="D2715" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2715" t="s" s="3">
         <v>5388</v>
@@ -62565,7 +62562,7 @@
         <v>767</v>
       </c>
       <c r="D2716" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2716" t="s" s="3">
         <v>5390</v>
@@ -62582,7 +62579,7 @@
         <v>767</v>
       </c>
       <c r="D2717" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2717" t="s" s="3">
         <v>5392</v>
@@ -62593,16 +62590,16 @@
         <v>2717.0</v>
       </c>
       <c r="B2718" t="s" s="3">
-        <v>5318</v>
+        <v>5393</v>
       </c>
       <c r="C2718" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2718" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2718" t="s" s="3">
-        <v>5393</v>
+        <v>5394</v>
       </c>
     </row>
     <row r="2719" ht="36.0" customHeight="true">
@@ -62610,13 +62607,13 @@
         <v>2718.0</v>
       </c>
       <c r="B2719" t="s" s="3">
-        <v>5394</v>
+        <v>5320</v>
       </c>
       <c r="C2719" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2719" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2719" t="s" s="3">
         <v>5395</v>
@@ -62633,7 +62630,7 @@
         <v>767</v>
       </c>
       <c r="D2720" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2720" t="s" s="3">
         <v>5397</v>
@@ -62650,7 +62647,7 @@
         <v>767</v>
       </c>
       <c r="D2721" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2721" t="s" s="3">
         <v>5399</v>
@@ -62667,7 +62664,7 @@
         <v>767</v>
       </c>
       <c r="D2722" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2722" t="s" s="3">
         <v>5401</v>
@@ -62684,7 +62681,7 @@
         <v>767</v>
       </c>
       <c r="D2723" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2723" t="s" s="3">
         <v>5403</v>
@@ -62701,7 +62698,7 @@
         <v>767</v>
       </c>
       <c r="D2724" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2724" t="s" s="3">
         <v>5405</v>
@@ -62718,7 +62715,7 @@
         <v>767</v>
       </c>
       <c r="D2725" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2725" t="s" s="3">
         <v>5407</v>
@@ -62735,7 +62732,7 @@
         <v>767</v>
       </c>
       <c r="D2726" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2726" t="s" s="3">
         <v>5409</v>
@@ -62752,7 +62749,7 @@
         <v>767</v>
       </c>
       <c r="D2727" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2727" t="s" s="3">
         <v>5411</v>
@@ -62769,7 +62766,7 @@
         <v>767</v>
       </c>
       <c r="D2728" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2728" t="s" s="3">
         <v>5413</v>
@@ -62786,7 +62783,7 @@
         <v>767</v>
       </c>
       <c r="D2729" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2729" t="s" s="3">
         <v>5415</v>
@@ -62803,7 +62800,7 @@
         <v>767</v>
       </c>
       <c r="D2730" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2730" t="s" s="3">
         <v>5417</v>
@@ -62820,7 +62817,7 @@
         <v>767</v>
       </c>
       <c r="D2731" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2731" t="s" s="3">
         <v>5419</v>
@@ -62837,7 +62834,7 @@
         <v>767</v>
       </c>
       <c r="D2732" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2732" t="s" s="3">
         <v>5421</v>
@@ -62854,7 +62851,7 @@
         <v>767</v>
       </c>
       <c r="D2733" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2733" t="s" s="3">
         <v>5423</v>
@@ -62871,7 +62868,7 @@
         <v>767</v>
       </c>
       <c r="D2734" t="s" s="2">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="E2734" t="s" s="3">
         <v>5425</v>
@@ -62888,10 +62885,10 @@
         <v>767</v>
       </c>
       <c r="D2735" t="s" s="2">
+        <v>5314</v>
+      </c>
+      <c r="E2735" t="s" s="3">
         <v>5427</v>
-      </c>
-      <c r="E2735" t="s" s="3">
-        <v>5428</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11021" uniqueCount="5468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11037" uniqueCount="5477">
   <si>
     <t>연번</t>
   </si>
@@ -3356,12 +3356,12 @@
     <t>전남광주통합특별시 화순군 도곡면 덕리길 10-5(1층)</t>
   </si>
   <si>
+    <t>전남광주통합특별시 서구 상무시민로 136(수성빌딩 1층 치평동)</t>
+  </si>
+  <si>
     <t>전남광주통합특별시 동구 동명로14번길 19-8(2층 동명동)</t>
   </si>
   <si>
-    <t>전남광주통합특별시 서구 상무시민로 136(수성빌딩 1층 치평동)</t>
-  </si>
-  <si>
     <t>쉘터커피로스터스</t>
   </si>
   <si>
@@ -7481,6 +7481,12 @@
     <t>경기도 성남시 수정구 대왕판교로 981(지하1층 136일부호 고등동, 판교밸리자이 2단지)</t>
   </si>
   <si>
+    <t>김복남맥주오산고현점</t>
+  </si>
+  <si>
+    <t>경기도 오산시 동부대로 332-13(오산더테라스퀘어 나동 129호 고현동)</t>
+  </si>
+  <si>
     <t>김성민커피 아이파크시티</t>
   </si>
   <si>
@@ -9185,12 +9191,12 @@
     <t>위자네</t>
   </si>
   <si>
+    <t>경기도 화성시 효행구 봉담읍 장등1길 3-10(1층)</t>
+  </si>
+  <si>
     <t>경기도 안양시 만안구 석천로 181(1층 석수동)</t>
   </si>
   <si>
-    <t>경기도 화성시 효행구 봉담읍 장등1길 3-10(1층)</t>
-  </si>
-  <si>
     <t>위클리베이글 평촌점</t>
   </si>
   <si>
@@ -10532,12 +10538,6 @@
     <t>경기도 하남시 미사강변한강로 220(1층 일부호 망월동)</t>
   </si>
   <si>
-    <t>딥로우커피(Deepraw coffee)</t>
-  </si>
-  <si>
-    <t>경기도 고양시 덕양구 청초로 66(덕은리버워크 1층 115호 덕은동)</t>
-  </si>
-  <si>
     <t>땃트 커피 광교카페거리점</t>
   </si>
   <si>
@@ -10874,6 +10874,12 @@
     <t>경기도 안양시 동안구 갈산로 82(102호 호계동)</t>
   </si>
   <si>
+    <t>아우더타인</t>
+  </si>
+  <si>
+    <t>경기도 고양시 일산동구 율천로8번길 7-11(1층 마두동)</t>
+  </si>
+  <si>
     <t>아이언앤우드 카페</t>
   </si>
   <si>
@@ -11465,6 +11471,12 @@
     <t>경기도 광주시 행정타운로 143-9(회덕동)</t>
   </si>
   <si>
+    <t>모렌지</t>
+  </si>
+  <si>
+    <t>경기도 파주시 가람로21번길 27-20(1층 일부 와동동)</t>
+  </si>
+  <si>
     <t>베이글라이즈(bagelize)</t>
   </si>
   <si>
@@ -12119,6 +12131,12 @@
     <t>충청남도 홍성군 홍북읍 의향로 273(세움펠리피아 2층 204호)</t>
   </si>
   <si>
+    <t>연심이네</t>
+  </si>
+  <si>
+    <t>충청남도 홍성군 서부면 남당항로213번길 1(A동 202호)</t>
+  </si>
+  <si>
     <t>연옥이네밥상</t>
   </si>
   <si>
@@ -16416,6 +16434,15 @@
   </si>
   <si>
     <t>전북특별자치도 김제시 만경읍 대동길 609</t>
+  </si>
+  <si>
+    <t>멍멍아 뛰놀자</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>전남광주통합특별시 광양시 용장길 207(1동 2층중 1,2층전부 성황동)</t>
   </si>
 </sst>
 </file>
@@ -38060,7 +38087,7 @@
         <v>1267.0</v>
       </c>
       <c r="B1268" t="s" s="3">
-        <v>1813</v>
+        <v>2527</v>
       </c>
       <c r="C1268" t="s" s="2">
         <v>6</v>
@@ -38069,7 +38096,7 @@
         <v>2375</v>
       </c>
       <c r="E1268" t="s" s="3">
-        <v>2527</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="1269" ht="36.0" customHeight="true">
@@ -38077,7 +38104,7 @@
         <v>1268.0</v>
       </c>
       <c r="B1269" t="s" s="3">
-        <v>2528</v>
+        <v>1813</v>
       </c>
       <c r="C1269" t="s" s="2">
         <v>6</v>
@@ -40066,7 +40093,7 @@
         <v>1385.0</v>
       </c>
       <c r="B1386" t="s" s="3">
-        <v>301</v>
+        <v>2762</v>
       </c>
       <c r="C1386" t="s" s="2">
         <v>6</v>
@@ -40075,7 +40102,7 @@
         <v>2375</v>
       </c>
       <c r="E1386" t="s" s="3">
-        <v>2762</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="1387" ht="36.0" customHeight="true">
@@ -40083,7 +40110,7 @@
         <v>1386.0</v>
       </c>
       <c r="B1387" t="s" s="3">
-        <v>2763</v>
+        <v>301</v>
       </c>
       <c r="C1387" t="s" s="2">
         <v>6</v>
@@ -41010,7 +41037,7 @@
         <v>2375</v>
       </c>
       <c r="E1441" t="s" s="3">
-        <v>2446</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="1442" ht="36.0" customHeight="true">
@@ -41018,7 +41045,7 @@
         <v>1441.0</v>
       </c>
       <c r="B1442" t="s" s="3">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="C1442" t="s" s="2">
         <v>6</v>
@@ -41027,7 +41054,7 @@
         <v>2375</v>
       </c>
       <c r="E1442" t="s" s="3">
-        <v>2873</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="1443" ht="36.0" customHeight="true">
@@ -41520,7 +41547,7 @@
         <v>2375</v>
       </c>
       <c r="E1471" t="s" s="3">
-        <v>2446</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="1472" ht="36.0" customHeight="true">
@@ -41528,7 +41555,7 @@
         <v>1471.0</v>
       </c>
       <c r="B1472" t="s" s="3">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="C1472" t="s" s="2">
         <v>6</v>
@@ -41537,7 +41564,7 @@
         <v>2375</v>
       </c>
       <c r="E1472" t="s" s="3">
-        <v>2932</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="1473" ht="36.0" customHeight="true">
@@ -41724,7 +41751,7 @@
         <v>2375</v>
       </c>
       <c r="E1483" t="s" s="3">
-        <v>2446</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="1484" ht="36.0" customHeight="true">
@@ -41732,7 +41759,7 @@
         <v>1483.0</v>
       </c>
       <c r="B1484" t="s" s="3">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="C1484" t="s" s="2">
         <v>6</v>
@@ -41741,7 +41768,7 @@
         <v>2375</v>
       </c>
       <c r="E1484" t="s" s="3">
-        <v>2955</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="1485" ht="36.0" customHeight="true">
@@ -42064,7 +42091,7 @@
         <v>2375</v>
       </c>
       <c r="E1503" t="s" s="3">
-        <v>2985</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="1504" ht="36.0" customHeight="true">
@@ -42072,7 +42099,7 @@
         <v>1503.0</v>
       </c>
       <c r="B1504" t="s" s="3">
-        <v>2993</v>
+        <v>2994</v>
       </c>
       <c r="C1504" t="s" s="2">
         <v>6</v>
@@ -42081,7 +42108,7 @@
         <v>2375</v>
       </c>
       <c r="E1504" t="s" s="3">
-        <v>2994</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="1505" ht="36.0" customHeight="true">
@@ -42336,7 +42363,7 @@
         <v>2375</v>
       </c>
       <c r="E1519" t="s" s="3">
-        <v>2446</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="1520" ht="36.0" customHeight="true">
@@ -42344,7 +42371,7 @@
         <v>1519.0</v>
       </c>
       <c r="B1520" t="s" s="3">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="C1520" t="s" s="2">
         <v>6</v>
@@ -42353,7 +42380,7 @@
         <v>2375</v>
       </c>
       <c r="E1520" t="s" s="3">
-        <v>3025</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="1521" ht="36.0" customHeight="true">
@@ -42370,7 +42397,7 @@
         <v>2375</v>
       </c>
       <c r="E1521" t="s" s="3">
-        <v>2971</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="1522" ht="36.0" customHeight="true">
@@ -42378,7 +42405,7 @@
         <v>1521.0</v>
       </c>
       <c r="B1522" t="s" s="3">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="C1522" t="s" s="2">
         <v>6</v>
@@ -42387,7 +42414,7 @@
         <v>2375</v>
       </c>
       <c r="E1522" t="s" s="3">
-        <v>3028</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="1523" ht="36.0" customHeight="true">
@@ -42455,7 +42482,7 @@
         <v>2375</v>
       </c>
       <c r="E1526" t="s" s="3">
-        <v>2446</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="1527" ht="36.0" customHeight="true">
@@ -42463,7 +42490,7 @@
         <v>1526.0</v>
       </c>
       <c r="B1527" t="s" s="3">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="C1527" t="s" s="2">
         <v>6</v>
@@ -42472,7 +42499,7 @@
         <v>2375</v>
       </c>
       <c r="E1527" t="s" s="3">
-        <v>3037</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="1528" ht="36.0" customHeight="true">
@@ -42650,7 +42677,7 @@
         <v>1537.0</v>
       </c>
       <c r="B1538" t="s" s="3">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C1538" t="s" s="2">
         <v>6</v>
@@ -42659,7 +42686,7 @@
         <v>2375</v>
       </c>
       <c r="E1538" t="s" s="3">
-        <v>3058</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="1539" ht="36.0" customHeight="true">
@@ -42667,7 +42694,7 @@
         <v>1538.0</v>
       </c>
       <c r="B1539" t="s" s="3">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C1539" t="s" s="2">
         <v>6</v>
@@ -43458,7 +43485,7 @@
         <v>2375</v>
       </c>
       <c r="E1585" t="s" s="3">
-        <v>2446</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="1586" ht="36.0" customHeight="true">
@@ -43466,7 +43493,7 @@
         <v>1585.0</v>
       </c>
       <c r="B1586" t="s" s="3">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="C1586" t="s" s="2">
         <v>6</v>
@@ -43475,7 +43502,7 @@
         <v>2375</v>
       </c>
       <c r="E1586" t="s" s="3">
-        <v>3153</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="1587" ht="36.0" customHeight="true">
@@ -44291,7 +44318,7 @@
         <v>2375</v>
       </c>
       <c r="E1634" t="s" s="3">
-        <v>2446</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="1635" ht="36.0" customHeight="true">
@@ -44299,7 +44326,7 @@
         <v>1634.0</v>
       </c>
       <c r="B1635" t="s" s="3">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="C1635" t="s" s="2">
         <v>6</v>
@@ -44308,7 +44335,7 @@
         <v>2375</v>
       </c>
       <c r="E1635" t="s" s="3">
-        <v>3250</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="1636" ht="36.0" customHeight="true">
@@ -45234,7 +45261,7 @@
         <v>1689.0</v>
       </c>
       <c r="B1690" t="s" s="3">
-        <v>698</v>
+        <v>3359</v>
       </c>
       <c r="C1690" t="s" s="2">
         <v>6</v>
@@ -45243,7 +45270,7 @@
         <v>2375</v>
       </c>
       <c r="E1690" t="s" s="3">
-        <v>3359</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="1691" ht="36.0" customHeight="true">
@@ -45251,7 +45278,7 @@
         <v>1690.0</v>
       </c>
       <c r="B1691" t="s" s="3">
-        <v>3360</v>
+        <v>698</v>
       </c>
       <c r="C1691" t="s" s="2">
         <v>6</v>
@@ -45798,7 +45825,7 @@
         <v>3424</v>
       </c>
       <c r="C1723" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D1723" t="s" s="2">
         <v>2375</v>
@@ -46237,7 +46264,7 @@
         <v>1748.0</v>
       </c>
       <c r="B1749" t="s" s="3">
-        <v>2523</v>
+        <v>3476</v>
       </c>
       <c r="C1749" t="s" s="2">
         <v>767</v>
@@ -46246,7 +46273,7 @@
         <v>2375</v>
       </c>
       <c r="E1749" t="s" s="3">
-        <v>3476</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="1750" ht="36.0" customHeight="true">
@@ -46254,7 +46281,7 @@
         <v>1749.0</v>
       </c>
       <c r="B1750" t="s" s="3">
-        <v>3477</v>
+        <v>2525</v>
       </c>
       <c r="C1750" t="s" s="2">
         <v>767</v>
@@ -46280,7 +46307,7 @@
         <v>2375</v>
       </c>
       <c r="E1751" t="s" s="3">
-        <v>2645</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="1752" ht="36.0" customHeight="true">
@@ -46288,7 +46315,7 @@
         <v>1751.0</v>
       </c>
       <c r="B1752" t="s" s="3">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="C1752" t="s" s="2">
         <v>767</v>
@@ -46297,7 +46324,7 @@
         <v>2375</v>
       </c>
       <c r="E1752" t="s" s="3">
-        <v>3481</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="1753" ht="36.0" customHeight="true">
@@ -46645,7 +46672,7 @@
         <v>1772.0</v>
       </c>
       <c r="B1773" t="s" s="3">
-        <v>2632</v>
+        <v>2634</v>
       </c>
       <c r="C1773" t="s" s="2">
         <v>767</v>
@@ -46654,7 +46681,7 @@
         <v>2375</v>
       </c>
       <c r="E1773" t="s" s="3">
-        <v>2633</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="1774" ht="36.0" customHeight="true">
@@ -48881,7 +48908,7 @@
         <v>2375</v>
       </c>
       <c r="E1904" t="s" s="3">
-        <v>3601</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="1905" ht="36.0" customHeight="true">
@@ -48889,7 +48916,7 @@
         <v>1904.0</v>
       </c>
       <c r="B1905" t="s" s="3">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="C1905" t="s" s="2">
         <v>767</v>
@@ -48898,7 +48925,7 @@
         <v>2375</v>
       </c>
       <c r="E1905" t="s" s="3">
-        <v>3784</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="1906" ht="36.0" customHeight="true">
@@ -48906,7 +48933,7 @@
         <v>1905.0</v>
       </c>
       <c r="B1906" t="s" s="3">
-        <v>3374</v>
+        <v>3785</v>
       </c>
       <c r="C1906" t="s" s="2">
         <v>767</v>
@@ -48915,7 +48942,7 @@
         <v>2375</v>
       </c>
       <c r="E1906" t="s" s="3">
-        <v>3375</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="1907" ht="36.0" customHeight="true">
@@ -48923,7 +48950,7 @@
         <v>1906.0</v>
       </c>
       <c r="B1907" t="s" s="3">
-        <v>3785</v>
+        <v>3376</v>
       </c>
       <c r="C1907" t="s" s="2">
         <v>767</v>
@@ -48932,7 +48959,7 @@
         <v>2375</v>
       </c>
       <c r="E1907" t="s" s="3">
-        <v>3786</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="1908" ht="36.0" customHeight="true">
@@ -49147,7 +49174,7 @@
         <v>3811</v>
       </c>
       <c r="C1920" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D1920" t="s" s="2">
         <v>2375</v>
@@ -49280,7 +49307,7 @@
         <v>1927.0</v>
       </c>
       <c r="B1928" t="s" s="3">
-        <v>3052</v>
+        <v>3827</v>
       </c>
       <c r="C1928" t="s" s="2">
         <v>986</v>
@@ -49289,7 +49316,7 @@
         <v>2375</v>
       </c>
       <c r="E1928" t="s" s="3">
-        <v>3053</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="1929" ht="36.0" customHeight="true">
@@ -49297,7 +49324,7 @@
         <v>1928.0</v>
       </c>
       <c r="B1929" t="s" s="3">
-        <v>3827</v>
+        <v>3829</v>
       </c>
       <c r="C1929" t="s" s="2">
         <v>986</v>
@@ -49306,7 +49333,7 @@
         <v>2375</v>
       </c>
       <c r="E1929" t="s" s="3">
-        <v>3828</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="1930" ht="36.0" customHeight="true">
@@ -49314,7 +49341,7 @@
         <v>1929.0</v>
       </c>
       <c r="B1930" t="s" s="3">
-        <v>3829</v>
+        <v>3054</v>
       </c>
       <c r="C1930" t="s" s="2">
         <v>986</v>
@@ -49323,7 +49350,7 @@
         <v>2375</v>
       </c>
       <c r="E1930" t="s" s="3">
-        <v>3830</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="1931" ht="36.0" customHeight="true">
@@ -49351,13 +49378,13 @@
         <v>3833</v>
       </c>
       <c r="C1932" t="s" s="2">
-        <v>6</v>
+        <v>986</v>
       </c>
       <c r="D1932" t="s" s="2">
+        <v>2375</v>
+      </c>
+      <c r="E1932" t="s" s="3">
         <v>3834</v>
-      </c>
-      <c r="E1932" t="s" s="3">
-        <v>3835</v>
       </c>
     </row>
     <row r="1933" ht="36.0" customHeight="true">
@@ -49365,16 +49392,16 @@
         <v>1932.0</v>
       </c>
       <c r="B1933" t="s" s="3">
+        <v>3835</v>
+      </c>
+      <c r="C1933" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D1933" t="s" s="2">
+        <v>2375</v>
+      </c>
+      <c r="E1933" t="s" s="3">
         <v>3836</v>
-      </c>
-      <c r="C1933" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1933" t="s" s="2">
-        <v>3834</v>
-      </c>
-      <c r="E1933" t="s" s="3">
-        <v>3837</v>
       </c>
     </row>
     <row r="1934" ht="36.0" customHeight="true">
@@ -49382,13 +49409,13 @@
         <v>1933.0</v>
       </c>
       <c r="B1934" t="s" s="3">
+        <v>3837</v>
+      </c>
+      <c r="C1934" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1934" t="s" s="2">
         <v>3838</v>
-      </c>
-      <c r="C1934" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1934" t="s" s="2">
-        <v>3834</v>
       </c>
       <c r="E1934" t="s" s="3">
         <v>3839</v>
@@ -49405,7 +49432,7 @@
         <v>6</v>
       </c>
       <c r="D1935" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1935" t="s" s="3">
         <v>3841</v>
@@ -49422,7 +49449,7 @@
         <v>6</v>
       </c>
       <c r="D1936" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1936" t="s" s="3">
         <v>3843</v>
@@ -49439,7 +49466,7 @@
         <v>6</v>
       </c>
       <c r="D1937" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1937" t="s" s="3">
         <v>3845</v>
@@ -49456,7 +49483,7 @@
         <v>6</v>
       </c>
       <c r="D1938" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1938" t="s" s="3">
         <v>3847</v>
@@ -49473,7 +49500,7 @@
         <v>6</v>
       </c>
       <c r="D1939" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1939" t="s" s="3">
         <v>3849</v>
@@ -49490,7 +49517,7 @@
         <v>6</v>
       </c>
       <c r="D1940" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1940" t="s" s="3">
         <v>3851</v>
@@ -49507,7 +49534,7 @@
         <v>6</v>
       </c>
       <c r="D1941" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1941" t="s" s="3">
         <v>3853</v>
@@ -49524,7 +49551,7 @@
         <v>6</v>
       </c>
       <c r="D1942" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1942" t="s" s="3">
         <v>3855</v>
@@ -49541,7 +49568,7 @@
         <v>6</v>
       </c>
       <c r="D1943" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1943" t="s" s="3">
         <v>3857</v>
@@ -49558,7 +49585,7 @@
         <v>6</v>
       </c>
       <c r="D1944" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1944" t="s" s="3">
         <v>3859</v>
@@ -49575,7 +49602,7 @@
         <v>6</v>
       </c>
       <c r="D1945" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1945" t="s" s="3">
         <v>3861</v>
@@ -49592,7 +49619,7 @@
         <v>6</v>
       </c>
       <c r="D1946" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1946" t="s" s="3">
         <v>3863</v>
@@ -49609,7 +49636,7 @@
         <v>6</v>
       </c>
       <c r="D1947" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1947" t="s" s="3">
         <v>3865</v>
@@ -49626,7 +49653,7 @@
         <v>6</v>
       </c>
       <c r="D1948" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1948" t="s" s="3">
         <v>3867</v>
@@ -49643,7 +49670,7 @@
         <v>6</v>
       </c>
       <c r="D1949" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1949" t="s" s="3">
         <v>3869</v>
@@ -49660,7 +49687,7 @@
         <v>6</v>
       </c>
       <c r="D1950" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1950" t="s" s="3">
         <v>3871</v>
@@ -49677,7 +49704,7 @@
         <v>6</v>
       </c>
       <c r="D1951" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1951" t="s" s="3">
         <v>3873</v>
@@ -49694,7 +49721,7 @@
         <v>6</v>
       </c>
       <c r="D1952" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1952" t="s" s="3">
         <v>3875</v>
@@ -49711,7 +49738,7 @@
         <v>6</v>
       </c>
       <c r="D1953" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1953" t="s" s="3">
         <v>3877</v>
@@ -49728,7 +49755,7 @@
         <v>6</v>
       </c>
       <c r="D1954" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1954" t="s" s="3">
         <v>3879</v>
@@ -49745,7 +49772,7 @@
         <v>6</v>
       </c>
       <c r="D1955" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1955" t="s" s="3">
         <v>3881</v>
@@ -49762,7 +49789,7 @@
         <v>6</v>
       </c>
       <c r="D1956" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1956" t="s" s="3">
         <v>3883</v>
@@ -49779,7 +49806,7 @@
         <v>6</v>
       </c>
       <c r="D1957" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1957" t="s" s="3">
         <v>3885</v>
@@ -49796,7 +49823,7 @@
         <v>6</v>
       </c>
       <c r="D1958" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1958" t="s" s="3">
         <v>3887</v>
@@ -49813,7 +49840,7 @@
         <v>6</v>
       </c>
       <c r="D1959" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1959" t="s" s="3">
         <v>3889</v>
@@ -49830,7 +49857,7 @@
         <v>6</v>
       </c>
       <c r="D1960" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1960" t="s" s="3">
         <v>3891</v>
@@ -49847,7 +49874,7 @@
         <v>6</v>
       </c>
       <c r="D1961" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1961" t="s" s="3">
         <v>3893</v>
@@ -49864,7 +49891,7 @@
         <v>6</v>
       </c>
       <c r="D1962" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1962" t="s" s="3">
         <v>3895</v>
@@ -49881,7 +49908,7 @@
         <v>6</v>
       </c>
       <c r="D1963" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1963" t="s" s="3">
         <v>3897</v>
@@ -49898,7 +49925,7 @@
         <v>6</v>
       </c>
       <c r="D1964" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1964" t="s" s="3">
         <v>3899</v>
@@ -49915,7 +49942,7 @@
         <v>6</v>
       </c>
       <c r="D1965" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1965" t="s" s="3">
         <v>3901</v>
@@ -49932,7 +49959,7 @@
         <v>6</v>
       </c>
       <c r="D1966" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1966" t="s" s="3">
         <v>3903</v>
@@ -49949,7 +49976,7 @@
         <v>6</v>
       </c>
       <c r="D1967" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1967" t="s" s="3">
         <v>3905</v>
@@ -49966,7 +49993,7 @@
         <v>6</v>
       </c>
       <c r="D1968" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1968" t="s" s="3">
         <v>3907</v>
@@ -49983,7 +50010,7 @@
         <v>6</v>
       </c>
       <c r="D1969" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1969" t="s" s="3">
         <v>3909</v>
@@ -50000,7 +50027,7 @@
         <v>6</v>
       </c>
       <c r="D1970" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1970" t="s" s="3">
         <v>3911</v>
@@ -50017,7 +50044,7 @@
         <v>6</v>
       </c>
       <c r="D1971" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1971" t="s" s="3">
         <v>3913</v>
@@ -50034,7 +50061,7 @@
         <v>6</v>
       </c>
       <c r="D1972" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1972" t="s" s="3">
         <v>3915</v>
@@ -50051,7 +50078,7 @@
         <v>6</v>
       </c>
       <c r="D1973" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1973" t="s" s="3">
         <v>3917</v>
@@ -50068,7 +50095,7 @@
         <v>6</v>
       </c>
       <c r="D1974" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1974" t="s" s="3">
         <v>3919</v>
@@ -50085,7 +50112,7 @@
         <v>6</v>
       </c>
       <c r="D1975" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1975" t="s" s="3">
         <v>3921</v>
@@ -50102,7 +50129,7 @@
         <v>6</v>
       </c>
       <c r="D1976" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1976" t="s" s="3">
         <v>3923</v>
@@ -50119,7 +50146,7 @@
         <v>6</v>
       </c>
       <c r="D1977" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1977" t="s" s="3">
         <v>3925</v>
@@ -50133,10 +50160,10 @@
         <v>3926</v>
       </c>
       <c r="C1978" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D1978" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1978" t="s" s="3">
         <v>3927</v>
@@ -50150,10 +50177,10 @@
         <v>3928</v>
       </c>
       <c r="C1979" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D1979" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1979" t="s" s="3">
         <v>3929</v>
@@ -50170,7 +50197,7 @@
         <v>767</v>
       </c>
       <c r="D1980" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1980" t="s" s="3">
         <v>3931</v>
@@ -50187,7 +50214,7 @@
         <v>767</v>
       </c>
       <c r="D1981" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1981" t="s" s="3">
         <v>3933</v>
@@ -50204,7 +50231,7 @@
         <v>767</v>
       </c>
       <c r="D1982" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1982" t="s" s="3">
         <v>3935</v>
@@ -50221,7 +50248,7 @@
         <v>767</v>
       </c>
       <c r="D1983" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1983" t="s" s="3">
         <v>3937</v>
@@ -50238,7 +50265,7 @@
         <v>767</v>
       </c>
       <c r="D1984" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1984" t="s" s="3">
         <v>3939</v>
@@ -50255,7 +50282,7 @@
         <v>767</v>
       </c>
       <c r="D1985" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1985" t="s" s="3">
         <v>3941</v>
@@ -50272,7 +50299,7 @@
         <v>767</v>
       </c>
       <c r="D1986" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1986" t="s" s="3">
         <v>3943</v>
@@ -50289,7 +50316,7 @@
         <v>767</v>
       </c>
       <c r="D1987" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1987" t="s" s="3">
         <v>3945</v>
@@ -50306,7 +50333,7 @@
         <v>767</v>
       </c>
       <c r="D1988" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1988" t="s" s="3">
         <v>3947</v>
@@ -50323,7 +50350,7 @@
         <v>767</v>
       </c>
       <c r="D1989" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1989" t="s" s="3">
         <v>3949</v>
@@ -50340,7 +50367,7 @@
         <v>767</v>
       </c>
       <c r="D1990" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1990" t="s" s="3">
         <v>3951</v>
@@ -50357,7 +50384,7 @@
         <v>767</v>
       </c>
       <c r="D1991" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1991" t="s" s="3">
         <v>3953</v>
@@ -50371,10 +50398,10 @@
         <v>3954</v>
       </c>
       <c r="C1992" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D1992" t="s" s="2">
-        <v>3834</v>
+        <v>3838</v>
       </c>
       <c r="E1992" t="s" s="3">
         <v>3955</v>
@@ -50388,13 +50415,13 @@
         <v>3956</v>
       </c>
       <c r="C1993" t="s" s="2">
-        <v>6</v>
+        <v>767</v>
       </c>
       <c r="D1993" t="s" s="2">
+        <v>3838</v>
+      </c>
+      <c r="E1993" t="s" s="3">
         <v>3957</v>
-      </c>
-      <c r="E1993" t="s" s="3">
-        <v>3958</v>
       </c>
     </row>
     <row r="1994" ht="36.0" customHeight="true">
@@ -50402,16 +50429,16 @@
         <v>1993.0</v>
       </c>
       <c r="B1994" t="s" s="3">
+        <v>3958</v>
+      </c>
+      <c r="C1994" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D1994" t="s" s="2">
+        <v>3838</v>
+      </c>
+      <c r="E1994" t="s" s="3">
         <v>3959</v>
-      </c>
-      <c r="C1994" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1994" t="s" s="2">
-        <v>3957</v>
-      </c>
-      <c r="E1994" t="s" s="3">
-        <v>3960</v>
       </c>
     </row>
     <row r="1995" ht="36.0" customHeight="true">
@@ -50419,13 +50446,13 @@
         <v>1994.0</v>
       </c>
       <c r="B1995" t="s" s="3">
+        <v>3960</v>
+      </c>
+      <c r="C1995" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1995" t="s" s="2">
         <v>3961</v>
-      </c>
-      <c r="C1995" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1995" t="s" s="2">
-        <v>3957</v>
       </c>
       <c r="E1995" t="s" s="3">
         <v>3962</v>
@@ -50442,7 +50469,7 @@
         <v>6</v>
       </c>
       <c r="D1996" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E1996" t="s" s="3">
         <v>3964</v>
@@ -50459,7 +50486,7 @@
         <v>6</v>
       </c>
       <c r="D1997" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E1997" t="s" s="3">
         <v>3966</v>
@@ -50476,7 +50503,7 @@
         <v>6</v>
       </c>
       <c r="D1998" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E1998" t="s" s="3">
         <v>3968</v>
@@ -50493,7 +50520,7 @@
         <v>6</v>
       </c>
       <c r="D1999" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E1999" t="s" s="3">
         <v>3970</v>
@@ -50510,7 +50537,7 @@
         <v>6</v>
       </c>
       <c r="D2000" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2000" t="s" s="3">
         <v>3972</v>
@@ -50527,7 +50554,7 @@
         <v>6</v>
       </c>
       <c r="D2001" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2001" t="s" s="3">
         <v>3974</v>
@@ -50544,7 +50571,7 @@
         <v>6</v>
       </c>
       <c r="D2002" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2002" t="s" s="3">
         <v>3976</v>
@@ -50561,7 +50588,7 @@
         <v>6</v>
       </c>
       <c r="D2003" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2003" t="s" s="3">
         <v>3978</v>
@@ -50578,7 +50605,7 @@
         <v>6</v>
       </c>
       <c r="D2004" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2004" t="s" s="3">
         <v>3980</v>
@@ -50595,7 +50622,7 @@
         <v>6</v>
       </c>
       <c r="D2005" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2005" t="s" s="3">
         <v>3982</v>
@@ -50612,7 +50639,7 @@
         <v>6</v>
       </c>
       <c r="D2006" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2006" t="s" s="3">
         <v>3984</v>
@@ -50629,7 +50656,7 @@
         <v>6</v>
       </c>
       <c r="D2007" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2007" t="s" s="3">
         <v>3986</v>
@@ -50646,7 +50673,7 @@
         <v>6</v>
       </c>
       <c r="D2008" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2008" t="s" s="3">
         <v>3988</v>
@@ -50663,7 +50690,7 @@
         <v>6</v>
       </c>
       <c r="D2009" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2009" t="s" s="3">
         <v>3990</v>
@@ -50680,7 +50707,7 @@
         <v>6</v>
       </c>
       <c r="D2010" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2010" t="s" s="3">
         <v>3992</v>
@@ -50697,7 +50724,7 @@
         <v>6</v>
       </c>
       <c r="D2011" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2011" t="s" s="3">
         <v>3994</v>
@@ -50714,7 +50741,7 @@
         <v>6</v>
       </c>
       <c r="D2012" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2012" t="s" s="3">
         <v>3996</v>
@@ -50731,7 +50758,7 @@
         <v>6</v>
       </c>
       <c r="D2013" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2013" t="s" s="3">
         <v>3998</v>
@@ -50748,7 +50775,7 @@
         <v>6</v>
       </c>
       <c r="D2014" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2014" t="s" s="3">
         <v>4000</v>
@@ -50765,7 +50792,7 @@
         <v>6</v>
       </c>
       <c r="D2015" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2015" t="s" s="3">
         <v>4002</v>
@@ -50782,7 +50809,7 @@
         <v>6</v>
       </c>
       <c r="D2016" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2016" t="s" s="3">
         <v>4004</v>
@@ -50799,7 +50826,7 @@
         <v>6</v>
       </c>
       <c r="D2017" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2017" t="s" s="3">
         <v>4006</v>
@@ -50816,7 +50843,7 @@
         <v>6</v>
       </c>
       <c r="D2018" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2018" t="s" s="3">
         <v>4008</v>
@@ -50833,7 +50860,7 @@
         <v>6</v>
       </c>
       <c r="D2019" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2019" t="s" s="3">
         <v>4010</v>
@@ -50850,7 +50877,7 @@
         <v>6</v>
       </c>
       <c r="D2020" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2020" t="s" s="3">
         <v>4012</v>
@@ -50867,7 +50894,7 @@
         <v>6</v>
       </c>
       <c r="D2021" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2021" t="s" s="3">
         <v>4014</v>
@@ -50884,7 +50911,7 @@
         <v>6</v>
       </c>
       <c r="D2022" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2022" t="s" s="3">
         <v>4016</v>
@@ -50901,7 +50928,7 @@
         <v>6</v>
       </c>
       <c r="D2023" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2023" t="s" s="3">
         <v>4018</v>
@@ -50918,7 +50945,7 @@
         <v>6</v>
       </c>
       <c r="D2024" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2024" t="s" s="3">
         <v>4020</v>
@@ -50935,7 +50962,7 @@
         <v>6</v>
       </c>
       <c r="D2025" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2025" t="s" s="3">
         <v>4022</v>
@@ -50952,7 +50979,7 @@
         <v>6</v>
       </c>
       <c r="D2026" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2026" t="s" s="3">
         <v>4024</v>
@@ -50969,7 +50996,7 @@
         <v>6</v>
       </c>
       <c r="D2027" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2027" t="s" s="3">
         <v>4026</v>
@@ -50986,7 +51013,7 @@
         <v>6</v>
       </c>
       <c r="D2028" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2028" t="s" s="3">
         <v>4028</v>
@@ -51003,7 +51030,7 @@
         <v>6</v>
       </c>
       <c r="D2029" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2029" t="s" s="3">
         <v>4030</v>
@@ -51020,7 +51047,7 @@
         <v>6</v>
       </c>
       <c r="D2030" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2030" t="s" s="3">
         <v>4032</v>
@@ -51037,7 +51064,7 @@
         <v>6</v>
       </c>
       <c r="D2031" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2031" t="s" s="3">
         <v>4034</v>
@@ -51054,7 +51081,7 @@
         <v>6</v>
       </c>
       <c r="D2032" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2032" t="s" s="3">
         <v>4036</v>
@@ -51071,7 +51098,7 @@
         <v>6</v>
       </c>
       <c r="D2033" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2033" t="s" s="3">
         <v>4038</v>
@@ -51088,7 +51115,7 @@
         <v>6</v>
       </c>
       <c r="D2034" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2034" t="s" s="3">
         <v>4040</v>
@@ -51105,7 +51132,7 @@
         <v>6</v>
       </c>
       <c r="D2035" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2035" t="s" s="3">
         <v>4042</v>
@@ -51122,7 +51149,7 @@
         <v>6</v>
       </c>
       <c r="D2036" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2036" t="s" s="3">
         <v>4044</v>
@@ -51139,7 +51166,7 @@
         <v>6</v>
       </c>
       <c r="D2037" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2037" t="s" s="3">
         <v>4046</v>
@@ -51156,7 +51183,7 @@
         <v>6</v>
       </c>
       <c r="D2038" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2038" t="s" s="3">
         <v>4048</v>
@@ -51173,7 +51200,7 @@
         <v>6</v>
       </c>
       <c r="D2039" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2039" t="s" s="3">
         <v>4050</v>
@@ -51190,7 +51217,7 @@
         <v>6</v>
       </c>
       <c r="D2040" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2040" t="s" s="3">
         <v>4052</v>
@@ -51207,7 +51234,7 @@
         <v>6</v>
       </c>
       <c r="D2041" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2041" t="s" s="3">
         <v>4054</v>
@@ -51224,7 +51251,7 @@
         <v>6</v>
       </c>
       <c r="D2042" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2042" t="s" s="3">
         <v>4056</v>
@@ -51241,7 +51268,7 @@
         <v>6</v>
       </c>
       <c r="D2043" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2043" t="s" s="3">
         <v>4058</v>
@@ -51258,7 +51285,7 @@
         <v>6</v>
       </c>
       <c r="D2044" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2044" t="s" s="3">
         <v>4060</v>
@@ -51275,7 +51302,7 @@
         <v>6</v>
       </c>
       <c r="D2045" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2045" t="s" s="3">
         <v>4062</v>
@@ -51292,7 +51319,7 @@
         <v>6</v>
       </c>
       <c r="D2046" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2046" t="s" s="3">
         <v>4064</v>
@@ -51309,7 +51336,7 @@
         <v>6</v>
       </c>
       <c r="D2047" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2047" t="s" s="3">
         <v>4066</v>
@@ -51326,7 +51353,7 @@
         <v>6</v>
       </c>
       <c r="D2048" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2048" t="s" s="3">
         <v>4068</v>
@@ -51343,7 +51370,7 @@
         <v>6</v>
       </c>
       <c r="D2049" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2049" t="s" s="3">
         <v>4070</v>
@@ -51360,7 +51387,7 @@
         <v>6</v>
       </c>
       <c r="D2050" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2050" t="s" s="3">
         <v>4072</v>
@@ -51377,7 +51404,7 @@
         <v>6</v>
       </c>
       <c r="D2051" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2051" t="s" s="3">
         <v>4074</v>
@@ -51394,7 +51421,7 @@
         <v>6</v>
       </c>
       <c r="D2052" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2052" t="s" s="3">
         <v>4076</v>
@@ -51408,10 +51435,10 @@
         <v>4077</v>
       </c>
       <c r="C2053" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2053" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2053" t="s" s="3">
         <v>4078</v>
@@ -51425,10 +51452,10 @@
         <v>4079</v>
       </c>
       <c r="C2054" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2054" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2054" t="s" s="3">
         <v>4080</v>
@@ -51442,10 +51469,10 @@
         <v>4081</v>
       </c>
       <c r="C2055" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2055" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2055" t="s" s="3">
         <v>4082</v>
@@ -51462,7 +51489,7 @@
         <v>767</v>
       </c>
       <c r="D2056" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2056" t="s" s="3">
         <v>4084</v>
@@ -51479,7 +51506,7 @@
         <v>767</v>
       </c>
       <c r="D2057" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2057" t="s" s="3">
         <v>4086</v>
@@ -51496,7 +51523,7 @@
         <v>767</v>
       </c>
       <c r="D2058" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2058" t="s" s="3">
         <v>4088</v>
@@ -51513,7 +51540,7 @@
         <v>767</v>
       </c>
       <c r="D2059" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2059" t="s" s="3">
         <v>4090</v>
@@ -51530,7 +51557,7 @@
         <v>767</v>
       </c>
       <c r="D2060" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2060" t="s" s="3">
         <v>4092</v>
@@ -51547,7 +51574,7 @@
         <v>767</v>
       </c>
       <c r="D2061" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2061" t="s" s="3">
         <v>4094</v>
@@ -51564,7 +51591,7 @@
         <v>767</v>
       </c>
       <c r="D2062" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2062" t="s" s="3">
         <v>4096</v>
@@ -51581,7 +51608,7 @@
         <v>767</v>
       </c>
       <c r="D2063" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2063" t="s" s="3">
         <v>4098</v>
@@ -51598,7 +51625,7 @@
         <v>767</v>
       </c>
       <c r="D2064" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2064" t="s" s="3">
         <v>4100</v>
@@ -51615,7 +51642,7 @@
         <v>767</v>
       </c>
       <c r="D2065" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2065" t="s" s="3">
         <v>4102</v>
@@ -51632,7 +51659,7 @@
         <v>767</v>
       </c>
       <c r="D2066" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2066" t="s" s="3">
         <v>4104</v>
@@ -51649,7 +51676,7 @@
         <v>767</v>
       </c>
       <c r="D2067" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2067" t="s" s="3">
         <v>4106</v>
@@ -51666,7 +51693,7 @@
         <v>767</v>
       </c>
       <c r="D2068" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2068" t="s" s="3">
         <v>4108</v>
@@ -51683,7 +51710,7 @@
         <v>767</v>
       </c>
       <c r="D2069" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2069" t="s" s="3">
         <v>4110</v>
@@ -51700,7 +51727,7 @@
         <v>767</v>
       </c>
       <c r="D2070" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2070" t="s" s="3">
         <v>4112</v>
@@ -51717,7 +51744,7 @@
         <v>767</v>
       </c>
       <c r="D2071" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2071" t="s" s="3">
         <v>4114</v>
@@ -51728,16 +51755,16 @@
         <v>2071.0</v>
       </c>
       <c r="B2072" t="s" s="3">
-        <v>4051</v>
+        <v>4115</v>
       </c>
       <c r="C2072" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2072" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2072" t="s" s="3">
-        <v>4052</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="2073" ht="36.0" customHeight="true">
@@ -51745,16 +51772,16 @@
         <v>2072.0</v>
       </c>
       <c r="B2073" t="s" s="3">
-        <v>4115</v>
+        <v>4117</v>
       </c>
       <c r="C2073" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2073" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2073" t="s" s="3">
-        <v>4116</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="2074" ht="36.0" customHeight="true">
@@ -51762,16 +51789,16 @@
         <v>2073.0</v>
       </c>
       <c r="B2074" t="s" s="3">
-        <v>4117</v>
+        <v>4119</v>
       </c>
       <c r="C2074" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2074" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2074" t="s" s="3">
-        <v>4118</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="2075" ht="36.0" customHeight="true">
@@ -51779,16 +51806,16 @@
         <v>2074.0</v>
       </c>
       <c r="B2075" t="s" s="3">
-        <v>4119</v>
+        <v>4057</v>
       </c>
       <c r="C2075" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2075" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2075" t="s" s="3">
-        <v>4120</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="2076" ht="36.0" customHeight="true">
@@ -51802,7 +51829,7 @@
         <v>767</v>
       </c>
       <c r="D2076" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2076" t="s" s="3">
         <v>4122</v>
@@ -51819,7 +51846,7 @@
         <v>767</v>
       </c>
       <c r="D2077" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2077" t="s" s="3">
         <v>4124</v>
@@ -51836,7 +51863,7 @@
         <v>767</v>
       </c>
       <c r="D2078" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2078" t="s" s="3">
         <v>4126</v>
@@ -51853,7 +51880,7 @@
         <v>767</v>
       </c>
       <c r="D2079" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2079" t="s" s="3">
         <v>4128</v>
@@ -51870,7 +51897,7 @@
         <v>767</v>
       </c>
       <c r="D2080" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2080" t="s" s="3">
         <v>4130</v>
@@ -51887,7 +51914,7 @@
         <v>767</v>
       </c>
       <c r="D2081" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2081" t="s" s="3">
         <v>4132</v>
@@ -51901,10 +51928,10 @@
         <v>4133</v>
       </c>
       <c r="C2082" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2082" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2082" t="s" s="3">
         <v>4134</v>
@@ -51918,10 +51945,10 @@
         <v>4135</v>
       </c>
       <c r="C2083" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2083" t="s" s="2">
-        <v>3957</v>
+        <v>3961</v>
       </c>
       <c r="E2083" t="s" s="3">
         <v>4136</v>
@@ -51935,13 +51962,13 @@
         <v>4137</v>
       </c>
       <c r="C2084" t="s" s="2">
-        <v>6</v>
+        <v>767</v>
       </c>
       <c r="D2084" t="s" s="2">
+        <v>3961</v>
+      </c>
+      <c r="E2084" t="s" s="3">
         <v>4138</v>
-      </c>
-      <c r="E2084" t="s" s="3">
-        <v>4139</v>
       </c>
     </row>
     <row r="2085" ht="36.0" customHeight="true">
@@ -51949,16 +51976,16 @@
         <v>2084.0</v>
       </c>
       <c r="B2085" t="s" s="3">
+        <v>4139</v>
+      </c>
+      <c r="C2085" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2085" t="s" s="2">
+        <v>3961</v>
+      </c>
+      <c r="E2085" t="s" s="3">
         <v>4140</v>
-      </c>
-      <c r="C2085" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2085" t="s" s="2">
-        <v>4138</v>
-      </c>
-      <c r="E2085" t="s" s="3">
-        <v>4141</v>
       </c>
     </row>
     <row r="2086" ht="36.0" customHeight="true">
@@ -51966,16 +51993,16 @@
         <v>2085.0</v>
       </c>
       <c r="B2086" t="s" s="3">
+        <v>4141</v>
+      </c>
+      <c r="C2086" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2086" t="s" s="2">
+        <v>3961</v>
+      </c>
+      <c r="E2086" t="s" s="3">
         <v>4142</v>
-      </c>
-      <c r="C2086" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2086" t="s" s="2">
-        <v>4138</v>
-      </c>
-      <c r="E2086" t="s" s="3">
-        <v>4143</v>
       </c>
     </row>
     <row r="2087" ht="36.0" customHeight="true">
@@ -51983,13 +52010,13 @@
         <v>2086.0</v>
       </c>
       <c r="B2087" t="s" s="3">
+        <v>4143</v>
+      </c>
+      <c r="C2087" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2087" t="s" s="2">
         <v>4144</v>
-      </c>
-      <c r="C2087" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2087" t="s" s="2">
-        <v>4138</v>
       </c>
       <c r="E2087" t="s" s="3">
         <v>4145</v>
@@ -52006,7 +52033,7 @@
         <v>6</v>
       </c>
       <c r="D2088" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2088" t="s" s="3">
         <v>4147</v>
@@ -52023,7 +52050,7 @@
         <v>6</v>
       </c>
       <c r="D2089" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2089" t="s" s="3">
         <v>4149</v>
@@ -52040,7 +52067,7 @@
         <v>6</v>
       </c>
       <c r="D2090" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2090" t="s" s="3">
         <v>4151</v>
@@ -52057,7 +52084,7 @@
         <v>6</v>
       </c>
       <c r="D2091" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2091" t="s" s="3">
         <v>4153</v>
@@ -52074,7 +52101,7 @@
         <v>6</v>
       </c>
       <c r="D2092" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2092" t="s" s="3">
         <v>4155</v>
@@ -52091,7 +52118,7 @@
         <v>6</v>
       </c>
       <c r="D2093" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2093" t="s" s="3">
         <v>4157</v>
@@ -52108,7 +52135,7 @@
         <v>6</v>
       </c>
       <c r="D2094" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2094" t="s" s="3">
         <v>4159</v>
@@ -52125,7 +52152,7 @@
         <v>6</v>
       </c>
       <c r="D2095" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2095" t="s" s="3">
         <v>4161</v>
@@ -52142,7 +52169,7 @@
         <v>6</v>
       </c>
       <c r="D2096" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2096" t="s" s="3">
         <v>4163</v>
@@ -52159,7 +52186,7 @@
         <v>6</v>
       </c>
       <c r="D2097" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2097" t="s" s="3">
         <v>4165</v>
@@ -52176,7 +52203,7 @@
         <v>6</v>
       </c>
       <c r="D2098" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2098" t="s" s="3">
         <v>4167</v>
@@ -52193,7 +52220,7 @@
         <v>6</v>
       </c>
       <c r="D2099" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2099" t="s" s="3">
         <v>4169</v>
@@ -52210,7 +52237,7 @@
         <v>6</v>
       </c>
       <c r="D2100" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2100" t="s" s="3">
         <v>4171</v>
@@ -52227,7 +52254,7 @@
         <v>6</v>
       </c>
       <c r="D2101" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2101" t="s" s="3">
         <v>4173</v>
@@ -52244,7 +52271,7 @@
         <v>6</v>
       </c>
       <c r="D2102" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2102" t="s" s="3">
         <v>4175</v>
@@ -52261,7 +52288,7 @@
         <v>6</v>
       </c>
       <c r="D2103" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2103" t="s" s="3">
         <v>4177</v>
@@ -52278,7 +52305,7 @@
         <v>6</v>
       </c>
       <c r="D2104" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2104" t="s" s="3">
         <v>4179</v>
@@ -52295,7 +52322,7 @@
         <v>6</v>
       </c>
       <c r="D2105" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2105" t="s" s="3">
         <v>4181</v>
@@ -52312,7 +52339,7 @@
         <v>6</v>
       </c>
       <c r="D2106" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2106" t="s" s="3">
         <v>4183</v>
@@ -52329,7 +52356,7 @@
         <v>6</v>
       </c>
       <c r="D2107" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2107" t="s" s="3">
         <v>4185</v>
@@ -52346,7 +52373,7 @@
         <v>6</v>
       </c>
       <c r="D2108" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2108" t="s" s="3">
         <v>4187</v>
@@ -52357,16 +52384,16 @@
         <v>2108.0</v>
       </c>
       <c r="B2109" t="s" s="3">
-        <v>865</v>
+        <v>4188</v>
       </c>
       <c r="C2109" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2109" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2109" t="s" s="3">
-        <v>4188</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="2110" ht="36.0" customHeight="true">
@@ -52374,16 +52401,16 @@
         <v>2109.0</v>
       </c>
       <c r="B2110" t="s" s="3">
-        <v>4189</v>
+        <v>4190</v>
       </c>
       <c r="C2110" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2110" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2110" t="s" s="3">
-        <v>4190</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="2111" ht="36.0" customHeight="true">
@@ -52391,16 +52418,16 @@
         <v>2110.0</v>
       </c>
       <c r="B2111" t="s" s="3">
-        <v>4191</v>
+        <v>4192</v>
       </c>
       <c r="C2111" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2111" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2111" t="s" s="3">
-        <v>4192</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="2112" ht="36.0" customHeight="true">
@@ -52408,13 +52435,13 @@
         <v>2111.0</v>
       </c>
       <c r="B2112" t="s" s="3">
-        <v>4193</v>
+        <v>865</v>
       </c>
       <c r="C2112" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2112" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2112" t="s" s="3">
         <v>4194</v>
@@ -52431,7 +52458,7 @@
         <v>6</v>
       </c>
       <c r="D2113" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2113" t="s" s="3">
         <v>4196</v>
@@ -52448,7 +52475,7 @@
         <v>6</v>
       </c>
       <c r="D2114" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2114" t="s" s="3">
         <v>4198</v>
@@ -52465,7 +52492,7 @@
         <v>6</v>
       </c>
       <c r="D2115" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2115" t="s" s="3">
         <v>4200</v>
@@ -52482,7 +52509,7 @@
         <v>6</v>
       </c>
       <c r="D2116" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2116" t="s" s="3">
         <v>4202</v>
@@ -52499,7 +52526,7 @@
         <v>6</v>
       </c>
       <c r="D2117" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2117" t="s" s="3">
         <v>4204</v>
@@ -52516,7 +52543,7 @@
         <v>6</v>
       </c>
       <c r="D2118" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2118" t="s" s="3">
         <v>4206</v>
@@ -52533,7 +52560,7 @@
         <v>6</v>
       </c>
       <c r="D2119" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2119" t="s" s="3">
         <v>4208</v>
@@ -52550,7 +52577,7 @@
         <v>6</v>
       </c>
       <c r="D2120" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2120" t="s" s="3">
         <v>4210</v>
@@ -52567,7 +52594,7 @@
         <v>6</v>
       </c>
       <c r="D2121" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2121" t="s" s="3">
         <v>4212</v>
@@ -52584,7 +52611,7 @@
         <v>6</v>
       </c>
       <c r="D2122" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2122" t="s" s="3">
         <v>4214</v>
@@ -52601,7 +52628,7 @@
         <v>6</v>
       </c>
       <c r="D2123" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2123" t="s" s="3">
         <v>4216</v>
@@ -52618,10 +52645,10 @@
         <v>6</v>
       </c>
       <c r="D2124" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2124" t="s" s="3">
-        <v>4190</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="2125" ht="36.0" customHeight="true">
@@ -52629,16 +52656,16 @@
         <v>2124.0</v>
       </c>
       <c r="B2125" t="s" s="3">
-        <v>4218</v>
+        <v>4219</v>
       </c>
       <c r="C2125" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2125" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2125" t="s" s="3">
-        <v>4219</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="2126" ht="36.0" customHeight="true">
@@ -52646,16 +52673,16 @@
         <v>2125.0</v>
       </c>
       <c r="B2126" t="s" s="3">
-        <v>3732</v>
+        <v>4221</v>
       </c>
       <c r="C2126" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2126" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2126" t="s" s="3">
-        <v>4220</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="2127" ht="36.0" customHeight="true">
@@ -52663,16 +52690,16 @@
         <v>2126.0</v>
       </c>
       <c r="B2127" t="s" s="3">
-        <v>4221</v>
+        <v>4223</v>
       </c>
       <c r="C2127" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2127" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2127" t="s" s="3">
-        <v>4222</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="2128" ht="36.0" customHeight="true">
@@ -52680,16 +52707,16 @@
         <v>2127.0</v>
       </c>
       <c r="B2128" t="s" s="3">
-        <v>4223</v>
+        <v>4224</v>
       </c>
       <c r="C2128" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2128" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2128" t="s" s="3">
-        <v>4224</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="2129" ht="36.0" customHeight="true">
@@ -52697,13 +52724,13 @@
         <v>2128.0</v>
       </c>
       <c r="B2129" t="s" s="3">
-        <v>4225</v>
+        <v>3734</v>
       </c>
       <c r="C2129" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2129" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2129" t="s" s="3">
         <v>4226</v>
@@ -52720,7 +52747,7 @@
         <v>6</v>
       </c>
       <c r="D2130" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2130" t="s" s="3">
         <v>4228</v>
@@ -52737,7 +52764,7 @@
         <v>6</v>
       </c>
       <c r="D2131" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2131" t="s" s="3">
         <v>4230</v>
@@ -52754,7 +52781,7 @@
         <v>6</v>
       </c>
       <c r="D2132" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2132" t="s" s="3">
         <v>4232</v>
@@ -52771,7 +52798,7 @@
         <v>6</v>
       </c>
       <c r="D2133" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2133" t="s" s="3">
         <v>4234</v>
@@ -52785,10 +52812,10 @@
         <v>4235</v>
       </c>
       <c r="C2134" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2134" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2134" t="s" s="3">
         <v>4236</v>
@@ -52802,10 +52829,10 @@
         <v>4237</v>
       </c>
       <c r="C2135" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2135" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2135" t="s" s="3">
         <v>4238</v>
@@ -52819,10 +52846,10 @@
         <v>4239</v>
       </c>
       <c r="C2136" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2136" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2136" t="s" s="3">
         <v>4240</v>
@@ -52839,7 +52866,7 @@
         <v>767</v>
       </c>
       <c r="D2137" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2137" t="s" s="3">
         <v>4242</v>
@@ -52856,7 +52883,7 @@
         <v>767</v>
       </c>
       <c r="D2138" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2138" t="s" s="3">
         <v>4244</v>
@@ -52873,7 +52900,7 @@
         <v>767</v>
       </c>
       <c r="D2139" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2139" t="s" s="3">
         <v>4246</v>
@@ -52890,7 +52917,7 @@
         <v>767</v>
       </c>
       <c r="D2140" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2140" t="s" s="3">
         <v>4248</v>
@@ -52907,7 +52934,7 @@
         <v>767</v>
       </c>
       <c r="D2141" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2141" t="s" s="3">
         <v>4250</v>
@@ -52924,7 +52951,7 @@
         <v>767</v>
       </c>
       <c r="D2142" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2142" t="s" s="3">
         <v>4252</v>
@@ -52941,7 +52968,7 @@
         <v>767</v>
       </c>
       <c r="D2143" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2143" t="s" s="3">
         <v>4254</v>
@@ -52958,7 +52985,7 @@
         <v>767</v>
       </c>
       <c r="D2144" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2144" t="s" s="3">
         <v>4256</v>
@@ -52975,7 +53002,7 @@
         <v>767</v>
       </c>
       <c r="D2145" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2145" t="s" s="3">
         <v>4258</v>
@@ -52992,7 +53019,7 @@
         <v>767</v>
       </c>
       <c r="D2146" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2146" t="s" s="3">
         <v>4260</v>
@@ -53009,7 +53036,7 @@
         <v>767</v>
       </c>
       <c r="D2147" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2147" t="s" s="3">
         <v>4262</v>
@@ -53026,7 +53053,7 @@
         <v>767</v>
       </c>
       <c r="D2148" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2148" t="s" s="3">
         <v>4264</v>
@@ -53043,7 +53070,7 @@
         <v>767</v>
       </c>
       <c r="D2149" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2149" t="s" s="3">
         <v>4266</v>
@@ -53060,7 +53087,7 @@
         <v>767</v>
       </c>
       <c r="D2150" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2150" t="s" s="3">
         <v>4268</v>
@@ -53077,7 +53104,7 @@
         <v>767</v>
       </c>
       <c r="D2151" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2151" t="s" s="3">
         <v>4270</v>
@@ -53094,7 +53121,7 @@
         <v>767</v>
       </c>
       <c r="D2152" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2152" t="s" s="3">
         <v>4272</v>
@@ -53111,7 +53138,7 @@
         <v>767</v>
       </c>
       <c r="D2153" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2153" t="s" s="3">
         <v>4274</v>
@@ -53128,7 +53155,7 @@
         <v>767</v>
       </c>
       <c r="D2154" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2154" t="s" s="3">
         <v>4276</v>
@@ -53145,7 +53172,7 @@
         <v>767</v>
       </c>
       <c r="D2155" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2155" t="s" s="3">
         <v>4278</v>
@@ -53162,7 +53189,7 @@
         <v>767</v>
       </c>
       <c r="D2156" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2156" t="s" s="3">
         <v>4280</v>
@@ -53179,7 +53206,7 @@
         <v>767</v>
       </c>
       <c r="D2157" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2157" t="s" s="3">
         <v>4282</v>
@@ -53196,7 +53223,7 @@
         <v>767</v>
       </c>
       <c r="D2158" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2158" t="s" s="3">
         <v>4284</v>
@@ -53213,7 +53240,7 @@
         <v>767</v>
       </c>
       <c r="D2159" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2159" t="s" s="3">
         <v>4286</v>
@@ -53230,7 +53257,7 @@
         <v>767</v>
       </c>
       <c r="D2160" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2160" t="s" s="3">
         <v>4288</v>
@@ -53247,7 +53274,7 @@
         <v>767</v>
       </c>
       <c r="D2161" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2161" t="s" s="3">
         <v>4290</v>
@@ -53264,7 +53291,7 @@
         <v>767</v>
       </c>
       <c r="D2162" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2162" t="s" s="3">
         <v>4292</v>
@@ -53278,10 +53305,10 @@
         <v>4293</v>
       </c>
       <c r="C2163" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2163" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2163" t="s" s="3">
         <v>4294</v>
@@ -53292,16 +53319,16 @@
         <v>2163.0</v>
       </c>
       <c r="B2164" t="s" s="3">
-        <v>4249</v>
+        <v>4295</v>
       </c>
       <c r="C2164" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2164" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2164" t="s" s="3">
-        <v>4295</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="2165" ht="36.0" customHeight="true">
@@ -53309,16 +53336,16 @@
         <v>2164.0</v>
       </c>
       <c r="B2165" t="s" s="3">
-        <v>4296</v>
+        <v>4297</v>
       </c>
       <c r="C2165" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2165" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2165" t="s" s="3">
-        <v>4297</v>
+        <v>4298</v>
       </c>
     </row>
     <row r="2166" ht="36.0" customHeight="true">
@@ -53326,16 +53353,16 @@
         <v>2165.0</v>
       </c>
       <c r="B2166" t="s" s="3">
-        <v>4218</v>
+        <v>4299</v>
       </c>
       <c r="C2166" t="s" s="2">
         <v>986</v>
       </c>
       <c r="D2166" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2166" t="s" s="3">
-        <v>4219</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="2167" ht="36.0" customHeight="true">
@@ -53343,16 +53370,16 @@
         <v>2166.0</v>
       </c>
       <c r="B2167" t="s" s="3">
-        <v>4298</v>
+        <v>4255</v>
       </c>
       <c r="C2167" t="s" s="2">
         <v>986</v>
       </c>
       <c r="D2167" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2167" t="s" s="3">
-        <v>4299</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="2168" ht="36.0" customHeight="true">
@@ -53360,16 +53387,16 @@
         <v>2167.0</v>
       </c>
       <c r="B2168" t="s" s="3">
-        <v>4300</v>
+        <v>4302</v>
       </c>
       <c r="C2168" t="s" s="2">
         <v>986</v>
       </c>
       <c r="D2168" t="s" s="2">
-        <v>4138</v>
+        <v>4144</v>
       </c>
       <c r="E2168" t="s" s="3">
-        <v>4301</v>
+        <v>4303</v>
       </c>
     </row>
     <row r="2169" ht="36.0" customHeight="true">
@@ -53377,16 +53404,16 @@
         <v>2168.0</v>
       </c>
       <c r="B2169" t="s" s="3">
-        <v>4302</v>
+        <v>4224</v>
       </c>
       <c r="C2169" t="s" s="2">
-        <v>6</v>
+        <v>986</v>
       </c>
       <c r="D2169" t="s" s="2">
-        <v>4303</v>
+        <v>4144</v>
       </c>
       <c r="E2169" t="s" s="3">
-        <v>4304</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="2170" ht="36.0" customHeight="true">
@@ -53394,16 +53421,16 @@
         <v>2169.0</v>
       </c>
       <c r="B2170" t="s" s="3">
+        <v>4304</v>
+      </c>
+      <c r="C2170" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2170" t="s" s="2">
+        <v>4144</v>
+      </c>
+      <c r="E2170" t="s" s="3">
         <v>4305</v>
-      </c>
-      <c r="C2170" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2170" t="s" s="2">
-        <v>4303</v>
-      </c>
-      <c r="E2170" t="s" s="3">
-        <v>4306</v>
       </c>
     </row>
     <row r="2171" ht="36.0" customHeight="true">
@@ -53411,16 +53438,16 @@
         <v>2170.0</v>
       </c>
       <c r="B2171" t="s" s="3">
+        <v>4306</v>
+      </c>
+      <c r="C2171" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2171" t="s" s="2">
+        <v>4144</v>
+      </c>
+      <c r="E2171" t="s" s="3">
         <v>4307</v>
-      </c>
-      <c r="C2171" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2171" t="s" s="2">
-        <v>4303</v>
-      </c>
-      <c r="E2171" t="s" s="3">
-        <v>4308</v>
       </c>
     </row>
     <row r="2172" ht="36.0" customHeight="true">
@@ -53428,13 +53455,13 @@
         <v>2171.0</v>
       </c>
       <c r="B2172" t="s" s="3">
+        <v>4308</v>
+      </c>
+      <c r="C2172" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2172" t="s" s="2">
         <v>4309</v>
-      </c>
-      <c r="C2172" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2172" t="s" s="2">
-        <v>4303</v>
       </c>
       <c r="E2172" t="s" s="3">
         <v>4310</v>
@@ -53451,7 +53478,7 @@
         <v>6</v>
       </c>
       <c r="D2173" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2173" t="s" s="3">
         <v>4312</v>
@@ -53468,7 +53495,7 @@
         <v>6</v>
       </c>
       <c r="D2174" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2174" t="s" s="3">
         <v>4314</v>
@@ -53485,7 +53512,7 @@
         <v>6</v>
       </c>
       <c r="D2175" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2175" t="s" s="3">
         <v>4316</v>
@@ -53502,7 +53529,7 @@
         <v>6</v>
       </c>
       <c r="D2176" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2176" t="s" s="3">
         <v>4318</v>
@@ -53519,7 +53546,7 @@
         <v>6</v>
       </c>
       <c r="D2177" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2177" t="s" s="3">
         <v>4320</v>
@@ -53536,7 +53563,7 @@
         <v>6</v>
       </c>
       <c r="D2178" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2178" t="s" s="3">
         <v>4322</v>
@@ -53553,7 +53580,7 @@
         <v>6</v>
       </c>
       <c r="D2179" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2179" t="s" s="3">
         <v>4324</v>
@@ -53570,7 +53597,7 @@
         <v>6</v>
       </c>
       <c r="D2180" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2180" t="s" s="3">
         <v>4326</v>
@@ -53587,7 +53614,7 @@
         <v>6</v>
       </c>
       <c r="D2181" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2181" t="s" s="3">
         <v>4328</v>
@@ -53604,7 +53631,7 @@
         <v>6</v>
       </c>
       <c r="D2182" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2182" t="s" s="3">
         <v>4330</v>
@@ -53621,7 +53648,7 @@
         <v>6</v>
       </c>
       <c r="D2183" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2183" t="s" s="3">
         <v>4332</v>
@@ -53638,7 +53665,7 @@
         <v>6</v>
       </c>
       <c r="D2184" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2184" t="s" s="3">
         <v>4334</v>
@@ -53655,7 +53682,7 @@
         <v>6</v>
       </c>
       <c r="D2185" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2185" t="s" s="3">
         <v>4336</v>
@@ -53672,7 +53699,7 @@
         <v>6</v>
       </c>
       <c r="D2186" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2186" t="s" s="3">
         <v>4338</v>
@@ -53689,7 +53716,7 @@
         <v>6</v>
       </c>
       <c r="D2187" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2187" t="s" s="3">
         <v>4340</v>
@@ -53706,7 +53733,7 @@
         <v>6</v>
       </c>
       <c r="D2188" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2188" t="s" s="3">
         <v>4342</v>
@@ -53723,7 +53750,7 @@
         <v>6</v>
       </c>
       <c r="D2189" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2189" t="s" s="3">
         <v>4344</v>
@@ -53740,7 +53767,7 @@
         <v>6</v>
       </c>
       <c r="D2190" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2190" t="s" s="3">
         <v>4346</v>
@@ -53757,7 +53784,7 @@
         <v>6</v>
       </c>
       <c r="D2191" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2191" t="s" s="3">
         <v>4348</v>
@@ -53774,7 +53801,7 @@
         <v>6</v>
       </c>
       <c r="D2192" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2192" t="s" s="3">
         <v>4350</v>
@@ -53791,7 +53818,7 @@
         <v>6</v>
       </c>
       <c r="D2193" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2193" t="s" s="3">
         <v>4352</v>
@@ -53808,7 +53835,7 @@
         <v>6</v>
       </c>
       <c r="D2194" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2194" t="s" s="3">
         <v>4354</v>
@@ -53825,7 +53852,7 @@
         <v>6</v>
       </c>
       <c r="D2195" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2195" t="s" s="3">
         <v>4356</v>
@@ -53842,7 +53869,7 @@
         <v>6</v>
       </c>
       <c r="D2196" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2196" t="s" s="3">
         <v>4358</v>
@@ -53859,7 +53886,7 @@
         <v>6</v>
       </c>
       <c r="D2197" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2197" t="s" s="3">
         <v>4360</v>
@@ -53876,7 +53903,7 @@
         <v>6</v>
       </c>
       <c r="D2198" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2198" t="s" s="3">
         <v>4362</v>
@@ -53893,7 +53920,7 @@
         <v>6</v>
       </c>
       <c r="D2199" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2199" t="s" s="3">
         <v>4364</v>
@@ -53910,7 +53937,7 @@
         <v>6</v>
       </c>
       <c r="D2200" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2200" t="s" s="3">
         <v>4366</v>
@@ -53927,7 +53954,7 @@
         <v>6</v>
       </c>
       <c r="D2201" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2201" t="s" s="3">
         <v>4368</v>
@@ -53944,7 +53971,7 @@
         <v>6</v>
       </c>
       <c r="D2202" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2202" t="s" s="3">
         <v>4370</v>
@@ -53961,7 +53988,7 @@
         <v>6</v>
       </c>
       <c r="D2203" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2203" t="s" s="3">
         <v>4372</v>
@@ -53978,7 +54005,7 @@
         <v>6</v>
       </c>
       <c r="D2204" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2204" t="s" s="3">
         <v>4374</v>
@@ -53995,7 +54022,7 @@
         <v>6</v>
       </c>
       <c r="D2205" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2205" t="s" s="3">
         <v>4376</v>
@@ -54012,7 +54039,7 @@
         <v>6</v>
       </c>
       <c r="D2206" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2206" t="s" s="3">
         <v>4378</v>
@@ -54029,7 +54056,7 @@
         <v>6</v>
       </c>
       <c r="D2207" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2207" t="s" s="3">
         <v>4380</v>
@@ -54046,7 +54073,7 @@
         <v>6</v>
       </c>
       <c r="D2208" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2208" t="s" s="3">
         <v>4382</v>
@@ -54063,7 +54090,7 @@
         <v>6</v>
       </c>
       <c r="D2209" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2209" t="s" s="3">
         <v>4384</v>
@@ -54080,7 +54107,7 @@
         <v>6</v>
       </c>
       <c r="D2210" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2210" t="s" s="3">
         <v>4386</v>
@@ -54097,7 +54124,7 @@
         <v>6</v>
       </c>
       <c r="D2211" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2211" t="s" s="3">
         <v>4388</v>
@@ -54114,7 +54141,7 @@
         <v>6</v>
       </c>
       <c r="D2212" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2212" t="s" s="3">
         <v>4390</v>
@@ -54131,7 +54158,7 @@
         <v>6</v>
       </c>
       <c r="D2213" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2213" t="s" s="3">
         <v>4392</v>
@@ -54148,7 +54175,7 @@
         <v>6</v>
       </c>
       <c r="D2214" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2214" t="s" s="3">
         <v>4394</v>
@@ -54165,7 +54192,7 @@
         <v>6</v>
       </c>
       <c r="D2215" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2215" t="s" s="3">
         <v>4396</v>
@@ -54182,7 +54209,7 @@
         <v>6</v>
       </c>
       <c r="D2216" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2216" t="s" s="3">
         <v>4398</v>
@@ -54199,7 +54226,7 @@
         <v>6</v>
       </c>
       <c r="D2217" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2217" t="s" s="3">
         <v>4400</v>
@@ -54216,7 +54243,7 @@
         <v>6</v>
       </c>
       <c r="D2218" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2218" t="s" s="3">
         <v>4402</v>
@@ -54233,7 +54260,7 @@
         <v>6</v>
       </c>
       <c r="D2219" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2219" t="s" s="3">
         <v>4404</v>
@@ -54250,7 +54277,7 @@
         <v>6</v>
       </c>
       <c r="D2220" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2220" t="s" s="3">
         <v>4406</v>
@@ -54267,7 +54294,7 @@
         <v>6</v>
       </c>
       <c r="D2221" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2221" t="s" s="3">
         <v>4408</v>
@@ -54284,7 +54311,7 @@
         <v>6</v>
       </c>
       <c r="D2222" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2222" t="s" s="3">
         <v>4410</v>
@@ -54301,7 +54328,7 @@
         <v>6</v>
       </c>
       <c r="D2223" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2223" t="s" s="3">
         <v>4412</v>
@@ -54318,7 +54345,7 @@
         <v>6</v>
       </c>
       <c r="D2224" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2224" t="s" s="3">
         <v>4414</v>
@@ -54335,7 +54362,7 @@
         <v>6</v>
       </c>
       <c r="D2225" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2225" t="s" s="3">
         <v>4416</v>
@@ -54352,7 +54379,7 @@
         <v>6</v>
       </c>
       <c r="D2226" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2226" t="s" s="3">
         <v>4418</v>
@@ -54369,7 +54396,7 @@
         <v>6</v>
       </c>
       <c r="D2227" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2227" t="s" s="3">
         <v>4420</v>
@@ -54386,7 +54413,7 @@
         <v>6</v>
       </c>
       <c r="D2228" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2228" t="s" s="3">
         <v>4422</v>
@@ -54403,7 +54430,7 @@
         <v>6</v>
       </c>
       <c r="D2229" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2229" t="s" s="3">
         <v>4424</v>
@@ -54420,7 +54447,7 @@
         <v>6</v>
       </c>
       <c r="D2230" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2230" t="s" s="3">
         <v>4426</v>
@@ -54437,7 +54464,7 @@
         <v>6</v>
       </c>
       <c r="D2231" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2231" t="s" s="3">
         <v>4428</v>
@@ -54454,7 +54481,7 @@
         <v>6</v>
       </c>
       <c r="D2232" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2232" t="s" s="3">
         <v>4430</v>
@@ -54471,7 +54498,7 @@
         <v>6</v>
       </c>
       <c r="D2233" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2233" t="s" s="3">
         <v>4432</v>
@@ -54488,7 +54515,7 @@
         <v>6</v>
       </c>
       <c r="D2234" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2234" t="s" s="3">
         <v>4434</v>
@@ -54505,7 +54532,7 @@
         <v>6</v>
       </c>
       <c r="D2235" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2235" t="s" s="3">
         <v>4436</v>
@@ -54522,7 +54549,7 @@
         <v>6</v>
       </c>
       <c r="D2236" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2236" t="s" s="3">
         <v>4438</v>
@@ -54539,7 +54566,7 @@
         <v>6</v>
       </c>
       <c r="D2237" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2237" t="s" s="3">
         <v>4440</v>
@@ -54556,7 +54583,7 @@
         <v>6</v>
       </c>
       <c r="D2238" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2238" t="s" s="3">
         <v>4442</v>
@@ -54573,7 +54600,7 @@
         <v>6</v>
       </c>
       <c r="D2239" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2239" t="s" s="3">
         <v>4444</v>
@@ -54590,7 +54617,7 @@
         <v>6</v>
       </c>
       <c r="D2240" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2240" t="s" s="3">
         <v>4446</v>
@@ -54607,7 +54634,7 @@
         <v>6</v>
       </c>
       <c r="D2241" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2241" t="s" s="3">
         <v>4448</v>
@@ -54624,7 +54651,7 @@
         <v>6</v>
       </c>
       <c r="D2242" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2242" t="s" s="3">
         <v>4450</v>
@@ -54641,7 +54668,7 @@
         <v>6</v>
       </c>
       <c r="D2243" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2243" t="s" s="3">
         <v>4452</v>
@@ -54658,7 +54685,7 @@
         <v>6</v>
       </c>
       <c r="D2244" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2244" t="s" s="3">
         <v>4454</v>
@@ -54675,7 +54702,7 @@
         <v>6</v>
       </c>
       <c r="D2245" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2245" t="s" s="3">
         <v>4456</v>
@@ -54692,7 +54719,7 @@
         <v>6</v>
       </c>
       <c r="D2246" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2246" t="s" s="3">
         <v>4458</v>
@@ -54709,7 +54736,7 @@
         <v>6</v>
       </c>
       <c r="D2247" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2247" t="s" s="3">
         <v>4460</v>
@@ -54726,7 +54753,7 @@
         <v>6</v>
       </c>
       <c r="D2248" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2248" t="s" s="3">
         <v>4462</v>
@@ -54743,7 +54770,7 @@
         <v>6</v>
       </c>
       <c r="D2249" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2249" t="s" s="3">
         <v>4464</v>
@@ -54760,7 +54787,7 @@
         <v>6</v>
       </c>
       <c r="D2250" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2250" t="s" s="3">
         <v>4466</v>
@@ -54777,7 +54804,7 @@
         <v>6</v>
       </c>
       <c r="D2251" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2251" t="s" s="3">
         <v>4468</v>
@@ -54794,7 +54821,7 @@
         <v>6</v>
       </c>
       <c r="D2252" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2252" t="s" s="3">
         <v>4470</v>
@@ -54811,7 +54838,7 @@
         <v>6</v>
       </c>
       <c r="D2253" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2253" t="s" s="3">
         <v>4472</v>
@@ -54828,7 +54855,7 @@
         <v>6</v>
       </c>
       <c r="D2254" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2254" t="s" s="3">
         <v>4474</v>
@@ -54845,7 +54872,7 @@
         <v>6</v>
       </c>
       <c r="D2255" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2255" t="s" s="3">
         <v>4476</v>
@@ -54862,7 +54889,7 @@
         <v>6</v>
       </c>
       <c r="D2256" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2256" t="s" s="3">
         <v>4478</v>
@@ -54879,7 +54906,7 @@
         <v>6</v>
       </c>
       <c r="D2257" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2257" t="s" s="3">
         <v>4480</v>
@@ -54896,7 +54923,7 @@
         <v>6</v>
       </c>
       <c r="D2258" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2258" t="s" s="3">
         <v>4482</v>
@@ -54913,7 +54940,7 @@
         <v>6</v>
       </c>
       <c r="D2259" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2259" t="s" s="3">
         <v>4484</v>
@@ -54930,7 +54957,7 @@
         <v>6</v>
       </c>
       <c r="D2260" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2260" t="s" s="3">
         <v>4486</v>
@@ -54947,7 +54974,7 @@
         <v>6</v>
       </c>
       <c r="D2261" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2261" t="s" s="3">
         <v>4488</v>
@@ -54964,7 +54991,7 @@
         <v>6</v>
       </c>
       <c r="D2262" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2262" t="s" s="3">
         <v>4490</v>
@@ -54981,7 +55008,7 @@
         <v>6</v>
       </c>
       <c r="D2263" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2263" t="s" s="3">
         <v>4492</v>
@@ -54998,7 +55025,7 @@
         <v>6</v>
       </c>
       <c r="D2264" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2264" t="s" s="3">
         <v>4494</v>
@@ -55015,7 +55042,7 @@
         <v>6</v>
       </c>
       <c r="D2265" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2265" t="s" s="3">
         <v>4496</v>
@@ -55032,7 +55059,7 @@
         <v>6</v>
       </c>
       <c r="D2266" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2266" t="s" s="3">
         <v>4498</v>
@@ -55049,7 +55076,7 @@
         <v>6</v>
       </c>
       <c r="D2267" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2267" t="s" s="3">
         <v>4500</v>
@@ -55066,7 +55093,7 @@
         <v>6</v>
       </c>
       <c r="D2268" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2268" t="s" s="3">
         <v>4502</v>
@@ -55083,7 +55110,7 @@
         <v>6</v>
       </c>
       <c r="D2269" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2269" t="s" s="3">
         <v>4504</v>
@@ -55100,7 +55127,7 @@
         <v>6</v>
       </c>
       <c r="D2270" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2270" t="s" s="3">
         <v>4506</v>
@@ -55117,7 +55144,7 @@
         <v>6</v>
       </c>
       <c r="D2271" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2271" t="s" s="3">
         <v>4508</v>
@@ -55128,16 +55155,16 @@
         <v>2271.0</v>
       </c>
       <c r="B2272" t="s" s="3">
-        <v>1432</v>
+        <v>4509</v>
       </c>
       <c r="C2272" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2272" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2272" t="s" s="3">
-        <v>4509</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="2273" ht="36.0" customHeight="true">
@@ -55145,16 +55172,16 @@
         <v>2272.0</v>
       </c>
       <c r="B2273" t="s" s="3">
-        <v>4510</v>
+        <v>4511</v>
       </c>
       <c r="C2273" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2273" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2273" t="s" s="3">
-        <v>4511</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="2274" ht="36.0" customHeight="true">
@@ -55162,16 +55189,16 @@
         <v>2273.0</v>
       </c>
       <c r="B2274" t="s" s="3">
-        <v>4512</v>
+        <v>4513</v>
       </c>
       <c r="C2274" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2274" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2274" t="s" s="3">
-        <v>4513</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="2275" ht="36.0" customHeight="true">
@@ -55179,13 +55206,13 @@
         <v>2274.0</v>
       </c>
       <c r="B2275" t="s" s="3">
-        <v>4514</v>
+        <v>1432</v>
       </c>
       <c r="C2275" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2275" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2275" t="s" s="3">
         <v>4515</v>
@@ -55202,7 +55229,7 @@
         <v>6</v>
       </c>
       <c r="D2276" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2276" t="s" s="3">
         <v>4517</v>
@@ -55219,7 +55246,7 @@
         <v>6</v>
       </c>
       <c r="D2277" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2277" t="s" s="3">
         <v>4519</v>
@@ -55236,7 +55263,7 @@
         <v>6</v>
       </c>
       <c r="D2278" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2278" t="s" s="3">
         <v>4521</v>
@@ -55253,7 +55280,7 @@
         <v>6</v>
       </c>
       <c r="D2279" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2279" t="s" s="3">
         <v>4523</v>
@@ -55270,7 +55297,7 @@
         <v>6</v>
       </c>
       <c r="D2280" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2280" t="s" s="3">
         <v>4525</v>
@@ -55287,7 +55314,7 @@
         <v>6</v>
       </c>
       <c r="D2281" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2281" t="s" s="3">
         <v>4527</v>
@@ -55304,7 +55331,7 @@
         <v>6</v>
       </c>
       <c r="D2282" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2282" t="s" s="3">
         <v>4529</v>
@@ -55321,7 +55348,7 @@
         <v>6</v>
       </c>
       <c r="D2283" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2283" t="s" s="3">
         <v>4531</v>
@@ -55338,7 +55365,7 @@
         <v>6</v>
       </c>
       <c r="D2284" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2284" t="s" s="3">
         <v>4533</v>
@@ -55355,7 +55382,7 @@
         <v>6</v>
       </c>
       <c r="D2285" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2285" t="s" s="3">
         <v>4535</v>
@@ -55372,7 +55399,7 @@
         <v>6</v>
       </c>
       <c r="D2286" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2286" t="s" s="3">
         <v>4537</v>
@@ -55389,7 +55416,7 @@
         <v>6</v>
       </c>
       <c r="D2287" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2287" t="s" s="3">
         <v>4539</v>
@@ -55406,7 +55433,7 @@
         <v>6</v>
       </c>
       <c r="D2288" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2288" t="s" s="3">
         <v>4541</v>
@@ -55423,7 +55450,7 @@
         <v>6</v>
       </c>
       <c r="D2289" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2289" t="s" s="3">
         <v>4543</v>
@@ -55440,7 +55467,7 @@
         <v>6</v>
       </c>
       <c r="D2290" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2290" t="s" s="3">
         <v>4545</v>
@@ -55457,7 +55484,7 @@
         <v>6</v>
       </c>
       <c r="D2291" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2291" t="s" s="3">
         <v>4547</v>
@@ -55474,7 +55501,7 @@
         <v>6</v>
       </c>
       <c r="D2292" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2292" t="s" s="3">
         <v>4549</v>
@@ -55491,7 +55518,7 @@
         <v>6</v>
       </c>
       <c r="D2293" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2293" t="s" s="3">
         <v>4551</v>
@@ -55508,7 +55535,7 @@
         <v>6</v>
       </c>
       <c r="D2294" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2294" t="s" s="3">
         <v>4553</v>
@@ -55525,7 +55552,7 @@
         <v>6</v>
       </c>
       <c r="D2295" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2295" t="s" s="3">
         <v>4555</v>
@@ -55542,7 +55569,7 @@
         <v>6</v>
       </c>
       <c r="D2296" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2296" t="s" s="3">
         <v>4557</v>
@@ -55559,7 +55586,7 @@
         <v>6</v>
       </c>
       <c r="D2297" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2297" t="s" s="3">
         <v>4559</v>
@@ -55576,7 +55603,7 @@
         <v>6</v>
       </c>
       <c r="D2298" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2298" t="s" s="3">
         <v>4561</v>
@@ -55593,7 +55620,7 @@
         <v>6</v>
       </c>
       <c r="D2299" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2299" t="s" s="3">
         <v>4563</v>
@@ -55610,7 +55637,7 @@
         <v>6</v>
       </c>
       <c r="D2300" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2300" t="s" s="3">
         <v>4565</v>
@@ -55627,7 +55654,7 @@
         <v>6</v>
       </c>
       <c r="D2301" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2301" t="s" s="3">
         <v>4567</v>
@@ -55644,7 +55671,7 @@
         <v>6</v>
       </c>
       <c r="D2302" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2302" t="s" s="3">
         <v>4569</v>
@@ -55661,7 +55688,7 @@
         <v>6</v>
       </c>
       <c r="D2303" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2303" t="s" s="3">
         <v>4571</v>
@@ -55678,7 +55705,7 @@
         <v>6</v>
       </c>
       <c r="D2304" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2304" t="s" s="3">
         <v>4573</v>
@@ -55695,7 +55722,7 @@
         <v>6</v>
       </c>
       <c r="D2305" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2305" t="s" s="3">
         <v>4575</v>
@@ -55712,7 +55739,7 @@
         <v>6</v>
       </c>
       <c r="D2306" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2306" t="s" s="3">
         <v>4577</v>
@@ -55729,7 +55756,7 @@
         <v>6</v>
       </c>
       <c r="D2307" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2307" t="s" s="3">
         <v>4579</v>
@@ -55746,7 +55773,7 @@
         <v>6</v>
       </c>
       <c r="D2308" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2308" t="s" s="3">
         <v>4581</v>
@@ -55763,7 +55790,7 @@
         <v>6</v>
       </c>
       <c r="D2309" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2309" t="s" s="3">
         <v>4583</v>
@@ -55780,7 +55807,7 @@
         <v>6</v>
       </c>
       <c r="D2310" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2310" t="s" s="3">
         <v>4585</v>
@@ -55797,7 +55824,7 @@
         <v>6</v>
       </c>
       <c r="D2311" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2311" t="s" s="3">
         <v>4587</v>
@@ -55814,7 +55841,7 @@
         <v>6</v>
       </c>
       <c r="D2312" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2312" t="s" s="3">
         <v>4589</v>
@@ -55831,7 +55858,7 @@
         <v>6</v>
       </c>
       <c r="D2313" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2313" t="s" s="3">
         <v>4591</v>
@@ -55845,10 +55872,10 @@
         <v>4592</v>
       </c>
       <c r="C2314" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2314" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2314" t="s" s="3">
         <v>4593</v>
@@ -55862,10 +55889,10 @@
         <v>4594</v>
       </c>
       <c r="C2315" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2315" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2315" t="s" s="3">
         <v>4595</v>
@@ -55879,10 +55906,10 @@
         <v>4596</v>
       </c>
       <c r="C2316" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2316" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2316" t="s" s="3">
         <v>4597</v>
@@ -55899,7 +55926,7 @@
         <v>767</v>
       </c>
       <c r="D2317" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2317" t="s" s="3">
         <v>4599</v>
@@ -55916,7 +55943,7 @@
         <v>767</v>
       </c>
       <c r="D2318" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2318" t="s" s="3">
         <v>4601</v>
@@ -55933,7 +55960,7 @@
         <v>767</v>
       </c>
       <c r="D2319" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2319" t="s" s="3">
         <v>4603</v>
@@ -55950,7 +55977,7 @@
         <v>767</v>
       </c>
       <c r="D2320" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2320" t="s" s="3">
         <v>4605</v>
@@ -55967,7 +55994,7 @@
         <v>767</v>
       </c>
       <c r="D2321" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2321" t="s" s="3">
         <v>4607</v>
@@ -55984,7 +56011,7 @@
         <v>767</v>
       </c>
       <c r="D2322" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2322" t="s" s="3">
         <v>4609</v>
@@ -56001,7 +56028,7 @@
         <v>767</v>
       </c>
       <c r="D2323" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2323" t="s" s="3">
         <v>4611</v>
@@ -56018,7 +56045,7 @@
         <v>767</v>
       </c>
       <c r="D2324" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2324" t="s" s="3">
         <v>4613</v>
@@ -56035,7 +56062,7 @@
         <v>767</v>
       </c>
       <c r="D2325" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2325" t="s" s="3">
         <v>4615</v>
@@ -56052,7 +56079,7 @@
         <v>767</v>
       </c>
       <c r="D2326" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2326" t="s" s="3">
         <v>4617</v>
@@ -56069,7 +56096,7 @@
         <v>767</v>
       </c>
       <c r="D2327" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2327" t="s" s="3">
         <v>4619</v>
@@ -56086,7 +56113,7 @@
         <v>767</v>
       </c>
       <c r="D2328" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2328" t="s" s="3">
         <v>4621</v>
@@ -56103,7 +56130,7 @@
         <v>767</v>
       </c>
       <c r="D2329" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2329" t="s" s="3">
         <v>4623</v>
@@ -56120,7 +56147,7 @@
         <v>767</v>
       </c>
       <c r="D2330" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2330" t="s" s="3">
         <v>4625</v>
@@ -56137,7 +56164,7 @@
         <v>767</v>
       </c>
       <c r="D2331" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2331" t="s" s="3">
         <v>4627</v>
@@ -56154,7 +56181,7 @@
         <v>767</v>
       </c>
       <c r="D2332" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2332" t="s" s="3">
         <v>4629</v>
@@ -56171,7 +56198,7 @@
         <v>767</v>
       </c>
       <c r="D2333" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2333" t="s" s="3">
         <v>4631</v>
@@ -56188,10 +56215,10 @@
         <v>767</v>
       </c>
       <c r="D2334" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2334" t="s" s="3">
-        <v>4525</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="2335" ht="36.0" customHeight="true">
@@ -56199,16 +56226,16 @@
         <v>2334.0</v>
       </c>
       <c r="B2335" t="s" s="3">
-        <v>4633</v>
+        <v>4634</v>
       </c>
       <c r="C2335" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2335" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2335" t="s" s="3">
-        <v>4634</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="2336" ht="36.0" customHeight="true">
@@ -56216,16 +56243,16 @@
         <v>2335.0</v>
       </c>
       <c r="B2336" t="s" s="3">
-        <v>4635</v>
+        <v>4636</v>
       </c>
       <c r="C2336" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2336" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2336" t="s" s="3">
-        <v>4636</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="2337" ht="36.0" customHeight="true">
@@ -56233,16 +56260,16 @@
         <v>2336.0</v>
       </c>
       <c r="B2337" t="s" s="3">
-        <v>4637</v>
+        <v>4638</v>
       </c>
       <c r="C2337" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2337" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2337" t="s" s="3">
-        <v>4638</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="2338" ht="36.0" customHeight="true">
@@ -56256,7 +56283,7 @@
         <v>767</v>
       </c>
       <c r="D2338" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2338" t="s" s="3">
         <v>4640</v>
@@ -56273,7 +56300,7 @@
         <v>767</v>
       </c>
       <c r="D2339" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2339" t="s" s="3">
         <v>4642</v>
@@ -56290,7 +56317,7 @@
         <v>767</v>
       </c>
       <c r="D2340" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2340" t="s" s="3">
         <v>4644</v>
@@ -56307,7 +56334,7 @@
         <v>767</v>
       </c>
       <c r="D2341" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2341" t="s" s="3">
         <v>4646</v>
@@ -56324,7 +56351,7 @@
         <v>767</v>
       </c>
       <c r="D2342" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2342" t="s" s="3">
         <v>4648</v>
@@ -56341,7 +56368,7 @@
         <v>767</v>
       </c>
       <c r="D2343" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2343" t="s" s="3">
         <v>4650</v>
@@ -56358,7 +56385,7 @@
         <v>767</v>
       </c>
       <c r="D2344" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2344" t="s" s="3">
         <v>4652</v>
@@ -56375,7 +56402,7 @@
         <v>767</v>
       </c>
       <c r="D2345" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2345" t="s" s="3">
         <v>4654</v>
@@ -56392,7 +56419,7 @@
         <v>767</v>
       </c>
       <c r="D2346" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2346" t="s" s="3">
         <v>4656</v>
@@ -56409,7 +56436,7 @@
         <v>767</v>
       </c>
       <c r="D2347" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2347" t="s" s="3">
         <v>4658</v>
@@ -56426,7 +56453,7 @@
         <v>767</v>
       </c>
       <c r="D2348" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2348" t="s" s="3">
         <v>4660</v>
@@ -56443,7 +56470,7 @@
         <v>767</v>
       </c>
       <c r="D2349" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2349" t="s" s="3">
         <v>4662</v>
@@ -56460,7 +56487,7 @@
         <v>767</v>
       </c>
       <c r="D2350" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2350" t="s" s="3">
         <v>4664</v>
@@ -56477,7 +56504,7 @@
         <v>767</v>
       </c>
       <c r="D2351" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2351" t="s" s="3">
         <v>4666</v>
@@ -56494,7 +56521,7 @@
         <v>767</v>
       </c>
       <c r="D2352" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2352" t="s" s="3">
         <v>4668</v>
@@ -56511,7 +56538,7 @@
         <v>767</v>
       </c>
       <c r="D2353" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2353" t="s" s="3">
         <v>4670</v>
@@ -56528,7 +56555,7 @@
         <v>767</v>
       </c>
       <c r="D2354" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2354" t="s" s="3">
         <v>4672</v>
@@ -56545,7 +56572,7 @@
         <v>767</v>
       </c>
       <c r="D2355" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2355" t="s" s="3">
         <v>4674</v>
@@ -56562,7 +56589,7 @@
         <v>767</v>
       </c>
       <c r="D2356" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2356" t="s" s="3">
         <v>4676</v>
@@ -56579,7 +56606,7 @@
         <v>767</v>
       </c>
       <c r="D2357" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2357" t="s" s="3">
         <v>4678</v>
@@ -56596,7 +56623,7 @@
         <v>767</v>
       </c>
       <c r="D2358" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2358" t="s" s="3">
         <v>4680</v>
@@ -56613,7 +56640,7 @@
         <v>767</v>
       </c>
       <c r="D2359" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2359" t="s" s="3">
         <v>4682</v>
@@ -56630,7 +56657,7 @@
         <v>767</v>
       </c>
       <c r="D2360" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2360" t="s" s="3">
         <v>4684</v>
@@ -56647,7 +56674,7 @@
         <v>767</v>
       </c>
       <c r="D2361" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2361" t="s" s="3">
         <v>4686</v>
@@ -56664,7 +56691,7 @@
         <v>767</v>
       </c>
       <c r="D2362" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2362" t="s" s="3">
         <v>4688</v>
@@ -56681,7 +56708,7 @@
         <v>767</v>
       </c>
       <c r="D2363" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2363" t="s" s="3">
         <v>4690</v>
@@ -56698,7 +56725,7 @@
         <v>767</v>
       </c>
       <c r="D2364" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2364" t="s" s="3">
         <v>4692</v>
@@ -56715,7 +56742,7 @@
         <v>767</v>
       </c>
       <c r="D2365" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2365" t="s" s="3">
         <v>4694</v>
@@ -56732,7 +56759,7 @@
         <v>767</v>
       </c>
       <c r="D2366" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2366" t="s" s="3">
         <v>4696</v>
@@ -56749,7 +56776,7 @@
         <v>767</v>
       </c>
       <c r="D2367" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2367" t="s" s="3">
         <v>4698</v>
@@ -56766,7 +56793,7 @@
         <v>767</v>
       </c>
       <c r="D2368" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2368" t="s" s="3">
         <v>4700</v>
@@ -56783,7 +56810,7 @@
         <v>767</v>
       </c>
       <c r="D2369" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2369" t="s" s="3">
         <v>4702</v>
@@ -56800,7 +56827,7 @@
         <v>767</v>
       </c>
       <c r="D2370" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2370" t="s" s="3">
         <v>4704</v>
@@ -56817,7 +56844,7 @@
         <v>767</v>
       </c>
       <c r="D2371" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2371" t="s" s="3">
         <v>4706</v>
@@ -56834,7 +56861,7 @@
         <v>767</v>
       </c>
       <c r="D2372" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2372" t="s" s="3">
         <v>4708</v>
@@ -56851,7 +56878,7 @@
         <v>767</v>
       </c>
       <c r="D2373" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2373" t="s" s="3">
         <v>4710</v>
@@ -56868,7 +56895,7 @@
         <v>767</v>
       </c>
       <c r="D2374" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2374" t="s" s="3">
         <v>4712</v>
@@ -56885,7 +56912,7 @@
         <v>767</v>
       </c>
       <c r="D2375" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2375" t="s" s="3">
         <v>4714</v>
@@ -56902,7 +56929,7 @@
         <v>767</v>
       </c>
       <c r="D2376" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2376" t="s" s="3">
         <v>4716</v>
@@ -56919,7 +56946,7 @@
         <v>767</v>
       </c>
       <c r="D2377" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2377" t="s" s="3">
         <v>4718</v>
@@ -56936,7 +56963,7 @@
         <v>767</v>
       </c>
       <c r="D2378" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2378" t="s" s="3">
         <v>4720</v>
@@ -56953,7 +56980,7 @@
         <v>767</v>
       </c>
       <c r="D2379" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2379" t="s" s="3">
         <v>4722</v>
@@ -56970,7 +56997,7 @@
         <v>767</v>
       </c>
       <c r="D2380" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2380" t="s" s="3">
         <v>4724</v>
@@ -56987,7 +57014,7 @@
         <v>767</v>
       </c>
       <c r="D2381" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2381" t="s" s="3">
         <v>4726</v>
@@ -57004,7 +57031,7 @@
         <v>767</v>
       </c>
       <c r="D2382" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2382" t="s" s="3">
         <v>4728</v>
@@ -57021,7 +57048,7 @@
         <v>767</v>
       </c>
       <c r="D2383" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2383" t="s" s="3">
         <v>4730</v>
@@ -57038,7 +57065,7 @@
         <v>767</v>
       </c>
       <c r="D2384" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2384" t="s" s="3">
         <v>4732</v>
@@ -57055,7 +57082,7 @@
         <v>767</v>
       </c>
       <c r="D2385" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2385" t="s" s="3">
         <v>4734</v>
@@ -57072,7 +57099,7 @@
         <v>767</v>
       </c>
       <c r="D2386" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2386" t="s" s="3">
         <v>4736</v>
@@ -57089,7 +57116,7 @@
         <v>767</v>
       </c>
       <c r="D2387" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2387" t="s" s="3">
         <v>4738</v>
@@ -57103,10 +57130,10 @@
         <v>4739</v>
       </c>
       <c r="C2388" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2388" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2388" t="s" s="3">
         <v>4740</v>
@@ -57120,10 +57147,10 @@
         <v>4741</v>
       </c>
       <c r="C2389" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2389" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2389" t="s" s="3">
         <v>4742</v>
@@ -57137,10 +57164,10 @@
         <v>4743</v>
       </c>
       <c r="C2390" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2390" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2390" t="s" s="3">
         <v>4744</v>
@@ -57157,7 +57184,7 @@
         <v>986</v>
       </c>
       <c r="D2391" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2391" t="s" s="3">
         <v>4746</v>
@@ -57174,7 +57201,7 @@
         <v>986</v>
       </c>
       <c r="D2392" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2392" t="s" s="3">
         <v>4748</v>
@@ -57191,7 +57218,7 @@
         <v>986</v>
       </c>
       <c r="D2393" t="s" s="2">
-        <v>4303</v>
+        <v>4309</v>
       </c>
       <c r="E2393" t="s" s="3">
         <v>4750</v>
@@ -57205,13 +57232,13 @@
         <v>4751</v>
       </c>
       <c r="C2394" t="s" s="2">
-        <v>6</v>
+        <v>986</v>
       </c>
       <c r="D2394" t="s" s="2">
+        <v>4309</v>
+      </c>
+      <c r="E2394" t="s" s="3">
         <v>4752</v>
-      </c>
-      <c r="E2394" t="s" s="3">
-        <v>4753</v>
       </c>
     </row>
     <row r="2395" ht="36.0" customHeight="true">
@@ -57219,16 +57246,16 @@
         <v>2394.0</v>
       </c>
       <c r="B2395" t="s" s="3">
+        <v>4753</v>
+      </c>
+      <c r="C2395" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2395" t="s" s="2">
+        <v>4309</v>
+      </c>
+      <c r="E2395" t="s" s="3">
         <v>4754</v>
-      </c>
-      <c r="C2395" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2395" t="s" s="2">
-        <v>4752</v>
-      </c>
-      <c r="E2395" t="s" s="3">
-        <v>4755</v>
       </c>
     </row>
     <row r="2396" ht="36.0" customHeight="true">
@@ -57236,16 +57263,16 @@
         <v>2395.0</v>
       </c>
       <c r="B2396" t="s" s="3">
+        <v>4755</v>
+      </c>
+      <c r="C2396" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2396" t="s" s="2">
+        <v>4309</v>
+      </c>
+      <c r="E2396" t="s" s="3">
         <v>4756</v>
-      </c>
-      <c r="C2396" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2396" t="s" s="2">
-        <v>4752</v>
-      </c>
-      <c r="E2396" t="s" s="3">
-        <v>4757</v>
       </c>
     </row>
     <row r="2397" ht="36.0" customHeight="true">
@@ -57253,13 +57280,13 @@
         <v>2396.0</v>
       </c>
       <c r="B2397" t="s" s="3">
+        <v>4757</v>
+      </c>
+      <c r="C2397" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2397" t="s" s="2">
         <v>4758</v>
-      </c>
-      <c r="C2397" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2397" t="s" s="2">
-        <v>4752</v>
       </c>
       <c r="E2397" t="s" s="3">
         <v>4759</v>
@@ -57276,7 +57303,7 @@
         <v>6</v>
       </c>
       <c r="D2398" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2398" t="s" s="3">
         <v>4761</v>
@@ -57293,7 +57320,7 @@
         <v>6</v>
       </c>
       <c r="D2399" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2399" t="s" s="3">
         <v>4763</v>
@@ -57310,7 +57337,7 @@
         <v>6</v>
       </c>
       <c r="D2400" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2400" t="s" s="3">
         <v>4765</v>
@@ -57327,7 +57354,7 @@
         <v>6</v>
       </c>
       <c r="D2401" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2401" t="s" s="3">
         <v>4767</v>
@@ -57344,7 +57371,7 @@
         <v>6</v>
       </c>
       <c r="D2402" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2402" t="s" s="3">
         <v>4769</v>
@@ -57361,7 +57388,7 @@
         <v>6</v>
       </c>
       <c r="D2403" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2403" t="s" s="3">
         <v>4771</v>
@@ -57378,7 +57405,7 @@
         <v>6</v>
       </c>
       <c r="D2404" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2404" t="s" s="3">
         <v>4773</v>
@@ -57395,7 +57422,7 @@
         <v>6</v>
       </c>
       <c r="D2405" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2405" t="s" s="3">
         <v>4775</v>
@@ -57412,7 +57439,7 @@
         <v>6</v>
       </c>
       <c r="D2406" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2406" t="s" s="3">
         <v>4777</v>
@@ -57429,7 +57456,7 @@
         <v>6</v>
       </c>
       <c r="D2407" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2407" t="s" s="3">
         <v>4779</v>
@@ -57446,7 +57473,7 @@
         <v>6</v>
       </c>
       <c r="D2408" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2408" t="s" s="3">
         <v>4781</v>
@@ -57463,7 +57490,7 @@
         <v>6</v>
       </c>
       <c r="D2409" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2409" t="s" s="3">
         <v>4783</v>
@@ -57480,7 +57507,7 @@
         <v>6</v>
       </c>
       <c r="D2410" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2410" t="s" s="3">
         <v>4785</v>
@@ -57497,7 +57524,7 @@
         <v>6</v>
       </c>
       <c r="D2411" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2411" t="s" s="3">
         <v>4787</v>
@@ -57514,7 +57541,7 @@
         <v>6</v>
       </c>
       <c r="D2412" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2412" t="s" s="3">
         <v>4789</v>
@@ -57531,7 +57558,7 @@
         <v>6</v>
       </c>
       <c r="D2413" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2413" t="s" s="3">
         <v>4791</v>
@@ -57548,7 +57575,7 @@
         <v>6</v>
       </c>
       <c r="D2414" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2414" t="s" s="3">
         <v>4793</v>
@@ -57565,7 +57592,7 @@
         <v>6</v>
       </c>
       <c r="D2415" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2415" t="s" s="3">
         <v>4795</v>
@@ -57582,7 +57609,7 @@
         <v>6</v>
       </c>
       <c r="D2416" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2416" t="s" s="3">
         <v>4797</v>
@@ -57599,7 +57626,7 @@
         <v>6</v>
       </c>
       <c r="D2417" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2417" t="s" s="3">
         <v>4799</v>
@@ -57616,7 +57643,7 @@
         <v>6</v>
       </c>
       <c r="D2418" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2418" t="s" s="3">
         <v>4801</v>
@@ -57633,7 +57660,7 @@
         <v>6</v>
       </c>
       <c r="D2419" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2419" t="s" s="3">
         <v>4803</v>
@@ -57650,7 +57677,7 @@
         <v>6</v>
       </c>
       <c r="D2420" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2420" t="s" s="3">
         <v>4805</v>
@@ -57667,7 +57694,7 @@
         <v>6</v>
       </c>
       <c r="D2421" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2421" t="s" s="3">
         <v>4807</v>
@@ -57684,7 +57711,7 @@
         <v>6</v>
       </c>
       <c r="D2422" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2422" t="s" s="3">
         <v>4809</v>
@@ -57701,7 +57728,7 @@
         <v>6</v>
       </c>
       <c r="D2423" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2423" t="s" s="3">
         <v>4811</v>
@@ -57718,7 +57745,7 @@
         <v>6</v>
       </c>
       <c r="D2424" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2424" t="s" s="3">
         <v>4813</v>
@@ -57735,7 +57762,7 @@
         <v>6</v>
       </c>
       <c r="D2425" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2425" t="s" s="3">
         <v>4815</v>
@@ -57752,7 +57779,7 @@
         <v>6</v>
       </c>
       <c r="D2426" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2426" t="s" s="3">
         <v>4817</v>
@@ -57769,7 +57796,7 @@
         <v>6</v>
       </c>
       <c r="D2427" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2427" t="s" s="3">
         <v>4819</v>
@@ -57786,7 +57813,7 @@
         <v>6</v>
       </c>
       <c r="D2428" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2428" t="s" s="3">
         <v>4821</v>
@@ -57803,7 +57830,7 @@
         <v>6</v>
       </c>
       <c r="D2429" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2429" t="s" s="3">
         <v>4823</v>
@@ -57820,7 +57847,7 @@
         <v>6</v>
       </c>
       <c r="D2430" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2430" t="s" s="3">
         <v>4825</v>
@@ -57837,7 +57864,7 @@
         <v>6</v>
       </c>
       <c r="D2431" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2431" t="s" s="3">
         <v>4827</v>
@@ -57854,7 +57881,7 @@
         <v>6</v>
       </c>
       <c r="D2432" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2432" t="s" s="3">
         <v>4829</v>
@@ -57871,7 +57898,7 @@
         <v>6</v>
       </c>
       <c r="D2433" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2433" t="s" s="3">
         <v>4831</v>
@@ -57888,7 +57915,7 @@
         <v>6</v>
       </c>
       <c r="D2434" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2434" t="s" s="3">
         <v>4833</v>
@@ -57905,7 +57932,7 @@
         <v>6</v>
       </c>
       <c r="D2435" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2435" t="s" s="3">
         <v>4835</v>
@@ -57922,7 +57949,7 @@
         <v>6</v>
       </c>
       <c r="D2436" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2436" t="s" s="3">
         <v>4837</v>
@@ -57939,7 +57966,7 @@
         <v>6</v>
       </c>
       <c r="D2437" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2437" t="s" s="3">
         <v>4839</v>
@@ -57956,7 +57983,7 @@
         <v>6</v>
       </c>
       <c r="D2438" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2438" t="s" s="3">
         <v>4841</v>
@@ -57973,7 +58000,7 @@
         <v>6</v>
       </c>
       <c r="D2439" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2439" t="s" s="3">
         <v>4843</v>
@@ -57990,7 +58017,7 @@
         <v>6</v>
       </c>
       <c r="D2440" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2440" t="s" s="3">
         <v>4845</v>
@@ -58007,7 +58034,7 @@
         <v>6</v>
       </c>
       <c r="D2441" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2441" t="s" s="3">
         <v>4847</v>
@@ -58024,7 +58051,7 @@
         <v>6</v>
       </c>
       <c r="D2442" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2442" t="s" s="3">
         <v>4849</v>
@@ -58041,7 +58068,7 @@
         <v>6</v>
       </c>
       <c r="D2443" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2443" t="s" s="3">
         <v>4851</v>
@@ -58058,7 +58085,7 @@
         <v>6</v>
       </c>
       <c r="D2444" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2444" t="s" s="3">
         <v>4853</v>
@@ -58075,7 +58102,7 @@
         <v>6</v>
       </c>
       <c r="D2445" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2445" t="s" s="3">
         <v>4855</v>
@@ -58092,7 +58119,7 @@
         <v>6</v>
       </c>
       <c r="D2446" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2446" t="s" s="3">
         <v>4857</v>
@@ -58109,7 +58136,7 @@
         <v>6</v>
       </c>
       <c r="D2447" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2447" t="s" s="3">
         <v>4859</v>
@@ -58126,7 +58153,7 @@
         <v>6</v>
       </c>
       <c r="D2448" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2448" t="s" s="3">
         <v>4861</v>
@@ -58140,10 +58167,10 @@
         <v>4862</v>
       </c>
       <c r="C2449" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2449" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2449" t="s" s="3">
         <v>4863</v>
@@ -58157,10 +58184,10 @@
         <v>4864</v>
       </c>
       <c r="C2450" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2450" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2450" t="s" s="3">
         <v>4865</v>
@@ -58174,10 +58201,10 @@
         <v>4866</v>
       </c>
       <c r="C2451" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2451" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2451" t="s" s="3">
         <v>4867</v>
@@ -58194,7 +58221,7 @@
         <v>767</v>
       </c>
       <c r="D2452" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2452" t="s" s="3">
         <v>4869</v>
@@ -58211,7 +58238,7 @@
         <v>767</v>
       </c>
       <c r="D2453" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2453" t="s" s="3">
         <v>4871</v>
@@ -58228,7 +58255,7 @@
         <v>767</v>
       </c>
       <c r="D2454" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2454" t="s" s="3">
         <v>4873</v>
@@ -58245,7 +58272,7 @@
         <v>767</v>
       </c>
       <c r="D2455" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2455" t="s" s="3">
         <v>4875</v>
@@ -58262,7 +58289,7 @@
         <v>767</v>
       </c>
       <c r="D2456" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2456" t="s" s="3">
         <v>4877</v>
@@ -58279,7 +58306,7 @@
         <v>767</v>
       </c>
       <c r="D2457" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2457" t="s" s="3">
         <v>4879</v>
@@ -58296,7 +58323,7 @@
         <v>767</v>
       </c>
       <c r="D2458" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2458" t="s" s="3">
         <v>4881</v>
@@ -58313,7 +58340,7 @@
         <v>767</v>
       </c>
       <c r="D2459" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2459" t="s" s="3">
         <v>4883</v>
@@ -58330,7 +58357,7 @@
         <v>767</v>
       </c>
       <c r="D2460" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2460" t="s" s="3">
         <v>4885</v>
@@ -58347,7 +58374,7 @@
         <v>767</v>
       </c>
       <c r="D2461" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2461" t="s" s="3">
         <v>4887</v>
@@ -58364,7 +58391,7 @@
         <v>767</v>
       </c>
       <c r="D2462" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2462" t="s" s="3">
         <v>4889</v>
@@ -58381,7 +58408,7 @@
         <v>767</v>
       </c>
       <c r="D2463" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2463" t="s" s="3">
         <v>4891</v>
@@ -58398,7 +58425,7 @@
         <v>767</v>
       </c>
       <c r="D2464" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2464" t="s" s="3">
         <v>4893</v>
@@ -58415,7 +58442,7 @@
         <v>767</v>
       </c>
       <c r="D2465" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2465" t="s" s="3">
         <v>4895</v>
@@ -58432,7 +58459,7 @@
         <v>767</v>
       </c>
       <c r="D2466" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2466" t="s" s="3">
         <v>4897</v>
@@ -58449,7 +58476,7 @@
         <v>767</v>
       </c>
       <c r="D2467" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2467" t="s" s="3">
         <v>4899</v>
@@ -58466,7 +58493,7 @@
         <v>767</v>
       </c>
       <c r="D2468" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2468" t="s" s="3">
         <v>4901</v>
@@ -58483,7 +58510,7 @@
         <v>767</v>
       </c>
       <c r="D2469" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2469" t="s" s="3">
         <v>4903</v>
@@ -58500,7 +58527,7 @@
         <v>767</v>
       </c>
       <c r="D2470" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2470" t="s" s="3">
         <v>4905</v>
@@ -58517,7 +58544,7 @@
         <v>767</v>
       </c>
       <c r="D2471" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2471" t="s" s="3">
         <v>4907</v>
@@ -58534,7 +58561,7 @@
         <v>767</v>
       </c>
       <c r="D2472" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2472" t="s" s="3">
         <v>4909</v>
@@ -58551,7 +58578,7 @@
         <v>767</v>
       </c>
       <c r="D2473" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2473" t="s" s="3">
         <v>4911</v>
@@ -58568,7 +58595,7 @@
         <v>767</v>
       </c>
       <c r="D2474" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2474" t="s" s="3">
         <v>4913</v>
@@ -58585,7 +58612,7 @@
         <v>767</v>
       </c>
       <c r="D2475" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2475" t="s" s="3">
         <v>4915</v>
@@ -58602,7 +58629,7 @@
         <v>767</v>
       </c>
       <c r="D2476" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2476" t="s" s="3">
         <v>4917</v>
@@ -58619,7 +58646,7 @@
         <v>767</v>
       </c>
       <c r="D2477" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2477" t="s" s="3">
         <v>4919</v>
@@ -58636,7 +58663,7 @@
         <v>767</v>
       </c>
       <c r="D2478" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2478" t="s" s="3">
         <v>4921</v>
@@ -58653,7 +58680,7 @@
         <v>767</v>
       </c>
       <c r="D2479" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2479" t="s" s="3">
         <v>4923</v>
@@ -58670,7 +58697,7 @@
         <v>767</v>
       </c>
       <c r="D2480" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2480" t="s" s="3">
         <v>4925</v>
@@ -58687,7 +58714,7 @@
         <v>767</v>
       </c>
       <c r="D2481" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2481" t="s" s="3">
         <v>4927</v>
@@ -58704,7 +58731,7 @@
         <v>767</v>
       </c>
       <c r="D2482" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2482" t="s" s="3">
         <v>4929</v>
@@ -58721,7 +58748,7 @@
         <v>767</v>
       </c>
       <c r="D2483" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2483" t="s" s="3">
         <v>4931</v>
@@ -58738,7 +58765,7 @@
         <v>767</v>
       </c>
       <c r="D2484" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2484" t="s" s="3">
         <v>4933</v>
@@ -58755,7 +58782,7 @@
         <v>767</v>
       </c>
       <c r="D2485" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2485" t="s" s="3">
         <v>4935</v>
@@ -58772,7 +58799,7 @@
         <v>767</v>
       </c>
       <c r="D2486" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2486" t="s" s="3">
         <v>4937</v>
@@ -58786,10 +58813,10 @@
         <v>4938</v>
       </c>
       <c r="C2487" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2487" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2487" t="s" s="3">
         <v>4939</v>
@@ -58803,10 +58830,10 @@
         <v>4940</v>
       </c>
       <c r="C2488" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2488" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2488" t="s" s="3">
         <v>4941</v>
@@ -58820,10 +58847,10 @@
         <v>4942</v>
       </c>
       <c r="C2489" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2489" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2489" t="s" s="3">
         <v>4943</v>
@@ -58840,7 +58867,7 @@
         <v>986</v>
       </c>
       <c r="D2490" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2490" t="s" s="3">
         <v>4945</v>
@@ -58857,7 +58884,7 @@
         <v>986</v>
       </c>
       <c r="D2491" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2491" t="s" s="3">
         <v>4947</v>
@@ -58874,7 +58901,7 @@
         <v>986</v>
       </c>
       <c r="D2492" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2492" t="s" s="3">
         <v>4949</v>
@@ -58891,7 +58918,7 @@
         <v>986</v>
       </c>
       <c r="D2493" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2493" t="s" s="3">
         <v>4951</v>
@@ -58908,7 +58935,7 @@
         <v>986</v>
       </c>
       <c r="D2494" t="s" s="2">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E2494" t="s" s="3">
         <v>4953</v>
@@ -58922,13 +58949,13 @@
         <v>4954</v>
       </c>
       <c r="C2495" t="s" s="2">
-        <v>6</v>
+        <v>986</v>
       </c>
       <c r="D2495" t="s" s="2">
+        <v>4758</v>
+      </c>
+      <c r="E2495" t="s" s="3">
         <v>4955</v>
-      </c>
-      <c r="E2495" t="s" s="3">
-        <v>4956</v>
       </c>
     </row>
     <row r="2496" ht="36.0" customHeight="true">
@@ -58936,16 +58963,16 @@
         <v>2495.0</v>
       </c>
       <c r="B2496" t="s" s="3">
+        <v>4956</v>
+      </c>
+      <c r="C2496" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2496" t="s" s="2">
+        <v>4758</v>
+      </c>
+      <c r="E2496" t="s" s="3">
         <v>4957</v>
-      </c>
-      <c r="C2496" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2496" t="s" s="2">
-        <v>4955</v>
-      </c>
-      <c r="E2496" t="s" s="3">
-        <v>4958</v>
       </c>
     </row>
     <row r="2497" ht="36.0" customHeight="true">
@@ -58953,16 +58980,16 @@
         <v>2496.0</v>
       </c>
       <c r="B2497" t="s" s="3">
+        <v>4958</v>
+      </c>
+      <c r="C2497" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2497" t="s" s="2">
+        <v>4758</v>
+      </c>
+      <c r="E2497" t="s" s="3">
         <v>4959</v>
-      </c>
-      <c r="C2497" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2497" t="s" s="2">
-        <v>4955</v>
-      </c>
-      <c r="E2497" t="s" s="3">
-        <v>4960</v>
       </c>
     </row>
     <row r="2498" ht="36.0" customHeight="true">
@@ -58970,13 +58997,13 @@
         <v>2497.0</v>
       </c>
       <c r="B2498" t="s" s="3">
+        <v>4960</v>
+      </c>
+      <c r="C2498" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2498" t="s" s="2">
         <v>4961</v>
-      </c>
-      <c r="C2498" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2498" t="s" s="2">
-        <v>4955</v>
       </c>
       <c r="E2498" t="s" s="3">
         <v>4962</v>
@@ -58993,7 +59020,7 @@
         <v>6</v>
       </c>
       <c r="D2499" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2499" t="s" s="3">
         <v>4964</v>
@@ -59010,7 +59037,7 @@
         <v>6</v>
       </c>
       <c r="D2500" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2500" t="s" s="3">
         <v>4966</v>
@@ -59027,7 +59054,7 @@
         <v>6</v>
       </c>
       <c r="D2501" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2501" t="s" s="3">
         <v>4968</v>
@@ -59044,7 +59071,7 @@
         <v>6</v>
       </c>
       <c r="D2502" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2502" t="s" s="3">
         <v>4970</v>
@@ -59061,7 +59088,7 @@
         <v>6</v>
       </c>
       <c r="D2503" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2503" t="s" s="3">
         <v>4972</v>
@@ -59078,7 +59105,7 @@
         <v>6</v>
       </c>
       <c r="D2504" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2504" t="s" s="3">
         <v>4974</v>
@@ -59095,7 +59122,7 @@
         <v>6</v>
       </c>
       <c r="D2505" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2505" t="s" s="3">
         <v>4976</v>
@@ -59112,7 +59139,7 @@
         <v>6</v>
       </c>
       <c r="D2506" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2506" t="s" s="3">
         <v>4978</v>
@@ -59129,7 +59156,7 @@
         <v>6</v>
       </c>
       <c r="D2507" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2507" t="s" s="3">
         <v>4980</v>
@@ -59146,7 +59173,7 @@
         <v>6</v>
       </c>
       <c r="D2508" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2508" t="s" s="3">
         <v>4982</v>
@@ -59163,7 +59190,7 @@
         <v>6</v>
       </c>
       <c r="D2509" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2509" t="s" s="3">
         <v>4984</v>
@@ -59180,7 +59207,7 @@
         <v>6</v>
       </c>
       <c r="D2510" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2510" t="s" s="3">
         <v>4986</v>
@@ -59197,7 +59224,7 @@
         <v>6</v>
       </c>
       <c r="D2511" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2511" t="s" s="3">
         <v>4988</v>
@@ -59214,7 +59241,7 @@
         <v>6</v>
       </c>
       <c r="D2512" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2512" t="s" s="3">
         <v>4990</v>
@@ -59231,7 +59258,7 @@
         <v>6</v>
       </c>
       <c r="D2513" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2513" t="s" s="3">
         <v>4992</v>
@@ -59248,7 +59275,7 @@
         <v>6</v>
       </c>
       <c r="D2514" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2514" t="s" s="3">
         <v>4994</v>
@@ -59265,7 +59292,7 @@
         <v>6</v>
       </c>
       <c r="D2515" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2515" t="s" s="3">
         <v>4996</v>
@@ -59282,7 +59309,7 @@
         <v>6</v>
       </c>
       <c r="D2516" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2516" t="s" s="3">
         <v>4998</v>
@@ -59299,7 +59326,7 @@
         <v>6</v>
       </c>
       <c r="D2517" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2517" t="s" s="3">
         <v>5000</v>
@@ -59316,7 +59343,7 @@
         <v>6</v>
       </c>
       <c r="D2518" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2518" t="s" s="3">
         <v>5002</v>
@@ -59333,7 +59360,7 @@
         <v>6</v>
       </c>
       <c r="D2519" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2519" t="s" s="3">
         <v>5004</v>
@@ -59350,7 +59377,7 @@
         <v>6</v>
       </c>
       <c r="D2520" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2520" t="s" s="3">
         <v>5006</v>
@@ -59367,7 +59394,7 @@
         <v>6</v>
       </c>
       <c r="D2521" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2521" t="s" s="3">
         <v>5008</v>
@@ -59384,7 +59411,7 @@
         <v>6</v>
       </c>
       <c r="D2522" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2522" t="s" s="3">
         <v>5010</v>
@@ -59401,7 +59428,7 @@
         <v>6</v>
       </c>
       <c r="D2523" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2523" t="s" s="3">
         <v>5012</v>
@@ -59418,7 +59445,7 @@
         <v>6</v>
       </c>
       <c r="D2524" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2524" t="s" s="3">
         <v>5014</v>
@@ -59435,7 +59462,7 @@
         <v>6</v>
       </c>
       <c r="D2525" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2525" t="s" s="3">
         <v>5016</v>
@@ -59452,7 +59479,7 @@
         <v>6</v>
       </c>
       <c r="D2526" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2526" t="s" s="3">
         <v>5018</v>
@@ -59469,7 +59496,7 @@
         <v>6</v>
       </c>
       <c r="D2527" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2527" t="s" s="3">
         <v>5020</v>
@@ -59486,7 +59513,7 @@
         <v>6</v>
       </c>
       <c r="D2528" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2528" t="s" s="3">
         <v>5022</v>
@@ -59503,7 +59530,7 @@
         <v>6</v>
       </c>
       <c r="D2529" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2529" t="s" s="3">
         <v>5024</v>
@@ -59520,7 +59547,7 @@
         <v>6</v>
       </c>
       <c r="D2530" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2530" t="s" s="3">
         <v>5026</v>
@@ -59537,7 +59564,7 @@
         <v>6</v>
       </c>
       <c r="D2531" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2531" t="s" s="3">
         <v>5028</v>
@@ -59554,7 +59581,7 @@
         <v>6</v>
       </c>
       <c r="D2532" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2532" t="s" s="3">
         <v>5030</v>
@@ -59571,7 +59598,7 @@
         <v>6</v>
       </c>
       <c r="D2533" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2533" t="s" s="3">
         <v>5032</v>
@@ -59588,7 +59615,7 @@
         <v>6</v>
       </c>
       <c r="D2534" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2534" t="s" s="3">
         <v>5034</v>
@@ -59605,7 +59632,7 @@
         <v>6</v>
       </c>
       <c r="D2535" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2535" t="s" s="3">
         <v>5036</v>
@@ -59622,7 +59649,7 @@
         <v>6</v>
       </c>
       <c r="D2536" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2536" t="s" s="3">
         <v>5038</v>
@@ -59639,7 +59666,7 @@
         <v>6</v>
       </c>
       <c r="D2537" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2537" t="s" s="3">
         <v>5040</v>
@@ -59656,7 +59683,7 @@
         <v>6</v>
       </c>
       <c r="D2538" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2538" t="s" s="3">
         <v>5042</v>
@@ -59673,7 +59700,7 @@
         <v>6</v>
       </c>
       <c r="D2539" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2539" t="s" s="3">
         <v>5044</v>
@@ -59690,7 +59717,7 @@
         <v>6</v>
       </c>
       <c r="D2540" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2540" t="s" s="3">
         <v>5046</v>
@@ -59707,7 +59734,7 @@
         <v>6</v>
       </c>
       <c r="D2541" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2541" t="s" s="3">
         <v>5048</v>
@@ -59724,7 +59751,7 @@
         <v>6</v>
       </c>
       <c r="D2542" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2542" t="s" s="3">
         <v>5050</v>
@@ -59741,7 +59768,7 @@
         <v>6</v>
       </c>
       <c r="D2543" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2543" t="s" s="3">
         <v>5052</v>
@@ -59758,7 +59785,7 @@
         <v>6</v>
       </c>
       <c r="D2544" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2544" t="s" s="3">
         <v>5054</v>
@@ -59775,7 +59802,7 @@
         <v>6</v>
       </c>
       <c r="D2545" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2545" t="s" s="3">
         <v>5056</v>
@@ -59792,7 +59819,7 @@
         <v>6</v>
       </c>
       <c r="D2546" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2546" t="s" s="3">
         <v>5058</v>
@@ -59809,7 +59836,7 @@
         <v>6</v>
       </c>
       <c r="D2547" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2547" t="s" s="3">
         <v>5060</v>
@@ -59826,7 +59853,7 @@
         <v>6</v>
       </c>
       <c r="D2548" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2548" t="s" s="3">
         <v>5062</v>
@@ -59843,7 +59870,7 @@
         <v>6</v>
       </c>
       <c r="D2549" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2549" t="s" s="3">
         <v>5064</v>
@@ -59860,7 +59887,7 @@
         <v>6</v>
       </c>
       <c r="D2550" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2550" t="s" s="3">
         <v>5066</v>
@@ -59877,7 +59904,7 @@
         <v>6</v>
       </c>
       <c r="D2551" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2551" t="s" s="3">
         <v>5068</v>
@@ -59894,7 +59921,7 @@
         <v>6</v>
       </c>
       <c r="D2552" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2552" t="s" s="3">
         <v>5070</v>
@@ -59911,7 +59938,7 @@
         <v>6</v>
       </c>
       <c r="D2553" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2553" t="s" s="3">
         <v>5072</v>
@@ -59928,7 +59955,7 @@
         <v>6</v>
       </c>
       <c r="D2554" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2554" t="s" s="3">
         <v>5074</v>
@@ -59945,7 +59972,7 @@
         <v>6</v>
       </c>
       <c r="D2555" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2555" t="s" s="3">
         <v>5076</v>
@@ -59962,7 +59989,7 @@
         <v>6</v>
       </c>
       <c r="D2556" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2556" t="s" s="3">
         <v>5078</v>
@@ -59979,7 +60006,7 @@
         <v>6</v>
       </c>
       <c r="D2557" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2557" t="s" s="3">
         <v>5080</v>
@@ -59996,7 +60023,7 @@
         <v>6</v>
       </c>
       <c r="D2558" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2558" t="s" s="3">
         <v>5082</v>
@@ -60013,7 +60040,7 @@
         <v>6</v>
       </c>
       <c r="D2559" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2559" t="s" s="3">
         <v>5084</v>
@@ -60030,7 +60057,7 @@
         <v>6</v>
       </c>
       <c r="D2560" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2560" t="s" s="3">
         <v>5086</v>
@@ -60047,7 +60074,7 @@
         <v>6</v>
       </c>
       <c r="D2561" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2561" t="s" s="3">
         <v>5088</v>
@@ -60064,7 +60091,7 @@
         <v>6</v>
       </c>
       <c r="D2562" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2562" t="s" s="3">
         <v>5090</v>
@@ -60081,7 +60108,7 @@
         <v>6</v>
       </c>
       <c r="D2563" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2563" t="s" s="3">
         <v>5092</v>
@@ -60098,7 +60125,7 @@
         <v>6</v>
       </c>
       <c r="D2564" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2564" t="s" s="3">
         <v>5094</v>
@@ -60115,10 +60142,10 @@
         <v>6</v>
       </c>
       <c r="D2565" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2565" t="s" s="3">
-        <v>5068</v>
+        <v>5096</v>
       </c>
     </row>
     <row r="2566" ht="36.0" customHeight="true">
@@ -60126,16 +60153,16 @@
         <v>2565.0</v>
       </c>
       <c r="B2566" t="s" s="3">
-        <v>5096</v>
+        <v>5097</v>
       </c>
       <c r="C2566" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2566" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2566" t="s" s="3">
-        <v>5097</v>
+        <v>5098</v>
       </c>
     </row>
     <row r="2567" ht="36.0" customHeight="true">
@@ -60143,16 +60170,16 @@
         <v>2566.0</v>
       </c>
       <c r="B2567" t="s" s="3">
-        <v>5098</v>
+        <v>5099</v>
       </c>
       <c r="C2567" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2567" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2567" t="s" s="3">
-        <v>5099</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="2568" ht="36.0" customHeight="true">
@@ -60160,16 +60187,16 @@
         <v>2567.0</v>
       </c>
       <c r="B2568" t="s" s="3">
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="C2568" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2568" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2568" t="s" s="3">
-        <v>5101</v>
+        <v>5074</v>
       </c>
     </row>
     <row r="2569" ht="36.0" customHeight="true">
@@ -60183,7 +60210,7 @@
         <v>6</v>
       </c>
       <c r="D2569" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2569" t="s" s="3">
         <v>5103</v>
@@ -60200,7 +60227,7 @@
         <v>6</v>
       </c>
       <c r="D2570" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2570" t="s" s="3">
         <v>5105</v>
@@ -60217,7 +60244,7 @@
         <v>6</v>
       </c>
       <c r="D2571" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2571" t="s" s="3">
         <v>5107</v>
@@ -60234,7 +60261,7 @@
         <v>6</v>
       </c>
       <c r="D2572" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2572" t="s" s="3">
         <v>5109</v>
@@ -60251,7 +60278,7 @@
         <v>6</v>
       </c>
       <c r="D2573" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2573" t="s" s="3">
         <v>5111</v>
@@ -60268,10 +60295,10 @@
         <v>6</v>
       </c>
       <c r="D2574" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2574" t="s" s="3">
-        <v>5030</v>
+        <v>5113</v>
       </c>
     </row>
     <row r="2575" ht="36.0" customHeight="true">
@@ -60279,16 +60306,16 @@
         <v>2574.0</v>
       </c>
       <c r="B2575" t="s" s="3">
-        <v>4101</v>
+        <v>5114</v>
       </c>
       <c r="C2575" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2575" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2575" t="s" s="3">
-        <v>5113</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="2576" ht="36.0" customHeight="true">
@@ -60296,16 +60323,16 @@
         <v>2575.0</v>
       </c>
       <c r="B2576" t="s" s="3">
-        <v>5114</v>
+        <v>5116</v>
       </c>
       <c r="C2576" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2576" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2576" t="s" s="3">
-        <v>5068</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="2577" ht="36.0" customHeight="true">
@@ -60313,16 +60340,16 @@
         <v>2576.0</v>
       </c>
       <c r="B2577" t="s" s="3">
-        <v>5115</v>
+        <v>5118</v>
       </c>
       <c r="C2577" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2577" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2577" t="s" s="3">
-        <v>5116</v>
+        <v>5036</v>
       </c>
     </row>
     <row r="2578" ht="36.0" customHeight="true">
@@ -60330,16 +60357,16 @@
         <v>2577.0</v>
       </c>
       <c r="B2578" t="s" s="3">
-        <v>5117</v>
+        <v>4107</v>
       </c>
       <c r="C2578" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2578" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2578" t="s" s="3">
-        <v>5118</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="2579" ht="36.0" customHeight="true">
@@ -60347,16 +60374,16 @@
         <v>2578.0</v>
       </c>
       <c r="B2579" t="s" s="3">
-        <v>5119</v>
+        <v>5120</v>
       </c>
       <c r="C2579" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2579" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2579" t="s" s="3">
-        <v>5120</v>
+        <v>5074</v>
       </c>
     </row>
     <row r="2580" ht="36.0" customHeight="true">
@@ -60370,7 +60397,7 @@
         <v>6</v>
       </c>
       <c r="D2580" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2580" t="s" s="3">
         <v>5122</v>
@@ -60387,7 +60414,7 @@
         <v>6</v>
       </c>
       <c r="D2581" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2581" t="s" s="3">
         <v>5124</v>
@@ -60404,7 +60431,7 @@
         <v>6</v>
       </c>
       <c r="D2582" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2582" t="s" s="3">
         <v>5126</v>
@@ -60421,7 +60448,7 @@
         <v>6</v>
       </c>
       <c r="D2583" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2583" t="s" s="3">
         <v>5128</v>
@@ -60438,7 +60465,7 @@
         <v>6</v>
       </c>
       <c r="D2584" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2584" t="s" s="3">
         <v>5130</v>
@@ -60455,7 +60482,7 @@
         <v>6</v>
       </c>
       <c r="D2585" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2585" t="s" s="3">
         <v>5132</v>
@@ -60472,7 +60499,7 @@
         <v>6</v>
       </c>
       <c r="D2586" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2586" t="s" s="3">
         <v>5134</v>
@@ -60489,7 +60516,7 @@
         <v>6</v>
       </c>
       <c r="D2587" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2587" t="s" s="3">
         <v>5136</v>
@@ -60506,7 +60533,7 @@
         <v>6</v>
       </c>
       <c r="D2588" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2588" t="s" s="3">
         <v>5138</v>
@@ -60523,7 +60550,7 @@
         <v>6</v>
       </c>
       <c r="D2589" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2589" t="s" s="3">
         <v>5140</v>
@@ -60540,7 +60567,7 @@
         <v>6</v>
       </c>
       <c r="D2590" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2590" t="s" s="3">
         <v>5142</v>
@@ -60557,7 +60584,7 @@
         <v>6</v>
       </c>
       <c r="D2591" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2591" t="s" s="3">
         <v>5144</v>
@@ -60574,7 +60601,7 @@
         <v>6</v>
       </c>
       <c r="D2592" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2592" t="s" s="3">
         <v>5146</v>
@@ -60591,7 +60618,7 @@
         <v>6</v>
       </c>
       <c r="D2593" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2593" t="s" s="3">
         <v>5148</v>
@@ -60608,7 +60635,7 @@
         <v>6</v>
       </c>
       <c r="D2594" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2594" t="s" s="3">
         <v>5150</v>
@@ -60625,7 +60652,7 @@
         <v>6</v>
       </c>
       <c r="D2595" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2595" t="s" s="3">
         <v>5152</v>
@@ -60642,7 +60669,7 @@
         <v>6</v>
       </c>
       <c r="D2596" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2596" t="s" s="3">
         <v>5154</v>
@@ -60659,7 +60686,7 @@
         <v>6</v>
       </c>
       <c r="D2597" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2597" t="s" s="3">
         <v>5156</v>
@@ -60676,7 +60703,7 @@
         <v>6</v>
       </c>
       <c r="D2598" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2598" t="s" s="3">
         <v>5158</v>
@@ -60693,7 +60720,7 @@
         <v>6</v>
       </c>
       <c r="D2599" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2599" t="s" s="3">
         <v>5160</v>
@@ -60710,7 +60737,7 @@
         <v>6</v>
       </c>
       <c r="D2600" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2600" t="s" s="3">
         <v>5162</v>
@@ -60727,7 +60754,7 @@
         <v>6</v>
       </c>
       <c r="D2601" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2601" t="s" s="3">
         <v>5164</v>
@@ -60744,7 +60771,7 @@
         <v>6</v>
       </c>
       <c r="D2602" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2602" t="s" s="3">
         <v>5166</v>
@@ -60761,7 +60788,7 @@
         <v>6</v>
       </c>
       <c r="D2603" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2603" t="s" s="3">
         <v>5168</v>
@@ -60778,7 +60805,7 @@
         <v>6</v>
       </c>
       <c r="D2604" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2604" t="s" s="3">
         <v>5170</v>
@@ -60795,7 +60822,7 @@
         <v>6</v>
       </c>
       <c r="D2605" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2605" t="s" s="3">
         <v>5172</v>
@@ -60812,7 +60839,7 @@
         <v>6</v>
       </c>
       <c r="D2606" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2606" t="s" s="3">
         <v>5174</v>
@@ -60829,7 +60856,7 @@
         <v>6</v>
       </c>
       <c r="D2607" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2607" t="s" s="3">
         <v>5176</v>
@@ -60846,7 +60873,7 @@
         <v>6</v>
       </c>
       <c r="D2608" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2608" t="s" s="3">
         <v>5178</v>
@@ -60863,7 +60890,7 @@
         <v>6</v>
       </c>
       <c r="D2609" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2609" t="s" s="3">
         <v>5180</v>
@@ -60880,7 +60907,7 @@
         <v>6</v>
       </c>
       <c r="D2610" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2610" t="s" s="3">
         <v>5182</v>
@@ -60897,7 +60924,7 @@
         <v>6</v>
       </c>
       <c r="D2611" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2611" t="s" s="3">
         <v>5184</v>
@@ -60914,7 +60941,7 @@
         <v>6</v>
       </c>
       <c r="D2612" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2612" t="s" s="3">
         <v>5186</v>
@@ -60931,7 +60958,7 @@
         <v>6</v>
       </c>
       <c r="D2613" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2613" t="s" s="3">
         <v>5188</v>
@@ -60948,7 +60975,7 @@
         <v>6</v>
       </c>
       <c r="D2614" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2614" t="s" s="3">
         <v>5190</v>
@@ -60965,7 +60992,7 @@
         <v>6</v>
       </c>
       <c r="D2615" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2615" t="s" s="3">
         <v>5192</v>
@@ -60982,7 +61009,7 @@
         <v>6</v>
       </c>
       <c r="D2616" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2616" t="s" s="3">
         <v>5194</v>
@@ -60999,7 +61026,7 @@
         <v>6</v>
       </c>
       <c r="D2617" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2617" t="s" s="3">
         <v>5196</v>
@@ -61016,7 +61043,7 @@
         <v>6</v>
       </c>
       <c r="D2618" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2618" t="s" s="3">
         <v>5198</v>
@@ -61033,7 +61060,7 @@
         <v>6</v>
       </c>
       <c r="D2619" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2619" t="s" s="3">
         <v>5200</v>
@@ -61050,7 +61077,7 @@
         <v>6</v>
       </c>
       <c r="D2620" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2620" t="s" s="3">
         <v>5202</v>
@@ -61067,7 +61094,7 @@
         <v>6</v>
       </c>
       <c r="D2621" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2621" t="s" s="3">
         <v>5204</v>
@@ -61084,7 +61111,7 @@
         <v>6</v>
       </c>
       <c r="D2622" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2622" t="s" s="3">
         <v>5206</v>
@@ -61101,7 +61128,7 @@
         <v>6</v>
       </c>
       <c r="D2623" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2623" t="s" s="3">
         <v>5208</v>
@@ -61118,7 +61145,7 @@
         <v>6</v>
       </c>
       <c r="D2624" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2624" t="s" s="3">
         <v>5210</v>
@@ -61135,7 +61162,7 @@
         <v>6</v>
       </c>
       <c r="D2625" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2625" t="s" s="3">
         <v>5212</v>
@@ -61152,7 +61179,7 @@
         <v>6</v>
       </c>
       <c r="D2626" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2626" t="s" s="3">
         <v>5214</v>
@@ -61169,7 +61196,7 @@
         <v>6</v>
       </c>
       <c r="D2627" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2627" t="s" s="3">
         <v>5216</v>
@@ -61186,7 +61213,7 @@
         <v>6</v>
       </c>
       <c r="D2628" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2628" t="s" s="3">
         <v>5218</v>
@@ -61203,7 +61230,7 @@
         <v>6</v>
       </c>
       <c r="D2629" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2629" t="s" s="3">
         <v>5220</v>
@@ -61214,16 +61241,16 @@
         <v>2629.0</v>
       </c>
       <c r="B2630" t="s" s="3">
-        <v>3370</v>
+        <v>5221</v>
       </c>
       <c r="C2630" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2630" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2630" t="s" s="3">
-        <v>5221</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="2631" ht="36.0" customHeight="true">
@@ -61231,16 +61258,16 @@
         <v>2630.0</v>
       </c>
       <c r="B2631" t="s" s="3">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C2631" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2631" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2631" t="s" s="3">
-        <v>5223</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="2632" ht="36.0" customHeight="true">
@@ -61248,16 +61275,16 @@
         <v>2631.0</v>
       </c>
       <c r="B2632" t="s" s="3">
-        <v>5224</v>
+        <v>5225</v>
       </c>
       <c r="C2632" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2632" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2632" t="s" s="3">
-        <v>5225</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="2633" ht="36.0" customHeight="true">
@@ -61265,16 +61292,16 @@
         <v>2632.0</v>
       </c>
       <c r="B2633" t="s" s="3">
-        <v>5226</v>
+        <v>3372</v>
       </c>
       <c r="C2633" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2633" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2633" t="s" s="3">
-        <v>5072</v>
+        <v>5227</v>
       </c>
     </row>
     <row r="2634" ht="36.0" customHeight="true">
@@ -61282,16 +61309,16 @@
         <v>2633.0</v>
       </c>
       <c r="B2634" t="s" s="3">
-        <v>5227</v>
+        <v>5228</v>
       </c>
       <c r="C2634" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2634" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2634" t="s" s="3">
-        <v>5228</v>
+        <v>5229</v>
       </c>
     </row>
     <row r="2635" ht="36.0" customHeight="true">
@@ -61299,16 +61326,16 @@
         <v>2634.0</v>
       </c>
       <c r="B2635" t="s" s="3">
-        <v>5229</v>
+        <v>5230</v>
       </c>
       <c r="C2635" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2635" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2635" t="s" s="3">
-        <v>5230</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="2636" ht="36.0" customHeight="true">
@@ -61316,16 +61343,16 @@
         <v>2635.0</v>
       </c>
       <c r="B2636" t="s" s="3">
-        <v>5231</v>
+        <v>5232</v>
       </c>
       <c r="C2636" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2636" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2636" t="s" s="3">
-        <v>5232</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="2637" ht="36.0" customHeight="true">
@@ -61339,7 +61366,7 @@
         <v>6</v>
       </c>
       <c r="D2637" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2637" t="s" s="3">
         <v>5234</v>
@@ -61356,7 +61383,7 @@
         <v>6</v>
       </c>
       <c r="D2638" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2638" t="s" s="3">
         <v>5236</v>
@@ -61373,7 +61400,7 @@
         <v>6</v>
       </c>
       <c r="D2639" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2639" t="s" s="3">
         <v>5238</v>
@@ -61390,7 +61417,7 @@
         <v>6</v>
       </c>
       <c r="D2640" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2640" t="s" s="3">
         <v>5240</v>
@@ -61404,10 +61431,10 @@
         <v>5241</v>
       </c>
       <c r="C2641" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2641" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2641" t="s" s="3">
         <v>5242</v>
@@ -61421,10 +61448,10 @@
         <v>5243</v>
       </c>
       <c r="C2642" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2642" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2642" t="s" s="3">
         <v>5244</v>
@@ -61438,10 +61465,10 @@
         <v>5245</v>
       </c>
       <c r="C2643" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2643" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2643" t="s" s="3">
         <v>5246</v>
@@ -61458,7 +61485,7 @@
         <v>767</v>
       </c>
       <c r="D2644" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2644" t="s" s="3">
         <v>5248</v>
@@ -61475,7 +61502,7 @@
         <v>767</v>
       </c>
       <c r="D2645" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2645" t="s" s="3">
         <v>5250</v>
@@ -61492,7 +61519,7 @@
         <v>767</v>
       </c>
       <c r="D2646" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2646" t="s" s="3">
         <v>5252</v>
@@ -61509,7 +61536,7 @@
         <v>767</v>
       </c>
       <c r="D2647" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2647" t="s" s="3">
         <v>5254</v>
@@ -61526,7 +61553,7 @@
         <v>767</v>
       </c>
       <c r="D2648" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2648" t="s" s="3">
         <v>5256</v>
@@ -61543,7 +61570,7 @@
         <v>767</v>
       </c>
       <c r="D2649" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2649" t="s" s="3">
         <v>5258</v>
@@ -61560,7 +61587,7 @@
         <v>767</v>
       </c>
       <c r="D2650" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2650" t="s" s="3">
         <v>5260</v>
@@ -61577,7 +61604,7 @@
         <v>767</v>
       </c>
       <c r="D2651" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2651" t="s" s="3">
         <v>5262</v>
@@ -61594,7 +61621,7 @@
         <v>767</v>
       </c>
       <c r="D2652" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2652" t="s" s="3">
         <v>5264</v>
@@ -61611,7 +61638,7 @@
         <v>767</v>
       </c>
       <c r="D2653" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2653" t="s" s="3">
         <v>5266</v>
@@ -61628,7 +61655,7 @@
         <v>767</v>
       </c>
       <c r="D2654" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2654" t="s" s="3">
         <v>5268</v>
@@ -61645,7 +61672,7 @@
         <v>767</v>
       </c>
       <c r="D2655" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2655" t="s" s="3">
         <v>5270</v>
@@ -61662,7 +61689,7 @@
         <v>767</v>
       </c>
       <c r="D2656" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2656" t="s" s="3">
         <v>5272</v>
@@ -61679,7 +61706,7 @@
         <v>767</v>
       </c>
       <c r="D2657" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2657" t="s" s="3">
         <v>5274</v>
@@ -61696,7 +61723,7 @@
         <v>767</v>
       </c>
       <c r="D2658" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2658" t="s" s="3">
         <v>5276</v>
@@ -61713,7 +61740,7 @@
         <v>767</v>
       </c>
       <c r="D2659" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2659" t="s" s="3">
         <v>5278</v>
@@ -61730,7 +61757,7 @@
         <v>767</v>
       </c>
       <c r="D2660" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2660" t="s" s="3">
         <v>5280</v>
@@ -61747,7 +61774,7 @@
         <v>767</v>
       </c>
       <c r="D2661" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2661" t="s" s="3">
         <v>5282</v>
@@ -61764,7 +61791,7 @@
         <v>767</v>
       </c>
       <c r="D2662" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2662" t="s" s="3">
         <v>5284</v>
@@ -61781,7 +61808,7 @@
         <v>767</v>
       </c>
       <c r="D2663" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2663" t="s" s="3">
         <v>5286</v>
@@ -61798,7 +61825,7 @@
         <v>767</v>
       </c>
       <c r="D2664" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2664" t="s" s="3">
         <v>5288</v>
@@ -61815,7 +61842,7 @@
         <v>767</v>
       </c>
       <c r="D2665" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2665" t="s" s="3">
         <v>5290</v>
@@ -61832,7 +61859,7 @@
         <v>767</v>
       </c>
       <c r="D2666" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2666" t="s" s="3">
         <v>5292</v>
@@ -61849,7 +61876,7 @@
         <v>767</v>
       </c>
       <c r="D2667" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2667" t="s" s="3">
         <v>5294</v>
@@ -61866,7 +61893,7 @@
         <v>767</v>
       </c>
       <c r="D2668" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2668" t="s" s="3">
         <v>5296</v>
@@ -61883,7 +61910,7 @@
         <v>767</v>
       </c>
       <c r="D2669" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2669" t="s" s="3">
         <v>5298</v>
@@ -61900,7 +61927,7 @@
         <v>767</v>
       </c>
       <c r="D2670" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2670" t="s" s="3">
         <v>5300</v>
@@ -61917,7 +61944,7 @@
         <v>767</v>
       </c>
       <c r="D2671" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2671" t="s" s="3">
         <v>5302</v>
@@ -61934,7 +61961,7 @@
         <v>767</v>
       </c>
       <c r="D2672" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2672" t="s" s="3">
         <v>5304</v>
@@ -61951,7 +61978,7 @@
         <v>767</v>
       </c>
       <c r="D2673" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2673" t="s" s="3">
         <v>5306</v>
@@ -61968,7 +61995,7 @@
         <v>767</v>
       </c>
       <c r="D2674" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2674" t="s" s="3">
         <v>5308</v>
@@ -61985,7 +62012,7 @@
         <v>767</v>
       </c>
       <c r="D2675" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2675" t="s" s="3">
         <v>5310</v>
@@ -62002,7 +62029,7 @@
         <v>767</v>
       </c>
       <c r="D2676" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2676" t="s" s="3">
         <v>5312</v>
@@ -62019,7 +62046,7 @@
         <v>767</v>
       </c>
       <c r="D2677" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2677" t="s" s="3">
         <v>5314</v>
@@ -62036,7 +62063,7 @@
         <v>767</v>
       </c>
       <c r="D2678" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2678" t="s" s="3">
         <v>5316</v>
@@ -62053,7 +62080,7 @@
         <v>767</v>
       </c>
       <c r="D2679" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2679" t="s" s="3">
         <v>5318</v>
@@ -62070,7 +62097,7 @@
         <v>767</v>
       </c>
       <c r="D2680" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2680" t="s" s="3">
         <v>5320</v>
@@ -62087,7 +62114,7 @@
         <v>767</v>
       </c>
       <c r="D2681" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2681" t="s" s="3">
         <v>5322</v>
@@ -62104,7 +62131,7 @@
         <v>767</v>
       </c>
       <c r="D2682" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2682" t="s" s="3">
         <v>5324</v>
@@ -62121,7 +62148,7 @@
         <v>767</v>
       </c>
       <c r="D2683" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2683" t="s" s="3">
         <v>5326</v>
@@ -62138,7 +62165,7 @@
         <v>767</v>
       </c>
       <c r="D2684" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2684" t="s" s="3">
         <v>5328</v>
@@ -62155,7 +62182,7 @@
         <v>767</v>
       </c>
       <c r="D2685" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2685" t="s" s="3">
         <v>5330</v>
@@ -62172,10 +62199,10 @@
         <v>767</v>
       </c>
       <c r="D2686" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2686" t="s" s="3">
-        <v>5008</v>
+        <v>5332</v>
       </c>
     </row>
     <row r="2687" ht="36.0" customHeight="true">
@@ -62183,16 +62210,16 @@
         <v>2686.0</v>
       </c>
       <c r="B2687" t="s" s="3">
-        <v>5332</v>
+        <v>5333</v>
       </c>
       <c r="C2687" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2687" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2687" t="s" s="3">
-        <v>5333</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="2688" ht="36.0" customHeight="true">
@@ -62200,16 +62227,16 @@
         <v>2687.0</v>
       </c>
       <c r="B2688" t="s" s="3">
-        <v>5334</v>
+        <v>5335</v>
       </c>
       <c r="C2688" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2688" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2688" t="s" s="3">
-        <v>5335</v>
+        <v>5336</v>
       </c>
     </row>
     <row r="2689" ht="36.0" customHeight="true">
@@ -62217,16 +62244,16 @@
         <v>2688.0</v>
       </c>
       <c r="B2689" t="s" s="3">
-        <v>5336</v>
+        <v>5337</v>
       </c>
       <c r="C2689" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2689" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2689" t="s" s="3">
-        <v>5337</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="2690" ht="36.0" customHeight="true">
@@ -62240,7 +62267,7 @@
         <v>767</v>
       </c>
       <c r="D2690" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2690" t="s" s="3">
         <v>5339</v>
@@ -62257,7 +62284,7 @@
         <v>767</v>
       </c>
       <c r="D2691" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2691" t="s" s="3">
         <v>5341</v>
@@ -62274,7 +62301,7 @@
         <v>767</v>
       </c>
       <c r="D2692" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2692" t="s" s="3">
         <v>5343</v>
@@ -62291,7 +62318,7 @@
         <v>767</v>
       </c>
       <c r="D2693" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2693" t="s" s="3">
         <v>5345</v>
@@ -62305,10 +62332,10 @@
         <v>5346</v>
       </c>
       <c r="C2694" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2694" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2694" t="s" s="3">
         <v>5347</v>
@@ -62322,10 +62349,10 @@
         <v>5348</v>
       </c>
       <c r="C2695" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2695" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2695" t="s" s="3">
         <v>5349</v>
@@ -62336,16 +62363,16 @@
         <v>2695.0</v>
       </c>
       <c r="B2696" t="s" s="3">
-        <v>5327</v>
+        <v>5350</v>
       </c>
       <c r="C2696" t="s" s="2">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="D2696" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2696" t="s" s="3">
-        <v>5350</v>
+        <v>5351</v>
       </c>
     </row>
     <row r="2697" ht="36.0" customHeight="true">
@@ -62353,16 +62380,16 @@
         <v>2696.0</v>
       </c>
       <c r="B2697" t="s" s="3">
-        <v>5351</v>
+        <v>5352</v>
       </c>
       <c r="C2697" t="s" s="2">
         <v>986</v>
       </c>
       <c r="D2697" t="s" s="2">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="E2697" t="s" s="3">
-        <v>5352</v>
+        <v>5353</v>
       </c>
     </row>
     <row r="2698" ht="36.0" customHeight="true">
@@ -62370,13 +62397,13 @@
         <v>2697.0</v>
       </c>
       <c r="B2698" t="s" s="3">
-        <v>5353</v>
+        <v>5354</v>
       </c>
       <c r="C2698" t="s" s="2">
-        <v>6</v>
+        <v>986</v>
       </c>
       <c r="D2698" t="s" s="2">
-        <v>5354</v>
+        <v>4961</v>
       </c>
       <c r="E2698" t="s" s="3">
         <v>5355</v>
@@ -62387,16 +62414,16 @@
         <v>2698.0</v>
       </c>
       <c r="B2699" t="s" s="3">
+        <v>5333</v>
+      </c>
+      <c r="C2699" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2699" t="s" s="2">
+        <v>4961</v>
+      </c>
+      <c r="E2699" t="s" s="3">
         <v>5356</v>
-      </c>
-      <c r="C2699" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2699" t="s" s="2">
-        <v>5354</v>
-      </c>
-      <c r="E2699" t="s" s="3">
-        <v>5357</v>
       </c>
     </row>
     <row r="2700" ht="36.0" customHeight="true">
@@ -62404,16 +62431,16 @@
         <v>2699.0</v>
       </c>
       <c r="B2700" t="s" s="3">
+        <v>5357</v>
+      </c>
+      <c r="C2700" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D2700" t="s" s="2">
+        <v>4961</v>
+      </c>
+      <c r="E2700" t="s" s="3">
         <v>5358</v>
-      </c>
-      <c r="C2700" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2700" t="s" s="2">
-        <v>5354</v>
-      </c>
-      <c r="E2700" t="s" s="3">
-        <v>5359</v>
       </c>
     </row>
     <row r="2701" ht="36.0" customHeight="true">
@@ -62421,13 +62448,13 @@
         <v>2700.0</v>
       </c>
       <c r="B2701" t="s" s="3">
+        <v>5359</v>
+      </c>
+      <c r="C2701" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2701" t="s" s="2">
         <v>5360</v>
-      </c>
-      <c r="C2701" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2701" t="s" s="2">
-        <v>5354</v>
       </c>
       <c r="E2701" t="s" s="3">
         <v>5361</v>
@@ -62444,7 +62471,7 @@
         <v>6</v>
       </c>
       <c r="D2702" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2702" t="s" s="3">
         <v>5363</v>
@@ -62461,7 +62488,7 @@
         <v>6</v>
       </c>
       <c r="D2703" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2703" t="s" s="3">
         <v>5365</v>
@@ -62478,7 +62505,7 @@
         <v>6</v>
       </c>
       <c r="D2704" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2704" t="s" s="3">
         <v>5367</v>
@@ -62495,7 +62522,7 @@
         <v>6</v>
       </c>
       <c r="D2705" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2705" t="s" s="3">
         <v>5369</v>
@@ -62512,7 +62539,7 @@
         <v>6</v>
       </c>
       <c r="D2706" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2706" t="s" s="3">
         <v>5371</v>
@@ -62529,7 +62556,7 @@
         <v>6</v>
       </c>
       <c r="D2707" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2707" t="s" s="3">
         <v>5373</v>
@@ -62546,7 +62573,7 @@
         <v>6</v>
       </c>
       <c r="D2708" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2708" t="s" s="3">
         <v>5375</v>
@@ -62563,7 +62590,7 @@
         <v>6</v>
       </c>
       <c r="D2709" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2709" t="s" s="3">
         <v>5377</v>
@@ -62580,7 +62607,7 @@
         <v>6</v>
       </c>
       <c r="D2710" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2710" t="s" s="3">
         <v>5379</v>
@@ -62597,7 +62624,7 @@
         <v>6</v>
       </c>
       <c r="D2711" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2711" t="s" s="3">
         <v>5381</v>
@@ -62614,7 +62641,7 @@
         <v>6</v>
       </c>
       <c r="D2712" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2712" t="s" s="3">
         <v>5383</v>
@@ -62631,7 +62658,7 @@
         <v>6</v>
       </c>
       <c r="D2713" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2713" t="s" s="3">
         <v>5385</v>
@@ -62648,7 +62675,7 @@
         <v>6</v>
       </c>
       <c r="D2714" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2714" t="s" s="3">
         <v>5387</v>
@@ -62665,7 +62692,7 @@
         <v>6</v>
       </c>
       <c r="D2715" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2715" t="s" s="3">
         <v>5389</v>
@@ -62682,7 +62709,7 @@
         <v>6</v>
       </c>
       <c r="D2716" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2716" t="s" s="3">
         <v>5391</v>
@@ -62699,7 +62726,7 @@
         <v>6</v>
       </c>
       <c r="D2717" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2717" t="s" s="3">
         <v>5393</v>
@@ -62716,7 +62743,7 @@
         <v>6</v>
       </c>
       <c r="D2718" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2718" t="s" s="3">
         <v>5395</v>
@@ -62733,7 +62760,7 @@
         <v>6</v>
       </c>
       <c r="D2719" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2719" t="s" s="3">
         <v>5397</v>
@@ -62750,7 +62777,7 @@
         <v>6</v>
       </c>
       <c r="D2720" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2720" t="s" s="3">
         <v>5399</v>
@@ -62767,7 +62794,7 @@
         <v>6</v>
       </c>
       <c r="D2721" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2721" t="s" s="3">
         <v>5401</v>
@@ -62784,7 +62811,7 @@
         <v>6</v>
       </c>
       <c r="D2722" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2722" t="s" s="3">
         <v>5403</v>
@@ -62801,7 +62828,7 @@
         <v>6</v>
       </c>
       <c r="D2723" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2723" t="s" s="3">
         <v>5405</v>
@@ -62818,7 +62845,7 @@
         <v>6</v>
       </c>
       <c r="D2724" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2724" t="s" s="3">
         <v>5407</v>
@@ -62835,7 +62862,7 @@
         <v>6</v>
       </c>
       <c r="D2725" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2725" t="s" s="3">
         <v>5409</v>
@@ -62852,7 +62879,7 @@
         <v>6</v>
       </c>
       <c r="D2726" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2726" t="s" s="3">
         <v>5411</v>
@@ -62869,7 +62896,7 @@
         <v>6</v>
       </c>
       <c r="D2727" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2727" t="s" s="3">
         <v>5413</v>
@@ -62886,7 +62913,7 @@
         <v>6</v>
       </c>
       <c r="D2728" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2728" t="s" s="3">
         <v>5415</v>
@@ -62903,7 +62930,7 @@
         <v>6</v>
       </c>
       <c r="D2729" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2729" t="s" s="3">
         <v>5417</v>
@@ -62920,7 +62947,7 @@
         <v>6</v>
       </c>
       <c r="D2730" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2730" t="s" s="3">
         <v>5419</v>
@@ -62937,7 +62964,7 @@
         <v>6</v>
       </c>
       <c r="D2731" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2731" t="s" s="3">
         <v>5421</v>
@@ -62954,7 +62981,7 @@
         <v>6</v>
       </c>
       <c r="D2732" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2732" t="s" s="3">
         <v>5423</v>
@@ -62968,13 +62995,13 @@
         <v>5424</v>
       </c>
       <c r="C2733" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2733" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2733" t="s" s="3">
-        <v>5399</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="2734" ht="36.0" customHeight="true">
@@ -62982,16 +63009,16 @@
         <v>2733.0</v>
       </c>
       <c r="B2734" t="s" s="3">
-        <v>5425</v>
+        <v>5426</v>
       </c>
       <c r="C2734" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2734" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2734" t="s" s="3">
-        <v>5426</v>
+        <v>5427</v>
       </c>
     </row>
     <row r="2735" ht="36.0" customHeight="true">
@@ -62999,16 +63026,16 @@
         <v>2734.0</v>
       </c>
       <c r="B2735" t="s" s="3">
-        <v>5427</v>
+        <v>5428</v>
       </c>
       <c r="C2735" t="s" s="2">
-        <v>767</v>
+        <v>6</v>
       </c>
       <c r="D2735" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2735" t="s" s="3">
-        <v>5428</v>
+        <v>5429</v>
       </c>
     </row>
     <row r="2736" ht="36.0" customHeight="true">
@@ -63016,16 +63043,16 @@
         <v>2735.0</v>
       </c>
       <c r="B2736" t="s" s="3">
-        <v>5429</v>
+        <v>5430</v>
       </c>
       <c r="C2736" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2736" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2736" t="s" s="3">
-        <v>5430</v>
+        <v>5405</v>
       </c>
     </row>
     <row r="2737" ht="36.0" customHeight="true">
@@ -63039,7 +63066,7 @@
         <v>767</v>
       </c>
       <c r="D2737" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2737" t="s" s="3">
         <v>5432</v>
@@ -63056,7 +63083,7 @@
         <v>767</v>
       </c>
       <c r="D2738" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2738" t="s" s="3">
         <v>5434</v>
@@ -63067,16 +63094,16 @@
         <v>2738.0</v>
       </c>
       <c r="B2739" t="s" s="3">
+        <v>5435</v>
+      </c>
+      <c r="C2739" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="D2739" t="s" s="2">
         <v>5360</v>
       </c>
-      <c r="C2739" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="D2739" t="s" s="2">
-        <v>5354</v>
-      </c>
       <c r="E2739" t="s" s="3">
-        <v>5435</v>
+        <v>5436</v>
       </c>
     </row>
     <row r="2740" ht="36.0" customHeight="true">
@@ -63084,16 +63111,16 @@
         <v>2739.0</v>
       </c>
       <c r="B2740" t="s" s="3">
-        <v>5436</v>
+        <v>5437</v>
       </c>
       <c r="C2740" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2740" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2740" t="s" s="3">
-        <v>5437</v>
+        <v>5438</v>
       </c>
     </row>
     <row r="2741" ht="36.0" customHeight="true">
@@ -63101,16 +63128,16 @@
         <v>2740.0</v>
       </c>
       <c r="B2741" t="s" s="3">
-        <v>5438</v>
+        <v>5439</v>
       </c>
       <c r="C2741" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2741" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2741" t="s" s="3">
-        <v>5439</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="2742" ht="36.0" customHeight="true">
@@ -63118,13 +63145,13 @@
         <v>2741.0</v>
       </c>
       <c r="B2742" t="s" s="3">
-        <v>5440</v>
+        <v>5366</v>
       </c>
       <c r="C2742" t="s" s="2">
         <v>767</v>
       </c>
       <c r="D2742" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2742" t="s" s="3">
         <v>5441</v>
@@ -63141,7 +63168,7 @@
         <v>767</v>
       </c>
       <c r="D2743" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2743" t="s" s="3">
         <v>5443</v>
@@ -63158,7 +63185,7 @@
         <v>767</v>
       </c>
       <c r="D2744" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2744" t="s" s="3">
         <v>5445</v>
@@ -63175,7 +63202,7 @@
         <v>767</v>
       </c>
       <c r="D2745" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2745" t="s" s="3">
         <v>5447</v>
@@ -63192,7 +63219,7 @@
         <v>767</v>
       </c>
       <c r="D2746" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2746" t="s" s="3">
         <v>5449</v>
@@ -63209,7 +63236,7 @@
         <v>767</v>
       </c>
       <c r="D2747" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2747" t="s" s="3">
         <v>5451</v>
@@ -63226,7 +63253,7 @@
         <v>767</v>
       </c>
       <c r="D2748" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2748" t="s" s="3">
         <v>5453</v>
@@ -63243,7 +63270,7 @@
         <v>767</v>
       </c>
       <c r="D2749" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2749" t="s" s="3">
         <v>5455</v>
@@ -63260,7 +63287,7 @@
         <v>767</v>
       </c>
       <c r="D2750" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2750" t="s" s="3">
         <v>5457</v>
@@ -63277,7 +63304,7 @@
         <v>767</v>
       </c>
       <c r="D2751" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2751" t="s" s="3">
         <v>5459</v>
@@ -63294,7 +63321,7 @@
         <v>767</v>
       </c>
       <c r="D2752" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2752" t="s" s="3">
         <v>5461</v>
@@ -63311,7 +63338,7 @@
         <v>767</v>
       </c>
       <c r="D2753" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2753" t="s" s="3">
         <v>5463</v>
@@ -63328,7 +63355,7 @@
         <v>767</v>
       </c>
       <c r="D2754" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2754" t="s" s="3">
         <v>5465</v>
@@ -63345,10 +63372,78 @@
         <v>767</v>
       </c>
       <c r="D2755" t="s" s="2">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="E2755" t="s" s="3">
         <v>5467</v>
+      </c>
+    </row>
+    <row r="2756" ht="36.0" customHeight="true">
+      <c r="A2756" t="n" s="2">
+        <v>2755.0</v>
+      </c>
+      <c r="B2756" t="s" s="3">
+        <v>5468</v>
+      </c>
+      <c r="C2756" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="D2756" t="s" s="2">
+        <v>5360</v>
+      </c>
+      <c r="E2756" t="s" s="3">
+        <v>5469</v>
+      </c>
+    </row>
+    <row r="2757" ht="36.0" customHeight="true">
+      <c r="A2757" t="n" s="2">
+        <v>2756.0</v>
+      </c>
+      <c r="B2757" t="s" s="3">
+        <v>5470</v>
+      </c>
+      <c r="C2757" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="D2757" t="s" s="2">
+        <v>5360</v>
+      </c>
+      <c r="E2757" t="s" s="3">
+        <v>5471</v>
+      </c>
+    </row>
+    <row r="2758" ht="36.0" customHeight="true">
+      <c r="A2758" t="n" s="2">
+        <v>2757.0</v>
+      </c>
+      <c r="B2758" t="s" s="3">
+        <v>5472</v>
+      </c>
+      <c r="C2758" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="D2758" t="s" s="2">
+        <v>5360</v>
+      </c>
+      <c r="E2758" t="s" s="3">
+        <v>5473</v>
+      </c>
+    </row>
+    <row r="2759" ht="36.0" customHeight="true">
+      <c r="A2759" t="n" s="2">
+        <v>2758.0</v>
+      </c>
+      <c r="B2759" t="s" s="3">
+        <v>5474</v>
+      </c>
+      <c r="C2759" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="D2759" t="s" s="2">
+        <v>5475</v>
+      </c>
+      <c r="E2759" t="s" s="3">
+        <v>5476</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11205" uniqueCount="5556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11209" uniqueCount="5558">
   <si>
     <t>연번</t>
   </si>
@@ -1052,12 +1052,12 @@
     <t>사루</t>
   </si>
   <si>
+    <t>서울특별시 중구 동호로12길 53(1층 신당동)</t>
+  </si>
+  <si>
     <t>서울특별시 중구 장충단로7길 24(1층 쌍림동)</t>
   </si>
   <si>
-    <t>서울특별시 중구 동호로12길 53(1층 신당동)</t>
-  </si>
-  <si>
     <t>사직커피</t>
   </si>
   <si>
@@ -1541,12 +1541,12 @@
     <t>오르노 합정점</t>
   </si>
   <si>
+    <t>서울특별시 마포구 월드컵로3길 14(지1층 B113,114호 합정동, 마포 한강 2차 푸르지오)</t>
+  </si>
+  <si>
     <t>서울특별시 마포구 월드컵로3길 14(지1층 B149,B150,B151, B152,B153,B154호 합정동, 마포 한강 2차 푸르지오)</t>
   </si>
   <si>
-    <t>서울특별시 마포구 월드컵로3길 14(지1층 B113,114호 합정동, 마포 한강 2차 푸르지오)</t>
-  </si>
-  <si>
     <t>오베뉴 한남</t>
   </si>
   <si>
@@ -5996,12 +5996,12 @@
     <t>조선백호</t>
   </si>
   <si>
+    <t>인천광역시 제물포구 개항로96번길 11(1,2층 경동)</t>
+  </si>
+  <si>
     <t>인천광역시 제물포구 개항로96번길 11(1층 경동)</t>
   </si>
   <si>
-    <t>인천광역시 제물포구 개항로96번길 11(1,2층 경동)</t>
-  </si>
-  <si>
     <t>주윤 상차림</t>
   </si>
   <si>
@@ -6215,12 +6215,12 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 영종구 백운로 510(2동 1,2층 운북동)</t>
   </si>
   <si>
-    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
-  </si>
-  <si>
     <t>까페마인</t>
   </si>
   <si>
@@ -14712,6 +14712,12 @@
   </si>
   <si>
     <t>제주특별자치도 제주시 서부두길 22(1~3층 제4호 건입동)</t>
+  </si>
+  <si>
+    <t>오늘이크리스마스라면 사진관카페</t>
+  </si>
+  <si>
+    <t>제주특별자치도 서귀포시 성산읍 일주동로5154번길 5(1층)</t>
   </si>
   <si>
     <t>오롬마르</t>
@@ -59084,7 +59090,7 @@
         <v>4938</v>
       </c>
       <c r="C2489" t="s" s="2">
-        <v>792</v>
+        <v>6</v>
       </c>
       <c r="D2489" t="s" s="2">
         <v>4828</v>
@@ -59730,7 +59736,7 @@
         <v>5014</v>
       </c>
       <c r="C2527" t="s" s="2">
-        <v>1011</v>
+        <v>792</v>
       </c>
       <c r="D2527" t="s" s="2">
         <v>4828</v>
@@ -59866,13 +59872,13 @@
         <v>5030</v>
       </c>
       <c r="C2535" t="s" s="2">
-        <v>6</v>
+        <v>1011</v>
       </c>
       <c r="D2535" t="s" s="2">
+        <v>4828</v>
+      </c>
+      <c r="E2535" t="s" s="3">
         <v>5031</v>
-      </c>
-      <c r="E2535" t="s" s="3">
-        <v>5032</v>
       </c>
     </row>
     <row r="2536" ht="36.0" customHeight="true">
@@ -59880,13 +59886,13 @@
         <v>2535.0</v>
       </c>
       <c r="B2536" t="s" s="3">
+        <v>5032</v>
+      </c>
+      <c r="C2536" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2536" t="s" s="2">
         <v>5033</v>
-      </c>
-      <c r="C2536" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2536" t="s" s="2">
-        <v>5031</v>
       </c>
       <c r="E2536" t="s" s="3">
         <v>5034</v>
@@ -59903,7 +59909,7 @@
         <v>6</v>
       </c>
       <c r="D2537" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2537" t="s" s="3">
         <v>5036</v>
@@ -59920,7 +59926,7 @@
         <v>6</v>
       </c>
       <c r="D2538" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2538" t="s" s="3">
         <v>5038</v>
@@ -59937,7 +59943,7 @@
         <v>6</v>
       </c>
       <c r="D2539" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2539" t="s" s="3">
         <v>5040</v>
@@ -59954,7 +59960,7 @@
         <v>6</v>
       </c>
       <c r="D2540" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2540" t="s" s="3">
         <v>5042</v>
@@ -59971,7 +59977,7 @@
         <v>6</v>
       </c>
       <c r="D2541" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2541" t="s" s="3">
         <v>5044</v>
@@ -59988,7 +59994,7 @@
         <v>6</v>
       </c>
       <c r="D2542" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2542" t="s" s="3">
         <v>5046</v>
@@ -60005,7 +60011,7 @@
         <v>6</v>
       </c>
       <c r="D2543" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2543" t="s" s="3">
         <v>5048</v>
@@ -60022,7 +60028,7 @@
         <v>6</v>
       </c>
       <c r="D2544" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2544" t="s" s="3">
         <v>5050</v>
@@ -60039,7 +60045,7 @@
         <v>6</v>
       </c>
       <c r="D2545" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2545" t="s" s="3">
         <v>5052</v>
@@ -60056,7 +60062,7 @@
         <v>6</v>
       </c>
       <c r="D2546" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2546" t="s" s="3">
         <v>5054</v>
@@ -60073,7 +60079,7 @@
         <v>6</v>
       </c>
       <c r="D2547" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2547" t="s" s="3">
         <v>5056</v>
@@ -60090,7 +60096,7 @@
         <v>6</v>
       </c>
       <c r="D2548" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2548" t="s" s="3">
         <v>5058</v>
@@ -60107,7 +60113,7 @@
         <v>6</v>
       </c>
       <c r="D2549" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2549" t="s" s="3">
         <v>5060</v>
@@ -60124,7 +60130,7 @@
         <v>6</v>
       </c>
       <c r="D2550" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2550" t="s" s="3">
         <v>5062</v>
@@ -60141,7 +60147,7 @@
         <v>6</v>
       </c>
       <c r="D2551" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2551" t="s" s="3">
         <v>5064</v>
@@ -60158,7 +60164,7 @@
         <v>6</v>
       </c>
       <c r="D2552" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2552" t="s" s="3">
         <v>5066</v>
@@ -60175,7 +60181,7 @@
         <v>6</v>
       </c>
       <c r="D2553" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2553" t="s" s="3">
         <v>5068</v>
@@ -60192,7 +60198,7 @@
         <v>6</v>
       </c>
       <c r="D2554" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2554" t="s" s="3">
         <v>5070</v>
@@ -60209,7 +60215,7 @@
         <v>6</v>
       </c>
       <c r="D2555" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2555" t="s" s="3">
         <v>5072</v>
@@ -60226,7 +60232,7 @@
         <v>6</v>
       </c>
       <c r="D2556" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2556" t="s" s="3">
         <v>5074</v>
@@ -60243,7 +60249,7 @@
         <v>6</v>
       </c>
       <c r="D2557" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2557" t="s" s="3">
         <v>5076</v>
@@ -60260,7 +60266,7 @@
         <v>6</v>
       </c>
       <c r="D2558" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2558" t="s" s="3">
         <v>5078</v>
@@ -60277,7 +60283,7 @@
         <v>6</v>
       </c>
       <c r="D2559" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2559" t="s" s="3">
         <v>5080</v>
@@ -60294,7 +60300,7 @@
         <v>6</v>
       </c>
       <c r="D2560" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2560" t="s" s="3">
         <v>5082</v>
@@ -60311,7 +60317,7 @@
         <v>6</v>
       </c>
       <c r="D2561" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2561" t="s" s="3">
         <v>5084</v>
@@ -60328,7 +60334,7 @@
         <v>6</v>
       </c>
       <c r="D2562" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2562" t="s" s="3">
         <v>5086</v>
@@ -60345,7 +60351,7 @@
         <v>6</v>
       </c>
       <c r="D2563" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2563" t="s" s="3">
         <v>5088</v>
@@ -60362,7 +60368,7 @@
         <v>6</v>
       </c>
       <c r="D2564" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2564" t="s" s="3">
         <v>5090</v>
@@ -60379,7 +60385,7 @@
         <v>6</v>
       </c>
       <c r="D2565" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2565" t="s" s="3">
         <v>5092</v>
@@ -60396,7 +60402,7 @@
         <v>6</v>
       </c>
       <c r="D2566" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2566" t="s" s="3">
         <v>5094</v>
@@ -60413,7 +60419,7 @@
         <v>6</v>
       </c>
       <c r="D2567" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2567" t="s" s="3">
         <v>5096</v>
@@ -60430,7 +60436,7 @@
         <v>6</v>
       </c>
       <c r="D2568" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2568" t="s" s="3">
         <v>5098</v>
@@ -60447,7 +60453,7 @@
         <v>6</v>
       </c>
       <c r="D2569" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2569" t="s" s="3">
         <v>5100</v>
@@ -60464,7 +60470,7 @@
         <v>6</v>
       </c>
       <c r="D2570" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2570" t="s" s="3">
         <v>5102</v>
@@ -60481,7 +60487,7 @@
         <v>6</v>
       </c>
       <c r="D2571" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2571" t="s" s="3">
         <v>5104</v>
@@ -60498,7 +60504,7 @@
         <v>6</v>
       </c>
       <c r="D2572" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2572" t="s" s="3">
         <v>5106</v>
@@ -60515,7 +60521,7 @@
         <v>6</v>
       </c>
       <c r="D2573" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2573" t="s" s="3">
         <v>5108</v>
@@ -60532,7 +60538,7 @@
         <v>6</v>
       </c>
       <c r="D2574" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2574" t="s" s="3">
         <v>5110</v>
@@ -60549,7 +60555,7 @@
         <v>6</v>
       </c>
       <c r="D2575" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2575" t="s" s="3">
         <v>5112</v>
@@ -60566,7 +60572,7 @@
         <v>6</v>
       </c>
       <c r="D2576" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2576" t="s" s="3">
         <v>5114</v>
@@ -60583,7 +60589,7 @@
         <v>6</v>
       </c>
       <c r="D2577" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2577" t="s" s="3">
         <v>5116</v>
@@ -60600,7 +60606,7 @@
         <v>6</v>
       </c>
       <c r="D2578" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2578" t="s" s="3">
         <v>5118</v>
@@ -60617,7 +60623,7 @@
         <v>6</v>
       </c>
       <c r="D2579" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2579" t="s" s="3">
         <v>5120</v>
@@ -60634,7 +60640,7 @@
         <v>6</v>
       </c>
       <c r="D2580" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2580" t="s" s="3">
         <v>5122</v>
@@ -60651,7 +60657,7 @@
         <v>6</v>
       </c>
       <c r="D2581" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2581" t="s" s="3">
         <v>5124</v>
@@ -60668,7 +60674,7 @@
         <v>6</v>
       </c>
       <c r="D2582" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2582" t="s" s="3">
         <v>5126</v>
@@ -60685,7 +60691,7 @@
         <v>6</v>
       </c>
       <c r="D2583" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2583" t="s" s="3">
         <v>5128</v>
@@ -60702,7 +60708,7 @@
         <v>6</v>
       </c>
       <c r="D2584" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2584" t="s" s="3">
         <v>5130</v>
@@ -60719,7 +60725,7 @@
         <v>6</v>
       </c>
       <c r="D2585" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2585" t="s" s="3">
         <v>5132</v>
@@ -60736,7 +60742,7 @@
         <v>6</v>
       </c>
       <c r="D2586" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2586" t="s" s="3">
         <v>5134</v>
@@ -60753,7 +60759,7 @@
         <v>6</v>
       </c>
       <c r="D2587" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2587" t="s" s="3">
         <v>5136</v>
@@ -60770,7 +60776,7 @@
         <v>6</v>
       </c>
       <c r="D2588" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2588" t="s" s="3">
         <v>5138</v>
@@ -60787,7 +60793,7 @@
         <v>6</v>
       </c>
       <c r="D2589" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2589" t="s" s="3">
         <v>5140</v>
@@ -60804,7 +60810,7 @@
         <v>6</v>
       </c>
       <c r="D2590" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2590" t="s" s="3">
         <v>5142</v>
@@ -60821,7 +60827,7 @@
         <v>6</v>
       </c>
       <c r="D2591" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2591" t="s" s="3">
         <v>5144</v>
@@ -60838,7 +60844,7 @@
         <v>6</v>
       </c>
       <c r="D2592" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2592" t="s" s="3">
         <v>5146</v>
@@ -60855,7 +60861,7 @@
         <v>6</v>
       </c>
       <c r="D2593" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2593" t="s" s="3">
         <v>5148</v>
@@ -60872,7 +60878,7 @@
         <v>6</v>
       </c>
       <c r="D2594" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2594" t="s" s="3">
         <v>5150</v>
@@ -60889,7 +60895,7 @@
         <v>6</v>
       </c>
       <c r="D2595" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2595" t="s" s="3">
         <v>5152</v>
@@ -60906,7 +60912,7 @@
         <v>6</v>
       </c>
       <c r="D2596" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2596" t="s" s="3">
         <v>5154</v>
@@ -60923,7 +60929,7 @@
         <v>6</v>
       </c>
       <c r="D2597" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2597" t="s" s="3">
         <v>5156</v>
@@ -60940,7 +60946,7 @@
         <v>6</v>
       </c>
       <c r="D2598" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2598" t="s" s="3">
         <v>5158</v>
@@ -60957,7 +60963,7 @@
         <v>6</v>
       </c>
       <c r="D2599" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2599" t="s" s="3">
         <v>5160</v>
@@ -60974,7 +60980,7 @@
         <v>6</v>
       </c>
       <c r="D2600" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2600" t="s" s="3">
         <v>5162</v>
@@ -60991,7 +60997,7 @@
         <v>6</v>
       </c>
       <c r="D2601" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2601" t="s" s="3">
         <v>5164</v>
@@ -61008,7 +61014,7 @@
         <v>6</v>
       </c>
       <c r="D2602" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2602" t="s" s="3">
         <v>5166</v>
@@ -61025,7 +61031,7 @@
         <v>6</v>
       </c>
       <c r="D2603" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2603" t="s" s="3">
         <v>5168</v>
@@ -61042,7 +61048,7 @@
         <v>6</v>
       </c>
       <c r="D2604" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2604" t="s" s="3">
         <v>5170</v>
@@ -61059,7 +61065,7 @@
         <v>6</v>
       </c>
       <c r="D2605" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2605" t="s" s="3">
         <v>5172</v>
@@ -61076,7 +61082,7 @@
         <v>6</v>
       </c>
       <c r="D2606" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2606" t="s" s="3">
         <v>5174</v>
@@ -61093,7 +61099,7 @@
         <v>6</v>
       </c>
       <c r="D2607" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2607" t="s" s="3">
         <v>5176</v>
@@ -61110,7 +61116,7 @@
         <v>6</v>
       </c>
       <c r="D2608" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2608" t="s" s="3">
         <v>5178</v>
@@ -61127,10 +61133,10 @@
         <v>6</v>
       </c>
       <c r="D2609" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2609" t="s" s="3">
-        <v>5148</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="2610" ht="36.0" customHeight="true">
@@ -61138,16 +61144,16 @@
         <v>2609.0</v>
       </c>
       <c r="B2610" t="s" s="3">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="C2610" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2610" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2610" t="s" s="3">
-        <v>5181</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="2611" ht="36.0" customHeight="true">
@@ -61161,7 +61167,7 @@
         <v>6</v>
       </c>
       <c r="D2611" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2611" t="s" s="3">
         <v>5183</v>
@@ -61178,7 +61184,7 @@
         <v>6</v>
       </c>
       <c r="D2612" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2612" t="s" s="3">
         <v>5185</v>
@@ -61195,7 +61201,7 @@
         <v>6</v>
       </c>
       <c r="D2613" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2613" t="s" s="3">
         <v>5187</v>
@@ -61212,7 +61218,7 @@
         <v>6</v>
       </c>
       <c r="D2614" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2614" t="s" s="3">
         <v>5189</v>
@@ -61229,7 +61235,7 @@
         <v>6</v>
       </c>
       <c r="D2615" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2615" t="s" s="3">
         <v>5191</v>
@@ -61246,7 +61252,7 @@
         <v>6</v>
       </c>
       <c r="D2616" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2616" t="s" s="3">
         <v>5193</v>
@@ -61263,10 +61269,10 @@
         <v>6</v>
       </c>
       <c r="D2617" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2617" t="s" s="3">
-        <v>5110</v>
+        <v>5195</v>
       </c>
     </row>
     <row r="2618" ht="36.0" customHeight="true">
@@ -61274,16 +61280,16 @@
         <v>2617.0</v>
       </c>
       <c r="B2618" t="s" s="3">
-        <v>4180</v>
+        <v>5196</v>
       </c>
       <c r="C2618" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2618" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2618" t="s" s="3">
-        <v>5195</v>
+        <v>5112</v>
       </c>
     </row>
     <row r="2619" ht="36.0" customHeight="true">
@@ -61291,16 +61297,16 @@
         <v>2618.0</v>
       </c>
       <c r="B2619" t="s" s="3">
-        <v>5196</v>
+        <v>4180</v>
       </c>
       <c r="C2619" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2619" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2619" t="s" s="3">
-        <v>5148</v>
+        <v>5197</v>
       </c>
     </row>
     <row r="2620" ht="36.0" customHeight="true">
@@ -61308,16 +61314,16 @@
         <v>2619.0</v>
       </c>
       <c r="B2620" t="s" s="3">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="C2620" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2620" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2620" t="s" s="3">
-        <v>5198</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="2621" ht="36.0" customHeight="true">
@@ -61331,7 +61337,7 @@
         <v>6</v>
       </c>
       <c r="D2621" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2621" t="s" s="3">
         <v>5200</v>
@@ -61348,7 +61354,7 @@
         <v>6</v>
       </c>
       <c r="D2622" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2622" t="s" s="3">
         <v>5202</v>
@@ -61365,7 +61371,7 @@
         <v>6</v>
       </c>
       <c r="D2623" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2623" t="s" s="3">
         <v>5204</v>
@@ -61382,7 +61388,7 @@
         <v>6</v>
       </c>
       <c r="D2624" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2624" t="s" s="3">
         <v>5206</v>
@@ -61399,7 +61405,7 @@
         <v>6</v>
       </c>
       <c r="D2625" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2625" t="s" s="3">
         <v>5208</v>
@@ -61416,7 +61422,7 @@
         <v>6</v>
       </c>
       <c r="D2626" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2626" t="s" s="3">
         <v>5210</v>
@@ -61433,7 +61439,7 @@
         <v>6</v>
       </c>
       <c r="D2627" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2627" t="s" s="3">
         <v>5212</v>
@@ -61450,7 +61456,7 @@
         <v>6</v>
       </c>
       <c r="D2628" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2628" t="s" s="3">
         <v>5214</v>
@@ -61467,7 +61473,7 @@
         <v>6</v>
       </c>
       <c r="D2629" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2629" t="s" s="3">
         <v>5216</v>
@@ -61484,7 +61490,7 @@
         <v>6</v>
       </c>
       <c r="D2630" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2630" t="s" s="3">
         <v>5218</v>
@@ -61501,7 +61507,7 @@
         <v>6</v>
       </c>
       <c r="D2631" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2631" t="s" s="3">
         <v>5220</v>
@@ -61518,7 +61524,7 @@
         <v>6</v>
       </c>
       <c r="D2632" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2632" t="s" s="3">
         <v>5222</v>
@@ -61535,7 +61541,7 @@
         <v>6</v>
       </c>
       <c r="D2633" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2633" t="s" s="3">
         <v>5224</v>
@@ -61552,7 +61558,7 @@
         <v>6</v>
       </c>
       <c r="D2634" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2634" t="s" s="3">
         <v>5226</v>
@@ -61569,7 +61575,7 @@
         <v>6</v>
       </c>
       <c r="D2635" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2635" t="s" s="3">
         <v>5228</v>
@@ -61586,7 +61592,7 @@
         <v>6</v>
       </c>
       <c r="D2636" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2636" t="s" s="3">
         <v>5230</v>
@@ -61603,7 +61609,7 @@
         <v>6</v>
       </c>
       <c r="D2637" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2637" t="s" s="3">
         <v>5232</v>
@@ -61620,7 +61626,7 @@
         <v>6</v>
       </c>
       <c r="D2638" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2638" t="s" s="3">
         <v>5234</v>
@@ -61637,7 +61643,7 @@
         <v>6</v>
       </c>
       <c r="D2639" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2639" t="s" s="3">
         <v>5236</v>
@@ -61654,7 +61660,7 @@
         <v>6</v>
       </c>
       <c r="D2640" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2640" t="s" s="3">
         <v>5238</v>
@@ -61671,7 +61677,7 @@
         <v>6</v>
       </c>
       <c r="D2641" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2641" t="s" s="3">
         <v>5240</v>
@@ -61688,7 +61694,7 @@
         <v>6</v>
       </c>
       <c r="D2642" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2642" t="s" s="3">
         <v>5242</v>
@@ -61705,7 +61711,7 @@
         <v>6</v>
       </c>
       <c r="D2643" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2643" t="s" s="3">
         <v>5244</v>
@@ -61722,7 +61728,7 @@
         <v>6</v>
       </c>
       <c r="D2644" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2644" t="s" s="3">
         <v>5246</v>
@@ -61739,7 +61745,7 @@
         <v>6</v>
       </c>
       <c r="D2645" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2645" t="s" s="3">
         <v>5248</v>
@@ -61756,7 +61762,7 @@
         <v>6</v>
       </c>
       <c r="D2646" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2646" t="s" s="3">
         <v>5250</v>
@@ -61773,7 +61779,7 @@
         <v>6</v>
       </c>
       <c r="D2647" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2647" t="s" s="3">
         <v>5252</v>
@@ -61790,7 +61796,7 @@
         <v>6</v>
       </c>
       <c r="D2648" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2648" t="s" s="3">
         <v>5254</v>
@@ -61807,7 +61813,7 @@
         <v>6</v>
       </c>
       <c r="D2649" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2649" t="s" s="3">
         <v>5256</v>
@@ -61824,7 +61830,7 @@
         <v>6</v>
       </c>
       <c r="D2650" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2650" t="s" s="3">
         <v>5258</v>
@@ -61841,7 +61847,7 @@
         <v>6</v>
       </c>
       <c r="D2651" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2651" t="s" s="3">
         <v>5260</v>
@@ -61858,7 +61864,7 @@
         <v>6</v>
       </c>
       <c r="D2652" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2652" t="s" s="3">
         <v>5262</v>
@@ -61875,7 +61881,7 @@
         <v>6</v>
       </c>
       <c r="D2653" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2653" t="s" s="3">
         <v>5264</v>
@@ -61892,7 +61898,7 @@
         <v>6</v>
       </c>
       <c r="D2654" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2654" t="s" s="3">
         <v>5266</v>
@@ -61909,7 +61915,7 @@
         <v>6</v>
       </c>
       <c r="D2655" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2655" t="s" s="3">
         <v>5268</v>
@@ -61926,7 +61932,7 @@
         <v>6</v>
       </c>
       <c r="D2656" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2656" t="s" s="3">
         <v>5270</v>
@@ -61943,7 +61949,7 @@
         <v>6</v>
       </c>
       <c r="D2657" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2657" t="s" s="3">
         <v>5272</v>
@@ -61960,7 +61966,7 @@
         <v>6</v>
       </c>
       <c r="D2658" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2658" t="s" s="3">
         <v>5274</v>
@@ -61977,7 +61983,7 @@
         <v>6</v>
       </c>
       <c r="D2659" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2659" t="s" s="3">
         <v>5276</v>
@@ -61994,7 +62000,7 @@
         <v>6</v>
       </c>
       <c r="D2660" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2660" t="s" s="3">
         <v>5278</v>
@@ -62011,7 +62017,7 @@
         <v>6</v>
       </c>
       <c r="D2661" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2661" t="s" s="3">
         <v>5280</v>
@@ -62028,7 +62034,7 @@
         <v>6</v>
       </c>
       <c r="D2662" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2662" t="s" s="3">
         <v>5282</v>
@@ -62045,7 +62051,7 @@
         <v>6</v>
       </c>
       <c r="D2663" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2663" t="s" s="3">
         <v>5284</v>
@@ -62062,7 +62068,7 @@
         <v>6</v>
       </c>
       <c r="D2664" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2664" t="s" s="3">
         <v>5286</v>
@@ -62079,7 +62085,7 @@
         <v>6</v>
       </c>
       <c r="D2665" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2665" t="s" s="3">
         <v>5288</v>
@@ -62096,7 +62102,7 @@
         <v>6</v>
       </c>
       <c r="D2666" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2666" t="s" s="3">
         <v>5290</v>
@@ -62113,7 +62119,7 @@
         <v>6</v>
       </c>
       <c r="D2667" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2667" t="s" s="3">
         <v>5292</v>
@@ -62130,7 +62136,7 @@
         <v>6</v>
       </c>
       <c r="D2668" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2668" t="s" s="3">
         <v>5294</v>
@@ -62147,7 +62153,7 @@
         <v>6</v>
       </c>
       <c r="D2669" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2669" t="s" s="3">
         <v>5296</v>
@@ -62164,7 +62170,7 @@
         <v>6</v>
       </c>
       <c r="D2670" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2670" t="s" s="3">
         <v>5298</v>
@@ -62181,7 +62187,7 @@
         <v>6</v>
       </c>
       <c r="D2671" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2671" t="s" s="3">
         <v>5300</v>
@@ -62198,7 +62204,7 @@
         <v>6</v>
       </c>
       <c r="D2672" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2672" t="s" s="3">
         <v>5302</v>
@@ -62215,7 +62221,7 @@
         <v>6</v>
       </c>
       <c r="D2673" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2673" t="s" s="3">
         <v>5304</v>
@@ -62226,16 +62232,16 @@
         <v>2673.0</v>
       </c>
       <c r="B2674" t="s" s="3">
-        <v>3439</v>
+        <v>5305</v>
       </c>
       <c r="C2674" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2674" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2674" t="s" s="3">
-        <v>5305</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="2675" ht="36.0" customHeight="true">
@@ -62243,13 +62249,13 @@
         <v>2674.0</v>
       </c>
       <c r="B2675" t="s" s="3">
-        <v>5306</v>
+        <v>3439</v>
       </c>
       <c r="C2675" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2675" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2675" t="s" s="3">
         <v>5307</v>
@@ -62266,7 +62272,7 @@
         <v>6</v>
       </c>
       <c r="D2676" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2676" t="s" s="3">
         <v>5309</v>
@@ -62283,10 +62289,10 @@
         <v>6</v>
       </c>
       <c r="D2677" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2677" t="s" s="3">
-        <v>5152</v>
+        <v>5311</v>
       </c>
     </row>
     <row r="2678" ht="36.0" customHeight="true">
@@ -62294,16 +62300,16 @@
         <v>2677.0</v>
       </c>
       <c r="B2678" t="s" s="3">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="C2678" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2678" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2678" t="s" s="3">
-        <v>5312</v>
+        <v>5154</v>
       </c>
     </row>
     <row r="2679" ht="36.0" customHeight="true">
@@ -62317,7 +62323,7 @@
         <v>6</v>
       </c>
       <c r="D2679" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2679" t="s" s="3">
         <v>5314</v>
@@ -62334,7 +62340,7 @@
         <v>6</v>
       </c>
       <c r="D2680" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2680" t="s" s="3">
         <v>5316</v>
@@ -62351,7 +62357,7 @@
         <v>6</v>
       </c>
       <c r="D2681" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2681" t="s" s="3">
         <v>5318</v>
@@ -62368,7 +62374,7 @@
         <v>6</v>
       </c>
       <c r="D2682" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2682" t="s" s="3">
         <v>5320</v>
@@ -62385,7 +62391,7 @@
         <v>6</v>
       </c>
       <c r="D2683" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2683" t="s" s="3">
         <v>5322</v>
@@ -62402,7 +62408,7 @@
         <v>6</v>
       </c>
       <c r="D2684" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2684" t="s" s="3">
         <v>5324</v>
@@ -62416,10 +62422,10 @@
         <v>5325</v>
       </c>
       <c r="C2685" t="s" s="2">
-        <v>792</v>
+        <v>6</v>
       </c>
       <c r="D2685" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2685" t="s" s="3">
         <v>5326</v>
@@ -62436,7 +62442,7 @@
         <v>792</v>
       </c>
       <c r="D2686" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2686" t="s" s="3">
         <v>5328</v>
@@ -62453,7 +62459,7 @@
         <v>792</v>
       </c>
       <c r="D2687" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2687" t="s" s="3">
         <v>5330</v>
@@ -62470,7 +62476,7 @@
         <v>792</v>
       </c>
       <c r="D2688" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2688" t="s" s="3">
         <v>5332</v>
@@ -62487,7 +62493,7 @@
         <v>792</v>
       </c>
       <c r="D2689" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2689" t="s" s="3">
         <v>5334</v>
@@ -62504,7 +62510,7 @@
         <v>792</v>
       </c>
       <c r="D2690" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2690" t="s" s="3">
         <v>5336</v>
@@ -62521,7 +62527,7 @@
         <v>792</v>
       </c>
       <c r="D2691" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2691" t="s" s="3">
         <v>5338</v>
@@ -62538,7 +62544,7 @@
         <v>792</v>
       </c>
       <c r="D2692" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2692" t="s" s="3">
         <v>5340</v>
@@ -62555,7 +62561,7 @@
         <v>792</v>
       </c>
       <c r="D2693" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2693" t="s" s="3">
         <v>5342</v>
@@ -62572,7 +62578,7 @@
         <v>792</v>
       </c>
       <c r="D2694" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2694" t="s" s="3">
         <v>5344</v>
@@ -62589,7 +62595,7 @@
         <v>792</v>
       </c>
       <c r="D2695" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2695" t="s" s="3">
         <v>5346</v>
@@ -62606,7 +62612,7 @@
         <v>792</v>
       </c>
       <c r="D2696" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2696" t="s" s="3">
         <v>5348</v>
@@ -62623,7 +62629,7 @@
         <v>792</v>
       </c>
       <c r="D2697" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2697" t="s" s="3">
         <v>5350</v>
@@ -62640,7 +62646,7 @@
         <v>792</v>
       </c>
       <c r="D2698" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2698" t="s" s="3">
         <v>5352</v>
@@ -62657,7 +62663,7 @@
         <v>792</v>
       </c>
       <c r="D2699" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2699" t="s" s="3">
         <v>5354</v>
@@ -62674,7 +62680,7 @@
         <v>792</v>
       </c>
       <c r="D2700" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2700" t="s" s="3">
         <v>5356</v>
@@ -62691,7 +62697,7 @@
         <v>792</v>
       </c>
       <c r="D2701" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2701" t="s" s="3">
         <v>5358</v>
@@ -62708,7 +62714,7 @@
         <v>792</v>
       </c>
       <c r="D2702" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2702" t="s" s="3">
         <v>5360</v>
@@ -62725,7 +62731,7 @@
         <v>792</v>
       </c>
       <c r="D2703" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2703" t="s" s="3">
         <v>5362</v>
@@ -62742,7 +62748,7 @@
         <v>792</v>
       </c>
       <c r="D2704" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2704" t="s" s="3">
         <v>5364</v>
@@ -62759,7 +62765,7 @@
         <v>792</v>
       </c>
       <c r="D2705" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2705" t="s" s="3">
         <v>5366</v>
@@ -62776,7 +62782,7 @@
         <v>792</v>
       </c>
       <c r="D2706" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2706" t="s" s="3">
         <v>5368</v>
@@ -62793,7 +62799,7 @@
         <v>792</v>
       </c>
       <c r="D2707" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2707" t="s" s="3">
         <v>5370</v>
@@ -62810,7 +62816,7 @@
         <v>792</v>
       </c>
       <c r="D2708" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2708" t="s" s="3">
         <v>5372</v>
@@ -62827,7 +62833,7 @@
         <v>792</v>
       </c>
       <c r="D2709" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2709" t="s" s="3">
         <v>5374</v>
@@ -62844,7 +62850,7 @@
         <v>792</v>
       </c>
       <c r="D2710" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2710" t="s" s="3">
         <v>5376</v>
@@ -62861,7 +62867,7 @@
         <v>792</v>
       </c>
       <c r="D2711" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2711" t="s" s="3">
         <v>5378</v>
@@ -62878,7 +62884,7 @@
         <v>792</v>
       </c>
       <c r="D2712" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2712" t="s" s="3">
         <v>5380</v>
@@ -62895,7 +62901,7 @@
         <v>792</v>
       </c>
       <c r="D2713" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2713" t="s" s="3">
         <v>5382</v>
@@ -62912,7 +62918,7 @@
         <v>792</v>
       </c>
       <c r="D2714" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2714" t="s" s="3">
         <v>5384</v>
@@ -62929,7 +62935,7 @@
         <v>792</v>
       </c>
       <c r="D2715" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2715" t="s" s="3">
         <v>5386</v>
@@ -62946,7 +62952,7 @@
         <v>792</v>
       </c>
       <c r="D2716" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2716" t="s" s="3">
         <v>5388</v>
@@ -62963,7 +62969,7 @@
         <v>792</v>
       </c>
       <c r="D2717" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2717" t="s" s="3">
         <v>5390</v>
@@ -62980,7 +62986,7 @@
         <v>792</v>
       </c>
       <c r="D2718" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2718" t="s" s="3">
         <v>5392</v>
@@ -62997,7 +63003,7 @@
         <v>792</v>
       </c>
       <c r="D2719" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2719" t="s" s="3">
         <v>5394</v>
@@ -63014,7 +63020,7 @@
         <v>792</v>
       </c>
       <c r="D2720" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2720" t="s" s="3">
         <v>5396</v>
@@ -63031,7 +63037,7 @@
         <v>792</v>
       </c>
       <c r="D2721" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2721" t="s" s="3">
         <v>5398</v>
@@ -63048,7 +63054,7 @@
         <v>792</v>
       </c>
       <c r="D2722" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2722" t="s" s="3">
         <v>5400</v>
@@ -63065,7 +63071,7 @@
         <v>792</v>
       </c>
       <c r="D2723" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2723" t="s" s="3">
         <v>5402</v>
@@ -63082,7 +63088,7 @@
         <v>792</v>
       </c>
       <c r="D2724" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2724" t="s" s="3">
         <v>5404</v>
@@ -63099,7 +63105,7 @@
         <v>792</v>
       </c>
       <c r="D2725" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2725" t="s" s="3">
         <v>5406</v>
@@ -63116,7 +63122,7 @@
         <v>792</v>
       </c>
       <c r="D2726" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2726" t="s" s="3">
         <v>5408</v>
@@ -63133,7 +63139,7 @@
         <v>792</v>
       </c>
       <c r="D2727" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2727" t="s" s="3">
         <v>5410</v>
@@ -63150,7 +63156,7 @@
         <v>792</v>
       </c>
       <c r="D2728" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2728" t="s" s="3">
         <v>5412</v>
@@ -63167,7 +63173,7 @@
         <v>792</v>
       </c>
       <c r="D2729" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2729" t="s" s="3">
         <v>5414</v>
@@ -63184,10 +63190,10 @@
         <v>792</v>
       </c>
       <c r="D2730" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2730" t="s" s="3">
-        <v>5088</v>
+        <v>5416</v>
       </c>
     </row>
     <row r="2731" ht="36.0" customHeight="true">
@@ -63195,16 +63201,16 @@
         <v>2730.0</v>
       </c>
       <c r="B2731" t="s" s="3">
-        <v>5416</v>
+        <v>5417</v>
       </c>
       <c r="C2731" t="s" s="2">
         <v>792</v>
       </c>
       <c r="D2731" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2731" t="s" s="3">
-        <v>5417</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="2732" ht="36.0" customHeight="true">
@@ -63218,7 +63224,7 @@
         <v>792</v>
       </c>
       <c r="D2732" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2732" t="s" s="3">
         <v>5419</v>
@@ -63235,7 +63241,7 @@
         <v>792</v>
       </c>
       <c r="D2733" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2733" t="s" s="3">
         <v>5421</v>
@@ -63252,7 +63258,7 @@
         <v>792</v>
       </c>
       <c r="D2734" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2734" t="s" s="3">
         <v>5423</v>
@@ -63269,7 +63275,7 @@
         <v>792</v>
       </c>
       <c r="D2735" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2735" t="s" s="3">
         <v>5425</v>
@@ -63286,7 +63292,7 @@
         <v>792</v>
       </c>
       <c r="D2736" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2736" t="s" s="3">
         <v>5427</v>
@@ -63303,7 +63309,7 @@
         <v>792</v>
       </c>
       <c r="D2737" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2737" t="s" s="3">
         <v>5429</v>
@@ -63317,10 +63323,10 @@
         <v>5430</v>
       </c>
       <c r="C2738" t="s" s="2">
-        <v>1011</v>
+        <v>792</v>
       </c>
       <c r="D2738" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2738" t="s" s="3">
         <v>5431</v>
@@ -63337,7 +63343,7 @@
         <v>1011</v>
       </c>
       <c r="D2739" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2739" t="s" s="3">
         <v>5433</v>
@@ -63348,16 +63354,16 @@
         <v>2739.0</v>
       </c>
       <c r="B2740" t="s" s="3">
-        <v>5411</v>
+        <v>5434</v>
       </c>
       <c r="C2740" t="s" s="2">
         <v>1011</v>
       </c>
       <c r="D2740" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2740" t="s" s="3">
-        <v>5434</v>
+        <v>5435</v>
       </c>
     </row>
     <row r="2741" ht="36.0" customHeight="true">
@@ -63365,13 +63371,13 @@
         <v>2740.0</v>
       </c>
       <c r="B2741" t="s" s="3">
-        <v>5435</v>
+        <v>5413</v>
       </c>
       <c r="C2741" t="s" s="2">
         <v>1011</v>
       </c>
       <c r="D2741" t="s" s="2">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="E2741" t="s" s="3">
         <v>5436</v>
@@ -63385,13 +63391,13 @@
         <v>5437</v>
       </c>
       <c r="C2742" t="s" s="2">
-        <v>6</v>
+        <v>1011</v>
       </c>
       <c r="D2742" t="s" s="2">
+        <v>5033</v>
+      </c>
+      <c r="E2742" t="s" s="3">
         <v>5438</v>
-      </c>
-      <c r="E2742" t="s" s="3">
-        <v>5439</v>
       </c>
     </row>
     <row r="2743" ht="36.0" customHeight="true">
@@ -63399,13 +63405,13 @@
         <v>2742.0</v>
       </c>
       <c r="B2743" t="s" s="3">
+        <v>5439</v>
+      </c>
+      <c r="C2743" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2743" t="s" s="2">
         <v>5440</v>
-      </c>
-      <c r="C2743" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2743" t="s" s="2">
-        <v>5438</v>
       </c>
       <c r="E2743" t="s" s="3">
         <v>5441</v>
@@ -63422,7 +63428,7 @@
         <v>6</v>
       </c>
       <c r="D2744" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2744" t="s" s="3">
         <v>5443</v>
@@ -63439,7 +63445,7 @@
         <v>6</v>
       </c>
       <c r="D2745" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2745" t="s" s="3">
         <v>5445</v>
@@ -63456,7 +63462,7 @@
         <v>6</v>
       </c>
       <c r="D2746" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2746" t="s" s="3">
         <v>5447</v>
@@ -63473,7 +63479,7 @@
         <v>6</v>
       </c>
       <c r="D2747" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2747" t="s" s="3">
         <v>5449</v>
@@ -63490,7 +63496,7 @@
         <v>6</v>
       </c>
       <c r="D2748" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2748" t="s" s="3">
         <v>5451</v>
@@ -63507,7 +63513,7 @@
         <v>6</v>
       </c>
       <c r="D2749" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2749" t="s" s="3">
         <v>5453</v>
@@ -63524,7 +63530,7 @@
         <v>6</v>
       </c>
       <c r="D2750" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2750" t="s" s="3">
         <v>5455</v>
@@ -63541,7 +63547,7 @@
         <v>6</v>
       </c>
       <c r="D2751" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2751" t="s" s="3">
         <v>5457</v>
@@ -63558,7 +63564,7 @@
         <v>6</v>
       </c>
       <c r="D2752" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2752" t="s" s="3">
         <v>5459</v>
@@ -63575,7 +63581,7 @@
         <v>6</v>
       </c>
       <c r="D2753" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2753" t="s" s="3">
         <v>5461</v>
@@ -63592,7 +63598,7 @@
         <v>6</v>
       </c>
       <c r="D2754" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2754" t="s" s="3">
         <v>5463</v>
@@ -63609,7 +63615,7 @@
         <v>6</v>
       </c>
       <c r="D2755" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2755" t="s" s="3">
         <v>5465</v>
@@ -63626,7 +63632,7 @@
         <v>6</v>
       </c>
       <c r="D2756" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2756" t="s" s="3">
         <v>5467</v>
@@ -63643,7 +63649,7 @@
         <v>6</v>
       </c>
       <c r="D2757" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2757" t="s" s="3">
         <v>5469</v>
@@ -63660,7 +63666,7 @@
         <v>6</v>
       </c>
       <c r="D2758" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2758" t="s" s="3">
         <v>5471</v>
@@ -63677,7 +63683,7 @@
         <v>6</v>
       </c>
       <c r="D2759" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2759" t="s" s="3">
         <v>5473</v>
@@ -63694,7 +63700,7 @@
         <v>6</v>
       </c>
       <c r="D2760" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2760" t="s" s="3">
         <v>5475</v>
@@ -63711,7 +63717,7 @@
         <v>6</v>
       </c>
       <c r="D2761" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2761" t="s" s="3">
         <v>5477</v>
@@ -63728,7 +63734,7 @@
         <v>6</v>
       </c>
       <c r="D2762" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2762" t="s" s="3">
         <v>5479</v>
@@ -63745,7 +63751,7 @@
         <v>6</v>
       </c>
       <c r="D2763" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2763" t="s" s="3">
         <v>5481</v>
@@ -63762,7 +63768,7 @@
         <v>6</v>
       </c>
       <c r="D2764" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2764" t="s" s="3">
         <v>5483</v>
@@ -63779,7 +63785,7 @@
         <v>6</v>
       </c>
       <c r="D2765" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2765" t="s" s="3">
         <v>5485</v>
@@ -63796,7 +63802,7 @@
         <v>6</v>
       </c>
       <c r="D2766" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2766" t="s" s="3">
         <v>5487</v>
@@ -63813,7 +63819,7 @@
         <v>6</v>
       </c>
       <c r="D2767" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2767" t="s" s="3">
         <v>5489</v>
@@ -63830,7 +63836,7 @@
         <v>6</v>
       </c>
       <c r="D2768" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2768" t="s" s="3">
         <v>5491</v>
@@ -63847,7 +63853,7 @@
         <v>6</v>
       </c>
       <c r="D2769" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2769" t="s" s="3">
         <v>5493</v>
@@ -63864,7 +63870,7 @@
         <v>6</v>
       </c>
       <c r="D2770" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2770" t="s" s="3">
         <v>5495</v>
@@ -63881,7 +63887,7 @@
         <v>6</v>
       </c>
       <c r="D2771" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2771" t="s" s="3">
         <v>5497</v>
@@ -63898,7 +63904,7 @@
         <v>6</v>
       </c>
       <c r="D2772" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2772" t="s" s="3">
         <v>5499</v>
@@ -63915,7 +63921,7 @@
         <v>6</v>
       </c>
       <c r="D2773" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2773" t="s" s="3">
         <v>5501</v>
@@ -63932,7 +63938,7 @@
         <v>6</v>
       </c>
       <c r="D2774" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2774" t="s" s="3">
         <v>5503</v>
@@ -63949,7 +63955,7 @@
         <v>6</v>
       </c>
       <c r="D2775" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2775" t="s" s="3">
         <v>5505</v>
@@ -63966,7 +63972,7 @@
         <v>6</v>
       </c>
       <c r="D2776" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2776" t="s" s="3">
         <v>5507</v>
@@ -63983,7 +63989,7 @@
         <v>6</v>
       </c>
       <c r="D2777" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2777" t="s" s="3">
         <v>5509</v>
@@ -64000,7 +64006,7 @@
         <v>6</v>
       </c>
       <c r="D2778" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2778" t="s" s="3">
         <v>5511</v>
@@ -64014,13 +64020,13 @@
         <v>5512</v>
       </c>
       <c r="C2779" t="s" s="2">
-        <v>792</v>
+        <v>6</v>
       </c>
       <c r="D2779" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2779" t="s" s="3">
-        <v>5485</v>
+        <v>5513</v>
       </c>
     </row>
     <row r="2780" ht="36.0" customHeight="true">
@@ -64028,16 +64034,16 @@
         <v>2779.0</v>
       </c>
       <c r="B2780" t="s" s="3">
-        <v>5513</v>
+        <v>5514</v>
       </c>
       <c r="C2780" t="s" s="2">
         <v>792</v>
       </c>
       <c r="D2780" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2780" t="s" s="3">
-        <v>5514</v>
+        <v>5487</v>
       </c>
     </row>
     <row r="2781" ht="36.0" customHeight="true">
@@ -64051,7 +64057,7 @@
         <v>792</v>
       </c>
       <c r="D2781" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2781" t="s" s="3">
         <v>5516</v>
@@ -64068,7 +64074,7 @@
         <v>792</v>
       </c>
       <c r="D2782" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2782" t="s" s="3">
         <v>5518</v>
@@ -64085,7 +64091,7 @@
         <v>792</v>
       </c>
       <c r="D2783" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2783" t="s" s="3">
         <v>5520</v>
@@ -64102,7 +64108,7 @@
         <v>792</v>
       </c>
       <c r="D2784" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2784" t="s" s="3">
         <v>5522</v>
@@ -64113,16 +64119,16 @@
         <v>2784.0</v>
       </c>
       <c r="B2785" t="s" s="3">
-        <v>5446</v>
+        <v>5523</v>
       </c>
       <c r="C2785" t="s" s="2">
         <v>792</v>
       </c>
       <c r="D2785" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2785" t="s" s="3">
-        <v>5523</v>
+        <v>5524</v>
       </c>
     </row>
     <row r="2786" ht="36.0" customHeight="true">
@@ -64130,13 +64136,13 @@
         <v>2785.0</v>
       </c>
       <c r="B2786" t="s" s="3">
-        <v>5524</v>
+        <v>5448</v>
       </c>
       <c r="C2786" t="s" s="2">
         <v>792</v>
       </c>
       <c r="D2786" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2786" t="s" s="3">
         <v>5525</v>
@@ -64153,7 +64159,7 @@
         <v>792</v>
       </c>
       <c r="D2787" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2787" t="s" s="3">
         <v>5527</v>
@@ -64170,7 +64176,7 @@
         <v>792</v>
       </c>
       <c r="D2788" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2788" t="s" s="3">
         <v>5529</v>
@@ -64187,7 +64193,7 @@
         <v>792</v>
       </c>
       <c r="D2789" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2789" t="s" s="3">
         <v>5531</v>
@@ -64204,7 +64210,7 @@
         <v>792</v>
       </c>
       <c r="D2790" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2790" t="s" s="3">
         <v>5533</v>
@@ -64221,7 +64227,7 @@
         <v>792</v>
       </c>
       <c r="D2791" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2791" t="s" s="3">
         <v>5535</v>
@@ -64238,7 +64244,7 @@
         <v>792</v>
       </c>
       <c r="D2792" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2792" t="s" s="3">
         <v>5537</v>
@@ -64255,7 +64261,7 @@
         <v>792</v>
       </c>
       <c r="D2793" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2793" t="s" s="3">
         <v>5539</v>
@@ -64272,7 +64278,7 @@
         <v>792</v>
       </c>
       <c r="D2794" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2794" t="s" s="3">
         <v>5541</v>
@@ -64289,7 +64295,7 @@
         <v>792</v>
       </c>
       <c r="D2795" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2795" t="s" s="3">
         <v>5543</v>
@@ -64306,7 +64312,7 @@
         <v>792</v>
       </c>
       <c r="D2796" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2796" t="s" s="3">
         <v>5545</v>
@@ -64323,7 +64329,7 @@
         <v>792</v>
       </c>
       <c r="D2797" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2797" t="s" s="3">
         <v>5547</v>
@@ -64340,7 +64346,7 @@
         <v>792</v>
       </c>
       <c r="D2798" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2798" t="s" s="3">
         <v>5549</v>
@@ -64357,7 +64363,7 @@
         <v>792</v>
       </c>
       <c r="D2799" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2799" t="s" s="3">
         <v>5551</v>
@@ -64374,7 +64380,7 @@
         <v>792</v>
       </c>
       <c r="D2800" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2800" t="s" s="3">
         <v>5553</v>
@@ -64391,10 +64397,27 @@
         <v>792</v>
       </c>
       <c r="D2801" t="s" s="2">
-        <v>5438</v>
+        <v>5440</v>
       </c>
       <c r="E2801" t="s" s="3">
         <v>5555</v>
+      </c>
+    </row>
+    <row r="2802" ht="36.0" customHeight="true">
+      <c r="A2802" t="n" s="2">
+        <v>2801.0</v>
+      </c>
+      <c r="B2802" t="s" s="3">
+        <v>5556</v>
+      </c>
+      <c r="C2802" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="D2802" t="s" s="2">
+        <v>5440</v>
+      </c>
+      <c r="E2802" t="s" s="3">
+        <v>5557</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -6374,10 +6374,10 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 영종구 백운로 510(2동 1,2층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
-  </si>
-  <si>
-    <t>인천광역시 영종구 백운로 510(2동 1,2층 운북동)</t>
   </si>
   <si>
     <t>까페마인</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11429" uniqueCount="5665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11449" uniqueCount="5676">
   <si>
     <t>연번</t>
   </si>
@@ -1112,6 +1112,12 @@
     <t>서울특별시 종로구 필운대로 6(1층 필운동)</t>
   </si>
   <si>
+    <t>석월당</t>
+  </si>
+  <si>
+    <t>서울특별시 송파구 송파대로 473(1층 101호 석촌동, 양지473)</t>
+  </si>
+  <si>
     <t>선유슬로우(sunu.slow)</t>
   </si>
   <si>
@@ -1571,12 +1577,12 @@
     <t>오르노 합정점</t>
   </si>
   <si>
+    <t>서울특별시 마포구 월드컵로3길 14(지1층 B113,114호 합정동, 마포 한강 2차 푸르지오)</t>
+  </si>
+  <si>
     <t>서울특별시 마포구 월드컵로3길 14(지1층 B149,B150,B151, B152,B153,B154호 합정동, 마포 한강 2차 푸르지오)</t>
   </si>
   <si>
-    <t>서울특별시 마포구 월드컵로3길 14(지1층 B113,114호 합정동, 마포 한강 2차 푸르지오)</t>
-  </si>
-  <si>
     <t>오베뉴 한남</t>
   </si>
   <si>
@@ -2021,12 +2027,6 @@
     <t>서울특별시 광진구 아차산로76길 34(1층 광장동)</t>
   </si>
   <si>
-    <t>크림베이글 잠실점</t>
-  </si>
-  <si>
-    <t>서울특별시 송파구 송파대로 473(1층 101호 석촌동, 양지473)</t>
-  </si>
-  <si>
     <t>크림빔(Cream Beam)</t>
   </si>
   <si>
@@ -3533,12 +3533,12 @@
     <t>전남광주통합특별시 화순군 도곡면 덕리길 10-5(1층)</t>
   </si>
   <si>
+    <t>전남광주통합특별시 서구 상무시민로 136(수성빌딩 1층 치평동)</t>
+  </si>
+  <si>
     <t>전남광주통합특별시 동구 동명로14번길 19-8(2층 동명동)</t>
   </si>
   <si>
-    <t>전남광주통합특별시 서구 상무시민로 136(수성빌딩 1층 치평동)</t>
-  </si>
-  <si>
     <t>쉘터커피로스터스</t>
   </si>
   <si>
@@ -4148,6 +4148,12 @@
     <t>부산광역시 기장군 기장읍 연화1길 147</t>
   </si>
   <si>
+    <t>대박포차</t>
+  </si>
+  <si>
+    <t>부산광역시 강서구 과학산단2로20번길 40(1층 일부 지사동)</t>
+  </si>
+  <si>
     <t>덴바</t>
   </si>
   <si>
@@ -4298,12 +4304,6 @@
     <t>부산광역시 수영구 수영로680번길 45(1층 광안동)</t>
   </si>
   <si>
-    <t>보스턴 샐러드 하우스</t>
-  </si>
-  <si>
-    <t>부산광역시 강서구 과학산단2로20번길 40(1층 일부 지사동)</t>
-  </si>
-  <si>
     <t>부바스</t>
   </si>
   <si>
@@ -4391,12 +4391,12 @@
     <t>스트럿</t>
   </si>
   <si>
+    <t>부산광역시 부산진구 동성로39번길 28(1층 전포동)</t>
+  </si>
+  <si>
     <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
   </si>
   <si>
-    <t>부산광역시 부산진구 동성로39번길 28(1층 전포동)</t>
-  </si>
-  <si>
     <t>스팅프리 로스팅하우스</t>
   </si>
   <si>
@@ -11132,6 +11132,12 @@
     <t>경기도 수원시 영통구 권선로882번길 26-51(1층 103호 신동)</t>
   </si>
   <si>
+    <t>베리굿즈</t>
+  </si>
+  <si>
+    <t>경기도 화성시 만세구 남양읍 시청로 52(1층 일부호)</t>
+  </si>
+  <si>
     <t>베비나</t>
   </si>
   <si>
@@ -12521,6 +12527,12 @@
     <t>충청남도 서산시 동헌로 76(읍내동)</t>
   </si>
   <si>
+    <t>바이콩즈</t>
+  </si>
+  <si>
+    <t>충청남도 공주시 반포면 동학사1로 82</t>
+  </si>
+  <si>
     <t>밤이네</t>
   </si>
   <si>
@@ -13259,6 +13271,12 @@
     <t>경상북도 김천시 아포읍 국사길 113(1층)</t>
   </si>
   <si>
+    <t>도어커피</t>
+  </si>
+  <si>
+    <t>경상북도 경산시 경안로36길 22-17(1층 중방동)</t>
+  </si>
+  <si>
     <t>도화</t>
   </si>
   <si>
@@ -17007,6 +17025,21 @@
   </si>
   <si>
     <t>전북특별자치도 김제시 만경읍 대동길 609</t>
+  </si>
+  <si>
+    <t>블랙쉽 니트카페(Black Sheep Knit Cafe)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 도림로 475(1층 103호 문래동4가)</t>
+  </si>
+  <si>
+    <t>연다원</t>
+  </si>
+  <si>
+    <t>전북특별자치도 고창군 아산면 복분자로 184-81</t>
   </si>
 </sst>
 </file>
@@ -21498,7 +21531,7 @@
         <v>258.0</v>
       </c>
       <c r="B259" t="s" s="3">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C259" t="s" s="2">
         <v>6</v>
@@ -21507,7 +21540,7 @@
         <v>7</v>
       </c>
       <c r="E259" t="s" s="3">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="260" ht="36.0" customHeight="true">
@@ -21515,7 +21548,7 @@
         <v>259.0</v>
       </c>
       <c r="B260" t="s" s="3">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C260" t="s" s="2">
         <v>6</v>
@@ -25961,7 +25994,7 @@
         <v>7</v>
       </c>
       <c r="E521" t="s" s="3">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="522" ht="36.0" customHeight="true">
@@ -27091,7 +27124,7 @@
         <v>587.0</v>
       </c>
       <c r="B588" t="s" s="3">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C588" t="s" s="2">
         <v>6</v>
@@ -27108,7 +27141,7 @@
         <v>588.0</v>
       </c>
       <c r="B589" t="s" s="3">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C589" t="s" s="2">
         <v>6</v>
@@ -27448,7 +27481,7 @@
         <v>608.0</v>
       </c>
       <c r="B609" t="s" s="3">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C609" t="s" s="2">
         <v>6</v>
@@ -50798,7 +50831,7 @@
         <v>2497</v>
       </c>
       <c r="E1982" t="s" s="3">
-        <v>3749</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="1983" ht="36.0" customHeight="true">
@@ -50806,7 +50839,7 @@
         <v>1982.0</v>
       </c>
       <c r="B1983" t="s" s="3">
-        <v>3933</v>
+        <v>3934</v>
       </c>
       <c r="C1983" t="s" s="2">
         <v>812</v>
@@ -50815,7 +50848,7 @@
         <v>2497</v>
       </c>
       <c r="E1983" t="s" s="3">
-        <v>3934</v>
+        <v>3751</v>
       </c>
     </row>
     <row r="1984" ht="36.0" customHeight="true">
@@ -50823,7 +50856,7 @@
         <v>1983.0</v>
       </c>
       <c r="B1984" t="s" s="3">
-        <v>3522</v>
+        <v>3935</v>
       </c>
       <c r="C1984" t="s" s="2">
         <v>812</v>
@@ -50832,7 +50865,7 @@
         <v>2497</v>
       </c>
       <c r="E1984" t="s" s="3">
-        <v>3523</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="1985" ht="36.0" customHeight="true">
@@ -50840,7 +50873,7 @@
         <v>1984.0</v>
       </c>
       <c r="B1985" t="s" s="3">
-        <v>3935</v>
+        <v>3522</v>
       </c>
       <c r="C1985" t="s" s="2">
         <v>812</v>
@@ -50849,7 +50882,7 @@
         <v>2497</v>
       </c>
       <c r="E1985" t="s" s="3">
-        <v>3936</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="1986" ht="36.0" customHeight="true">
@@ -51064,7 +51097,7 @@
         <v>3961</v>
       </c>
       <c r="C1998" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D1998" t="s" s="2">
         <v>2497</v>
@@ -51248,7 +51281,7 @@
         <v>2008.0</v>
       </c>
       <c r="B2009" t="s" s="3">
-        <v>3192</v>
+        <v>3983</v>
       </c>
       <c r="C2009" t="s" s="2">
         <v>1039</v>
@@ -51257,7 +51290,7 @@
         <v>2497</v>
       </c>
       <c r="E2009" t="s" s="3">
-        <v>3193</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="2010" ht="36.0" customHeight="true">
@@ -51265,7 +51298,7 @@
         <v>2009.0</v>
       </c>
       <c r="B2010" t="s" s="3">
-        <v>3983</v>
+        <v>3192</v>
       </c>
       <c r="C2010" t="s" s="2">
         <v>1039</v>
@@ -51274,7 +51307,7 @@
         <v>2497</v>
       </c>
       <c r="E2010" t="s" s="3">
-        <v>3984</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="2011" ht="36.0" customHeight="true">
@@ -51336,13 +51369,13 @@
         <v>3991</v>
       </c>
       <c r="C2014" t="s" s="2">
-        <v>6</v>
+        <v>1039</v>
       </c>
       <c r="D2014" t="s" s="2">
+        <v>2497</v>
+      </c>
+      <c r="E2014" t="s" s="3">
         <v>3992</v>
-      </c>
-      <c r="E2014" t="s" s="3">
-        <v>3993</v>
       </c>
     </row>
     <row r="2015" ht="36.0" customHeight="true">
@@ -51350,13 +51383,13 @@
         <v>2014.0</v>
       </c>
       <c r="B2015" t="s" s="3">
+        <v>3993</v>
+      </c>
+      <c r="C2015" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2015" t="s" s="2">
         <v>3994</v>
-      </c>
-      <c r="C2015" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2015" t="s" s="2">
-        <v>3992</v>
       </c>
       <c r="E2015" t="s" s="3">
         <v>3995</v>
@@ -51373,7 +51406,7 @@
         <v>6</v>
       </c>
       <c r="D2016" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2016" t="s" s="3">
         <v>3997</v>
@@ -51390,7 +51423,7 @@
         <v>6</v>
       </c>
       <c r="D2017" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2017" t="s" s="3">
         <v>3999</v>
@@ -51407,7 +51440,7 @@
         <v>6</v>
       </c>
       <c r="D2018" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2018" t="s" s="3">
         <v>4001</v>
@@ -51424,7 +51457,7 @@
         <v>6</v>
       </c>
       <c r="D2019" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2019" t="s" s="3">
         <v>4003</v>
@@ -51441,7 +51474,7 @@
         <v>6</v>
       </c>
       <c r="D2020" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2020" t="s" s="3">
         <v>4005</v>
@@ -51458,7 +51491,7 @@
         <v>6</v>
       </c>
       <c r="D2021" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2021" t="s" s="3">
         <v>4007</v>
@@ -51475,7 +51508,7 @@
         <v>6</v>
       </c>
       <c r="D2022" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2022" t="s" s="3">
         <v>4009</v>
@@ -51492,7 +51525,7 @@
         <v>6</v>
       </c>
       <c r="D2023" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2023" t="s" s="3">
         <v>4011</v>
@@ -51509,7 +51542,7 @@
         <v>6</v>
       </c>
       <c r="D2024" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2024" t="s" s="3">
         <v>4013</v>
@@ -51526,7 +51559,7 @@
         <v>6</v>
       </c>
       <c r="D2025" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2025" t="s" s="3">
         <v>4015</v>
@@ -51543,7 +51576,7 @@
         <v>6</v>
       </c>
       <c r="D2026" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2026" t="s" s="3">
         <v>4017</v>
@@ -51560,7 +51593,7 @@
         <v>6</v>
       </c>
       <c r="D2027" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2027" t="s" s="3">
         <v>4019</v>
@@ -51577,7 +51610,7 @@
         <v>6</v>
       </c>
       <c r="D2028" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2028" t="s" s="3">
         <v>4021</v>
@@ -51594,7 +51627,7 @@
         <v>6</v>
       </c>
       <c r="D2029" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2029" t="s" s="3">
         <v>4023</v>
@@ -51611,7 +51644,7 @@
         <v>6</v>
       </c>
       <c r="D2030" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2030" t="s" s="3">
         <v>4025</v>
@@ -51628,7 +51661,7 @@
         <v>6</v>
       </c>
       <c r="D2031" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2031" t="s" s="3">
         <v>4027</v>
@@ -51645,7 +51678,7 @@
         <v>6</v>
       </c>
       <c r="D2032" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2032" t="s" s="3">
         <v>4029</v>
@@ -51662,7 +51695,7 @@
         <v>6</v>
       </c>
       <c r="D2033" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2033" t="s" s="3">
         <v>4031</v>
@@ -51679,7 +51712,7 @@
         <v>6</v>
       </c>
       <c r="D2034" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2034" t="s" s="3">
         <v>4033</v>
@@ -51696,7 +51729,7 @@
         <v>6</v>
       </c>
       <c r="D2035" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2035" t="s" s="3">
         <v>4035</v>
@@ -51713,7 +51746,7 @@
         <v>6</v>
       </c>
       <c r="D2036" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2036" t="s" s="3">
         <v>4037</v>
@@ -51730,7 +51763,7 @@
         <v>6</v>
       </c>
       <c r="D2037" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2037" t="s" s="3">
         <v>4039</v>
@@ -51747,7 +51780,7 @@
         <v>6</v>
       </c>
       <c r="D2038" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2038" t="s" s="3">
         <v>4041</v>
@@ -51764,7 +51797,7 @@
         <v>6</v>
       </c>
       <c r="D2039" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2039" t="s" s="3">
         <v>4043</v>
@@ -51781,7 +51814,7 @@
         <v>6</v>
       </c>
       <c r="D2040" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2040" t="s" s="3">
         <v>4045</v>
@@ -51798,7 +51831,7 @@
         <v>6</v>
       </c>
       <c r="D2041" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2041" t="s" s="3">
         <v>4047</v>
@@ -51815,7 +51848,7 @@
         <v>6</v>
       </c>
       <c r="D2042" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2042" t="s" s="3">
         <v>4049</v>
@@ -51832,7 +51865,7 @@
         <v>6</v>
       </c>
       <c r="D2043" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2043" t="s" s="3">
         <v>4051</v>
@@ -51849,7 +51882,7 @@
         <v>6</v>
       </c>
       <c r="D2044" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2044" t="s" s="3">
         <v>4053</v>
@@ -51866,7 +51899,7 @@
         <v>6</v>
       </c>
       <c r="D2045" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2045" t="s" s="3">
         <v>4055</v>
@@ -51883,7 +51916,7 @@
         <v>6</v>
       </c>
       <c r="D2046" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2046" t="s" s="3">
         <v>4057</v>
@@ -51900,7 +51933,7 @@
         <v>6</v>
       </c>
       <c r="D2047" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2047" t="s" s="3">
         <v>4059</v>
@@ -51917,7 +51950,7 @@
         <v>6</v>
       </c>
       <c r="D2048" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2048" t="s" s="3">
         <v>4061</v>
@@ -51934,7 +51967,7 @@
         <v>6</v>
       </c>
       <c r="D2049" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2049" t="s" s="3">
         <v>4063</v>
@@ -51951,7 +51984,7 @@
         <v>6</v>
       </c>
       <c r="D2050" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2050" t="s" s="3">
         <v>4065</v>
@@ -51968,7 +52001,7 @@
         <v>6</v>
       </c>
       <c r="D2051" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2051" t="s" s="3">
         <v>4067</v>
@@ -51985,7 +52018,7 @@
         <v>6</v>
       </c>
       <c r="D2052" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2052" t="s" s="3">
         <v>4069</v>
@@ -52002,7 +52035,7 @@
         <v>6</v>
       </c>
       <c r="D2053" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2053" t="s" s="3">
         <v>4071</v>
@@ -52019,7 +52052,7 @@
         <v>6</v>
       </c>
       <c r="D2054" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2054" t="s" s="3">
         <v>4073</v>
@@ -52036,7 +52069,7 @@
         <v>6</v>
       </c>
       <c r="D2055" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2055" t="s" s="3">
         <v>4075</v>
@@ -52053,7 +52086,7 @@
         <v>6</v>
       </c>
       <c r="D2056" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2056" t="s" s="3">
         <v>4077</v>
@@ -52070,7 +52103,7 @@
         <v>6</v>
       </c>
       <c r="D2057" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2057" t="s" s="3">
         <v>4079</v>
@@ -52087,7 +52120,7 @@
         <v>6</v>
       </c>
       <c r="D2058" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2058" t="s" s="3">
         <v>4081</v>
@@ -52104,7 +52137,7 @@
         <v>6</v>
       </c>
       <c r="D2059" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2059" t="s" s="3">
         <v>4083</v>
@@ -52121,7 +52154,7 @@
         <v>6</v>
       </c>
       <c r="D2060" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2060" t="s" s="3">
         <v>4085</v>
@@ -52138,7 +52171,7 @@
         <v>6</v>
       </c>
       <c r="D2061" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2061" t="s" s="3">
         <v>4087</v>
@@ -52155,7 +52188,7 @@
         <v>6</v>
       </c>
       <c r="D2062" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2062" t="s" s="3">
         <v>4089</v>
@@ -52169,10 +52202,10 @@
         <v>4090</v>
       </c>
       <c r="C2063" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2063" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2063" t="s" s="3">
         <v>4091</v>
@@ -52189,7 +52222,7 @@
         <v>812</v>
       </c>
       <c r="D2064" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2064" t="s" s="3">
         <v>4093</v>
@@ -52206,7 +52239,7 @@
         <v>812</v>
       </c>
       <c r="D2065" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2065" t="s" s="3">
         <v>4095</v>
@@ -52223,7 +52256,7 @@
         <v>812</v>
       </c>
       <c r="D2066" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2066" t="s" s="3">
         <v>4097</v>
@@ -52240,7 +52273,7 @@
         <v>812</v>
       </c>
       <c r="D2067" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2067" t="s" s="3">
         <v>4099</v>
@@ -52257,7 +52290,7 @@
         <v>812</v>
       </c>
       <c r="D2068" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2068" t="s" s="3">
         <v>4101</v>
@@ -52274,7 +52307,7 @@
         <v>812</v>
       </c>
       <c r="D2069" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2069" t="s" s="3">
         <v>4103</v>
@@ -52291,7 +52324,7 @@
         <v>812</v>
       </c>
       <c r="D2070" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2070" t="s" s="3">
         <v>4105</v>
@@ -52308,7 +52341,7 @@
         <v>812</v>
       </c>
       <c r="D2071" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2071" t="s" s="3">
         <v>4107</v>
@@ -52325,7 +52358,7 @@
         <v>812</v>
       </c>
       <c r="D2072" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2072" t="s" s="3">
         <v>4109</v>
@@ -52342,7 +52375,7 @@
         <v>812</v>
       </c>
       <c r="D2073" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2073" t="s" s="3">
         <v>4111</v>
@@ -52359,7 +52392,7 @@
         <v>812</v>
       </c>
       <c r="D2074" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2074" t="s" s="3">
         <v>4113</v>
@@ -52376,7 +52409,7 @@
         <v>812</v>
       </c>
       <c r="D2075" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2075" t="s" s="3">
         <v>4115</v>
@@ -52393,7 +52426,7 @@
         <v>812</v>
       </c>
       <c r="D2076" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2076" t="s" s="3">
         <v>4117</v>
@@ -52410,7 +52443,7 @@
         <v>812</v>
       </c>
       <c r="D2077" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2077" t="s" s="3">
         <v>4119</v>
@@ -52427,7 +52460,7 @@
         <v>812</v>
       </c>
       <c r="D2078" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2078" t="s" s="3">
         <v>4121</v>
@@ -52441,10 +52474,10 @@
         <v>4122</v>
       </c>
       <c r="C2079" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2079" t="s" s="2">
-        <v>3992</v>
+        <v>3994</v>
       </c>
       <c r="E2079" t="s" s="3">
         <v>4123</v>
@@ -52458,13 +52491,13 @@
         <v>4124</v>
       </c>
       <c r="C2080" t="s" s="2">
-        <v>6</v>
+        <v>1039</v>
       </c>
       <c r="D2080" t="s" s="2">
+        <v>3994</v>
+      </c>
+      <c r="E2080" t="s" s="3">
         <v>4125</v>
-      </c>
-      <c r="E2080" t="s" s="3">
-        <v>4126</v>
       </c>
     </row>
     <row r="2081" ht="36.0" customHeight="true">
@@ -52472,13 +52505,13 @@
         <v>2080.0</v>
       </c>
       <c r="B2081" t="s" s="3">
+        <v>4126</v>
+      </c>
+      <c r="C2081" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2081" t="s" s="2">
         <v>4127</v>
-      </c>
-      <c r="C2081" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2081" t="s" s="2">
-        <v>4125</v>
       </c>
       <c r="E2081" t="s" s="3">
         <v>4128</v>
@@ -52495,7 +52528,7 @@
         <v>6</v>
       </c>
       <c r="D2082" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2082" t="s" s="3">
         <v>4130</v>
@@ -52512,7 +52545,7 @@
         <v>6</v>
       </c>
       <c r="D2083" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2083" t="s" s="3">
         <v>4132</v>
@@ -52529,7 +52562,7 @@
         <v>6</v>
       </c>
       <c r="D2084" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2084" t="s" s="3">
         <v>4134</v>
@@ -52546,7 +52579,7 @@
         <v>6</v>
       </c>
       <c r="D2085" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2085" t="s" s="3">
         <v>4136</v>
@@ -52563,7 +52596,7 @@
         <v>6</v>
       </c>
       <c r="D2086" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2086" t="s" s="3">
         <v>4138</v>
@@ -52580,7 +52613,7 @@
         <v>6</v>
       </c>
       <c r="D2087" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2087" t="s" s="3">
         <v>4140</v>
@@ -52597,7 +52630,7 @@
         <v>6</v>
       </c>
       <c r="D2088" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2088" t="s" s="3">
         <v>4142</v>
@@ -52614,7 +52647,7 @@
         <v>6</v>
       </c>
       <c r="D2089" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2089" t="s" s="3">
         <v>4144</v>
@@ -52631,7 +52664,7 @@
         <v>6</v>
       </c>
       <c r="D2090" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2090" t="s" s="3">
         <v>4146</v>
@@ -52648,7 +52681,7 @@
         <v>6</v>
       </c>
       <c r="D2091" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2091" t="s" s="3">
         <v>4148</v>
@@ -52665,7 +52698,7 @@
         <v>6</v>
       </c>
       <c r="D2092" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2092" t="s" s="3">
         <v>4150</v>
@@ -52682,7 +52715,7 @@
         <v>6</v>
       </c>
       <c r="D2093" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2093" t="s" s="3">
         <v>4152</v>
@@ -52699,7 +52732,7 @@
         <v>6</v>
       </c>
       <c r="D2094" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2094" t="s" s="3">
         <v>4154</v>
@@ -52716,7 +52749,7 @@
         <v>6</v>
       </c>
       <c r="D2095" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2095" t="s" s="3">
         <v>4156</v>
@@ -52733,7 +52766,7 @@
         <v>6</v>
       </c>
       <c r="D2096" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2096" t="s" s="3">
         <v>4158</v>
@@ -52750,7 +52783,7 @@
         <v>6</v>
       </c>
       <c r="D2097" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2097" t="s" s="3">
         <v>4160</v>
@@ -52767,7 +52800,7 @@
         <v>6</v>
       </c>
       <c r="D2098" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2098" t="s" s="3">
         <v>4162</v>
@@ -52784,7 +52817,7 @@
         <v>6</v>
       </c>
       <c r="D2099" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2099" t="s" s="3">
         <v>4164</v>
@@ -52801,7 +52834,7 @@
         <v>6</v>
       </c>
       <c r="D2100" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2100" t="s" s="3">
         <v>4166</v>
@@ -52818,7 +52851,7 @@
         <v>6</v>
       </c>
       <c r="D2101" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2101" t="s" s="3">
         <v>4168</v>
@@ -52835,7 +52868,7 @@
         <v>6</v>
       </c>
       <c r="D2102" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2102" t="s" s="3">
         <v>4170</v>
@@ -52852,7 +52885,7 @@
         <v>6</v>
       </c>
       <c r="D2103" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2103" t="s" s="3">
         <v>4172</v>
@@ -52869,7 +52902,7 @@
         <v>6</v>
       </c>
       <c r="D2104" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2104" t="s" s="3">
         <v>4174</v>
@@ -52886,7 +52919,7 @@
         <v>6</v>
       </c>
       <c r="D2105" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2105" t="s" s="3">
         <v>4176</v>
@@ -52903,7 +52936,7 @@
         <v>6</v>
       </c>
       <c r="D2106" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2106" t="s" s="3">
         <v>4178</v>
@@ -52920,7 +52953,7 @@
         <v>6</v>
       </c>
       <c r="D2107" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2107" t="s" s="3">
         <v>4180</v>
@@ -52937,7 +52970,7 @@
         <v>6</v>
       </c>
       <c r="D2108" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2108" t="s" s="3">
         <v>4182</v>
@@ -52954,7 +52987,7 @@
         <v>6</v>
       </c>
       <c r="D2109" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2109" t="s" s="3">
         <v>4184</v>
@@ -52971,7 +53004,7 @@
         <v>6</v>
       </c>
       <c r="D2110" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2110" t="s" s="3">
         <v>4186</v>
@@ -52988,7 +53021,7 @@
         <v>6</v>
       </c>
       <c r="D2111" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2111" t="s" s="3">
         <v>4188</v>
@@ -53005,7 +53038,7 @@
         <v>6</v>
       </c>
       <c r="D2112" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2112" t="s" s="3">
         <v>4190</v>
@@ -53022,7 +53055,7 @@
         <v>6</v>
       </c>
       <c r="D2113" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2113" t="s" s="3">
         <v>4192</v>
@@ -53039,7 +53072,7 @@
         <v>6</v>
       </c>
       <c r="D2114" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2114" t="s" s="3">
         <v>4194</v>
@@ -53056,7 +53089,7 @@
         <v>6</v>
       </c>
       <c r="D2115" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2115" t="s" s="3">
         <v>4196</v>
@@ -53073,7 +53106,7 @@
         <v>6</v>
       </c>
       <c r="D2116" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2116" t="s" s="3">
         <v>4198</v>
@@ -53090,7 +53123,7 @@
         <v>6</v>
       </c>
       <c r="D2117" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2117" t="s" s="3">
         <v>4200</v>
@@ -53107,7 +53140,7 @@
         <v>6</v>
       </c>
       <c r="D2118" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2118" t="s" s="3">
         <v>4202</v>
@@ -53124,7 +53157,7 @@
         <v>6</v>
       </c>
       <c r="D2119" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2119" t="s" s="3">
         <v>4204</v>
@@ -53141,7 +53174,7 @@
         <v>6</v>
       </c>
       <c r="D2120" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2120" t="s" s="3">
         <v>4206</v>
@@ -53158,7 +53191,7 @@
         <v>6</v>
       </c>
       <c r="D2121" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2121" t="s" s="3">
         <v>4208</v>
@@ -53175,7 +53208,7 @@
         <v>6</v>
       </c>
       <c r="D2122" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2122" t="s" s="3">
         <v>4210</v>
@@ -53192,7 +53225,7 @@
         <v>6</v>
       </c>
       <c r="D2123" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2123" t="s" s="3">
         <v>4212</v>
@@ -53209,7 +53242,7 @@
         <v>6</v>
       </c>
       <c r="D2124" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2124" t="s" s="3">
         <v>4214</v>
@@ -53226,7 +53259,7 @@
         <v>6</v>
       </c>
       <c r="D2125" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2125" t="s" s="3">
         <v>4216</v>
@@ -53243,7 +53276,7 @@
         <v>6</v>
       </c>
       <c r="D2126" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2126" t="s" s="3">
         <v>4218</v>
@@ -53260,7 +53293,7 @@
         <v>6</v>
       </c>
       <c r="D2127" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2127" t="s" s="3">
         <v>4220</v>
@@ -53277,7 +53310,7 @@
         <v>6</v>
       </c>
       <c r="D2128" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2128" t="s" s="3">
         <v>4222</v>
@@ -53294,7 +53327,7 @@
         <v>6</v>
       </c>
       <c r="D2129" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2129" t="s" s="3">
         <v>4224</v>
@@ -53311,7 +53344,7 @@
         <v>6</v>
       </c>
       <c r="D2130" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2130" t="s" s="3">
         <v>4226</v>
@@ -53328,7 +53361,7 @@
         <v>6</v>
       </c>
       <c r="D2131" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2131" t="s" s="3">
         <v>4228</v>
@@ -53345,7 +53378,7 @@
         <v>6</v>
       </c>
       <c r="D2132" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2132" t="s" s="3">
         <v>4230</v>
@@ -53362,7 +53395,7 @@
         <v>6</v>
       </c>
       <c r="D2133" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2133" t="s" s="3">
         <v>4232</v>
@@ -53379,7 +53412,7 @@
         <v>6</v>
       </c>
       <c r="D2134" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2134" t="s" s="3">
         <v>4234</v>
@@ -53396,7 +53429,7 @@
         <v>6</v>
       </c>
       <c r="D2135" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2135" t="s" s="3">
         <v>4236</v>
@@ -53413,7 +53446,7 @@
         <v>6</v>
       </c>
       <c r="D2136" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2136" t="s" s="3">
         <v>4238</v>
@@ -53430,7 +53463,7 @@
         <v>6</v>
       </c>
       <c r="D2137" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2137" t="s" s="3">
         <v>4240</v>
@@ -53447,7 +53480,7 @@
         <v>6</v>
       </c>
       <c r="D2138" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2138" t="s" s="3">
         <v>4242</v>
@@ -53464,7 +53497,7 @@
         <v>6</v>
       </c>
       <c r="D2139" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2139" t="s" s="3">
         <v>4244</v>
@@ -53481,7 +53514,7 @@
         <v>6</v>
       </c>
       <c r="D2140" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2140" t="s" s="3">
         <v>4246</v>
@@ -53498,7 +53531,7 @@
         <v>6</v>
       </c>
       <c r="D2141" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2141" t="s" s="3">
         <v>4248</v>
@@ -53512,10 +53545,10 @@
         <v>4249</v>
       </c>
       <c r="C2142" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2142" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2142" t="s" s="3">
         <v>4250</v>
@@ -53529,10 +53562,10 @@
         <v>4251</v>
       </c>
       <c r="C2143" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2143" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2143" t="s" s="3">
         <v>4252</v>
@@ -53549,7 +53582,7 @@
         <v>812</v>
       </c>
       <c r="D2144" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2144" t="s" s="3">
         <v>4254</v>
@@ -53566,7 +53599,7 @@
         <v>812</v>
       </c>
       <c r="D2145" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2145" t="s" s="3">
         <v>4256</v>
@@ -53583,7 +53616,7 @@
         <v>812</v>
       </c>
       <c r="D2146" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2146" t="s" s="3">
         <v>4258</v>
@@ -53600,7 +53633,7 @@
         <v>812</v>
       </c>
       <c r="D2147" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2147" t="s" s="3">
         <v>4260</v>
@@ -53617,7 +53650,7 @@
         <v>812</v>
       </c>
       <c r="D2148" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2148" t="s" s="3">
         <v>4262</v>
@@ -53634,7 +53667,7 @@
         <v>812</v>
       </c>
       <c r="D2149" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2149" t="s" s="3">
         <v>4264</v>
@@ -53651,7 +53684,7 @@
         <v>812</v>
       </c>
       <c r="D2150" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2150" t="s" s="3">
         <v>4266</v>
@@ -53668,7 +53701,7 @@
         <v>812</v>
       </c>
       <c r="D2151" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2151" t="s" s="3">
         <v>4268</v>
@@ -53685,7 +53718,7 @@
         <v>812</v>
       </c>
       <c r="D2152" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2152" t="s" s="3">
         <v>4270</v>
@@ -53702,7 +53735,7 @@
         <v>812</v>
       </c>
       <c r="D2153" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2153" t="s" s="3">
         <v>4272</v>
@@ -53719,7 +53752,7 @@
         <v>812</v>
       </c>
       <c r="D2154" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2154" t="s" s="3">
         <v>4274</v>
@@ -53736,7 +53769,7 @@
         <v>812</v>
       </c>
       <c r="D2155" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2155" t="s" s="3">
         <v>4276</v>
@@ -53753,7 +53786,7 @@
         <v>812</v>
       </c>
       <c r="D2156" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2156" t="s" s="3">
         <v>4278</v>
@@ -53770,7 +53803,7 @@
         <v>812</v>
       </c>
       <c r="D2157" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2157" t="s" s="3">
         <v>4280</v>
@@ -53787,7 +53820,7 @@
         <v>812</v>
       </c>
       <c r="D2158" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2158" t="s" s="3">
         <v>4282</v>
@@ -53804,7 +53837,7 @@
         <v>812</v>
       </c>
       <c r="D2159" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2159" t="s" s="3">
         <v>4284</v>
@@ -53821,7 +53854,7 @@
         <v>812</v>
       </c>
       <c r="D2160" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2160" t="s" s="3">
         <v>4286</v>
@@ -53832,16 +53865,16 @@
         <v>2160.0</v>
       </c>
       <c r="B2161" t="s" s="3">
-        <v>4223</v>
+        <v>4287</v>
       </c>
       <c r="C2161" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2161" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2161" t="s" s="3">
-        <v>4224</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="2162" ht="36.0" customHeight="true">
@@ -53849,16 +53882,16 @@
         <v>2161.0</v>
       </c>
       <c r="B2162" t="s" s="3">
-        <v>4287</v>
+        <v>4289</v>
       </c>
       <c r="C2162" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2162" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2162" t="s" s="3">
-        <v>4288</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="2163" ht="36.0" customHeight="true">
@@ -53866,16 +53899,16 @@
         <v>2162.0</v>
       </c>
       <c r="B2163" t="s" s="3">
-        <v>4289</v>
+        <v>4227</v>
       </c>
       <c r="C2163" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2163" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2163" t="s" s="3">
-        <v>4290</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="2164" ht="36.0" customHeight="true">
@@ -53889,7 +53922,7 @@
         <v>812</v>
       </c>
       <c r="D2164" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2164" t="s" s="3">
         <v>4292</v>
@@ -53906,7 +53939,7 @@
         <v>812</v>
       </c>
       <c r="D2165" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2165" t="s" s="3">
         <v>4294</v>
@@ -53923,7 +53956,7 @@
         <v>812</v>
       </c>
       <c r="D2166" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2166" t="s" s="3">
         <v>4296</v>
@@ -53940,7 +53973,7 @@
         <v>812</v>
       </c>
       <c r="D2167" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2167" t="s" s="3">
         <v>4298</v>
@@ -53957,7 +53990,7 @@
         <v>812</v>
       </c>
       <c r="D2168" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2168" t="s" s="3">
         <v>4300</v>
@@ -53974,7 +54007,7 @@
         <v>812</v>
       </c>
       <c r="D2169" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2169" t="s" s="3">
         <v>4302</v>
@@ -53991,7 +54024,7 @@
         <v>812</v>
       </c>
       <c r="D2170" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2170" t="s" s="3">
         <v>4304</v>
@@ -54005,10 +54038,10 @@
         <v>4305</v>
       </c>
       <c r="C2171" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2171" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2171" t="s" s="3">
         <v>4306</v>
@@ -54022,10 +54055,10 @@
         <v>4307</v>
       </c>
       <c r="C2172" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2172" t="s" s="2">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="E2172" t="s" s="3">
         <v>4308</v>
@@ -54039,13 +54072,13 @@
         <v>4309</v>
       </c>
       <c r="C2173" t="s" s="2">
-        <v>6</v>
+        <v>1039</v>
       </c>
       <c r="D2173" t="s" s="2">
+        <v>4127</v>
+      </c>
+      <c r="E2173" t="s" s="3">
         <v>4310</v>
-      </c>
-      <c r="E2173" t="s" s="3">
-        <v>4311</v>
       </c>
     </row>
     <row r="2174" ht="36.0" customHeight="true">
@@ -54053,16 +54086,16 @@
         <v>2173.0</v>
       </c>
       <c r="B2174" t="s" s="3">
+        <v>4311</v>
+      </c>
+      <c r="C2174" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2174" t="s" s="2">
+        <v>4127</v>
+      </c>
+      <c r="E2174" t="s" s="3">
         <v>4312</v>
-      </c>
-      <c r="C2174" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2174" t="s" s="2">
-        <v>4310</v>
-      </c>
-      <c r="E2174" t="s" s="3">
-        <v>4313</v>
       </c>
     </row>
     <row r="2175" ht="36.0" customHeight="true">
@@ -54070,13 +54103,13 @@
         <v>2174.0</v>
       </c>
       <c r="B2175" t="s" s="3">
+        <v>4313</v>
+      </c>
+      <c r="C2175" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2175" t="s" s="2">
         <v>4314</v>
-      </c>
-      <c r="C2175" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2175" t="s" s="2">
-        <v>4310</v>
       </c>
       <c r="E2175" t="s" s="3">
         <v>4315</v>
@@ -54093,7 +54126,7 @@
         <v>6</v>
       </c>
       <c r="D2176" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2176" t="s" s="3">
         <v>4317</v>
@@ -54110,7 +54143,7 @@
         <v>6</v>
       </c>
       <c r="D2177" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2177" t="s" s="3">
         <v>4319</v>
@@ -54127,7 +54160,7 @@
         <v>6</v>
       </c>
       <c r="D2178" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2178" t="s" s="3">
         <v>4321</v>
@@ -54144,7 +54177,7 @@
         <v>6</v>
       </c>
       <c r="D2179" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2179" t="s" s="3">
         <v>4323</v>
@@ -54161,7 +54194,7 @@
         <v>6</v>
       </c>
       <c r="D2180" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2180" t="s" s="3">
         <v>4325</v>
@@ -54178,7 +54211,7 @@
         <v>6</v>
       </c>
       <c r="D2181" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2181" t="s" s="3">
         <v>4327</v>
@@ -54195,7 +54228,7 @@
         <v>6</v>
       </c>
       <c r="D2182" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2182" t="s" s="3">
         <v>4329</v>
@@ -54212,7 +54245,7 @@
         <v>6</v>
       </c>
       <c r="D2183" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2183" t="s" s="3">
         <v>4331</v>
@@ -54229,7 +54262,7 @@
         <v>6</v>
       </c>
       <c r="D2184" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2184" t="s" s="3">
         <v>4333</v>
@@ -54246,7 +54279,7 @@
         <v>6</v>
       </c>
       <c r="D2185" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2185" t="s" s="3">
         <v>4335</v>
@@ -54263,7 +54296,7 @@
         <v>6</v>
       </c>
       <c r="D2186" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2186" t="s" s="3">
         <v>4337</v>
@@ -54280,7 +54313,7 @@
         <v>6</v>
       </c>
       <c r="D2187" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2187" t="s" s="3">
         <v>4339</v>
@@ -54297,7 +54330,7 @@
         <v>6</v>
       </c>
       <c r="D2188" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2188" t="s" s="3">
         <v>4341</v>
@@ -54314,7 +54347,7 @@
         <v>6</v>
       </c>
       <c r="D2189" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2189" t="s" s="3">
         <v>4343</v>
@@ -54331,7 +54364,7 @@
         <v>6</v>
       </c>
       <c r="D2190" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2190" t="s" s="3">
         <v>4345</v>
@@ -54348,7 +54381,7 @@
         <v>6</v>
       </c>
       <c r="D2191" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2191" t="s" s="3">
         <v>4347</v>
@@ -54365,7 +54398,7 @@
         <v>6</v>
       </c>
       <c r="D2192" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2192" t="s" s="3">
         <v>4349</v>
@@ -54382,7 +54415,7 @@
         <v>6</v>
       </c>
       <c r="D2193" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2193" t="s" s="3">
         <v>4351</v>
@@ -54399,7 +54432,7 @@
         <v>6</v>
       </c>
       <c r="D2194" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2194" t="s" s="3">
         <v>4353</v>
@@ -54416,7 +54449,7 @@
         <v>6</v>
       </c>
       <c r="D2195" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2195" t="s" s="3">
         <v>4355</v>
@@ -54433,7 +54466,7 @@
         <v>6</v>
       </c>
       <c r="D2196" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2196" t="s" s="3">
         <v>4357</v>
@@ -54450,7 +54483,7 @@
         <v>6</v>
       </c>
       <c r="D2197" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2197" t="s" s="3">
         <v>4359</v>
@@ -54461,16 +54494,16 @@
         <v>2197.0</v>
       </c>
       <c r="B2198" t="s" s="3">
-        <v>908</v>
+        <v>4360</v>
       </c>
       <c r="C2198" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2198" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2198" t="s" s="3">
-        <v>4360</v>
+        <v>4361</v>
       </c>
     </row>
     <row r="2199" ht="36.0" customHeight="true">
@@ -54478,16 +54511,16 @@
         <v>2198.0</v>
       </c>
       <c r="B2199" t="s" s="3">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="C2199" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2199" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2199" t="s" s="3">
-        <v>4362</v>
+        <v>4363</v>
       </c>
     </row>
     <row r="2200" ht="36.0" customHeight="true">
@@ -54495,13 +54528,13 @@
         <v>2199.0</v>
       </c>
       <c r="B2200" t="s" s="3">
-        <v>4363</v>
+        <v>908</v>
       </c>
       <c r="C2200" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2200" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2200" t="s" s="3">
         <v>4364</v>
@@ -54518,7 +54551,7 @@
         <v>6</v>
       </c>
       <c r="D2201" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2201" t="s" s="3">
         <v>4366</v>
@@ -54535,7 +54568,7 @@
         <v>6</v>
       </c>
       <c r="D2202" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2202" t="s" s="3">
         <v>4368</v>
@@ -54552,7 +54585,7 @@
         <v>6</v>
       </c>
       <c r="D2203" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2203" t="s" s="3">
         <v>4370</v>
@@ -54569,7 +54602,7 @@
         <v>6</v>
       </c>
       <c r="D2204" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2204" t="s" s="3">
         <v>4372</v>
@@ -54586,7 +54619,7 @@
         <v>6</v>
       </c>
       <c r="D2205" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2205" t="s" s="3">
         <v>4374</v>
@@ -54603,7 +54636,7 @@
         <v>6</v>
       </c>
       <c r="D2206" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2206" t="s" s="3">
         <v>4376</v>
@@ -54620,7 +54653,7 @@
         <v>6</v>
       </c>
       <c r="D2207" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2207" t="s" s="3">
         <v>4378</v>
@@ -54637,7 +54670,7 @@
         <v>6</v>
       </c>
       <c r="D2208" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2208" t="s" s="3">
         <v>4380</v>
@@ -54654,7 +54687,7 @@
         <v>6</v>
       </c>
       <c r="D2209" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2209" t="s" s="3">
         <v>4382</v>
@@ -54671,7 +54704,7 @@
         <v>6</v>
       </c>
       <c r="D2210" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2210" t="s" s="3">
         <v>4384</v>
@@ -54688,7 +54721,7 @@
         <v>6</v>
       </c>
       <c r="D2211" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2211" t="s" s="3">
         <v>4386</v>
@@ -54705,10 +54738,10 @@
         <v>6</v>
       </c>
       <c r="D2212" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2212" t="s" s="3">
-        <v>4362</v>
+        <v>4388</v>
       </c>
     </row>
     <row r="2213" ht="36.0" customHeight="true">
@@ -54716,16 +54749,16 @@
         <v>2212.0</v>
       </c>
       <c r="B2213" t="s" s="3">
-        <v>4388</v>
+        <v>4389</v>
       </c>
       <c r="C2213" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2213" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2213" t="s" s="3">
-        <v>4389</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="2214" ht="36.0" customHeight="true">
@@ -54733,16 +54766,16 @@
         <v>2213.0</v>
       </c>
       <c r="B2214" t="s" s="3">
-        <v>3882</v>
+        <v>4391</v>
       </c>
       <c r="C2214" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2214" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2214" t="s" s="3">
-        <v>4390</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="2215" ht="36.0" customHeight="true">
@@ -54750,16 +54783,16 @@
         <v>2214.0</v>
       </c>
       <c r="B2215" t="s" s="3">
-        <v>4391</v>
+        <v>4392</v>
       </c>
       <c r="C2215" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2215" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2215" t="s" s="3">
-        <v>4392</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="2216" ht="36.0" customHeight="true">
@@ -54767,13 +54800,13 @@
         <v>2215.0</v>
       </c>
       <c r="B2216" t="s" s="3">
-        <v>4393</v>
+        <v>3884</v>
       </c>
       <c r="C2216" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2216" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2216" t="s" s="3">
         <v>4394</v>
@@ -54790,7 +54823,7 @@
         <v>6</v>
       </c>
       <c r="D2217" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2217" t="s" s="3">
         <v>4396</v>
@@ -54807,7 +54840,7 @@
         <v>6</v>
       </c>
       <c r="D2218" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2218" t="s" s="3">
         <v>4398</v>
@@ -54824,7 +54857,7 @@
         <v>6</v>
       </c>
       <c r="D2219" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2219" t="s" s="3">
         <v>4400</v>
@@ -54841,7 +54874,7 @@
         <v>6</v>
       </c>
       <c r="D2220" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2220" t="s" s="3">
         <v>4402</v>
@@ -54858,7 +54891,7 @@
         <v>6</v>
       </c>
       <c r="D2221" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2221" t="s" s="3">
         <v>4404</v>
@@ -54875,7 +54908,7 @@
         <v>6</v>
       </c>
       <c r="D2222" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2222" t="s" s="3">
         <v>4406</v>
@@ -54889,10 +54922,10 @@
         <v>4407</v>
       </c>
       <c r="C2223" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2223" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2223" t="s" s="3">
         <v>4408</v>
@@ -54906,10 +54939,10 @@
         <v>4409</v>
       </c>
       <c r="C2224" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2224" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2224" t="s" s="3">
         <v>4410</v>
@@ -54926,7 +54959,7 @@
         <v>812</v>
       </c>
       <c r="D2225" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2225" t="s" s="3">
         <v>4412</v>
@@ -54943,7 +54976,7 @@
         <v>812</v>
       </c>
       <c r="D2226" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2226" t="s" s="3">
         <v>4414</v>
@@ -54960,7 +54993,7 @@
         <v>812</v>
       </c>
       <c r="D2227" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2227" t="s" s="3">
         <v>4416</v>
@@ -54977,7 +55010,7 @@
         <v>812</v>
       </c>
       <c r="D2228" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2228" t="s" s="3">
         <v>4418</v>
@@ -54994,7 +55027,7 @@
         <v>812</v>
       </c>
       <c r="D2229" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2229" t="s" s="3">
         <v>4420</v>
@@ -55011,7 +55044,7 @@
         <v>812</v>
       </c>
       <c r="D2230" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2230" t="s" s="3">
         <v>4422</v>
@@ -55028,7 +55061,7 @@
         <v>812</v>
       </c>
       <c r="D2231" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2231" t="s" s="3">
         <v>4424</v>
@@ -55045,7 +55078,7 @@
         <v>812</v>
       </c>
       <c r="D2232" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2232" t="s" s="3">
         <v>4426</v>
@@ -55062,7 +55095,7 @@
         <v>812</v>
       </c>
       <c r="D2233" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2233" t="s" s="3">
         <v>4428</v>
@@ -55079,7 +55112,7 @@
         <v>812</v>
       </c>
       <c r="D2234" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2234" t="s" s="3">
         <v>4430</v>
@@ -55096,7 +55129,7 @@
         <v>812</v>
       </c>
       <c r="D2235" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2235" t="s" s="3">
         <v>4432</v>
@@ -55113,7 +55146,7 @@
         <v>812</v>
       </c>
       <c r="D2236" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2236" t="s" s="3">
         <v>4434</v>
@@ -55130,7 +55163,7 @@
         <v>812</v>
       </c>
       <c r="D2237" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2237" t="s" s="3">
         <v>4436</v>
@@ -55147,7 +55180,7 @@
         <v>812</v>
       </c>
       <c r="D2238" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2238" t="s" s="3">
         <v>4438</v>
@@ -55164,7 +55197,7 @@
         <v>812</v>
       </c>
       <c r="D2239" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2239" t="s" s="3">
         <v>4440</v>
@@ -55181,7 +55214,7 @@
         <v>812</v>
       </c>
       <c r="D2240" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2240" t="s" s="3">
         <v>4442</v>
@@ -55198,7 +55231,7 @@
         <v>812</v>
       </c>
       <c r="D2241" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2241" t="s" s="3">
         <v>4444</v>
@@ -55215,7 +55248,7 @@
         <v>812</v>
       </c>
       <c r="D2242" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2242" t="s" s="3">
         <v>4446</v>
@@ -55232,7 +55265,7 @@
         <v>812</v>
       </c>
       <c r="D2243" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2243" t="s" s="3">
         <v>4448</v>
@@ -55249,7 +55282,7 @@
         <v>812</v>
       </c>
       <c r="D2244" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2244" t="s" s="3">
         <v>4450</v>
@@ -55266,7 +55299,7 @@
         <v>812</v>
       </c>
       <c r="D2245" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2245" t="s" s="3">
         <v>4452</v>
@@ -55283,7 +55316,7 @@
         <v>812</v>
       </c>
       <c r="D2246" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2246" t="s" s="3">
         <v>4454</v>
@@ -55300,7 +55333,7 @@
         <v>812</v>
       </c>
       <c r="D2247" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2247" t="s" s="3">
         <v>4456</v>
@@ -55317,7 +55350,7 @@
         <v>812</v>
       </c>
       <c r="D2248" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2248" t="s" s="3">
         <v>4458</v>
@@ -55334,7 +55367,7 @@
         <v>812</v>
       </c>
       <c r="D2249" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2249" t="s" s="3">
         <v>4460</v>
@@ -55351,7 +55384,7 @@
         <v>812</v>
       </c>
       <c r="D2250" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2250" t="s" s="3">
         <v>4462</v>
@@ -55368,7 +55401,7 @@
         <v>812</v>
       </c>
       <c r="D2251" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2251" t="s" s="3">
         <v>4464</v>
@@ -55385,7 +55418,7 @@
         <v>812</v>
       </c>
       <c r="D2252" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2252" t="s" s="3">
         <v>4466</v>
@@ -55402,7 +55435,7 @@
         <v>812</v>
       </c>
       <c r="D2253" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2253" t="s" s="3">
         <v>4468</v>
@@ -55416,10 +55449,10 @@
         <v>4469</v>
       </c>
       <c r="C2254" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2254" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2254" t="s" s="3">
         <v>4470</v>
@@ -55433,10 +55466,10 @@
         <v>4471</v>
       </c>
       <c r="C2255" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2255" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2255" t="s" s="3">
         <v>4472</v>
@@ -55447,16 +55480,16 @@
         <v>2255.0</v>
       </c>
       <c r="B2256" t="s" s="3">
-        <v>4421</v>
+        <v>4473</v>
       </c>
       <c r="C2256" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2256" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2256" t="s" s="3">
-        <v>4473</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="2257" ht="36.0" customHeight="true">
@@ -55464,16 +55497,16 @@
         <v>2256.0</v>
       </c>
       <c r="B2257" t="s" s="3">
-        <v>4474</v>
+        <v>4475</v>
       </c>
       <c r="C2257" t="s" s="2">
         <v>1039</v>
       </c>
       <c r="D2257" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2257" t="s" s="3">
-        <v>4475</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="2258" ht="36.0" customHeight="true">
@@ -55481,16 +55514,16 @@
         <v>2257.0</v>
       </c>
       <c r="B2258" t="s" s="3">
-        <v>4388</v>
+        <v>4477</v>
       </c>
       <c r="C2258" t="s" s="2">
         <v>1039</v>
       </c>
       <c r="D2258" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2258" t="s" s="3">
-        <v>4389</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="2259" ht="36.0" customHeight="true">
@@ -55498,16 +55531,16 @@
         <v>2258.0</v>
       </c>
       <c r="B2259" t="s" s="3">
-        <v>4476</v>
+        <v>4427</v>
       </c>
       <c r="C2259" t="s" s="2">
         <v>1039</v>
       </c>
       <c r="D2259" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2259" t="s" s="3">
-        <v>4477</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="2260" ht="36.0" customHeight="true">
@@ -55515,16 +55548,16 @@
         <v>2259.0</v>
       </c>
       <c r="B2260" t="s" s="3">
-        <v>4478</v>
+        <v>4480</v>
       </c>
       <c r="C2260" t="s" s="2">
         <v>1039</v>
       </c>
       <c r="D2260" t="s" s="2">
-        <v>4310</v>
+        <v>4314</v>
       </c>
       <c r="E2260" t="s" s="3">
-        <v>4479</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="2261" ht="36.0" customHeight="true">
@@ -55532,16 +55565,16 @@
         <v>2260.0</v>
       </c>
       <c r="B2261" t="s" s="3">
-        <v>4480</v>
+        <v>4392</v>
       </c>
       <c r="C2261" t="s" s="2">
-        <v>6</v>
+        <v>1039</v>
       </c>
       <c r="D2261" t="s" s="2">
-        <v>4481</v>
+        <v>4314</v>
       </c>
       <c r="E2261" t="s" s="3">
-        <v>4482</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="2262" ht="36.0" customHeight="true">
@@ -55549,16 +55582,16 @@
         <v>2261.0</v>
       </c>
       <c r="B2262" t="s" s="3">
+        <v>4482</v>
+      </c>
+      <c r="C2262" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2262" t="s" s="2">
+        <v>4314</v>
+      </c>
+      <c r="E2262" t="s" s="3">
         <v>4483</v>
-      </c>
-      <c r="C2262" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2262" t="s" s="2">
-        <v>4481</v>
-      </c>
-      <c r="E2262" t="s" s="3">
-        <v>4484</v>
       </c>
     </row>
     <row r="2263" ht="36.0" customHeight="true">
@@ -55566,16 +55599,16 @@
         <v>2262.0</v>
       </c>
       <c r="B2263" t="s" s="3">
+        <v>4484</v>
+      </c>
+      <c r="C2263" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2263" t="s" s="2">
+        <v>4314</v>
+      </c>
+      <c r="E2263" t="s" s="3">
         <v>4485</v>
-      </c>
-      <c r="C2263" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2263" t="s" s="2">
-        <v>4481</v>
-      </c>
-      <c r="E2263" t="s" s="3">
-        <v>4486</v>
       </c>
     </row>
     <row r="2264" ht="36.0" customHeight="true">
@@ -55583,13 +55616,13 @@
         <v>2263.0</v>
       </c>
       <c r="B2264" t="s" s="3">
+        <v>4486</v>
+      </c>
+      <c r="C2264" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2264" t="s" s="2">
         <v>4487</v>
-      </c>
-      <c r="C2264" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2264" t="s" s="2">
-        <v>4481</v>
       </c>
       <c r="E2264" t="s" s="3">
         <v>4488</v>
@@ -55606,7 +55639,7 @@
         <v>6</v>
       </c>
       <c r="D2265" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2265" t="s" s="3">
         <v>4490</v>
@@ -55623,7 +55656,7 @@
         <v>6</v>
       </c>
       <c r="D2266" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2266" t="s" s="3">
         <v>4492</v>
@@ -55640,7 +55673,7 @@
         <v>6</v>
       </c>
       <c r="D2267" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2267" t="s" s="3">
         <v>4494</v>
@@ -55657,7 +55690,7 @@
         <v>6</v>
       </c>
       <c r="D2268" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2268" t="s" s="3">
         <v>4496</v>
@@ -55674,7 +55707,7 @@
         <v>6</v>
       </c>
       <c r="D2269" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2269" t="s" s="3">
         <v>4498</v>
@@ -55691,7 +55724,7 @@
         <v>6</v>
       </c>
       <c r="D2270" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2270" t="s" s="3">
         <v>4500</v>
@@ -55708,7 +55741,7 @@
         <v>6</v>
       </c>
       <c r="D2271" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2271" t="s" s="3">
         <v>4502</v>
@@ -55725,7 +55758,7 @@
         <v>6</v>
       </c>
       <c r="D2272" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2272" t="s" s="3">
         <v>4504</v>
@@ -55742,7 +55775,7 @@
         <v>6</v>
       </c>
       <c r="D2273" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2273" t="s" s="3">
         <v>4506</v>
@@ -55759,7 +55792,7 @@
         <v>6</v>
       </c>
       <c r="D2274" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2274" t="s" s="3">
         <v>4508</v>
@@ -55776,7 +55809,7 @@
         <v>6</v>
       </c>
       <c r="D2275" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2275" t="s" s="3">
         <v>4510</v>
@@ -55793,7 +55826,7 @@
         <v>6</v>
       </c>
       <c r="D2276" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2276" t="s" s="3">
         <v>4512</v>
@@ -55810,7 +55843,7 @@
         <v>6</v>
       </c>
       <c r="D2277" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2277" t="s" s="3">
         <v>4514</v>
@@ -55827,7 +55860,7 @@
         <v>6</v>
       </c>
       <c r="D2278" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2278" t="s" s="3">
         <v>4516</v>
@@ -55844,7 +55877,7 @@
         <v>6</v>
       </c>
       <c r="D2279" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2279" t="s" s="3">
         <v>4518</v>
@@ -55861,7 +55894,7 @@
         <v>6</v>
       </c>
       <c r="D2280" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2280" t="s" s="3">
         <v>4520</v>
@@ -55878,7 +55911,7 @@
         <v>6</v>
       </c>
       <c r="D2281" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2281" t="s" s="3">
         <v>4522</v>
@@ -55895,7 +55928,7 @@
         <v>6</v>
       </c>
       <c r="D2282" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2282" t="s" s="3">
         <v>4524</v>
@@ -55912,7 +55945,7 @@
         <v>6</v>
       </c>
       <c r="D2283" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2283" t="s" s="3">
         <v>4526</v>
@@ -55929,7 +55962,7 @@
         <v>6</v>
       </c>
       <c r="D2284" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2284" t="s" s="3">
         <v>4528</v>
@@ -55946,7 +55979,7 @@
         <v>6</v>
       </c>
       <c r="D2285" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2285" t="s" s="3">
         <v>4530</v>
@@ -55963,7 +55996,7 @@
         <v>6</v>
       </c>
       <c r="D2286" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2286" t="s" s="3">
         <v>4532</v>
@@ -55980,7 +56013,7 @@
         <v>6</v>
       </c>
       <c r="D2287" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2287" t="s" s="3">
         <v>4534</v>
@@ -55997,7 +56030,7 @@
         <v>6</v>
       </c>
       <c r="D2288" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2288" t="s" s="3">
         <v>4536</v>
@@ -56014,7 +56047,7 @@
         <v>6</v>
       </c>
       <c r="D2289" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2289" t="s" s="3">
         <v>4538</v>
@@ -56031,7 +56064,7 @@
         <v>6</v>
       </c>
       <c r="D2290" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2290" t="s" s="3">
         <v>4540</v>
@@ -56048,7 +56081,7 @@
         <v>6</v>
       </c>
       <c r="D2291" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2291" t="s" s="3">
         <v>4542</v>
@@ -56065,7 +56098,7 @@
         <v>6</v>
       </c>
       <c r="D2292" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2292" t="s" s="3">
         <v>4544</v>
@@ -56082,7 +56115,7 @@
         <v>6</v>
       </c>
       <c r="D2293" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2293" t="s" s="3">
         <v>4546</v>
@@ -56099,7 +56132,7 @@
         <v>6</v>
       </c>
       <c r="D2294" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2294" t="s" s="3">
         <v>4548</v>
@@ -56116,7 +56149,7 @@
         <v>6</v>
       </c>
       <c r="D2295" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2295" t="s" s="3">
         <v>4550</v>
@@ -56133,7 +56166,7 @@
         <v>6</v>
       </c>
       <c r="D2296" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2296" t="s" s="3">
         <v>4552</v>
@@ -56150,7 +56183,7 @@
         <v>6</v>
       </c>
       <c r="D2297" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2297" t="s" s="3">
         <v>4554</v>
@@ -56167,7 +56200,7 @@
         <v>6</v>
       </c>
       <c r="D2298" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2298" t="s" s="3">
         <v>4556</v>
@@ -56184,7 +56217,7 @@
         <v>6</v>
       </c>
       <c r="D2299" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2299" t="s" s="3">
         <v>4558</v>
@@ -56201,7 +56234,7 @@
         <v>6</v>
       </c>
       <c r="D2300" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2300" t="s" s="3">
         <v>4560</v>
@@ -56218,7 +56251,7 @@
         <v>6</v>
       </c>
       <c r="D2301" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2301" t="s" s="3">
         <v>4562</v>
@@ -56235,7 +56268,7 @@
         <v>6</v>
       </c>
       <c r="D2302" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2302" t="s" s="3">
         <v>4564</v>
@@ -56252,7 +56285,7 @@
         <v>6</v>
       </c>
       <c r="D2303" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2303" t="s" s="3">
         <v>4566</v>
@@ -56269,7 +56302,7 @@
         <v>6</v>
       </c>
       <c r="D2304" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2304" t="s" s="3">
         <v>4568</v>
@@ -56286,7 +56319,7 @@
         <v>6</v>
       </c>
       <c r="D2305" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2305" t="s" s="3">
         <v>4570</v>
@@ -56303,7 +56336,7 @@
         <v>6</v>
       </c>
       <c r="D2306" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2306" t="s" s="3">
         <v>4572</v>
@@ -56320,7 +56353,7 @@
         <v>6</v>
       </c>
       <c r="D2307" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2307" t="s" s="3">
         <v>4574</v>
@@ -56337,7 +56370,7 @@
         <v>6</v>
       </c>
       <c r="D2308" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2308" t="s" s="3">
         <v>4576</v>
@@ -56354,7 +56387,7 @@
         <v>6</v>
       </c>
       <c r="D2309" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2309" t="s" s="3">
         <v>4578</v>
@@ -56371,7 +56404,7 @@
         <v>6</v>
       </c>
       <c r="D2310" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2310" t="s" s="3">
         <v>4580</v>
@@ -56388,7 +56421,7 @@
         <v>6</v>
       </c>
       <c r="D2311" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2311" t="s" s="3">
         <v>4582</v>
@@ -56405,7 +56438,7 @@
         <v>6</v>
       </c>
       <c r="D2312" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2312" t="s" s="3">
         <v>4584</v>
@@ -56422,7 +56455,7 @@
         <v>6</v>
       </c>
       <c r="D2313" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2313" t="s" s="3">
         <v>4586</v>
@@ -56439,7 +56472,7 @@
         <v>6</v>
       </c>
       <c r="D2314" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2314" t="s" s="3">
         <v>4588</v>
@@ -56456,7 +56489,7 @@
         <v>6</v>
       </c>
       <c r="D2315" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2315" t="s" s="3">
         <v>4590</v>
@@ -56473,7 +56506,7 @@
         <v>6</v>
       </c>
       <c r="D2316" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2316" t="s" s="3">
         <v>4592</v>
@@ -56490,7 +56523,7 @@
         <v>6</v>
       </c>
       <c r="D2317" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2317" t="s" s="3">
         <v>4594</v>
@@ -56507,7 +56540,7 @@
         <v>6</v>
       </c>
       <c r="D2318" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2318" t="s" s="3">
         <v>4596</v>
@@ -56524,7 +56557,7 @@
         <v>6</v>
       </c>
       <c r="D2319" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2319" t="s" s="3">
         <v>4598</v>
@@ -56541,7 +56574,7 @@
         <v>6</v>
       </c>
       <c r="D2320" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2320" t="s" s="3">
         <v>4600</v>
@@ -56558,7 +56591,7 @@
         <v>6</v>
       </c>
       <c r="D2321" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2321" t="s" s="3">
         <v>4602</v>
@@ -56575,7 +56608,7 @@
         <v>6</v>
       </c>
       <c r="D2322" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2322" t="s" s="3">
         <v>4604</v>
@@ -56592,7 +56625,7 @@
         <v>6</v>
       </c>
       <c r="D2323" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2323" t="s" s="3">
         <v>4606</v>
@@ -56609,7 +56642,7 @@
         <v>6</v>
       </c>
       <c r="D2324" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2324" t="s" s="3">
         <v>4608</v>
@@ -56626,7 +56659,7 @@
         <v>6</v>
       </c>
       <c r="D2325" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2325" t="s" s="3">
         <v>4610</v>
@@ -56643,7 +56676,7 @@
         <v>6</v>
       </c>
       <c r="D2326" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2326" t="s" s="3">
         <v>4612</v>
@@ -56660,7 +56693,7 @@
         <v>6</v>
       </c>
       <c r="D2327" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2327" t="s" s="3">
         <v>4614</v>
@@ -56677,7 +56710,7 @@
         <v>6</v>
       </c>
       <c r="D2328" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2328" t="s" s="3">
         <v>4616</v>
@@ -56694,7 +56727,7 @@
         <v>6</v>
       </c>
       <c r="D2329" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2329" t="s" s="3">
         <v>4618</v>
@@ -56711,7 +56744,7 @@
         <v>6</v>
       </c>
       <c r="D2330" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2330" t="s" s="3">
         <v>4620</v>
@@ -56728,7 +56761,7 @@
         <v>6</v>
       </c>
       <c r="D2331" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2331" t="s" s="3">
         <v>4622</v>
@@ -56745,7 +56778,7 @@
         <v>6</v>
       </c>
       <c r="D2332" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2332" t="s" s="3">
         <v>4624</v>
@@ -56762,7 +56795,7 @@
         <v>6</v>
       </c>
       <c r="D2333" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2333" t="s" s="3">
         <v>4626</v>
@@ -56779,7 +56812,7 @@
         <v>6</v>
       </c>
       <c r="D2334" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2334" t="s" s="3">
         <v>4628</v>
@@ -56796,7 +56829,7 @@
         <v>6</v>
       </c>
       <c r="D2335" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2335" t="s" s="3">
         <v>4630</v>
@@ -56813,7 +56846,7 @@
         <v>6</v>
       </c>
       <c r="D2336" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2336" t="s" s="3">
         <v>4632</v>
@@ -56830,7 +56863,7 @@
         <v>6</v>
       </c>
       <c r="D2337" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2337" t="s" s="3">
         <v>4634</v>
@@ -56847,7 +56880,7 @@
         <v>6</v>
       </c>
       <c r="D2338" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2338" t="s" s="3">
         <v>4636</v>
@@ -56864,7 +56897,7 @@
         <v>6</v>
       </c>
       <c r="D2339" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2339" t="s" s="3">
         <v>4638</v>
@@ -56881,7 +56914,7 @@
         <v>6</v>
       </c>
       <c r="D2340" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2340" t="s" s="3">
         <v>4640</v>
@@ -56898,7 +56931,7 @@
         <v>6</v>
       </c>
       <c r="D2341" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2341" t="s" s="3">
         <v>4642</v>
@@ -56915,7 +56948,7 @@
         <v>6</v>
       </c>
       <c r="D2342" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2342" t="s" s="3">
         <v>4644</v>
@@ -56932,7 +56965,7 @@
         <v>6</v>
       </c>
       <c r="D2343" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2343" t="s" s="3">
         <v>4646</v>
@@ -56949,7 +56982,7 @@
         <v>6</v>
       </c>
       <c r="D2344" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2344" t="s" s="3">
         <v>4648</v>
@@ -56966,7 +56999,7 @@
         <v>6</v>
       </c>
       <c r="D2345" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2345" t="s" s="3">
         <v>4650</v>
@@ -56983,7 +57016,7 @@
         <v>6</v>
       </c>
       <c r="D2346" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2346" t="s" s="3">
         <v>4652</v>
@@ -57000,7 +57033,7 @@
         <v>6</v>
       </c>
       <c r="D2347" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2347" t="s" s="3">
         <v>4654</v>
@@ -57017,7 +57050,7 @@
         <v>6</v>
       </c>
       <c r="D2348" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2348" t="s" s="3">
         <v>4656</v>
@@ -57034,7 +57067,7 @@
         <v>6</v>
       </c>
       <c r="D2349" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2349" t="s" s="3">
         <v>4658</v>
@@ -57045,16 +57078,16 @@
         <v>2349.0</v>
       </c>
       <c r="B2350" t="s" s="3">
-        <v>525</v>
+        <v>4659</v>
       </c>
       <c r="C2350" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2350" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2350" t="s" s="3">
-        <v>4659</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="2351" ht="36.0" customHeight="true">
@@ -57062,16 +57095,16 @@
         <v>2350.0</v>
       </c>
       <c r="B2351" t="s" s="3">
-        <v>4660</v>
+        <v>4661</v>
       </c>
       <c r="C2351" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2351" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2351" t="s" s="3">
-        <v>4661</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="2352" ht="36.0" customHeight="true">
@@ -57079,16 +57112,16 @@
         <v>2351.0</v>
       </c>
       <c r="B2352" t="s" s="3">
-        <v>4662</v>
+        <v>4663</v>
       </c>
       <c r="C2352" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2352" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2352" t="s" s="3">
-        <v>4663</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="2353" ht="36.0" customHeight="true">
@@ -57096,13 +57129,13 @@
         <v>2352.0</v>
       </c>
       <c r="B2353" t="s" s="3">
-        <v>4664</v>
+        <v>527</v>
       </c>
       <c r="C2353" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2353" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2353" t="s" s="3">
         <v>4665</v>
@@ -57119,7 +57152,7 @@
         <v>6</v>
       </c>
       <c r="D2354" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2354" t="s" s="3">
         <v>4667</v>
@@ -57136,7 +57169,7 @@
         <v>6</v>
       </c>
       <c r="D2355" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2355" t="s" s="3">
         <v>4669</v>
@@ -57153,7 +57186,7 @@
         <v>6</v>
       </c>
       <c r="D2356" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2356" t="s" s="3">
         <v>4671</v>
@@ -57170,7 +57203,7 @@
         <v>6</v>
       </c>
       <c r="D2357" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2357" t="s" s="3">
         <v>4673</v>
@@ -57187,7 +57220,7 @@
         <v>6</v>
       </c>
       <c r="D2358" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2358" t="s" s="3">
         <v>4675</v>
@@ -57204,7 +57237,7 @@
         <v>6</v>
       </c>
       <c r="D2359" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2359" t="s" s="3">
         <v>4677</v>
@@ -57221,7 +57254,7 @@
         <v>6</v>
       </c>
       <c r="D2360" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2360" t="s" s="3">
         <v>4679</v>
@@ -57238,7 +57271,7 @@
         <v>6</v>
       </c>
       <c r="D2361" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2361" t="s" s="3">
         <v>4681</v>
@@ -57255,7 +57288,7 @@
         <v>6</v>
       </c>
       <c r="D2362" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2362" t="s" s="3">
         <v>4683</v>
@@ -57272,7 +57305,7 @@
         <v>6</v>
       </c>
       <c r="D2363" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2363" t="s" s="3">
         <v>4685</v>
@@ -57283,16 +57316,16 @@
         <v>2363.0</v>
       </c>
       <c r="B2364" t="s" s="3">
-        <v>1510</v>
+        <v>4686</v>
       </c>
       <c r="C2364" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2364" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2364" t="s" s="3">
-        <v>4686</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="2365" ht="36.0" customHeight="true">
@@ -57300,16 +57333,16 @@
         <v>2364.0</v>
       </c>
       <c r="B2365" t="s" s="3">
-        <v>4687</v>
+        <v>4688</v>
       </c>
       <c r="C2365" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2365" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2365" t="s" s="3">
-        <v>4688</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="2366" ht="36.0" customHeight="true">
@@ -57317,16 +57350,16 @@
         <v>2365.0</v>
       </c>
       <c r="B2366" t="s" s="3">
-        <v>4689</v>
+        <v>4690</v>
       </c>
       <c r="C2366" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2366" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2366" t="s" s="3">
-        <v>4690</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="2367" ht="36.0" customHeight="true">
@@ -57334,13 +57367,13 @@
         <v>2366.0</v>
       </c>
       <c r="B2367" t="s" s="3">
-        <v>4691</v>
+        <v>1510</v>
       </c>
       <c r="C2367" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2367" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2367" t="s" s="3">
         <v>4692</v>
@@ -57357,7 +57390,7 @@
         <v>6</v>
       </c>
       <c r="D2368" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2368" t="s" s="3">
         <v>4694</v>
@@ -57374,7 +57407,7 @@
         <v>6</v>
       </c>
       <c r="D2369" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2369" t="s" s="3">
         <v>4696</v>
@@ -57391,7 +57424,7 @@
         <v>6</v>
       </c>
       <c r="D2370" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2370" t="s" s="3">
         <v>4698</v>
@@ -57408,7 +57441,7 @@
         <v>6</v>
       </c>
       <c r="D2371" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2371" t="s" s="3">
         <v>4700</v>
@@ -57425,7 +57458,7 @@
         <v>6</v>
       </c>
       <c r="D2372" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2372" t="s" s="3">
         <v>4702</v>
@@ -57442,7 +57475,7 @@
         <v>6</v>
       </c>
       <c r="D2373" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2373" t="s" s="3">
         <v>4704</v>
@@ -57459,7 +57492,7 @@
         <v>6</v>
       </c>
       <c r="D2374" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2374" t="s" s="3">
         <v>4706</v>
@@ -57476,7 +57509,7 @@
         <v>6</v>
       </c>
       <c r="D2375" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2375" t="s" s="3">
         <v>4708</v>
@@ -57493,7 +57526,7 @@
         <v>6</v>
       </c>
       <c r="D2376" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2376" t="s" s="3">
         <v>4710</v>
@@ -57510,7 +57543,7 @@
         <v>6</v>
       </c>
       <c r="D2377" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2377" t="s" s="3">
         <v>4712</v>
@@ -57527,7 +57560,7 @@
         <v>6</v>
       </c>
       <c r="D2378" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2378" t="s" s="3">
         <v>4714</v>
@@ -57544,7 +57577,7 @@
         <v>6</v>
       </c>
       <c r="D2379" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2379" t="s" s="3">
         <v>4716</v>
@@ -57561,7 +57594,7 @@
         <v>6</v>
       </c>
       <c r="D2380" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2380" t="s" s="3">
         <v>4718</v>
@@ -57578,7 +57611,7 @@
         <v>6</v>
       </c>
       <c r="D2381" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2381" t="s" s="3">
         <v>4720</v>
@@ -57595,7 +57628,7 @@
         <v>6</v>
       </c>
       <c r="D2382" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2382" t="s" s="3">
         <v>4722</v>
@@ -57612,7 +57645,7 @@
         <v>6</v>
       </c>
       <c r="D2383" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2383" t="s" s="3">
         <v>4724</v>
@@ -57629,7 +57662,7 @@
         <v>6</v>
       </c>
       <c r="D2384" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2384" t="s" s="3">
         <v>4726</v>
@@ -57646,7 +57679,7 @@
         <v>6</v>
       </c>
       <c r="D2385" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2385" t="s" s="3">
         <v>4728</v>
@@ -57663,7 +57696,7 @@
         <v>6</v>
       </c>
       <c r="D2386" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2386" t="s" s="3">
         <v>4730</v>
@@ -57680,7 +57713,7 @@
         <v>6</v>
       </c>
       <c r="D2387" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2387" t="s" s="3">
         <v>4732</v>
@@ -57697,7 +57730,7 @@
         <v>6</v>
       </c>
       <c r="D2388" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2388" t="s" s="3">
         <v>4734</v>
@@ -57714,7 +57747,7 @@
         <v>6</v>
       </c>
       <c r="D2389" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2389" t="s" s="3">
         <v>4736</v>
@@ -57731,7 +57764,7 @@
         <v>6</v>
       </c>
       <c r="D2390" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2390" t="s" s="3">
         <v>4738</v>
@@ -57748,7 +57781,7 @@
         <v>6</v>
       </c>
       <c r="D2391" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2391" t="s" s="3">
         <v>4740</v>
@@ -57765,7 +57798,7 @@
         <v>6</v>
       </c>
       <c r="D2392" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2392" t="s" s="3">
         <v>4742</v>
@@ -57782,7 +57815,7 @@
         <v>6</v>
       </c>
       <c r="D2393" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2393" t="s" s="3">
         <v>4744</v>
@@ -57799,7 +57832,7 @@
         <v>6</v>
       </c>
       <c r="D2394" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2394" t="s" s="3">
         <v>4746</v>
@@ -57816,7 +57849,7 @@
         <v>6</v>
       </c>
       <c r="D2395" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2395" t="s" s="3">
         <v>4748</v>
@@ -57833,7 +57866,7 @@
         <v>6</v>
       </c>
       <c r="D2396" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2396" t="s" s="3">
         <v>4750</v>
@@ -57850,7 +57883,7 @@
         <v>6</v>
       </c>
       <c r="D2397" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2397" t="s" s="3">
         <v>4752</v>
@@ -57867,7 +57900,7 @@
         <v>6</v>
       </c>
       <c r="D2398" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2398" t="s" s="3">
         <v>4754</v>
@@ -57884,7 +57917,7 @@
         <v>6</v>
       </c>
       <c r="D2399" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2399" t="s" s="3">
         <v>4756</v>
@@ -57901,7 +57934,7 @@
         <v>6</v>
       </c>
       <c r="D2400" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2400" t="s" s="3">
         <v>4758</v>
@@ -57918,7 +57951,7 @@
         <v>6</v>
       </c>
       <c r="D2401" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2401" t="s" s="3">
         <v>4760</v>
@@ -57935,7 +57968,7 @@
         <v>6</v>
       </c>
       <c r="D2402" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2402" t="s" s="3">
         <v>4762</v>
@@ -57952,7 +57985,7 @@
         <v>6</v>
       </c>
       <c r="D2403" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2403" t="s" s="3">
         <v>4764</v>
@@ -57969,7 +58002,7 @@
         <v>6</v>
       </c>
       <c r="D2404" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2404" t="s" s="3">
         <v>4766</v>
@@ -57986,7 +58019,7 @@
         <v>6</v>
       </c>
       <c r="D2405" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2405" t="s" s="3">
         <v>4768</v>
@@ -58000,10 +58033,10 @@
         <v>4769</v>
       </c>
       <c r="C2406" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2406" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2406" t="s" s="3">
         <v>4770</v>
@@ -58017,10 +58050,10 @@
         <v>4771</v>
       </c>
       <c r="C2407" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2407" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2407" t="s" s="3">
         <v>4772</v>
@@ -58034,10 +58067,10 @@
         <v>4773</v>
       </c>
       <c r="C2408" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2408" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2408" t="s" s="3">
         <v>4774</v>
@@ -58054,7 +58087,7 @@
         <v>812</v>
       </c>
       <c r="D2409" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2409" t="s" s="3">
         <v>4776</v>
@@ -58071,7 +58104,7 @@
         <v>812</v>
       </c>
       <c r="D2410" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2410" t="s" s="3">
         <v>4778</v>
@@ -58088,7 +58121,7 @@
         <v>812</v>
       </c>
       <c r="D2411" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2411" t="s" s="3">
         <v>4780</v>
@@ -58105,7 +58138,7 @@
         <v>812</v>
       </c>
       <c r="D2412" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2412" t="s" s="3">
         <v>4782</v>
@@ -58122,7 +58155,7 @@
         <v>812</v>
       </c>
       <c r="D2413" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2413" t="s" s="3">
         <v>4784</v>
@@ -58139,7 +58172,7 @@
         <v>812</v>
       </c>
       <c r="D2414" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2414" t="s" s="3">
         <v>4786</v>
@@ -58156,7 +58189,7 @@
         <v>812</v>
       </c>
       <c r="D2415" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2415" t="s" s="3">
         <v>4788</v>
@@ -58173,7 +58206,7 @@
         <v>812</v>
       </c>
       <c r="D2416" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2416" t="s" s="3">
         <v>4790</v>
@@ -58190,7 +58223,7 @@
         <v>812</v>
       </c>
       <c r="D2417" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2417" t="s" s="3">
         <v>4792</v>
@@ -58207,7 +58240,7 @@
         <v>812</v>
       </c>
       <c r="D2418" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2418" t="s" s="3">
         <v>4794</v>
@@ -58224,7 +58257,7 @@
         <v>812</v>
       </c>
       <c r="D2419" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2419" t="s" s="3">
         <v>4796</v>
@@ -58241,7 +58274,7 @@
         <v>812</v>
       </c>
       <c r="D2420" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2420" t="s" s="3">
         <v>4798</v>
@@ -58258,7 +58291,7 @@
         <v>812</v>
       </c>
       <c r="D2421" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2421" t="s" s="3">
         <v>4800</v>
@@ -58275,7 +58308,7 @@
         <v>812</v>
       </c>
       <c r="D2422" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2422" t="s" s="3">
         <v>4802</v>
@@ -58292,7 +58325,7 @@
         <v>812</v>
       </c>
       <c r="D2423" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2423" t="s" s="3">
         <v>4804</v>
@@ -58309,7 +58342,7 @@
         <v>812</v>
       </c>
       <c r="D2424" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2424" t="s" s="3">
         <v>4806</v>
@@ -58326,7 +58359,7 @@
         <v>812</v>
       </c>
       <c r="D2425" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2425" t="s" s="3">
         <v>4808</v>
@@ -58343,7 +58376,7 @@
         <v>812</v>
       </c>
       <c r="D2426" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2426" t="s" s="3">
         <v>4810</v>
@@ -58360,10 +58393,10 @@
         <v>812</v>
       </c>
       <c r="D2427" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2427" t="s" s="3">
-        <v>4702</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="2428" ht="36.0" customHeight="true">
@@ -58371,16 +58404,16 @@
         <v>2427.0</v>
       </c>
       <c r="B2428" t="s" s="3">
-        <v>4812</v>
+        <v>4813</v>
       </c>
       <c r="C2428" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2428" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2428" t="s" s="3">
-        <v>4813</v>
+        <v>4814</v>
       </c>
     </row>
     <row r="2429" ht="36.0" customHeight="true">
@@ -58388,16 +58421,16 @@
         <v>2428.0</v>
       </c>
       <c r="B2429" t="s" s="3">
-        <v>4814</v>
+        <v>4815</v>
       </c>
       <c r="C2429" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2429" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2429" t="s" s="3">
-        <v>4815</v>
+        <v>4816</v>
       </c>
     </row>
     <row r="2430" ht="36.0" customHeight="true">
@@ -58405,16 +58438,16 @@
         <v>2429.0</v>
       </c>
       <c r="B2430" t="s" s="3">
-        <v>4816</v>
+        <v>4817</v>
       </c>
       <c r="C2430" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2430" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2430" t="s" s="3">
-        <v>4817</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="2431" ht="36.0" customHeight="true">
@@ -58428,7 +58461,7 @@
         <v>812</v>
       </c>
       <c r="D2431" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2431" t="s" s="3">
         <v>4819</v>
@@ -58445,7 +58478,7 @@
         <v>812</v>
       </c>
       <c r="D2432" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2432" t="s" s="3">
         <v>4821</v>
@@ -58462,7 +58495,7 @@
         <v>812</v>
       </c>
       <c r="D2433" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2433" t="s" s="3">
         <v>4823</v>
@@ -58479,7 +58512,7 @@
         <v>812</v>
       </c>
       <c r="D2434" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2434" t="s" s="3">
         <v>4825</v>
@@ -58496,7 +58529,7 @@
         <v>812</v>
       </c>
       <c r="D2435" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2435" t="s" s="3">
         <v>4827</v>
@@ -58513,7 +58546,7 @@
         <v>812</v>
       </c>
       <c r="D2436" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2436" t="s" s="3">
         <v>4829</v>
@@ -58530,7 +58563,7 @@
         <v>812</v>
       </c>
       <c r="D2437" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2437" t="s" s="3">
         <v>4831</v>
@@ -58547,7 +58580,7 @@
         <v>812</v>
       </c>
       <c r="D2438" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2438" t="s" s="3">
         <v>4833</v>
@@ -58564,7 +58597,7 @@
         <v>812</v>
       </c>
       <c r="D2439" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2439" t="s" s="3">
         <v>4835</v>
@@ -58581,7 +58614,7 @@
         <v>812</v>
       </c>
       <c r="D2440" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2440" t="s" s="3">
         <v>4837</v>
@@ -58598,7 +58631,7 @@
         <v>812</v>
       </c>
       <c r="D2441" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2441" t="s" s="3">
         <v>4839</v>
@@ -58615,7 +58648,7 @@
         <v>812</v>
       </c>
       <c r="D2442" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2442" t="s" s="3">
         <v>4841</v>
@@ -58632,7 +58665,7 @@
         <v>812</v>
       </c>
       <c r="D2443" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2443" t="s" s="3">
         <v>4843</v>
@@ -58649,7 +58682,7 @@
         <v>812</v>
       </c>
       <c r="D2444" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2444" t="s" s="3">
         <v>4845</v>
@@ -58666,7 +58699,7 @@
         <v>812</v>
       </c>
       <c r="D2445" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2445" t="s" s="3">
         <v>4847</v>
@@ -58683,7 +58716,7 @@
         <v>812</v>
       </c>
       <c r="D2446" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2446" t="s" s="3">
         <v>4849</v>
@@ -58700,7 +58733,7 @@
         <v>812</v>
       </c>
       <c r="D2447" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2447" t="s" s="3">
         <v>4851</v>
@@ -58717,7 +58750,7 @@
         <v>812</v>
       </c>
       <c r="D2448" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2448" t="s" s="3">
         <v>4853</v>
@@ -58734,7 +58767,7 @@
         <v>812</v>
       </c>
       <c r="D2449" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2449" t="s" s="3">
         <v>4855</v>
@@ -58751,7 +58784,7 @@
         <v>812</v>
       </c>
       <c r="D2450" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2450" t="s" s="3">
         <v>4857</v>
@@ -58768,7 +58801,7 @@
         <v>812</v>
       </c>
       <c r="D2451" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2451" t="s" s="3">
         <v>4859</v>
@@ -58785,7 +58818,7 @@
         <v>812</v>
       </c>
       <c r="D2452" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2452" t="s" s="3">
         <v>4861</v>
@@ -58802,7 +58835,7 @@
         <v>812</v>
       </c>
       <c r="D2453" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2453" t="s" s="3">
         <v>4863</v>
@@ -58819,7 +58852,7 @@
         <v>812</v>
       </c>
       <c r="D2454" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2454" t="s" s="3">
         <v>4865</v>
@@ -58836,7 +58869,7 @@
         <v>812</v>
       </c>
       <c r="D2455" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2455" t="s" s="3">
         <v>4867</v>
@@ -58853,7 +58886,7 @@
         <v>812</v>
       </c>
       <c r="D2456" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2456" t="s" s="3">
         <v>4869</v>
@@ -58870,7 +58903,7 @@
         <v>812</v>
       </c>
       <c r="D2457" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2457" t="s" s="3">
         <v>4871</v>
@@ -58887,7 +58920,7 @@
         <v>812</v>
       </c>
       <c r="D2458" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2458" t="s" s="3">
         <v>4873</v>
@@ -58904,7 +58937,7 @@
         <v>812</v>
       </c>
       <c r="D2459" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2459" t="s" s="3">
         <v>4875</v>
@@ -58921,7 +58954,7 @@
         <v>812</v>
       </c>
       <c r="D2460" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2460" t="s" s="3">
         <v>4877</v>
@@ -58938,7 +58971,7 @@
         <v>812</v>
       </c>
       <c r="D2461" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2461" t="s" s="3">
         <v>4879</v>
@@ -58955,7 +58988,7 @@
         <v>812</v>
       </c>
       <c r="D2462" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2462" t="s" s="3">
         <v>4881</v>
@@ -58972,7 +59005,7 @@
         <v>812</v>
       </c>
       <c r="D2463" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2463" t="s" s="3">
         <v>4883</v>
@@ -58989,7 +59022,7 @@
         <v>812</v>
       </c>
       <c r="D2464" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2464" t="s" s="3">
         <v>4885</v>
@@ -59006,7 +59039,7 @@
         <v>812</v>
       </c>
       <c r="D2465" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2465" t="s" s="3">
         <v>4887</v>
@@ -59023,7 +59056,7 @@
         <v>812</v>
       </c>
       <c r="D2466" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2466" t="s" s="3">
         <v>4889</v>
@@ -59040,7 +59073,7 @@
         <v>812</v>
       </c>
       <c r="D2467" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2467" t="s" s="3">
         <v>4891</v>
@@ -59057,7 +59090,7 @@
         <v>812</v>
       </c>
       <c r="D2468" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2468" t="s" s="3">
         <v>4893</v>
@@ -59074,7 +59107,7 @@
         <v>812</v>
       </c>
       <c r="D2469" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2469" t="s" s="3">
         <v>4895</v>
@@ -59091,7 +59124,7 @@
         <v>812</v>
       </c>
       <c r="D2470" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2470" t="s" s="3">
         <v>4897</v>
@@ -59108,7 +59141,7 @@
         <v>812</v>
       </c>
       <c r="D2471" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2471" t="s" s="3">
         <v>4899</v>
@@ -59125,7 +59158,7 @@
         <v>812</v>
       </c>
       <c r="D2472" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2472" t="s" s="3">
         <v>4901</v>
@@ -59142,7 +59175,7 @@
         <v>812</v>
       </c>
       <c r="D2473" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2473" t="s" s="3">
         <v>4903</v>
@@ -59159,7 +59192,7 @@
         <v>812</v>
       </c>
       <c r="D2474" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2474" t="s" s="3">
         <v>4905</v>
@@ -59176,7 +59209,7 @@
         <v>812</v>
       </c>
       <c r="D2475" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2475" t="s" s="3">
         <v>4907</v>
@@ -59193,7 +59226,7 @@
         <v>812</v>
       </c>
       <c r="D2476" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2476" t="s" s="3">
         <v>4909</v>
@@ -59210,7 +59243,7 @@
         <v>812</v>
       </c>
       <c r="D2477" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2477" t="s" s="3">
         <v>4911</v>
@@ -59227,7 +59260,7 @@
         <v>812</v>
       </c>
       <c r="D2478" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2478" t="s" s="3">
         <v>4913</v>
@@ -59244,7 +59277,7 @@
         <v>812</v>
       </c>
       <c r="D2479" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2479" t="s" s="3">
         <v>4915</v>
@@ -59261,7 +59294,7 @@
         <v>812</v>
       </c>
       <c r="D2480" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2480" t="s" s="3">
         <v>4917</v>
@@ -59278,7 +59311,7 @@
         <v>812</v>
       </c>
       <c r="D2481" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2481" t="s" s="3">
         <v>4919</v>
@@ -59292,10 +59325,10 @@
         <v>4920</v>
       </c>
       <c r="C2482" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2482" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2482" t="s" s="3">
         <v>4921</v>
@@ -59309,10 +59342,10 @@
         <v>4922</v>
       </c>
       <c r="C2483" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2483" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2483" t="s" s="3">
         <v>4923</v>
@@ -59326,10 +59359,10 @@
         <v>4924</v>
       </c>
       <c r="C2484" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2484" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2484" t="s" s="3">
         <v>4925</v>
@@ -59346,7 +59379,7 @@
         <v>1039</v>
       </c>
       <c r="D2485" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2485" t="s" s="3">
         <v>4927</v>
@@ -59363,7 +59396,7 @@
         <v>1039</v>
       </c>
       <c r="D2486" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2486" t="s" s="3">
         <v>4929</v>
@@ -59380,7 +59413,7 @@
         <v>1039</v>
       </c>
       <c r="D2487" t="s" s="2">
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="E2487" t="s" s="3">
         <v>4931</v>
@@ -59394,13 +59427,13 @@
         <v>4932</v>
       </c>
       <c r="C2488" t="s" s="2">
-        <v>6</v>
+        <v>1039</v>
       </c>
       <c r="D2488" t="s" s="2">
+        <v>4487</v>
+      </c>
+      <c r="E2488" t="s" s="3">
         <v>4933</v>
-      </c>
-      <c r="E2488" t="s" s="3">
-        <v>4934</v>
       </c>
     </row>
     <row r="2489" ht="36.0" customHeight="true">
@@ -59408,16 +59441,16 @@
         <v>2488.0</v>
       </c>
       <c r="B2489" t="s" s="3">
+        <v>4934</v>
+      </c>
+      <c r="C2489" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2489" t="s" s="2">
+        <v>4487</v>
+      </c>
+      <c r="E2489" t="s" s="3">
         <v>4935</v>
-      </c>
-      <c r="C2489" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2489" t="s" s="2">
-        <v>4933</v>
-      </c>
-      <c r="E2489" t="s" s="3">
-        <v>4936</v>
       </c>
     </row>
     <row r="2490" ht="36.0" customHeight="true">
@@ -59425,16 +59458,16 @@
         <v>2489.0</v>
       </c>
       <c r="B2490" t="s" s="3">
+        <v>4936</v>
+      </c>
+      <c r="C2490" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2490" t="s" s="2">
+        <v>4487</v>
+      </c>
+      <c r="E2490" t="s" s="3">
         <v>4937</v>
-      </c>
-      <c r="C2490" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2490" t="s" s="2">
-        <v>4933</v>
-      </c>
-      <c r="E2490" t="s" s="3">
-        <v>4938</v>
       </c>
     </row>
     <row r="2491" ht="36.0" customHeight="true">
@@ -59442,13 +59475,13 @@
         <v>2490.0</v>
       </c>
       <c r="B2491" t="s" s="3">
+        <v>4938</v>
+      </c>
+      <c r="C2491" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2491" t="s" s="2">
         <v>4939</v>
-      </c>
-      <c r="C2491" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2491" t="s" s="2">
-        <v>4933</v>
       </c>
       <c r="E2491" t="s" s="3">
         <v>4940</v>
@@ -59465,7 +59498,7 @@
         <v>6</v>
       </c>
       <c r="D2492" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2492" t="s" s="3">
         <v>4942</v>
@@ -59482,7 +59515,7 @@
         <v>6</v>
       </c>
       <c r="D2493" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2493" t="s" s="3">
         <v>4944</v>
@@ -59499,7 +59532,7 @@
         <v>6</v>
       </c>
       <c r="D2494" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2494" t="s" s="3">
         <v>4946</v>
@@ -59516,7 +59549,7 @@
         <v>6</v>
       </c>
       <c r="D2495" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2495" t="s" s="3">
         <v>4948</v>
@@ -59533,7 +59566,7 @@
         <v>6</v>
       </c>
       <c r="D2496" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2496" t="s" s="3">
         <v>4950</v>
@@ -59550,7 +59583,7 @@
         <v>6</v>
       </c>
       <c r="D2497" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2497" t="s" s="3">
         <v>4952</v>
@@ -59567,7 +59600,7 @@
         <v>6</v>
       </c>
       <c r="D2498" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2498" t="s" s="3">
         <v>4954</v>
@@ -59584,7 +59617,7 @@
         <v>6</v>
       </c>
       <c r="D2499" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2499" t="s" s="3">
         <v>4956</v>
@@ -59601,7 +59634,7 @@
         <v>6</v>
       </c>
       <c r="D2500" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2500" t="s" s="3">
         <v>4958</v>
@@ -59618,7 +59651,7 @@
         <v>6</v>
       </c>
       <c r="D2501" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2501" t="s" s="3">
         <v>4960</v>
@@ -59635,7 +59668,7 @@
         <v>6</v>
       </c>
       <c r="D2502" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2502" t="s" s="3">
         <v>4962</v>
@@ -59652,7 +59685,7 @@
         <v>6</v>
       </c>
       <c r="D2503" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2503" t="s" s="3">
         <v>4964</v>
@@ -59669,7 +59702,7 @@
         <v>6</v>
       </c>
       <c r="D2504" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2504" t="s" s="3">
         <v>4966</v>
@@ -59686,7 +59719,7 @@
         <v>6</v>
       </c>
       <c r="D2505" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2505" t="s" s="3">
         <v>4968</v>
@@ -59703,7 +59736,7 @@
         <v>6</v>
       </c>
       <c r="D2506" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2506" t="s" s="3">
         <v>4970</v>
@@ -59720,7 +59753,7 @@
         <v>6</v>
       </c>
       <c r="D2507" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2507" t="s" s="3">
         <v>4972</v>
@@ -59737,7 +59770,7 @@
         <v>6</v>
       </c>
       <c r="D2508" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2508" t="s" s="3">
         <v>4974</v>
@@ -59754,7 +59787,7 @@
         <v>6</v>
       </c>
       <c r="D2509" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2509" t="s" s="3">
         <v>4976</v>
@@ -59771,7 +59804,7 @@
         <v>6</v>
       </c>
       <c r="D2510" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2510" t="s" s="3">
         <v>4978</v>
@@ -59788,7 +59821,7 @@
         <v>6</v>
       </c>
       <c r="D2511" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2511" t="s" s="3">
         <v>4980</v>
@@ -59805,7 +59838,7 @@
         <v>6</v>
       </c>
       <c r="D2512" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2512" t="s" s="3">
         <v>4982</v>
@@ -59822,7 +59855,7 @@
         <v>6</v>
       </c>
       <c r="D2513" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2513" t="s" s="3">
         <v>4984</v>
@@ -59839,7 +59872,7 @@
         <v>6</v>
       </c>
       <c r="D2514" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2514" t="s" s="3">
         <v>4986</v>
@@ -59856,7 +59889,7 @@
         <v>6</v>
       </c>
       <c r="D2515" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2515" t="s" s="3">
         <v>4988</v>
@@ -59873,7 +59906,7 @@
         <v>6</v>
       </c>
       <c r="D2516" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2516" t="s" s="3">
         <v>4990</v>
@@ -59890,7 +59923,7 @@
         <v>6</v>
       </c>
       <c r="D2517" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2517" t="s" s="3">
         <v>4992</v>
@@ -59907,7 +59940,7 @@
         <v>6</v>
       </c>
       <c r="D2518" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2518" t="s" s="3">
         <v>4994</v>
@@ -59924,7 +59957,7 @@
         <v>6</v>
       </c>
       <c r="D2519" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2519" t="s" s="3">
         <v>4996</v>
@@ -59941,7 +59974,7 @@
         <v>6</v>
       </c>
       <c r="D2520" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2520" t="s" s="3">
         <v>4998</v>
@@ -59958,7 +59991,7 @@
         <v>6</v>
       </c>
       <c r="D2521" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2521" t="s" s="3">
         <v>5000</v>
@@ -59975,7 +60008,7 @@
         <v>6</v>
       </c>
       <c r="D2522" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2522" t="s" s="3">
         <v>5002</v>
@@ -59992,7 +60025,7 @@
         <v>6</v>
       </c>
       <c r="D2523" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2523" t="s" s="3">
         <v>5004</v>
@@ -60009,7 +60042,7 @@
         <v>6</v>
       </c>
       <c r="D2524" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2524" t="s" s="3">
         <v>5006</v>
@@ -60026,7 +60059,7 @@
         <v>6</v>
       </c>
       <c r="D2525" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2525" t="s" s="3">
         <v>5008</v>
@@ -60043,7 +60076,7 @@
         <v>6</v>
       </c>
       <c r="D2526" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2526" t="s" s="3">
         <v>5010</v>
@@ -60060,7 +60093,7 @@
         <v>6</v>
       </c>
       <c r="D2527" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2527" t="s" s="3">
         <v>5012</v>
@@ -60077,7 +60110,7 @@
         <v>6</v>
       </c>
       <c r="D2528" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2528" t="s" s="3">
         <v>5014</v>
@@ -60094,7 +60127,7 @@
         <v>6</v>
       </c>
       <c r="D2529" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2529" t="s" s="3">
         <v>5016</v>
@@ -60111,7 +60144,7 @@
         <v>6</v>
       </c>
       <c r="D2530" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2530" t="s" s="3">
         <v>5018</v>
@@ -60128,7 +60161,7 @@
         <v>6</v>
       </c>
       <c r="D2531" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2531" t="s" s="3">
         <v>5020</v>
@@ -60145,7 +60178,7 @@
         <v>6</v>
       </c>
       <c r="D2532" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2532" t="s" s="3">
         <v>5022</v>
@@ -60162,7 +60195,7 @@
         <v>6</v>
       </c>
       <c r="D2533" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2533" t="s" s="3">
         <v>5024</v>
@@ -60179,7 +60212,7 @@
         <v>6</v>
       </c>
       <c r="D2534" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2534" t="s" s="3">
         <v>5026</v>
@@ -60196,7 +60229,7 @@
         <v>6</v>
       </c>
       <c r="D2535" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2535" t="s" s="3">
         <v>5028</v>
@@ -60213,7 +60246,7 @@
         <v>6</v>
       </c>
       <c r="D2536" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2536" t="s" s="3">
         <v>5030</v>
@@ -60230,7 +60263,7 @@
         <v>6</v>
       </c>
       <c r="D2537" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2537" t="s" s="3">
         <v>5032</v>
@@ -60247,7 +60280,7 @@
         <v>6</v>
       </c>
       <c r="D2538" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2538" t="s" s="3">
         <v>5034</v>
@@ -60264,7 +60297,7 @@
         <v>6</v>
       </c>
       <c r="D2539" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2539" t="s" s="3">
         <v>5036</v>
@@ -60281,7 +60314,7 @@
         <v>6</v>
       </c>
       <c r="D2540" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2540" t="s" s="3">
         <v>5038</v>
@@ -60298,7 +60331,7 @@
         <v>6</v>
       </c>
       <c r="D2541" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2541" t="s" s="3">
         <v>5040</v>
@@ -60315,7 +60348,7 @@
         <v>6</v>
       </c>
       <c r="D2542" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2542" t="s" s="3">
         <v>5042</v>
@@ -60332,7 +60365,7 @@
         <v>6</v>
       </c>
       <c r="D2543" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2543" t="s" s="3">
         <v>5044</v>
@@ -60349,7 +60382,7 @@
         <v>6</v>
       </c>
       <c r="D2544" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2544" t="s" s="3">
         <v>5046</v>
@@ -60363,10 +60396,10 @@
         <v>5047</v>
       </c>
       <c r="C2545" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2545" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2545" t="s" s="3">
         <v>5048</v>
@@ -60380,10 +60413,10 @@
         <v>5049</v>
       </c>
       <c r="C2546" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2546" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2546" t="s" s="3">
         <v>5050</v>
@@ -60397,10 +60430,10 @@
         <v>5051</v>
       </c>
       <c r="C2547" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2547" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2547" t="s" s="3">
         <v>5052</v>
@@ -60417,7 +60450,7 @@
         <v>812</v>
       </c>
       <c r="D2548" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2548" t="s" s="3">
         <v>5054</v>
@@ -60434,7 +60467,7 @@
         <v>812</v>
       </c>
       <c r="D2549" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2549" t="s" s="3">
         <v>5056</v>
@@ -60451,7 +60484,7 @@
         <v>812</v>
       </c>
       <c r="D2550" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2550" t="s" s="3">
         <v>5058</v>
@@ -60468,7 +60501,7 @@
         <v>812</v>
       </c>
       <c r="D2551" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2551" t="s" s="3">
         <v>5060</v>
@@ -60485,7 +60518,7 @@
         <v>812</v>
       </c>
       <c r="D2552" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2552" t="s" s="3">
         <v>5062</v>
@@ -60502,7 +60535,7 @@
         <v>812</v>
       </c>
       <c r="D2553" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2553" t="s" s="3">
         <v>5064</v>
@@ -60519,7 +60552,7 @@
         <v>812</v>
       </c>
       <c r="D2554" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2554" t="s" s="3">
         <v>5066</v>
@@ -60536,7 +60569,7 @@
         <v>812</v>
       </c>
       <c r="D2555" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2555" t="s" s="3">
         <v>5068</v>
@@ -60553,7 +60586,7 @@
         <v>812</v>
       </c>
       <c r="D2556" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2556" t="s" s="3">
         <v>5070</v>
@@ -60570,7 +60603,7 @@
         <v>812</v>
       </c>
       <c r="D2557" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2557" t="s" s="3">
         <v>5072</v>
@@ -60587,7 +60620,7 @@
         <v>812</v>
       </c>
       <c r="D2558" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2558" t="s" s="3">
         <v>5074</v>
@@ -60604,7 +60637,7 @@
         <v>812</v>
       </c>
       <c r="D2559" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2559" t="s" s="3">
         <v>5076</v>
@@ -60621,7 +60654,7 @@
         <v>812</v>
       </c>
       <c r="D2560" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2560" t="s" s="3">
         <v>5078</v>
@@ -60638,7 +60671,7 @@
         <v>812</v>
       </c>
       <c r="D2561" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2561" t="s" s="3">
         <v>5080</v>
@@ -60655,7 +60688,7 @@
         <v>812</v>
       </c>
       <c r="D2562" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2562" t="s" s="3">
         <v>5082</v>
@@ -60672,7 +60705,7 @@
         <v>812</v>
       </c>
       <c r="D2563" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2563" t="s" s="3">
         <v>5084</v>
@@ -60689,7 +60722,7 @@
         <v>812</v>
       </c>
       <c r="D2564" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2564" t="s" s="3">
         <v>5086</v>
@@ -60706,7 +60739,7 @@
         <v>812</v>
       </c>
       <c r="D2565" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2565" t="s" s="3">
         <v>5088</v>
@@ -60723,7 +60756,7 @@
         <v>812</v>
       </c>
       <c r="D2566" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2566" t="s" s="3">
         <v>5090</v>
@@ -60740,7 +60773,7 @@
         <v>812</v>
       </c>
       <c r="D2567" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2567" t="s" s="3">
         <v>5092</v>
@@ -60757,7 +60790,7 @@
         <v>812</v>
       </c>
       <c r="D2568" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2568" t="s" s="3">
         <v>5094</v>
@@ -60774,7 +60807,7 @@
         <v>812</v>
       </c>
       <c r="D2569" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2569" t="s" s="3">
         <v>5096</v>
@@ -60791,7 +60824,7 @@
         <v>812</v>
       </c>
       <c r="D2570" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2570" t="s" s="3">
         <v>5098</v>
@@ -60808,7 +60841,7 @@
         <v>812</v>
       </c>
       <c r="D2571" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2571" t="s" s="3">
         <v>5100</v>
@@ -60825,7 +60858,7 @@
         <v>812</v>
       </c>
       <c r="D2572" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2572" t="s" s="3">
         <v>5102</v>
@@ -60842,7 +60875,7 @@
         <v>812</v>
       </c>
       <c r="D2573" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2573" t="s" s="3">
         <v>5104</v>
@@ -60859,7 +60892,7 @@
         <v>812</v>
       </c>
       <c r="D2574" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2574" t="s" s="3">
         <v>5106</v>
@@ -60876,7 +60909,7 @@
         <v>812</v>
       </c>
       <c r="D2575" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2575" t="s" s="3">
         <v>5108</v>
@@ -60893,7 +60926,7 @@
         <v>812</v>
       </c>
       <c r="D2576" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2576" t="s" s="3">
         <v>5110</v>
@@ -60910,7 +60943,7 @@
         <v>812</v>
       </c>
       <c r="D2577" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2577" t="s" s="3">
         <v>5112</v>
@@ -60927,7 +60960,7 @@
         <v>812</v>
       </c>
       <c r="D2578" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2578" t="s" s="3">
         <v>5114</v>
@@ -60944,7 +60977,7 @@
         <v>812</v>
       </c>
       <c r="D2579" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2579" t="s" s="3">
         <v>5116</v>
@@ -60961,7 +60994,7 @@
         <v>812</v>
       </c>
       <c r="D2580" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2580" t="s" s="3">
         <v>5118</v>
@@ -60978,7 +61011,7 @@
         <v>812</v>
       </c>
       <c r="D2581" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2581" t="s" s="3">
         <v>5120</v>
@@ -60995,7 +61028,7 @@
         <v>812</v>
       </c>
       <c r="D2582" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2582" t="s" s="3">
         <v>5122</v>
@@ -61009,10 +61042,10 @@
         <v>5123</v>
       </c>
       <c r="C2583" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2583" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2583" t="s" s="3">
         <v>5124</v>
@@ -61026,10 +61059,10 @@
         <v>5125</v>
       </c>
       <c r="C2584" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2584" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2584" t="s" s="3">
         <v>5126</v>
@@ -61043,10 +61076,10 @@
         <v>5127</v>
       </c>
       <c r="C2585" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2585" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2585" t="s" s="3">
         <v>5128</v>
@@ -61063,7 +61096,7 @@
         <v>1039</v>
       </c>
       <c r="D2586" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2586" t="s" s="3">
         <v>5130</v>
@@ -61080,7 +61113,7 @@
         <v>1039</v>
       </c>
       <c r="D2587" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2587" t="s" s="3">
         <v>5132</v>
@@ -61097,7 +61130,7 @@
         <v>1039</v>
       </c>
       <c r="D2588" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2588" t="s" s="3">
         <v>5134</v>
@@ -61114,7 +61147,7 @@
         <v>1039</v>
       </c>
       <c r="D2589" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2589" t="s" s="3">
         <v>5136</v>
@@ -61131,7 +61164,7 @@
         <v>1039</v>
       </c>
       <c r="D2590" t="s" s="2">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="E2590" t="s" s="3">
         <v>5138</v>
@@ -61145,13 +61178,13 @@
         <v>5139</v>
       </c>
       <c r="C2591" t="s" s="2">
-        <v>6</v>
+        <v>1039</v>
       </c>
       <c r="D2591" t="s" s="2">
+        <v>4939</v>
+      </c>
+      <c r="E2591" t="s" s="3">
         <v>5140</v>
-      </c>
-      <c r="E2591" t="s" s="3">
-        <v>5141</v>
       </c>
     </row>
     <row r="2592" ht="36.0" customHeight="true">
@@ -61159,16 +61192,16 @@
         <v>2591.0</v>
       </c>
       <c r="B2592" t="s" s="3">
+        <v>5141</v>
+      </c>
+      <c r="C2592" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2592" t="s" s="2">
+        <v>4939</v>
+      </c>
+      <c r="E2592" t="s" s="3">
         <v>5142</v>
-      </c>
-      <c r="C2592" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2592" t="s" s="2">
-        <v>5140</v>
-      </c>
-      <c r="E2592" t="s" s="3">
-        <v>5143</v>
       </c>
     </row>
     <row r="2593" ht="36.0" customHeight="true">
@@ -61176,16 +61209,16 @@
         <v>2592.0</v>
       </c>
       <c r="B2593" t="s" s="3">
+        <v>5143</v>
+      </c>
+      <c r="C2593" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2593" t="s" s="2">
+        <v>4939</v>
+      </c>
+      <c r="E2593" t="s" s="3">
         <v>5144</v>
-      </c>
-      <c r="C2593" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2593" t="s" s="2">
-        <v>5140</v>
-      </c>
-      <c r="E2593" t="s" s="3">
-        <v>5145</v>
       </c>
     </row>
     <row r="2594" ht="36.0" customHeight="true">
@@ -61193,13 +61226,13 @@
         <v>2593.0</v>
       </c>
       <c r="B2594" t="s" s="3">
+        <v>5145</v>
+      </c>
+      <c r="C2594" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2594" t="s" s="2">
         <v>5146</v>
-      </c>
-      <c r="C2594" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2594" t="s" s="2">
-        <v>5140</v>
       </c>
       <c r="E2594" t="s" s="3">
         <v>5147</v>
@@ -61216,7 +61249,7 @@
         <v>6</v>
       </c>
       <c r="D2595" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2595" t="s" s="3">
         <v>5149</v>
@@ -61233,7 +61266,7 @@
         <v>6</v>
       </c>
       <c r="D2596" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2596" t="s" s="3">
         <v>5151</v>
@@ -61250,7 +61283,7 @@
         <v>6</v>
       </c>
       <c r="D2597" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2597" t="s" s="3">
         <v>5153</v>
@@ -61267,7 +61300,7 @@
         <v>6</v>
       </c>
       <c r="D2598" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2598" t="s" s="3">
         <v>5155</v>
@@ -61284,7 +61317,7 @@
         <v>6</v>
       </c>
       <c r="D2599" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2599" t="s" s="3">
         <v>5157</v>
@@ -61301,7 +61334,7 @@
         <v>6</v>
       </c>
       <c r="D2600" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2600" t="s" s="3">
         <v>5159</v>
@@ -61318,7 +61351,7 @@
         <v>6</v>
       </c>
       <c r="D2601" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2601" t="s" s="3">
         <v>5161</v>
@@ -61335,7 +61368,7 @@
         <v>6</v>
       </c>
       <c r="D2602" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2602" t="s" s="3">
         <v>5163</v>
@@ -61352,7 +61385,7 @@
         <v>6</v>
       </c>
       <c r="D2603" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2603" t="s" s="3">
         <v>5165</v>
@@ -61369,7 +61402,7 @@
         <v>6</v>
       </c>
       <c r="D2604" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2604" t="s" s="3">
         <v>5167</v>
@@ -61386,7 +61419,7 @@
         <v>6</v>
       </c>
       <c r="D2605" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2605" t="s" s="3">
         <v>5169</v>
@@ -61403,7 +61436,7 @@
         <v>6</v>
       </c>
       <c r="D2606" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2606" t="s" s="3">
         <v>5171</v>
@@ -61420,7 +61453,7 @@
         <v>6</v>
       </c>
       <c r="D2607" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2607" t="s" s="3">
         <v>5173</v>
@@ -61437,7 +61470,7 @@
         <v>6</v>
       </c>
       <c r="D2608" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2608" t="s" s="3">
         <v>5175</v>
@@ -61454,7 +61487,7 @@
         <v>6</v>
       </c>
       <c r="D2609" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2609" t="s" s="3">
         <v>5177</v>
@@ -61471,7 +61504,7 @@
         <v>6</v>
       </c>
       <c r="D2610" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2610" t="s" s="3">
         <v>5179</v>
@@ -61488,7 +61521,7 @@
         <v>6</v>
       </c>
       <c r="D2611" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2611" t="s" s="3">
         <v>5181</v>
@@ -61505,7 +61538,7 @@
         <v>6</v>
       </c>
       <c r="D2612" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2612" t="s" s="3">
         <v>5183</v>
@@ -61522,7 +61555,7 @@
         <v>6</v>
       </c>
       <c r="D2613" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2613" t="s" s="3">
         <v>5185</v>
@@ -61539,7 +61572,7 @@
         <v>6</v>
       </c>
       <c r="D2614" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2614" t="s" s="3">
         <v>5187</v>
@@ -61556,7 +61589,7 @@
         <v>6</v>
       </c>
       <c r="D2615" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2615" t="s" s="3">
         <v>5189</v>
@@ -61573,7 +61606,7 @@
         <v>6</v>
       </c>
       <c r="D2616" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2616" t="s" s="3">
         <v>5191</v>
@@ -61590,7 +61623,7 @@
         <v>6</v>
       </c>
       <c r="D2617" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2617" t="s" s="3">
         <v>5193</v>
@@ -61607,7 +61640,7 @@
         <v>6</v>
       </c>
       <c r="D2618" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2618" t="s" s="3">
         <v>5195</v>
@@ -61624,7 +61657,7 @@
         <v>6</v>
       </c>
       <c r="D2619" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2619" t="s" s="3">
         <v>5197</v>
@@ -61641,7 +61674,7 @@
         <v>6</v>
       </c>
       <c r="D2620" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2620" t="s" s="3">
         <v>5199</v>
@@ -61658,7 +61691,7 @@
         <v>6</v>
       </c>
       <c r="D2621" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2621" t="s" s="3">
         <v>5201</v>
@@ -61675,7 +61708,7 @@
         <v>6</v>
       </c>
       <c r="D2622" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2622" t="s" s="3">
         <v>5203</v>
@@ -61692,7 +61725,7 @@
         <v>6</v>
       </c>
       <c r="D2623" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2623" t="s" s="3">
         <v>5205</v>
@@ -61709,7 +61742,7 @@
         <v>6</v>
       </c>
       <c r="D2624" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2624" t="s" s="3">
         <v>5207</v>
@@ -61726,7 +61759,7 @@
         <v>6</v>
       </c>
       <c r="D2625" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2625" t="s" s="3">
         <v>5209</v>
@@ -61743,7 +61776,7 @@
         <v>6</v>
       </c>
       <c r="D2626" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2626" t="s" s="3">
         <v>5211</v>
@@ -61760,7 +61793,7 @@
         <v>6</v>
       </c>
       <c r="D2627" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2627" t="s" s="3">
         <v>5213</v>
@@ -61777,7 +61810,7 @@
         <v>6</v>
       </c>
       <c r="D2628" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2628" t="s" s="3">
         <v>5215</v>
@@ -61794,7 +61827,7 @@
         <v>6</v>
       </c>
       <c r="D2629" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2629" t="s" s="3">
         <v>5217</v>
@@ -61811,7 +61844,7 @@
         <v>6</v>
       </c>
       <c r="D2630" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2630" t="s" s="3">
         <v>5219</v>
@@ -61828,7 +61861,7 @@
         <v>6</v>
       </c>
       <c r="D2631" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2631" t="s" s="3">
         <v>5221</v>
@@ -61845,7 +61878,7 @@
         <v>6</v>
       </c>
       <c r="D2632" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2632" t="s" s="3">
         <v>5223</v>
@@ -61862,7 +61895,7 @@
         <v>6</v>
       </c>
       <c r="D2633" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2633" t="s" s="3">
         <v>5225</v>
@@ -61879,7 +61912,7 @@
         <v>6</v>
       </c>
       <c r="D2634" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2634" t="s" s="3">
         <v>5227</v>
@@ -61896,7 +61929,7 @@
         <v>6</v>
       </c>
       <c r="D2635" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2635" t="s" s="3">
         <v>5229</v>
@@ -61913,7 +61946,7 @@
         <v>6</v>
       </c>
       <c r="D2636" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2636" t="s" s="3">
         <v>5231</v>
@@ -61930,7 +61963,7 @@
         <v>6</v>
       </c>
       <c r="D2637" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2637" t="s" s="3">
         <v>5233</v>
@@ -61947,7 +61980,7 @@
         <v>6</v>
       </c>
       <c r="D2638" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2638" t="s" s="3">
         <v>5235</v>
@@ -61964,7 +61997,7 @@
         <v>6</v>
       </c>
       <c r="D2639" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2639" t="s" s="3">
         <v>5237</v>
@@ -61981,7 +62014,7 @@
         <v>6</v>
       </c>
       <c r="D2640" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2640" t="s" s="3">
         <v>5239</v>
@@ -61998,7 +62031,7 @@
         <v>6</v>
       </c>
       <c r="D2641" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2641" t="s" s="3">
         <v>5241</v>
@@ -62015,7 +62048,7 @@
         <v>6</v>
       </c>
       <c r="D2642" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2642" t="s" s="3">
         <v>5243</v>
@@ -62032,7 +62065,7 @@
         <v>6</v>
       </c>
       <c r="D2643" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2643" t="s" s="3">
         <v>5245</v>
@@ -62049,7 +62082,7 @@
         <v>6</v>
       </c>
       <c r="D2644" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2644" t="s" s="3">
         <v>5247</v>
@@ -62066,7 +62099,7 @@
         <v>6</v>
       </c>
       <c r="D2645" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2645" t="s" s="3">
         <v>5249</v>
@@ -62083,7 +62116,7 @@
         <v>6</v>
       </c>
       <c r="D2646" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2646" t="s" s="3">
         <v>5251</v>
@@ -62100,7 +62133,7 @@
         <v>6</v>
       </c>
       <c r="D2647" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2647" t="s" s="3">
         <v>5253</v>
@@ -62117,7 +62150,7 @@
         <v>6</v>
       </c>
       <c r="D2648" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2648" t="s" s="3">
         <v>5255</v>
@@ -62134,7 +62167,7 @@
         <v>6</v>
       </c>
       <c r="D2649" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2649" t="s" s="3">
         <v>5257</v>
@@ -62151,7 +62184,7 @@
         <v>6</v>
       </c>
       <c r="D2650" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2650" t="s" s="3">
         <v>5259</v>
@@ -62168,7 +62201,7 @@
         <v>6</v>
       </c>
       <c r="D2651" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2651" t="s" s="3">
         <v>5261</v>
@@ -62185,7 +62218,7 @@
         <v>6</v>
       </c>
       <c r="D2652" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2652" t="s" s="3">
         <v>5263</v>
@@ -62202,7 +62235,7 @@
         <v>6</v>
       </c>
       <c r="D2653" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2653" t="s" s="3">
         <v>5265</v>
@@ -62219,7 +62252,7 @@
         <v>6</v>
       </c>
       <c r="D2654" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2654" t="s" s="3">
         <v>5267</v>
@@ -62236,7 +62269,7 @@
         <v>6</v>
       </c>
       <c r="D2655" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2655" t="s" s="3">
         <v>5269</v>
@@ -62253,7 +62286,7 @@
         <v>6</v>
       </c>
       <c r="D2656" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2656" t="s" s="3">
         <v>5271</v>
@@ -62270,7 +62303,7 @@
         <v>6</v>
       </c>
       <c r="D2657" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2657" t="s" s="3">
         <v>5273</v>
@@ -62287,7 +62320,7 @@
         <v>6</v>
       </c>
       <c r="D2658" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2658" t="s" s="3">
         <v>5275</v>
@@ -62304,7 +62337,7 @@
         <v>6</v>
       </c>
       <c r="D2659" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2659" t="s" s="3">
         <v>5277</v>
@@ -62321,7 +62354,7 @@
         <v>6</v>
       </c>
       <c r="D2660" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2660" t="s" s="3">
         <v>5279</v>
@@ -62338,7 +62371,7 @@
         <v>6</v>
       </c>
       <c r="D2661" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2661" t="s" s="3">
         <v>5281</v>
@@ -62355,7 +62388,7 @@
         <v>6</v>
       </c>
       <c r="D2662" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2662" t="s" s="3">
         <v>5283</v>
@@ -62372,7 +62405,7 @@
         <v>6</v>
       </c>
       <c r="D2663" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2663" t="s" s="3">
         <v>5285</v>
@@ -62389,7 +62422,7 @@
         <v>6</v>
       </c>
       <c r="D2664" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2664" t="s" s="3">
         <v>5287</v>
@@ -62406,10 +62439,10 @@
         <v>6</v>
       </c>
       <c r="D2665" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2665" t="s" s="3">
-        <v>5257</v>
+        <v>5289</v>
       </c>
     </row>
     <row r="2666" ht="36.0" customHeight="true">
@@ -62417,16 +62450,16 @@
         <v>2665.0</v>
       </c>
       <c r="B2666" t="s" s="3">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="C2666" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2666" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2666" t="s" s="3">
-        <v>5290</v>
+        <v>5291</v>
       </c>
     </row>
     <row r="2667" ht="36.0" customHeight="true">
@@ -62434,16 +62467,16 @@
         <v>2666.0</v>
       </c>
       <c r="B2667" t="s" s="3">
-        <v>5291</v>
+        <v>5292</v>
       </c>
       <c r="C2667" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2667" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2667" t="s" s="3">
-        <v>5292</v>
+        <v>5293</v>
       </c>
     </row>
     <row r="2668" ht="36.0" customHeight="true">
@@ -62451,16 +62484,16 @@
         <v>2667.0</v>
       </c>
       <c r="B2668" t="s" s="3">
-        <v>5293</v>
+        <v>5294</v>
       </c>
       <c r="C2668" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2668" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2668" t="s" s="3">
-        <v>5294</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="2669" ht="36.0" customHeight="true">
@@ -62474,7 +62507,7 @@
         <v>6</v>
       </c>
       <c r="D2669" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2669" t="s" s="3">
         <v>5296</v>
@@ -62491,7 +62524,7 @@
         <v>6</v>
       </c>
       <c r="D2670" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2670" t="s" s="3">
         <v>5298</v>
@@ -62508,7 +62541,7 @@
         <v>6</v>
       </c>
       <c r="D2671" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2671" t="s" s="3">
         <v>5300</v>
@@ -62525,7 +62558,7 @@
         <v>6</v>
       </c>
       <c r="D2672" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2672" t="s" s="3">
         <v>5302</v>
@@ -62542,10 +62575,10 @@
         <v>6</v>
       </c>
       <c r="D2673" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2673" t="s" s="3">
-        <v>5219</v>
+        <v>5304</v>
       </c>
     </row>
     <row r="2674" ht="36.0" customHeight="true">
@@ -62553,16 +62586,16 @@
         <v>2673.0</v>
       </c>
       <c r="B2674" t="s" s="3">
-        <v>4273</v>
+        <v>5305</v>
       </c>
       <c r="C2674" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2674" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2674" t="s" s="3">
-        <v>5304</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="2675" ht="36.0" customHeight="true">
@@ -62570,16 +62603,16 @@
         <v>2674.0</v>
       </c>
       <c r="B2675" t="s" s="3">
-        <v>5305</v>
+        <v>5307</v>
       </c>
       <c r="C2675" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2675" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2675" t="s" s="3">
-        <v>5257</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="2676" ht="36.0" customHeight="true">
@@ -62587,16 +62620,16 @@
         <v>2675.0</v>
       </c>
       <c r="B2676" t="s" s="3">
-        <v>5306</v>
+        <v>5309</v>
       </c>
       <c r="C2676" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2676" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2676" t="s" s="3">
-        <v>5307</v>
+        <v>5225</v>
       </c>
     </row>
     <row r="2677" ht="36.0" customHeight="true">
@@ -62604,16 +62637,16 @@
         <v>2676.0</v>
       </c>
       <c r="B2677" t="s" s="3">
-        <v>5308</v>
+        <v>4277</v>
       </c>
       <c r="C2677" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2677" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2677" t="s" s="3">
-        <v>5309</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="2678" ht="36.0" customHeight="true">
@@ -62621,16 +62654,16 @@
         <v>2677.0</v>
       </c>
       <c r="B2678" t="s" s="3">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="C2678" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2678" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2678" t="s" s="3">
-        <v>5311</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="2679" ht="36.0" customHeight="true">
@@ -62644,7 +62677,7 @@
         <v>6</v>
       </c>
       <c r="D2679" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2679" t="s" s="3">
         <v>5313</v>
@@ -62661,7 +62694,7 @@
         <v>6</v>
       </c>
       <c r="D2680" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2680" t="s" s="3">
         <v>5315</v>
@@ -62678,7 +62711,7 @@
         <v>6</v>
       </c>
       <c r="D2681" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2681" t="s" s="3">
         <v>5317</v>
@@ -62695,7 +62728,7 @@
         <v>6</v>
       </c>
       <c r="D2682" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2682" t="s" s="3">
         <v>5319</v>
@@ -62712,7 +62745,7 @@
         <v>6</v>
       </c>
       <c r="D2683" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2683" t="s" s="3">
         <v>5321</v>
@@ -62729,7 +62762,7 @@
         <v>6</v>
       </c>
       <c r="D2684" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2684" t="s" s="3">
         <v>5323</v>
@@ -62746,7 +62779,7 @@
         <v>6</v>
       </c>
       <c r="D2685" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2685" t="s" s="3">
         <v>5325</v>
@@ -62763,7 +62796,7 @@
         <v>6</v>
       </c>
       <c r="D2686" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2686" t="s" s="3">
         <v>5327</v>
@@ -62780,7 +62813,7 @@
         <v>6</v>
       </c>
       <c r="D2687" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2687" t="s" s="3">
         <v>5329</v>
@@ -62797,7 +62830,7 @@
         <v>6</v>
       </c>
       <c r="D2688" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2688" t="s" s="3">
         <v>5331</v>
@@ -62814,7 +62847,7 @@
         <v>6</v>
       </c>
       <c r="D2689" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2689" t="s" s="3">
         <v>5333</v>
@@ -62831,7 +62864,7 @@
         <v>6</v>
       </c>
       <c r="D2690" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2690" t="s" s="3">
         <v>5335</v>
@@ -62848,7 +62881,7 @@
         <v>6</v>
       </c>
       <c r="D2691" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2691" t="s" s="3">
         <v>5337</v>
@@ -62865,7 +62898,7 @@
         <v>6</v>
       </c>
       <c r="D2692" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2692" t="s" s="3">
         <v>5339</v>
@@ -62882,7 +62915,7 @@
         <v>6</v>
       </c>
       <c r="D2693" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2693" t="s" s="3">
         <v>5341</v>
@@ -62899,7 +62932,7 @@
         <v>6</v>
       </c>
       <c r="D2694" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2694" t="s" s="3">
         <v>5343</v>
@@ -62916,7 +62949,7 @@
         <v>6</v>
       </c>
       <c r="D2695" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2695" t="s" s="3">
         <v>5345</v>
@@ -62933,7 +62966,7 @@
         <v>6</v>
       </c>
       <c r="D2696" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2696" t="s" s="3">
         <v>5347</v>
@@ -62950,7 +62983,7 @@
         <v>6</v>
       </c>
       <c r="D2697" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2697" t="s" s="3">
         <v>5349</v>
@@ -62967,7 +63000,7 @@
         <v>6</v>
       </c>
       <c r="D2698" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2698" t="s" s="3">
         <v>5351</v>
@@ -62984,7 +63017,7 @@
         <v>6</v>
       </c>
       <c r="D2699" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2699" t="s" s="3">
         <v>5353</v>
@@ -63001,7 +63034,7 @@
         <v>6</v>
       </c>
       <c r="D2700" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2700" t="s" s="3">
         <v>5355</v>
@@ -63018,7 +63051,7 @@
         <v>6</v>
       </c>
       <c r="D2701" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2701" t="s" s="3">
         <v>5357</v>
@@ -63035,7 +63068,7 @@
         <v>6</v>
       </c>
       <c r="D2702" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2702" t="s" s="3">
         <v>5359</v>
@@ -63052,7 +63085,7 @@
         <v>6</v>
       </c>
       <c r="D2703" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2703" t="s" s="3">
         <v>5361</v>
@@ -63069,7 +63102,7 @@
         <v>6</v>
       </c>
       <c r="D2704" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2704" t="s" s="3">
         <v>5363</v>
@@ -63086,7 +63119,7 @@
         <v>6</v>
       </c>
       <c r="D2705" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2705" t="s" s="3">
         <v>5365</v>
@@ -63103,7 +63136,7 @@
         <v>6</v>
       </c>
       <c r="D2706" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2706" t="s" s="3">
         <v>5367</v>
@@ -63120,7 +63153,7 @@
         <v>6</v>
       </c>
       <c r="D2707" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2707" t="s" s="3">
         <v>5369</v>
@@ -63137,7 +63170,7 @@
         <v>6</v>
       </c>
       <c r="D2708" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2708" t="s" s="3">
         <v>5371</v>
@@ -63154,7 +63187,7 @@
         <v>6</v>
       </c>
       <c r="D2709" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2709" t="s" s="3">
         <v>5373</v>
@@ -63171,7 +63204,7 @@
         <v>6</v>
       </c>
       <c r="D2710" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2710" t="s" s="3">
         <v>5375</v>
@@ -63188,7 +63221,7 @@
         <v>6</v>
       </c>
       <c r="D2711" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2711" t="s" s="3">
         <v>5377</v>
@@ -63205,7 +63238,7 @@
         <v>6</v>
       </c>
       <c r="D2712" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2712" t="s" s="3">
         <v>5379</v>
@@ -63222,7 +63255,7 @@
         <v>6</v>
       </c>
       <c r="D2713" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2713" t="s" s="3">
         <v>5381</v>
@@ -63239,7 +63272,7 @@
         <v>6</v>
       </c>
       <c r="D2714" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2714" t="s" s="3">
         <v>5383</v>
@@ -63256,7 +63289,7 @@
         <v>6</v>
       </c>
       <c r="D2715" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2715" t="s" s="3">
         <v>5385</v>
@@ -63273,7 +63306,7 @@
         <v>6</v>
       </c>
       <c r="D2716" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2716" t="s" s="3">
         <v>5387</v>
@@ -63290,7 +63323,7 @@
         <v>6</v>
       </c>
       <c r="D2717" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2717" t="s" s="3">
         <v>5389</v>
@@ -63307,7 +63340,7 @@
         <v>6</v>
       </c>
       <c r="D2718" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2718" t="s" s="3">
         <v>5391</v>
@@ -63324,7 +63357,7 @@
         <v>6</v>
       </c>
       <c r="D2719" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2719" t="s" s="3">
         <v>5393</v>
@@ -63341,7 +63374,7 @@
         <v>6</v>
       </c>
       <c r="D2720" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2720" t="s" s="3">
         <v>5395</v>
@@ -63358,7 +63391,7 @@
         <v>6</v>
       </c>
       <c r="D2721" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2721" t="s" s="3">
         <v>5397</v>
@@ -63375,7 +63408,7 @@
         <v>6</v>
       </c>
       <c r="D2722" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2722" t="s" s="3">
         <v>5399</v>
@@ -63392,7 +63425,7 @@
         <v>6</v>
       </c>
       <c r="D2723" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2723" t="s" s="3">
         <v>5401</v>
@@ -63409,7 +63442,7 @@
         <v>6</v>
       </c>
       <c r="D2724" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2724" t="s" s="3">
         <v>5403</v>
@@ -63426,7 +63459,7 @@
         <v>6</v>
       </c>
       <c r="D2725" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2725" t="s" s="3">
         <v>5405</v>
@@ -63443,7 +63476,7 @@
         <v>6</v>
       </c>
       <c r="D2726" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2726" t="s" s="3">
         <v>5407</v>
@@ -63460,7 +63493,7 @@
         <v>6</v>
       </c>
       <c r="D2727" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2727" t="s" s="3">
         <v>5409</v>
@@ -63477,7 +63510,7 @@
         <v>6</v>
       </c>
       <c r="D2728" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2728" t="s" s="3">
         <v>5411</v>
@@ -63494,7 +63527,7 @@
         <v>6</v>
       </c>
       <c r="D2729" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2729" t="s" s="3">
         <v>5413</v>
@@ -63505,16 +63538,16 @@
         <v>2729.0</v>
       </c>
       <c r="B2730" t="s" s="3">
-        <v>3518</v>
+        <v>5414</v>
       </c>
       <c r="C2730" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2730" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2730" t="s" s="3">
-        <v>5414</v>
+        <v>5415</v>
       </c>
     </row>
     <row r="2731" ht="36.0" customHeight="true">
@@ -63522,16 +63555,16 @@
         <v>2730.0</v>
       </c>
       <c r="B2731" t="s" s="3">
-        <v>5415</v>
+        <v>5416</v>
       </c>
       <c r="C2731" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2731" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2731" t="s" s="3">
-        <v>5416</v>
+        <v>5417</v>
       </c>
     </row>
     <row r="2732" ht="36.0" customHeight="true">
@@ -63539,16 +63572,16 @@
         <v>2731.0</v>
       </c>
       <c r="B2732" t="s" s="3">
-        <v>5417</v>
+        <v>5418</v>
       </c>
       <c r="C2732" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2732" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2732" t="s" s="3">
-        <v>5418</v>
+        <v>5419</v>
       </c>
     </row>
     <row r="2733" ht="36.0" customHeight="true">
@@ -63556,16 +63589,16 @@
         <v>2732.0</v>
       </c>
       <c r="B2733" t="s" s="3">
-        <v>5419</v>
+        <v>3518</v>
       </c>
       <c r="C2733" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2733" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2733" t="s" s="3">
-        <v>5261</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="2734" ht="36.0" customHeight="true">
@@ -63573,16 +63606,16 @@
         <v>2733.0</v>
       </c>
       <c r="B2734" t="s" s="3">
-        <v>5420</v>
+        <v>5421</v>
       </c>
       <c r="C2734" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2734" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2734" t="s" s="3">
-        <v>5421</v>
+        <v>5422</v>
       </c>
     </row>
     <row r="2735" ht="36.0" customHeight="true">
@@ -63590,16 +63623,16 @@
         <v>2734.0</v>
       </c>
       <c r="B2735" t="s" s="3">
-        <v>5422</v>
+        <v>5423</v>
       </c>
       <c r="C2735" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2735" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2735" t="s" s="3">
-        <v>5423</v>
+        <v>5424</v>
       </c>
     </row>
     <row r="2736" ht="36.0" customHeight="true">
@@ -63607,16 +63640,16 @@
         <v>2735.0</v>
       </c>
       <c r="B2736" t="s" s="3">
-        <v>5424</v>
+        <v>5425</v>
       </c>
       <c r="C2736" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2736" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2736" t="s" s="3">
-        <v>5425</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="2737" ht="36.0" customHeight="true">
@@ -63630,7 +63663,7 @@
         <v>6</v>
       </c>
       <c r="D2737" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2737" t="s" s="3">
         <v>5427</v>
@@ -63647,7 +63680,7 @@
         <v>6</v>
       </c>
       <c r="D2738" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2738" t="s" s="3">
         <v>5429</v>
@@ -63664,7 +63697,7 @@
         <v>6</v>
       </c>
       <c r="D2739" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2739" t="s" s="3">
         <v>5431</v>
@@ -63678,10 +63711,10 @@
         <v>5432</v>
       </c>
       <c r="C2740" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2740" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2740" t="s" s="3">
         <v>5433</v>
@@ -63695,10 +63728,10 @@
         <v>5434</v>
       </c>
       <c r="C2741" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2741" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2741" t="s" s="3">
         <v>5435</v>
@@ -63712,10 +63745,10 @@
         <v>5436</v>
       </c>
       <c r="C2742" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2742" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2742" t="s" s="3">
         <v>5437</v>
@@ -63732,7 +63765,7 @@
         <v>812</v>
       </c>
       <c r="D2743" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2743" t="s" s="3">
         <v>5439</v>
@@ -63749,7 +63782,7 @@
         <v>812</v>
       </c>
       <c r="D2744" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2744" t="s" s="3">
         <v>5441</v>
@@ -63766,7 +63799,7 @@
         <v>812</v>
       </c>
       <c r="D2745" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2745" t="s" s="3">
         <v>5443</v>
@@ -63783,7 +63816,7 @@
         <v>812</v>
       </c>
       <c r="D2746" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2746" t="s" s="3">
         <v>5445</v>
@@ -63800,7 +63833,7 @@
         <v>812</v>
       </c>
       <c r="D2747" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2747" t="s" s="3">
         <v>5447</v>
@@ -63817,7 +63850,7 @@
         <v>812</v>
       </c>
       <c r="D2748" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2748" t="s" s="3">
         <v>5449</v>
@@ -63834,7 +63867,7 @@
         <v>812</v>
       </c>
       <c r="D2749" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2749" t="s" s="3">
         <v>5451</v>
@@ -63851,7 +63884,7 @@
         <v>812</v>
       </c>
       <c r="D2750" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2750" t="s" s="3">
         <v>5453</v>
@@ -63868,7 +63901,7 @@
         <v>812</v>
       </c>
       <c r="D2751" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2751" t="s" s="3">
         <v>5455</v>
@@ -63885,7 +63918,7 @@
         <v>812</v>
       </c>
       <c r="D2752" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2752" t="s" s="3">
         <v>5457</v>
@@ -63902,7 +63935,7 @@
         <v>812</v>
       </c>
       <c r="D2753" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2753" t="s" s="3">
         <v>5459</v>
@@ -63919,7 +63952,7 @@
         <v>812</v>
       </c>
       <c r="D2754" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2754" t="s" s="3">
         <v>5461</v>
@@ -63936,7 +63969,7 @@
         <v>812</v>
       </c>
       <c r="D2755" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2755" t="s" s="3">
         <v>5463</v>
@@ -63953,7 +63986,7 @@
         <v>812</v>
       </c>
       <c r="D2756" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2756" t="s" s="3">
         <v>5465</v>
@@ -63970,7 +64003,7 @@
         <v>812</v>
       </c>
       <c r="D2757" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2757" t="s" s="3">
         <v>5467</v>
@@ -63987,7 +64020,7 @@
         <v>812</v>
       </c>
       <c r="D2758" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2758" t="s" s="3">
         <v>5469</v>
@@ -64004,7 +64037,7 @@
         <v>812</v>
       </c>
       <c r="D2759" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2759" t="s" s="3">
         <v>5471</v>
@@ -64021,7 +64054,7 @@
         <v>812</v>
       </c>
       <c r="D2760" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2760" t="s" s="3">
         <v>5473</v>
@@ -64038,7 +64071,7 @@
         <v>812</v>
       </c>
       <c r="D2761" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2761" t="s" s="3">
         <v>5475</v>
@@ -64055,7 +64088,7 @@
         <v>812</v>
       </c>
       <c r="D2762" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2762" t="s" s="3">
         <v>5477</v>
@@ -64072,7 +64105,7 @@
         <v>812</v>
       </c>
       <c r="D2763" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2763" t="s" s="3">
         <v>5479</v>
@@ -64089,7 +64122,7 @@
         <v>812</v>
       </c>
       <c r="D2764" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2764" t="s" s="3">
         <v>5481</v>
@@ -64106,7 +64139,7 @@
         <v>812</v>
       </c>
       <c r="D2765" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2765" t="s" s="3">
         <v>5483</v>
@@ -64123,7 +64156,7 @@
         <v>812</v>
       </c>
       <c r="D2766" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2766" t="s" s="3">
         <v>5485</v>
@@ -64140,7 +64173,7 @@
         <v>812</v>
       </c>
       <c r="D2767" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2767" t="s" s="3">
         <v>5487</v>
@@ -64157,7 +64190,7 @@
         <v>812</v>
       </c>
       <c r="D2768" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2768" t="s" s="3">
         <v>5489</v>
@@ -64174,7 +64207,7 @@
         <v>812</v>
       </c>
       <c r="D2769" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2769" t="s" s="3">
         <v>5491</v>
@@ -64191,7 +64224,7 @@
         <v>812</v>
       </c>
       <c r="D2770" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2770" t="s" s="3">
         <v>5493</v>
@@ -64208,7 +64241,7 @@
         <v>812</v>
       </c>
       <c r="D2771" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2771" t="s" s="3">
         <v>5495</v>
@@ -64225,7 +64258,7 @@
         <v>812</v>
       </c>
       <c r="D2772" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2772" t="s" s="3">
         <v>5497</v>
@@ -64242,7 +64275,7 @@
         <v>812</v>
       </c>
       <c r="D2773" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2773" t="s" s="3">
         <v>5499</v>
@@ -64259,7 +64292,7 @@
         <v>812</v>
       </c>
       <c r="D2774" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2774" t="s" s="3">
         <v>5501</v>
@@ -64276,7 +64309,7 @@
         <v>812</v>
       </c>
       <c r="D2775" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2775" t="s" s="3">
         <v>5503</v>
@@ -64293,7 +64326,7 @@
         <v>812</v>
       </c>
       <c r="D2776" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2776" t="s" s="3">
         <v>5505</v>
@@ -64310,7 +64343,7 @@
         <v>812</v>
       </c>
       <c r="D2777" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2777" t="s" s="3">
         <v>5507</v>
@@ -64327,7 +64360,7 @@
         <v>812</v>
       </c>
       <c r="D2778" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2778" t="s" s="3">
         <v>5509</v>
@@ -64344,7 +64377,7 @@
         <v>812</v>
       </c>
       <c r="D2779" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2779" t="s" s="3">
         <v>5511</v>
@@ -64361,7 +64394,7 @@
         <v>812</v>
       </c>
       <c r="D2780" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2780" t="s" s="3">
         <v>5513</v>
@@ -64378,7 +64411,7 @@
         <v>812</v>
       </c>
       <c r="D2781" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2781" t="s" s="3">
         <v>5515</v>
@@ -64395,7 +64428,7 @@
         <v>812</v>
       </c>
       <c r="D2782" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2782" t="s" s="3">
         <v>5517</v>
@@ -64412,7 +64445,7 @@
         <v>812</v>
       </c>
       <c r="D2783" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2783" t="s" s="3">
         <v>5519</v>
@@ -64429,7 +64462,7 @@
         <v>812</v>
       </c>
       <c r="D2784" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2784" t="s" s="3">
         <v>5521</v>
@@ -64446,7 +64479,7 @@
         <v>812</v>
       </c>
       <c r="D2785" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2785" t="s" s="3">
         <v>5523</v>
@@ -64463,10 +64496,10 @@
         <v>812</v>
       </c>
       <c r="D2786" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2786" t="s" s="3">
-        <v>5197</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="2787" ht="36.0" customHeight="true">
@@ -64474,16 +64507,16 @@
         <v>2786.0</v>
       </c>
       <c r="B2787" t="s" s="3">
-        <v>5525</v>
+        <v>5526</v>
       </c>
       <c r="C2787" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2787" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2787" t="s" s="3">
-        <v>5526</v>
+        <v>5527</v>
       </c>
     </row>
     <row r="2788" ht="36.0" customHeight="true">
@@ -64491,16 +64524,16 @@
         <v>2787.0</v>
       </c>
       <c r="B2788" t="s" s="3">
-        <v>5527</v>
+        <v>5528</v>
       </c>
       <c r="C2788" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2788" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2788" t="s" s="3">
-        <v>5528</v>
+        <v>5529</v>
       </c>
     </row>
     <row r="2789" ht="36.0" customHeight="true">
@@ -64508,16 +64541,16 @@
         <v>2788.0</v>
       </c>
       <c r="B2789" t="s" s="3">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="C2789" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2789" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2789" t="s" s="3">
-        <v>5530</v>
+        <v>5203</v>
       </c>
     </row>
     <row r="2790" ht="36.0" customHeight="true">
@@ -64531,7 +64564,7 @@
         <v>812</v>
       </c>
       <c r="D2790" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2790" t="s" s="3">
         <v>5532</v>
@@ -64548,7 +64581,7 @@
         <v>812</v>
       </c>
       <c r="D2791" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2791" t="s" s="3">
         <v>5534</v>
@@ -64565,7 +64598,7 @@
         <v>812</v>
       </c>
       <c r="D2792" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2792" t="s" s="3">
         <v>5536</v>
@@ -64582,7 +64615,7 @@
         <v>812</v>
       </c>
       <c r="D2793" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2793" t="s" s="3">
         <v>5538</v>
@@ -64596,10 +64629,10 @@
         <v>5539</v>
       </c>
       <c r="C2794" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2794" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2794" t="s" s="3">
         <v>5540</v>
@@ -64613,10 +64646,10 @@
         <v>5541</v>
       </c>
       <c r="C2795" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2795" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2795" t="s" s="3">
         <v>5542</v>
@@ -64627,16 +64660,16 @@
         <v>2795.0</v>
       </c>
       <c r="B2796" t="s" s="3">
-        <v>5520</v>
+        <v>5543</v>
       </c>
       <c r="C2796" t="s" s="2">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="D2796" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2796" t="s" s="3">
-        <v>5543</v>
+        <v>5544</v>
       </c>
     </row>
     <row r="2797" ht="36.0" customHeight="true">
@@ -64644,16 +64677,16 @@
         <v>2796.0</v>
       </c>
       <c r="B2797" t="s" s="3">
-        <v>5544</v>
+        <v>5545</v>
       </c>
       <c r="C2797" t="s" s="2">
         <v>1039</v>
       </c>
       <c r="D2797" t="s" s="2">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="E2797" t="s" s="3">
-        <v>5545</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="2798" ht="36.0" customHeight="true">
@@ -64661,13 +64694,13 @@
         <v>2797.0</v>
       </c>
       <c r="B2798" t="s" s="3">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="C2798" t="s" s="2">
-        <v>6</v>
+        <v>1039</v>
       </c>
       <c r="D2798" t="s" s="2">
-        <v>5547</v>
+        <v>5146</v>
       </c>
       <c r="E2798" t="s" s="3">
         <v>5548</v>
@@ -64678,16 +64711,16 @@
         <v>2798.0</v>
       </c>
       <c r="B2799" t="s" s="3">
+        <v>5526</v>
+      </c>
+      <c r="C2799" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2799" t="s" s="2">
+        <v>5146</v>
+      </c>
+      <c r="E2799" t="s" s="3">
         <v>5549</v>
-      </c>
-      <c r="C2799" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2799" t="s" s="2">
-        <v>5547</v>
-      </c>
-      <c r="E2799" t="s" s="3">
-        <v>5550</v>
       </c>
     </row>
     <row r="2800" ht="36.0" customHeight="true">
@@ -64695,16 +64728,16 @@
         <v>2799.0</v>
       </c>
       <c r="B2800" t="s" s="3">
+        <v>5550</v>
+      </c>
+      <c r="C2800" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D2800" t="s" s="2">
+        <v>5146</v>
+      </c>
+      <c r="E2800" t="s" s="3">
         <v>5551</v>
-      </c>
-      <c r="C2800" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2800" t="s" s="2">
-        <v>5547</v>
-      </c>
-      <c r="E2800" t="s" s="3">
-        <v>5552</v>
       </c>
     </row>
     <row r="2801" ht="36.0" customHeight="true">
@@ -64712,13 +64745,13 @@
         <v>2800.0</v>
       </c>
       <c r="B2801" t="s" s="3">
+        <v>5552</v>
+      </c>
+      <c r="C2801" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2801" t="s" s="2">
         <v>5553</v>
-      </c>
-      <c r="C2801" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2801" t="s" s="2">
-        <v>5547</v>
       </c>
       <c r="E2801" t="s" s="3">
         <v>5554</v>
@@ -64735,7 +64768,7 @@
         <v>6</v>
       </c>
       <c r="D2802" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2802" t="s" s="3">
         <v>5556</v>
@@ -64752,7 +64785,7 @@
         <v>6</v>
       </c>
       <c r="D2803" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2803" t="s" s="3">
         <v>5558</v>
@@ -64769,7 +64802,7 @@
         <v>6</v>
       </c>
       <c r="D2804" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2804" t="s" s="3">
         <v>5560</v>
@@ -64786,7 +64819,7 @@
         <v>6</v>
       </c>
       <c r="D2805" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2805" t="s" s="3">
         <v>5562</v>
@@ -64803,7 +64836,7 @@
         <v>6</v>
       </c>
       <c r="D2806" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2806" t="s" s="3">
         <v>5564</v>
@@ -64820,7 +64853,7 @@
         <v>6</v>
       </c>
       <c r="D2807" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2807" t="s" s="3">
         <v>5566</v>
@@ -64837,7 +64870,7 @@
         <v>6</v>
       </c>
       <c r="D2808" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2808" t="s" s="3">
         <v>5568</v>
@@ -64854,7 +64887,7 @@
         <v>6</v>
       </c>
       <c r="D2809" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2809" t="s" s="3">
         <v>5570</v>
@@ -64871,7 +64904,7 @@
         <v>6</v>
       </c>
       <c r="D2810" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2810" t="s" s="3">
         <v>5572</v>
@@ -64888,7 +64921,7 @@
         <v>6</v>
       </c>
       <c r="D2811" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2811" t="s" s="3">
         <v>5574</v>
@@ -64905,7 +64938,7 @@
         <v>6</v>
       </c>
       <c r="D2812" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2812" t="s" s="3">
         <v>5576</v>
@@ -64922,7 +64955,7 @@
         <v>6</v>
       </c>
       <c r="D2813" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2813" t="s" s="3">
         <v>5578</v>
@@ -64939,7 +64972,7 @@
         <v>6</v>
       </c>
       <c r="D2814" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2814" t="s" s="3">
         <v>5580</v>
@@ -64956,7 +64989,7 @@
         <v>6</v>
       </c>
       <c r="D2815" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2815" t="s" s="3">
         <v>5582</v>
@@ -64973,7 +65006,7 @@
         <v>6</v>
       </c>
       <c r="D2816" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2816" t="s" s="3">
         <v>5584</v>
@@ -64990,7 +65023,7 @@
         <v>6</v>
       </c>
       <c r="D2817" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2817" t="s" s="3">
         <v>5586</v>
@@ -65007,7 +65040,7 @@
         <v>6</v>
       </c>
       <c r="D2818" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2818" t="s" s="3">
         <v>5588</v>
@@ -65024,7 +65057,7 @@
         <v>6</v>
       </c>
       <c r="D2819" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2819" t="s" s="3">
         <v>5590</v>
@@ -65041,7 +65074,7 @@
         <v>6</v>
       </c>
       <c r="D2820" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2820" t="s" s="3">
         <v>5592</v>
@@ -65058,7 +65091,7 @@
         <v>6</v>
       </c>
       <c r="D2821" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2821" t="s" s="3">
         <v>5594</v>
@@ -65075,7 +65108,7 @@
         <v>6</v>
       </c>
       <c r="D2822" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2822" t="s" s="3">
         <v>5596</v>
@@ -65092,7 +65125,7 @@
         <v>6</v>
       </c>
       <c r="D2823" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2823" t="s" s="3">
         <v>5598</v>
@@ -65109,7 +65142,7 @@
         <v>6</v>
       </c>
       <c r="D2824" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2824" t="s" s="3">
         <v>5600</v>
@@ -65126,7 +65159,7 @@
         <v>6</v>
       </c>
       <c r="D2825" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2825" t="s" s="3">
         <v>5602</v>
@@ -65143,7 +65176,7 @@
         <v>6</v>
       </c>
       <c r="D2826" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2826" t="s" s="3">
         <v>5604</v>
@@ -65160,7 +65193,7 @@
         <v>6</v>
       </c>
       <c r="D2827" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2827" t="s" s="3">
         <v>5606</v>
@@ -65177,7 +65210,7 @@
         <v>6</v>
       </c>
       <c r="D2828" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2828" t="s" s="3">
         <v>5608</v>
@@ -65194,7 +65227,7 @@
         <v>6</v>
       </c>
       <c r="D2829" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2829" t="s" s="3">
         <v>5610</v>
@@ -65211,7 +65244,7 @@
         <v>6</v>
       </c>
       <c r="D2830" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2830" t="s" s="3">
         <v>5612</v>
@@ -65228,7 +65261,7 @@
         <v>6</v>
       </c>
       <c r="D2831" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2831" t="s" s="3">
         <v>5614</v>
@@ -65245,7 +65278,7 @@
         <v>6</v>
       </c>
       <c r="D2832" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2832" t="s" s="3">
         <v>5616</v>
@@ -65262,7 +65295,7 @@
         <v>6</v>
       </c>
       <c r="D2833" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2833" t="s" s="3">
         <v>5618</v>
@@ -65279,7 +65312,7 @@
         <v>6</v>
       </c>
       <c r="D2834" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2834" t="s" s="3">
         <v>5620</v>
@@ -65293,13 +65326,13 @@
         <v>5621</v>
       </c>
       <c r="C2835" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2835" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2835" t="s" s="3">
-        <v>5594</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="2836" ht="36.0" customHeight="true">
@@ -65307,16 +65340,16 @@
         <v>2835.0</v>
       </c>
       <c r="B2836" t="s" s="3">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="C2836" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2836" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2836" t="s" s="3">
-        <v>5623</v>
+        <v>5624</v>
       </c>
     </row>
     <row r="2837" ht="36.0" customHeight="true">
@@ -65324,16 +65357,16 @@
         <v>2836.0</v>
       </c>
       <c r="B2837" t="s" s="3">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="C2837" t="s" s="2">
-        <v>812</v>
+        <v>6</v>
       </c>
       <c r="D2837" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2837" t="s" s="3">
-        <v>5625</v>
+        <v>5626</v>
       </c>
     </row>
     <row r="2838" ht="36.0" customHeight="true">
@@ -65341,16 +65374,16 @@
         <v>2837.0</v>
       </c>
       <c r="B2838" t="s" s="3">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="C2838" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2838" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2838" t="s" s="3">
-        <v>5627</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="2839" ht="36.0" customHeight="true">
@@ -65364,7 +65397,7 @@
         <v>812</v>
       </c>
       <c r="D2839" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2839" t="s" s="3">
         <v>5629</v>
@@ -65381,7 +65414,7 @@
         <v>812</v>
       </c>
       <c r="D2840" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2840" t="s" s="3">
         <v>5631</v>
@@ -65392,16 +65425,16 @@
         <v>2840.0</v>
       </c>
       <c r="B2841" t="s" s="3">
-        <v>5555</v>
+        <v>5632</v>
       </c>
       <c r="C2841" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2841" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2841" t="s" s="3">
-        <v>5632</v>
+        <v>5633</v>
       </c>
     </row>
     <row r="2842" ht="36.0" customHeight="true">
@@ -65409,16 +65442,16 @@
         <v>2841.0</v>
       </c>
       <c r="B2842" t="s" s="3">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="C2842" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2842" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2842" t="s" s="3">
-        <v>5634</v>
+        <v>5635</v>
       </c>
     </row>
     <row r="2843" ht="36.0" customHeight="true">
@@ -65426,16 +65459,16 @@
         <v>2842.0</v>
       </c>
       <c r="B2843" t="s" s="3">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="C2843" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2843" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2843" t="s" s="3">
-        <v>5636</v>
+        <v>5637</v>
       </c>
     </row>
     <row r="2844" ht="36.0" customHeight="true">
@@ -65443,13 +65476,13 @@
         <v>2843.0</v>
       </c>
       <c r="B2844" t="s" s="3">
-        <v>5637</v>
+        <v>5561</v>
       </c>
       <c r="C2844" t="s" s="2">
         <v>812</v>
       </c>
       <c r="D2844" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2844" t="s" s="3">
         <v>5638</v>
@@ -65466,7 +65499,7 @@
         <v>812</v>
       </c>
       <c r="D2845" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2845" t="s" s="3">
         <v>5640</v>
@@ -65483,7 +65516,7 @@
         <v>812</v>
       </c>
       <c r="D2846" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2846" t="s" s="3">
         <v>5642</v>
@@ -65500,7 +65533,7 @@
         <v>812</v>
       </c>
       <c r="D2847" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2847" t="s" s="3">
         <v>5644</v>
@@ -65517,7 +65550,7 @@
         <v>812</v>
       </c>
       <c r="D2848" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2848" t="s" s="3">
         <v>5646</v>
@@ -65534,7 +65567,7 @@
         <v>812</v>
       </c>
       <c r="D2849" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2849" t="s" s="3">
         <v>5648</v>
@@ -65551,7 +65584,7 @@
         <v>812</v>
       </c>
       <c r="D2850" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2850" t="s" s="3">
         <v>5650</v>
@@ -65568,7 +65601,7 @@
         <v>812</v>
       </c>
       <c r="D2851" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2851" t="s" s="3">
         <v>5652</v>
@@ -65585,7 +65618,7 @@
         <v>812</v>
       </c>
       <c r="D2852" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2852" t="s" s="3">
         <v>5654</v>
@@ -65602,7 +65635,7 @@
         <v>812</v>
       </c>
       <c r="D2853" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2853" t="s" s="3">
         <v>5656</v>
@@ -65619,7 +65652,7 @@
         <v>812</v>
       </c>
       <c r="D2854" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2854" t="s" s="3">
         <v>5658</v>
@@ -65636,7 +65669,7 @@
         <v>812</v>
       </c>
       <c r="D2855" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2855" t="s" s="3">
         <v>5660</v>
@@ -65653,7 +65686,7 @@
         <v>812</v>
       </c>
       <c r="D2856" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2856" t="s" s="3">
         <v>5662</v>
@@ -65670,10 +65703,95 @@
         <v>812</v>
       </c>
       <c r="D2857" t="s" s="2">
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="E2857" t="s" s="3">
         <v>5664</v>
+      </c>
+    </row>
+    <row r="2858" ht="36.0" customHeight="true">
+      <c r="A2858" t="n" s="2">
+        <v>2857.0</v>
+      </c>
+      <c r="B2858" t="s" s="3">
+        <v>5665</v>
+      </c>
+      <c r="C2858" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="D2858" t="s" s="2">
+        <v>5553</v>
+      </c>
+      <c r="E2858" t="s" s="3">
+        <v>5666</v>
+      </c>
+    </row>
+    <row r="2859" ht="36.0" customHeight="true">
+      <c r="A2859" t="n" s="2">
+        <v>2858.0</v>
+      </c>
+      <c r="B2859" t="s" s="3">
+        <v>5667</v>
+      </c>
+      <c r="C2859" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="D2859" t="s" s="2">
+        <v>5553</v>
+      </c>
+      <c r="E2859" t="s" s="3">
+        <v>5668</v>
+      </c>
+    </row>
+    <row r="2860" ht="36.0" customHeight="true">
+      <c r="A2860" t="n" s="2">
+        <v>2859.0</v>
+      </c>
+      <c r="B2860" t="s" s="3">
+        <v>5669</v>
+      </c>
+      <c r="C2860" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="D2860" t="s" s="2">
+        <v>5553</v>
+      </c>
+      <c r="E2860" t="s" s="3">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="2861" ht="36.0" customHeight="true">
+      <c r="A2861" t="n" s="2">
+        <v>2860.0</v>
+      </c>
+      <c r="B2861" t="s" s="3">
+        <v>5671</v>
+      </c>
+      <c r="C2861" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2861" t="s" s="2">
+        <v>5672</v>
+      </c>
+      <c r="E2861" t="s" s="3">
+        <v>5673</v>
+      </c>
+    </row>
+    <row r="2862" ht="36.0" customHeight="true">
+      <c r="A2862" t="n" s="2">
+        <v>2861.0</v>
+      </c>
+      <c r="B2862" t="s" s="3">
+        <v>5674</v>
+      </c>
+      <c r="C2862" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="D2862" t="s" s="2">
+        <v>5672</v>
+      </c>
+      <c r="E2862" t="s" s="3">
+        <v>5675</v>
       </c>
     </row>
   </sheetData>
